--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1665"/>
+  <dimension ref="A1:H1666"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -43809,9 +43809,35 @@
         <v/>
       </c>
     </row>
+    <row r="1666">
+      <c r="A1666" t="str">
+        <v>Kmtgty0ayi8su</v>
+      </c>
+      <c r="B1666" t="str">
+        <v>Direktur Jenderal Anggaran</v>
+      </c>
+      <c r="C1666" t="str">
+        <v/>
+      </c>
+      <c r="D1666" t="str">
+        <v/>
+      </c>
+      <c r="E1666" t="str">
+        <v/>
+      </c>
+      <c r="F1666" t="str">
+        <v/>
+      </c>
+      <c r="G1666" t="str">
+        <v/>
+      </c>
+      <c r="H1666" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1665"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1666"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1666"/>
+  <dimension ref="A1:H1667"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -43835,9 +43835,35 @@
         <v/>
       </c>
     </row>
+    <row r="1667">
+      <c r="A1667" t="str">
+        <v>Kmtgtzhgg6j7d</v>
+      </c>
+      <c r="B1667" t="str">
+        <v>Direktur Jenderal Bea dan Cukai</v>
+      </c>
+      <c r="C1667" t="str">
+        <v/>
+      </c>
+      <c r="D1667" t="str">
+        <v/>
+      </c>
+      <c r="E1667" t="str">
+        <v/>
+      </c>
+      <c r="F1667" t="str">
+        <v/>
+      </c>
+      <c r="G1667" t="str">
+        <v/>
+      </c>
+      <c r="H1667" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1666"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1667"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1667"/>
+  <dimension ref="A1:H1668"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -43861,9 +43861,35 @@
         <v/>
       </c>
     </row>
+    <row r="1668">
+      <c r="A1668" t="str">
+        <v>Kmtgu6bw7dnyn</v>
+      </c>
+      <c r="B1668" t="str">
+        <v>Direktur Jenderal Perbendaharaan</v>
+      </c>
+      <c r="C1668" t="str">
+        <v/>
+      </c>
+      <c r="D1668" t="str">
+        <v/>
+      </c>
+      <c r="E1668" t="str">
+        <v/>
+      </c>
+      <c r="F1668" t="str">
+        <v/>
+      </c>
+      <c r="G1668" t="str">
+        <v/>
+      </c>
+      <c r="H1668" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1667"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1668"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1668"/>
+  <dimension ref="A1:H1665"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -882,7 +882,7 @@
         <v>Kmsr8e1jrje7e</v>
       </c>
       <c r="B19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Madya</v>
       </c>
       <c r="C19" t="str">
@@ -909,7 +909,7 @@
         <v>Kmsr8e1jrbt4d</v>
       </c>
       <c r="B20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C20" t="str">
@@ -936,7 +936,7 @@
         <v>Kmsr8e1jrr6uq</v>
       </c>
       <c r="B21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C21" t="str">
@@ -963,7 +963,7 @@
         <v>Kmsr8e1jrja9j</v>
       </c>
       <c r="B22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C22" t="str">
@@ -990,7 +990,7 @@
         <v>Kmsr8e1jritte</v>
       </c>
       <c r="B23" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C23" t="str">
@@ -1017,7 +1017,7 @@
         <v>Kmsr8e1jr3ibl</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C24" t="str">
@@ -3774,7 +3774,7 @@
         <v>Kmsr8e1jr7ety</v>
       </c>
       <c r="B130" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Madya</v>
       </c>
       <c r="C130" t="str">
@@ -3801,7 +3801,7 @@
         <v>Kmsr8e1jrg3pl</v>
       </c>
       <c r="B131" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C131" t="str">
@@ -3828,7 +3828,7 @@
         <v>Kmsr8e1jr18cq</v>
       </c>
       <c r="B132" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C132" t="str">
@@ -4167,7 +4167,7 @@
         <v>Kmsr8e1jrcbj6</v>
       </c>
       <c r="B145" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C145" t="str">
@@ -4194,7 +4194,7 @@
         <v>Kmsr8e1jrzulb</v>
       </c>
       <c r="B146" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C146" t="str">
@@ -4221,7 +4221,7 @@
         <v>Kmsr8e1jr9qt1</v>
       </c>
       <c r="B147" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C147" t="str">
@@ -4248,7 +4248,7 @@
         <v>Kmsr8e1jrq0u0</v>
       </c>
       <c r="B148" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C148" t="str">
@@ -4275,7 +4275,7 @@
         <v>Kmsr8e1jrvbgu</v>
       </c>
       <c r="B149" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C149" t="str">
@@ -4406,7 +4406,7 @@
         <v>Kmsr8e1jrq73c</v>
       </c>
       <c r="B154" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C154" t="str">
@@ -4433,7 +4433,7 @@
         <v>Kmsr8e1jrlp7d</v>
       </c>
       <c r="B155" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C155" t="str">
@@ -4460,7 +4460,7 @@
         <v>Kmsr8e1jr2iw3</v>
       </c>
       <c r="B156" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C156" t="str">
@@ -4487,7 +4487,7 @@
         <v>Kmsr8e1jr4vq5</v>
       </c>
       <c r="B157" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C157" t="str">
@@ -4514,7 +4514,7 @@
         <v>Kmsr8e1jrs51b</v>
       </c>
       <c r="B158" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C158" t="str">
@@ -4645,7 +4645,7 @@
         <v>Kmsr8e1jraxe5</v>
       </c>
       <c r="B163" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C163" t="str">
@@ -4672,7 +4672,7 @@
         <v>Kmsr8e1jrt3mp</v>
       </c>
       <c r="B164" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d_
+        <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C164" t="str">
@@ -4699,7 +4699,7 @@
         <v>Kmsr8e1jry5i9</v>
       </c>
       <c r="B165" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C165" t="str">
@@ -4726,7 +4726,7 @@
         <v>Kmsr8e1jrjrd2</v>
       </c>
       <c r="B166" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C166" t="str">
@@ -4753,7 +4753,7 @@
         <v>Kmsr8e1jrnyq7</v>
       </c>
       <c r="B167" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C167" t="str">
@@ -6574,7 +6574,7 @@
         <v>Kmsptmr4s2rvq</v>
       </c>
       <c r="B237" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Pengelolaan_x000d__x000d__x000d_
+        <v xml:space="preserve">Kepala Subbagian Pengelolaan_x000d__x000d__x000d__x000d_
 Barang Milik Negara</v>
       </c>
       <c r="C237" t="str">
@@ -11001,7 +11001,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D407" t="str">
-        <v>Tenaga Pengkaji Bidang Sumber Daya Aparatur</v>
+        <v/>
       </c>
       <c r="E407" t="str">
         <v/>
@@ -11027,7 +11027,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D408" t="str">
-        <v>Tenaga Pengkaji Bidang Perencanaan Strategik</v>
+        <v/>
       </c>
       <c r="E408" t="str">
         <v/>
@@ -11053,7 +11053,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D409" t="str">
-        <v>Tenaga Pengkaji Bidang Pengelolaan Kekayaan Negara</v>
+        <v/>
       </c>
       <c r="E409" t="str">
         <v/>
@@ -11079,7 +11079,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D410" t="str">
-        <v>Biro Perencanaan Dan Keuangan</v>
+        <v/>
       </c>
       <c r="E410" t="str">
         <v/>
@@ -12581,7 +12581,7 @@
         <v>Kmt2nkws5uezz</v>
       </c>
       <c r="B468" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d__x000d_
 Analis Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C468" t="str">
@@ -12608,7 +12608,7 @@
         <v>Kmt2nkws5t9s4</v>
       </c>
       <c r="B469" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d__x000d_
 Analis Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C469" t="str">
@@ -13077,8 +13077,8 @@
         <v>Kmt2nkws5v5hr</v>
       </c>
       <c r="B487" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli _x000d_
-Madya/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli _x000d__x000d_
+Madya/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Madya </v>
       </c>
       <c r="C487" t="str">
@@ -13105,8 +13105,8 @@
         <v>Kmt2nkws55t5z</v>
       </c>
       <c r="B488" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli _x000d_
-Muda/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli _x000d__x000d_
+Muda/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C488" t="str">
@@ -13133,7 +13133,7 @@
         <v>Kmt2nkws5obnp</v>
       </c>
       <c r="B489" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C489" t="str">
@@ -13160,7 +13160,7 @@
         <v>Kmt2nkws5fy1j</v>
       </c>
       <c r="B490" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C490" t="str">
@@ -13187,7 +13187,7 @@
         <v>Kmt2nkws5ua4a</v>
       </c>
       <c r="B491" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C491" t="str">
@@ -13214,7 +13214,7 @@
         <v>Kmt2nkws55n0r</v>
       </c>
       <c r="B492" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C492" t="str">
@@ -13683,8 +13683,8 @@
         <v>Kmt2nkws5lcw4</v>
       </c>
       <c r="B510" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli _x000d_
-Muda/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli _x000d__x000d_
+Muda/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C510" t="str">
@@ -13711,7 +13711,7 @@
         <v>Kmt2nkws592fz</v>
       </c>
       <c r="B511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C511" t="str">
@@ -13738,7 +13738,7 @@
         <v>Kmt2nkws5vbtm</v>
       </c>
       <c r="B512" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C512" t="str">
@@ -13765,7 +13765,7 @@
         <v>Kmt2nkws5nifm</v>
       </c>
       <c r="B513" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C513" t="str">
@@ -13850,7 +13850,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D516" t="str">
-        <v>Biro Organisasi Dan Ketatalaksanaan</v>
+        <v/>
       </c>
       <c r="E516" t="str">
         <v/>
@@ -14364,7 +14364,7 @@
         <v>SJ0221</v>
       </c>
       <c r="B536" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Organisasi Bidang Pajak _x000d_
+        <v xml:space="preserve">Kepala Subbagian Organisasi Bidang Pajak _x000d__x000d_
 dan Dukungan Manajemen</v>
       </c>
       <c r="C536" t="str">
@@ -14469,7 +14469,7 @@
         <v>SJ0222</v>
       </c>
       <c r="B540" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Organisasi Bidang Kepabeanan _x000d_
+        <v xml:space="preserve">Kepala Subbagian Organisasi Bidang Kepabeanan _x000d__x000d_
 dan Cukai dan Teknologi Informasi Keuangan</v>
       </c>
       <c r="C540" t="str">
@@ -14574,7 +14574,7 @@
         <v>SJ0223</v>
       </c>
       <c r="B544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Jabatan Fungsional _x000d_
+        <v xml:space="preserve">Kepala Subbagian Jabatan Fungsional _x000d__x000d_
 Pengawas Keuangan Negara</v>
       </c>
       <c r="C544" t="str">
@@ -14939,7 +14939,7 @@
         <v>SJ0232</v>
       </c>
       <c r="B558" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Organisasi Bidang Anggaran dan_x000d_
+        <v xml:space="preserve">Kepala Subbagian Organisasi Bidang Anggaran dan_x000d__x000d_
 Kekayaan Negara</v>
       </c>
       <c r="C558" t="str">
@@ -15044,7 +15044,7 @@
         <v>SJ0233</v>
       </c>
       <c r="B562" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Jabatan Fungsional _x000d_
+        <v xml:space="preserve">Kepala Subbagian Jabatan Fungsional _x000d__x000d_
 Analis Keuangan Negara, Penilai, dan Pelelang</v>
       </c>
       <c r="C562" t="str">
@@ -15409,7 +15409,7 @@
         <v>SJ0242</v>
       </c>
       <c r="B576" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Analisis dan Evaluasi Jabatan _x000d_
+        <v xml:space="preserve">Kepala Subbagian Analisis dan Evaluasi Jabatan _x000d__x000d_
 Bidang Penerimaan dan Dukungan Manajemen</v>
       </c>
       <c r="C576" t="str">
@@ -15514,7 +15514,7 @@
         <v>SJ0243</v>
       </c>
       <c r="B580" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Analisis dan Evaluasi Jabatan _x000d_
+        <v xml:space="preserve">Kepala Subbagian Analisis dan Evaluasi Jabatan _x000d__x000d_
 Bidang Anggaran, Perbendaharaan, Kekayaan Negara, dan Sektor Keuangan</v>
       </c>
       <c r="C580" t="str">
@@ -15775,7 +15775,7 @@
         <v>SJ0251</v>
       </c>
       <c r="B590" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Tata Kelola_x000d_
+        <v xml:space="preserve">Kepala Subbagian Tata Kelola_x000d__x000d_
 Bidang Penerimaan dan Dukungan Manajemen</v>
       </c>
       <c r="C590" t="str">
@@ -15880,7 +15880,7 @@
         <v>SJ0252</v>
       </c>
       <c r="B594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Tata Kelola _x000d_
+        <v xml:space="preserve">Kepala Subbagian Tata Kelola _x000d__x000d_
 Bidang Anggaran, Perbendaharaan, Kekayaan Negara, dan Sektor Keuangan</v>
       </c>
       <c r="C594" t="str">
@@ -16381,7 +16381,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D613" t="str">
-        <v>Kepala Biro Hukum</v>
+        <v/>
       </c>
       <c r="E613" t="str">
         <v/>
@@ -16843,8 +16843,8 @@
         <v>SJ032</v>
       </c>
       <c r="B631" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Bagian Hukum Anggaran,_x000d_
-Perimbangan Keuangan, Perbendaharaan, _x000d_
+        <v xml:space="preserve">Kepala Bagian Hukum Anggaran,_x000d__x000d_
+Perimbangan Keuangan, Perbendaharaan, _x000d__x000d_
 dan Badan Layanan Umum</v>
       </c>
       <c r="C631" t="str">
@@ -18665,7 +18665,7 @@
         <v>SJ0362</v>
       </c>
       <c r="B701" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Hukum Organisasi, Ketatalaksanaan, _x000d_
+        <v xml:space="preserve">Kepala Subbagian Hukum Organisasi, Ketatalaksanaan, _x000d__x000d_
 dan Pengawasan Internal</v>
       </c>
       <c r="C701" t="str">
@@ -18770,7 +18770,7 @@
         <v>SJ0363</v>
       </c>
       <c r="B705" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Hukum Teknologi Informasi _x000d_
+        <v xml:space="preserve">Kepala Subbagian Hukum Teknologi Informasi _x000d__x000d_
 Keuangan dan Komunikasi</v>
       </c>
       <c r="C705" t="str">
@@ -18933,7 +18933,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D711" t="str">
-        <v>Kepala Biro Advokasi</v>
+        <v/>
       </c>
       <c r="E711" t="str">
         <v/>
@@ -19401,7 +19401,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D729" t="str">
-        <v>Kepala Biro Sumber Daya Manusia</v>
+        <v/>
       </c>
       <c r="E729" t="str">
         <v/>
@@ -19421,7 +19421,7 @@
         <v>SJ051</v>
       </c>
       <c r="B730" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Bagian Tata Kelola dan Pembinaan _x000d_
+        <v xml:space="preserve">Kepala Bagian Tata Kelola dan Pembinaan _x000d__x000d_
 Sumber Daya Manusia</v>
       </c>
       <c r="C730" t="str">
@@ -19448,7 +19448,7 @@
         <v>SJ0511</v>
       </c>
       <c r="B731" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Tata Kelola Informasi _x000d_
+        <v xml:space="preserve">Kepala Subbagian Tata Kelola Informasi _x000d__x000d_
 dan Administrasi Sumber Daya Manusia</v>
       </c>
       <c r="C731" t="str">
@@ -19631,7 +19631,7 @@
         <v>SJ0512</v>
       </c>
       <c r="B738" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kepala Subbagian Pembinaan Internal _x000d_
+        <v xml:space="preserve">Kepala Subbagian Pembinaan Internal _x000d__x000d_
 Jabatan Fungsional Bidang Sumber Daya Manusia</v>
       </c>
       <c r="C738" t="str">
@@ -20366,7 +20366,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D766" t="str">
-        <v>Kepala Biro Komunikasi Dan Layanan Informasi</v>
+        <v/>
       </c>
       <c r="E766" t="str">
         <v/>
@@ -24292,7 +24292,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D917" t="str">
-        <v>Kepala Biro Manajemen Barang Milik Negara Dan Pengadaan</v>
+        <v/>
       </c>
       <c r="E917" t="str">
         <v/>
@@ -25274,7 +25274,7 @@
         <v>Kmt2nkws61qgj</v>
       </c>
       <c r="B955" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Penyelia/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C955" t="str">
@@ -25301,7 +25301,7 @@
         <v>Kmt2nkws6vne2</v>
       </c>
       <c r="B956" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C956" t="str">
@@ -25328,7 +25328,7 @@
         <v>Kmt2nkws6ggol</v>
       </c>
       <c r="B957" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Terampil/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C957" t="str">
@@ -25849,7 +25849,7 @@
         <v>Kmt2nkws6asoq</v>
       </c>
       <c r="B977" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Penyelia/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C977" t="str">
@@ -25876,7 +25876,7 @@
         <v>Kmt2nkws6ybsj</v>
       </c>
       <c r="B978" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C978" t="str">
@@ -25903,7 +25903,7 @@
         <v>Kmt2nkws6dx5a</v>
       </c>
       <c r="B979" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Terampil/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C979" t="str">
@@ -26424,7 +26424,7 @@
         <v>Kmt2nkws62ime</v>
       </c>
       <c r="B999" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Penyelia/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C999" t="str">
@@ -26451,7 +26451,7 @@
         <v>Kmt2nkws6bnv7</v>
       </c>
       <c r="B1000" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1000" t="str">
@@ -26478,7 +26478,7 @@
         <v>Kmt2nkws6yt54</v>
       </c>
       <c r="B1001" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Terampil/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C1001" t="str">
@@ -26947,7 +26947,7 @@
         <v>Kmt2nkws6hby5</v>
       </c>
       <c r="B1019" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pengelola Pengadaan Barang/Jasa _x000d_
+        <v xml:space="preserve">Pengelola Pengadaan Barang/Jasa _x000d__x000d_
 Ahli Muda</v>
       </c>
       <c r="C1019" t="str">
@@ -26974,7 +26974,7 @@
         <v>Kmt2nkws674zx</v>
       </c>
       <c r="B1020" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pengelola Pengadaan Barang/Jasa _x000d_
+        <v xml:space="preserve">Pengelola Pengadaan Barang/Jasa _x000d__x000d_
 Ahli Pertama</v>
       </c>
       <c r="C1020" t="str">
@@ -27059,7 +27059,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D1023" t="str">
-        <v>Kepala Biro Umum</v>
+        <v/>
       </c>
       <c r="E1023" t="str">
         <v/>
@@ -28197,7 +28197,7 @@
         <v>Kmt2nkws76acn</v>
       </c>
       <c r="B1067" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1067" t="str">
@@ -28744,7 +28744,7 @@
         <v>Kmt2nkws7gnvd</v>
       </c>
       <c r="B1088" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Madya/ _x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Madya/ _x000d__x000d_
 Pengawas Keuangan Negara Ahli Madya</v>
       </c>
       <c r="C1088" t="str">
@@ -28771,7 +28771,7 @@
         <v>Kmt2nkws7e1z8</v>
       </c>
       <c r="B1089" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/ _x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/ _x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1089" t="str">
@@ -28824,7 +28824,7 @@
         <v>Kmt2nkws7y95z</v>
       </c>
       <c r="B1091" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C1091" t="str">
@@ -28851,7 +28851,7 @@
         <v>Kmt2nkws7oibz</v>
       </c>
       <c r="B1092" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1092" t="str">
@@ -28878,7 +28878,7 @@
         <v>Kmt2nkws7vw58</v>
       </c>
       <c r="B1093" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C1093" t="str">
@@ -32207,7 +32207,7 @@
         <v>Kmt2nkws7feb3</v>
       </c>
       <c r="B1221" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1221" t="str">
@@ -32266,7 +32266,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D1223" t="str">
-        <v>Kepala Pusat Analisis Dan Harmonisasi Kebijakan</v>
+        <v/>
       </c>
       <c r="E1223" t="str">
         <v/>
@@ -32650,7 +32650,7 @@
         <v>Kmt2nkws7dkcq</v>
       </c>
       <c r="B1238" t="str" xml:space="preserve">
-        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d_
+        <v xml:space="preserve">Penata Laksana Barang Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1238" t="str">
@@ -32807,7 +32807,7 @@
         <v>Kmt2nkws7hv8y</v>
       </c>
       <c r="B1244" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1244" t="str">
@@ -32834,7 +32834,7 @@
         <v>Kmt2nkws7j3b1</v>
       </c>
       <c r="B1245" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1245" t="str">
@@ -32861,7 +32861,7 @@
         <v>Kmt2nkws7oqm8</v>
       </c>
       <c r="B1246" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C1246" t="str">
@@ -32888,7 +32888,7 @@
         <v>Kmt2nkws7rq93</v>
       </c>
       <c r="B1247" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1247" t="str">
@@ -32915,7 +32915,7 @@
         <v>Kmt2nkws7foqy</v>
       </c>
       <c r="B1248" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C1248" t="str">
@@ -34242,7 +34242,7 @@
         <v>Kmt2nkws7o709</v>
       </c>
       <c r="B1299" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Kebijakan Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Kebijakan Ahli Muda/_x000d__x000d_
 Analis Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1299" t="str">
@@ -34269,7 +34269,7 @@
         <v>Kmt2nkws7ct7d</v>
       </c>
       <c r="B1300" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Kebijakan Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Kebijakan Ahli Pertama/_x000d__x000d_
 Analis Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1300" t="str">
@@ -34296,7 +34296,7 @@
         <v>Kmt2nkws7kze0</v>
       </c>
       <c r="B1301" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d__x000d_
 Analis Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1301" t="str">
@@ -34323,7 +34323,7 @@
         <v>Kmt2nkws7w7s3</v>
       </c>
       <c r="B1302" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d__x000d_
 Analis Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1302" t="str">
@@ -34350,7 +34350,7 @@
         <v>Kmt2nkws7oar2</v>
       </c>
       <c r="B1303" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Muda/_x000d__x000d_
 Analis Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1303" t="str">
@@ -34377,7 +34377,7 @@
         <v>Kmt2nkws7x3x9</v>
       </c>
       <c r="B1304" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Pertama/_x000d__x000d_
 Analis Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1304" t="str">
@@ -34846,7 +34846,7 @@
         <v>Kmt2nkws7fb7u</v>
       </c>
       <c r="B1322" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Kebijakan Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Kebijakan Ahli Muda/_x000d__x000d_
 Analis Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1322" t="str">
@@ -34873,7 +34873,7 @@
         <v>Kmt2nkws7jghq</v>
       </c>
       <c r="B1323" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Kebijakan Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Kebijakan Ahli Pertama/_x000d__x000d_
 Analis Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1323" t="str">
@@ -34900,7 +34900,7 @@
         <v>Kmt2nkws70yld</v>
       </c>
       <c r="B1324" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d__x000d_
 Analis Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1324" t="str">
@@ -34927,7 +34927,7 @@
         <v>Kmt2nkws7mc0x</v>
       </c>
       <c r="B1325" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d__x000d_
 Analis Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1325" t="str">
@@ -34954,7 +34954,7 @@
         <v>Kmt2nkws7kf5v</v>
       </c>
       <c r="B1326" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Muda/_x000d__x000d_
 Analis Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1326" t="str">
@@ -34981,7 +34981,7 @@
         <v>Kmt2nkws7prz8</v>
       </c>
       <c r="B1327" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Pertama/_x000d__x000d_
 Analis Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1327" t="str">
@@ -35008,7 +35008,7 @@
         <v>Kmt2nkws74uq4</v>
       </c>
       <c r="B1328" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Kebijakan Ahli Madya/_x000d_
+        <v xml:space="preserve">Analis Kebijakan Ahli Madya/_x000d__x000d_
 Analis Keuangan Negara Ahli Madya</v>
       </c>
       <c r="C1328" t="str">
@@ -35035,7 +35035,7 @@
         <v>Kmt2nkws7uvj6</v>
       </c>
       <c r="B1329" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d__x000d_
 Analis Keuangan Negara Ahli Madya</v>
       </c>
       <c r="C1329" t="str">
@@ -35062,7 +35062,7 @@
         <v>Kmt2nkws7bhbm</v>
       </c>
       <c r="B1330" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Madya/_x000d_
+        <v xml:space="preserve">Analis Keuangan Pusat dan Daerah Ahli Madya/_x000d__x000d_
 Analis Keuangan Negara Ahli Madya</v>
       </c>
       <c r="C1330" t="str">
@@ -35095,7 +35095,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D1331" t="str">
-        <v>Sekretaris Pengadilan Pajak</v>
+        <v/>
       </c>
       <c r="E1331" t="str">
         <v/>
@@ -35609,7 +35609,7 @@
         <v>Kmt2nkws7y37s</v>
       </c>
       <c r="B1351" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1351" t="str">
@@ -35636,7 +35636,7 @@
         <v>Kmt2nkws7d542</v>
       </c>
       <c r="B1352" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1352" t="str">
@@ -35663,7 +35663,7 @@
         <v>Kmt2nkws7fbrz</v>
       </c>
       <c r="B1353" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C1353" t="str">
@@ -35690,7 +35690,7 @@
         <v>Kmt2nkws7gykk</v>
       </c>
       <c r="B1354" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1354" t="str">
@@ -35717,7 +35717,7 @@
         <v>Kmt2nkws7vmp5</v>
       </c>
       <c r="B1355" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C1355" t="str">
@@ -37960,7 +37960,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D1441" t="str">
-        <v>Sekretaris Komite Pengawas Perpajakan</v>
+        <v/>
       </c>
       <c r="E1441" t="str">
         <v/>
@@ -38448,7 +38448,7 @@
         <v>Kmt2nkws86wvh</v>
       </c>
       <c r="B1460" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1460" t="str">
@@ -38475,7 +38475,7 @@
         <v>Kmt2nkws8mq58</v>
       </c>
       <c r="B1461" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Pertama/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Pertama</v>
       </c>
       <c r="C1461" t="str">
@@ -38502,7 +38502,7 @@
         <v>Kmt2nkws8mcvo</v>
       </c>
       <c r="B1462" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C1462" t="str">
@@ -38529,7 +38529,7 @@
         <v>Kmt2nkws8x7rk</v>
       </c>
       <c r="B1463" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1463" t="str">
@@ -38556,7 +38556,7 @@
         <v>Kmt2nkws88mfr</v>
       </c>
       <c r="B1464" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C1464" t="str">
@@ -38823,7 +38823,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D1474" t="str">
-        <v>Kepala Sekretariat Komite Nasional Ekonomi Dan Keuangan Syariah</v>
+        <v/>
       </c>
       <c r="E1474" t="str">
         <v/>
@@ -39655,7 +39655,7 @@
         <v>Kmsodueuksekq</v>
       </c>
       <c r="D1506" t="str">
-        <v>Direktur Utama Lembaga Pengelola Dana Pendidikan</v>
+        <v/>
       </c>
       <c r="E1506" t="str">
         <v/>
@@ -43185,7 +43185,7 @@
         <v>Kmt2nkws8zs9u</v>
       </c>
       <c r="B1642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
+        <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d__x000d_
 Analis Keuangan Negara Ahli Madya</v>
       </c>
       <c r="C1642" t="str">
@@ -43550,7 +43550,7 @@
         <v>Kmt2nkws8dgoe</v>
       </c>
       <c r="B1656" t="str" xml:space="preserve">
-        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d_
+        <v xml:space="preserve">Analis Pengelola Keuangan APBN Ahli Muda/_x000d__x000d_
 Pengawas Keuangan Negara Ahli Muda</v>
       </c>
       <c r="C1656" t="str">
@@ -43603,7 +43603,7 @@
         <v>Kmt2nkws8091x</v>
       </c>
       <c r="B1658" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Penyelia/_x000d__x000d_
 Pengawas Keuangan Negara Penyelia</v>
       </c>
       <c r="C1658" t="str">
@@ -43630,7 +43630,7 @@
         <v>Kmt2nkws8qzhm</v>
       </c>
       <c r="B1659" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN  Mahir/_x000d__x000d_
 Pengawas Keuangan Negara Mahir</v>
       </c>
       <c r="C1659" t="str">
@@ -43657,7 +43657,7 @@
         <v>Kmt2nkws8ekhz</v>
       </c>
       <c r="B1660" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
+        <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d__x000d_
 Pengawas Keuangan Negara Terampil</v>
       </c>
       <c r="C1660" t="str">
@@ -43809,87 +43809,9 @@
         <v/>
       </c>
     </row>
-    <row r="1666">
-      <c r="A1666" t="str">
-        <v>Kmtgty0ayi8su</v>
-      </c>
-      <c r="B1666" t="str">
-        <v>Direktur Jenderal Anggaran</v>
-      </c>
-      <c r="C1666" t="str">
-        <v/>
-      </c>
-      <c r="D1666" t="str">
-        <v/>
-      </c>
-      <c r="E1666" t="str">
-        <v/>
-      </c>
-      <c r="F1666" t="str">
-        <v/>
-      </c>
-      <c r="G1666" t="str">
-        <v/>
-      </c>
-      <c r="H1666" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1667">
-      <c r="A1667" t="str">
-        <v>Kmtgtzhgg6j7d</v>
-      </c>
-      <c r="B1667" t="str">
-        <v>Direktur Jenderal Bea dan Cukai</v>
-      </c>
-      <c r="C1667" t="str">
-        <v/>
-      </c>
-      <c r="D1667" t="str">
-        <v/>
-      </c>
-      <c r="E1667" t="str">
-        <v/>
-      </c>
-      <c r="F1667" t="str">
-        <v/>
-      </c>
-      <c r="G1667" t="str">
-        <v/>
-      </c>
-      <c r="H1667" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1668">
-      <c r="A1668" t="str">
-        <v>Kmtgu6bw7dnyn</v>
-      </c>
-      <c r="B1668" t="str">
-        <v>Direktur Jenderal Perbendaharaan</v>
-      </c>
-      <c r="C1668" t="str">
-        <v/>
-      </c>
-      <c r="D1668" t="str">
-        <v/>
-      </c>
-      <c r="E1668" t="str">
-        <v/>
-      </c>
-      <c r="F1668" t="str">
-        <v/>
-      </c>
-      <c r="G1668" t="str">
-        <v/>
-      </c>
-      <c r="H1668" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1668"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1665"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1665"/>
+  <dimension ref="A1:L1666"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -63793,9 +63793,47 @@
         <v/>
       </c>
     </row>
+    <row r="1666">
+      <c r="A1666" t="str">
+        <v>Kmti7gp97t9bf</v>
+      </c>
+      <c r="B1666" t="str">
+        <v>Direktur Jenderal Anggaran</v>
+      </c>
+      <c r="C1666" t="str">
+        <v/>
+      </c>
+      <c r="D1666" t="str">
+        <v/>
+      </c>
+      <c r="E1666" t="str">
+        <v/>
+      </c>
+      <c r="F1666" t="str">
+        <v/>
+      </c>
+      <c r="G1666" t="str">
+        <v/>
+      </c>
+      <c r="H1666" t="str">
+        <v/>
+      </c>
+      <c r="I1666" t="str">
+        <v/>
+      </c>
+      <c r="J1666" t="str">
+        <v/>
+      </c>
+      <c r="K1666" t="str">
+        <v/>
+      </c>
+      <c r="L1666" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1665"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1666"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -63909,7 +63909,7 @@
     </row>
     <row r="1669">
       <c r="A1669" t="str">
-        <v>Kmti9ur4w93p7</v>
+        <v>Kmti9yukcofxe</v>
       </c>
       <c r="B1669" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -63947,7 +63947,7 @@
     </row>
     <row r="1670">
       <c r="A1670" t="str">
-        <v>Kmti9ur4wudpu</v>
+        <v>Kmti9yukcfsz7</v>
       </c>
       <c r="B1670" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -63985,7 +63985,7 @@
     </row>
     <row r="1671">
       <c r="A1671" t="str">
-        <v>Kmti9ur4wdj11</v>
+        <v>Kmti9yukcf9iq</v>
       </c>
       <c r="B1671" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64023,7 +64023,7 @@
     </row>
     <row r="1672">
       <c r="A1672" t="str">
-        <v>Kmti9ur4w438b</v>
+        <v>Kmti9yukc58uh</v>
       </c>
       <c r="B1672" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64061,7 +64061,7 @@
     </row>
     <row r="1673">
       <c r="A1673" t="str">
-        <v>Kmti9ur4w8ztm</v>
+        <v>Kmti9yukcfnao</v>
       </c>
       <c r="B1673" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64099,7 +64099,7 @@
     </row>
     <row r="1674">
       <c r="A1674" t="str">
-        <v>Kmti9ur4wjf8w</v>
+        <v>Kmti9yukc81rb</v>
       </c>
       <c r="B1674" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64137,7 +64137,7 @@
     </row>
     <row r="1675">
       <c r="A1675" t="str">
-        <v>Kmti9ur4wfvjp</v>
+        <v>Kmti9yukcmk5n</v>
       </c>
       <c r="B1675" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64175,7 +64175,7 @@
     </row>
     <row r="1676">
       <c r="A1676" t="str">
-        <v>Kmti9ur4w499a</v>
+        <v>Kmti9yukctkgi</v>
       </c>
       <c r="B1676" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64251,7 +64251,7 @@
     </row>
     <row r="1678">
       <c r="A1678" t="str">
-        <v>Kmti9ur4wa4eg</v>
+        <v>Kmti9yukcp0hn</v>
       </c>
       <c r="B1678" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64289,7 +64289,7 @@
     </row>
     <row r="1679">
       <c r="A1679" t="str">
-        <v>Kmti9ur4wvqda</v>
+        <v>Kmti9yukcj4fo</v>
       </c>
       <c r="B1679" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64327,7 +64327,7 @@
     </row>
     <row r="1680">
       <c r="A1680" t="str">
-        <v>Kmti9ur4wk8cj</v>
+        <v>Kmti9yukc4zuf</v>
       </c>
       <c r="B1680" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64365,7 +64365,7 @@
     </row>
     <row r="1681">
       <c r="A1681" t="str">
-        <v>Kmti9ur4warqn</v>
+        <v>Kmti9yukczuqw</v>
       </c>
       <c r="B1681" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64403,7 +64403,7 @@
     </row>
     <row r="1682">
       <c r="A1682" t="str">
-        <v>Kmti9ur4wfe21</v>
+        <v>Kmti9yukc8u3w</v>
       </c>
       <c r="B1682" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64441,7 +64441,7 @@
     </row>
     <row r="1683">
       <c r="A1683" t="str">
-        <v>Kmti9ur4wt8pq</v>
+        <v>Kmti9yukckfny</v>
       </c>
       <c r="B1683" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64479,7 +64479,7 @@
     </row>
     <row r="1684">
       <c r="A1684" t="str">
-        <v>Kmti9ur4wxbwd</v>
+        <v>Kmti9yukcwern</v>
       </c>
       <c r="B1684" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64517,7 +64517,7 @@
     </row>
     <row r="1685">
       <c r="A1685" t="str">
-        <v>Kmti9ur4w9lqt</v>
+        <v>Kmti9yukck28r</v>
       </c>
       <c r="B1685" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64593,7 +64593,7 @@
     </row>
     <row r="1687">
       <c r="A1687" t="str">
-        <v>Kmti9ur4wsnjv</v>
+        <v>Kmti9yukcd9l6</v>
       </c>
       <c r="B1687" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64631,7 +64631,7 @@
     </row>
     <row r="1688">
       <c r="A1688" t="str">
-        <v>Kmti9ur4wywu3</v>
+        <v>Kmti9yukcrw7k</v>
       </c>
       <c r="B1688" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64669,7 +64669,7 @@
     </row>
     <row r="1689">
       <c r="A1689" t="str">
-        <v>Kmti9ur4wbk79</v>
+        <v>Kmti9yukc9eg8</v>
       </c>
       <c r="B1689" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64707,7 +64707,7 @@
     </row>
     <row r="1690">
       <c r="A1690" t="str">
-        <v>Kmti9ur4wd6za</v>
+        <v>Kmti9yukckemr</v>
       </c>
       <c r="B1690" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64745,7 +64745,7 @@
     </row>
     <row r="1691">
       <c r="A1691" t="str">
-        <v>Kmti9ur4w1uh4</v>
+        <v>Kmti9yukcky8f</v>
       </c>
       <c r="B1691" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64783,7 +64783,7 @@
     </row>
     <row r="1692">
       <c r="A1692" t="str">
-        <v>Kmti9ur4wpe6p</v>
+        <v>Kmti9yukc38w9</v>
       </c>
       <c r="B1692" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64821,7 +64821,7 @@
     </row>
     <row r="1693">
       <c r="A1693" t="str">
-        <v>Kmti9ur4wkale</v>
+        <v>Kmti9yukcyfpi</v>
       </c>
       <c r="B1693" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64859,7 +64859,7 @@
     </row>
     <row r="1694">
       <c r="A1694" t="str">
-        <v>Kmti9ur4w7oxh</v>
+        <v>Kmti9yukcourn</v>
       </c>
       <c r="B1694" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64897,7 +64897,7 @@
     </row>
     <row r="1695">
       <c r="A1695" t="str">
-        <v>Kmti9ur4wkn16</v>
+        <v>Kmti9yukcl2av</v>
       </c>
       <c r="B1695" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64935,7 +64935,7 @@
     </row>
     <row r="1696">
       <c r="A1696" t="str">
-        <v>Kmti9ur4wuj6g</v>
+        <v>Kmti9yukczj03</v>
       </c>
       <c r="B1696" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64973,7 +64973,7 @@
     </row>
     <row r="1697">
       <c r="A1697" t="str">
-        <v>Kmti9ur4war6f</v>
+        <v>Kmti9yukc6j0x</v>
       </c>
       <c r="B1697" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65087,7 +65087,7 @@
     </row>
     <row r="1700">
       <c r="A1700" t="str">
-        <v>Kmti9ur4wbymc</v>
+        <v>Kmti9yukc1hrv</v>
       </c>
       <c r="B1700" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65125,7 +65125,7 @@
     </row>
     <row r="1701">
       <c r="A1701" t="str">
-        <v>Kmti9ur4wfc65</v>
+        <v>Kmti9yukc74ou</v>
       </c>
       <c r="B1701" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65163,7 +65163,7 @@
     </row>
     <row r="1702">
       <c r="A1702" t="str">
-        <v>Kmti9ur4wk41p</v>
+        <v>Kmti9yukcqe1f</v>
       </c>
       <c r="B1702" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65201,7 +65201,7 @@
     </row>
     <row r="1703">
       <c r="A1703" t="str">
-        <v>Kmti9ur4wl4xr</v>
+        <v>Kmti9yukc1ni9</v>
       </c>
       <c r="B1703" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65239,7 +65239,7 @@
     </row>
     <row r="1704">
       <c r="A1704" t="str">
-        <v>Kmti9ur4wr1ck</v>
+        <v>Kmti9yukcau4s</v>
       </c>
       <c r="B1704" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65277,7 +65277,7 @@
     </row>
     <row r="1705">
       <c r="A1705" t="str">
-        <v>Kmti9ur4wjt6y</v>
+        <v>Kmti9yukcz88u</v>
       </c>
       <c r="B1705" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65315,7 +65315,7 @@
     </row>
     <row r="1706">
       <c r="A1706" t="str">
-        <v>Kmti9ur4wjl2b</v>
+        <v>Kmti9yukctog3</v>
       </c>
       <c r="B1706" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65353,7 +65353,7 @@
     </row>
     <row r="1707">
       <c r="A1707" t="str">
-        <v>Kmti9ur4wnr2d</v>
+        <v>Kmti9yukc0jz8</v>
       </c>
       <c r="B1707" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65391,7 +65391,7 @@
     </row>
     <row r="1708">
       <c r="A1708" t="str">
-        <v>Kmti9ur4wzqfx</v>
+        <v>Kmti9yukc8mjr</v>
       </c>
       <c r="B1708" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -65429,7 +65429,7 @@
     </row>
     <row r="1709">
       <c r="A1709" t="str">
-        <v>Kmti9ur4wgndm</v>
+        <v>Kmti9yukc0x73</v>
       </c>
       <c r="B1709" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -65505,7 +65505,7 @@
     </row>
     <row r="1711">
       <c r="A1711" t="str">
-        <v>Kmti9ur4wss60</v>
+        <v>Kmti9yukchmug</v>
       </c>
       <c r="B1711" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65543,7 +65543,7 @@
     </row>
     <row r="1712">
       <c r="A1712" t="str">
-        <v>Kmti9ur4wvdb2</v>
+        <v>Kmti9yukce7ib</v>
       </c>
       <c r="B1712" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65581,7 +65581,7 @@
     </row>
     <row r="1713">
       <c r="A1713" t="str">
-        <v>Kmti9ur4wgk0h</v>
+        <v>Kmti9yukcwch7</v>
       </c>
       <c r="B1713" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65619,7 +65619,7 @@
     </row>
     <row r="1714">
       <c r="A1714" t="str">
-        <v>Kmti9ur4wovmb</v>
+        <v>Kmti9yukd5n45</v>
       </c>
       <c r="B1714" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65657,7 +65657,7 @@
     </row>
     <row r="1715">
       <c r="A1715" t="str">
-        <v>Kmti9ur4wtdtp</v>
+        <v>Kmti9yukdbjt6</v>
       </c>
       <c r="B1715" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65695,7 +65695,7 @@
     </row>
     <row r="1716">
       <c r="A1716" t="str">
-        <v>Kmti9ur4w3bfu</v>
+        <v>Kmti9yukd8bkx</v>
       </c>
       <c r="B1716" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65733,7 +65733,7 @@
     </row>
     <row r="1717">
       <c r="A1717" t="str">
-        <v>Kmti9ur4wb7kr</v>
+        <v>Kmti9yukdr5rn</v>
       </c>
       <c r="B1717" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65771,7 +65771,7 @@
     </row>
     <row r="1718">
       <c r="A1718" t="str">
-        <v>Kmti9ur4wqby9</v>
+        <v>Kmti9yukd68w6</v>
       </c>
       <c r="B1718" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65847,7 +65847,7 @@
     </row>
     <row r="1720">
       <c r="A1720" t="str">
-        <v>Kmti9ur4wt3dc</v>
+        <v>Kmti9yukdttf6</v>
       </c>
       <c r="B1720" t="str">
         <v>Penata Layanan Operasional</v>
@@ -65885,7 +65885,7 @@
     </row>
     <row r="1721">
       <c r="A1721" t="str">
-        <v>Kmti9ur4woq0h</v>
+        <v>Kmti9yukdsgax</v>
       </c>
       <c r="B1721" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65923,7 +65923,7 @@
     </row>
     <row r="1722">
       <c r="A1722" t="str">
-        <v>Kmti9ur4wgwoj</v>
+        <v>Kmti9yukd1eo1</v>
       </c>
       <c r="B1722" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65961,7 +65961,7 @@
     </row>
     <row r="1723">
       <c r="A1723" t="str">
-        <v>Kmti9ur4ws1ti</v>
+        <v>Kmti9yukdbiv0</v>
       </c>
       <c r="B1723" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65999,7 +65999,7 @@
     </row>
     <row r="1724">
       <c r="A1724" t="str">
-        <v>Kmti9ur4wfrxm</v>
+        <v>Kmti9yukdtdrn</v>
       </c>
       <c r="B1724" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66037,7 +66037,7 @@
     </row>
     <row r="1725">
       <c r="A1725" t="str">
-        <v>Kmti9ur4wmzh7</v>
+        <v>Kmti9yukd3t41</v>
       </c>
       <c r="B1725" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66075,7 +66075,7 @@
     </row>
     <row r="1726">
       <c r="A1726" t="str">
-        <v>Kmti9ur4we75i</v>
+        <v>Kmti9yukd5ff9</v>
       </c>
       <c r="B1726" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66113,7 +66113,7 @@
     </row>
     <row r="1727">
       <c r="A1727" t="str">
-        <v>Kmti9ur4woyiq</v>
+        <v>Kmti9yukd5ywk</v>
       </c>
       <c r="B1727" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66189,7 +66189,7 @@
     </row>
     <row r="1729">
       <c r="A1729" t="str">
-        <v>Kmti9ur4wfz5y</v>
+        <v>Kmti9yukd1qen</v>
       </c>
       <c r="B1729" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66227,7 +66227,7 @@
     </row>
     <row r="1730">
       <c r="A1730" t="str">
-        <v>Kmti9ur4wo56u</v>
+        <v>Kmti9yukdt9eg</v>
       </c>
       <c r="B1730" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66265,7 +66265,7 @@
     </row>
     <row r="1731">
       <c r="A1731" t="str">
-        <v>Kmti9ur4wvbrx</v>
+        <v>Kmti9yukdd73v</v>
       </c>
       <c r="B1731" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66303,7 +66303,7 @@
     </row>
     <row r="1732">
       <c r="A1732" t="str">
-        <v>Kmti9ur4wbgqe</v>
+        <v>Kmti9yukdmgrp</v>
       </c>
       <c r="B1732" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66341,7 +66341,7 @@
     </row>
     <row r="1733">
       <c r="A1733" t="str">
-        <v>Kmti9ur4wot1u</v>
+        <v>Kmti9yukd38cl</v>
       </c>
       <c r="B1733" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66379,7 +66379,7 @@
     </row>
     <row r="1734">
       <c r="A1734" t="str">
-        <v>Kmti9ur4wyb4i</v>
+        <v>Kmti9yukd6vj8</v>
       </c>
       <c r="B1734" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66417,7 +66417,7 @@
     </row>
     <row r="1735">
       <c r="A1735" t="str">
-        <v>Kmti9ur4w3hc3</v>
+        <v>Kmti9yukdcc39</v>
       </c>
       <c r="B1735" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66455,7 +66455,7 @@
     </row>
     <row r="1736">
       <c r="A1736" t="str">
-        <v>Kmti9ur4wsq6k</v>
+        <v>Kmti9yukd2qa4</v>
       </c>
       <c r="B1736" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66493,7 +66493,7 @@
     </row>
     <row r="1737">
       <c r="A1737" t="str">
-        <v>Kmti9ur4wi9vv</v>
+        <v>Kmti9yukdn227</v>
       </c>
       <c r="B1737" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66531,7 +66531,7 @@
     </row>
     <row r="1738">
       <c r="A1738" t="str">
-        <v>Kmti9ur4wcrqp</v>
+        <v>Kmti9yukdtavb</v>
       </c>
       <c r="B1738" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66569,7 +66569,7 @@
     </row>
     <row r="1739">
       <c r="A1739" t="str">
-        <v>Kmti9ur4wqddr</v>
+        <v>Kmti9yukd06ri</v>
       </c>
       <c r="B1739" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66607,7 +66607,7 @@
     </row>
     <row r="1740">
       <c r="A1740" t="str">
-        <v>Kmti9ur4w2tt2</v>
+        <v>Kmti9yukd69i6</v>
       </c>
       <c r="B1740" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66645,7 +66645,7 @@
     </row>
     <row r="1741">
       <c r="A1741" t="str">
-        <v>Kmti9ur4wa8i9</v>
+        <v>Kmti9yukdfab6</v>
       </c>
       <c r="B1741" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66683,7 +66683,7 @@
     </row>
     <row r="1742">
       <c r="A1742" t="str">
-        <v>Kmti9ur4w501o</v>
+        <v>Kmti9yukdmc22</v>
       </c>
       <c r="B1742" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -66721,7 +66721,7 @@
     </row>
     <row r="1743">
       <c r="A1743" t="str">
-        <v>Kmti9ur4wwnsm</v>
+        <v>Kmti9yukdamse</v>
       </c>
       <c r="B1743" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -66835,7 +66835,7 @@
     </row>
     <row r="1746">
       <c r="A1746" t="str">
-        <v>Kmti9ur4wfl0h</v>
+        <v>Kmti9yukduryf</v>
       </c>
       <c r="B1746" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66873,7 +66873,7 @@
     </row>
     <row r="1747">
       <c r="A1747" t="str">
-        <v>Kmti9ur4wrlcr</v>
+        <v>Kmti9yukdo9fp</v>
       </c>
       <c r="B1747" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66911,7 +66911,7 @@
     </row>
     <row r="1748">
       <c r="A1748" t="str">
-        <v>Kmti9ur4wo6rc</v>
+        <v>Kmti9yukdl6ik</v>
       </c>
       <c r="B1748" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66949,7 +66949,7 @@
     </row>
     <row r="1749" xml:space="preserve">
       <c r="A1749" t="str">
-        <v>Kmti9ur4wixj1</v>
+        <v>Kmti9yukdfnw9</v>
       </c>
       <c r="B1749" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -66988,7 +66988,7 @@
     </row>
     <row r="1750">
       <c r="A1750" t="str">
-        <v>Kmti9ur4w9mg5</v>
+        <v>Kmti9yukdhnmb</v>
       </c>
       <c r="B1750" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67064,7 +67064,7 @@
     </row>
     <row r="1752">
       <c r="A1752" t="str">
-        <v>Kmti9ur4wyl98</v>
+        <v>Kmti9yukdnord</v>
       </c>
       <c r="B1752" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67102,7 +67102,7 @@
     </row>
     <row r="1753">
       <c r="A1753" t="str">
-        <v>Kmti9ur4wlzlk</v>
+        <v>Kmti9yukdayap</v>
       </c>
       <c r="B1753" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67140,7 +67140,7 @@
     </row>
     <row r="1754">
       <c r="A1754" t="str">
-        <v>Kmti9ur4w1bi9</v>
+        <v>Kmti9yukdzmt5</v>
       </c>
       <c r="B1754" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67178,7 +67178,7 @@
     </row>
     <row r="1755" xml:space="preserve">
       <c r="A1755" t="str">
-        <v>Kmti9ur4w5o5m</v>
+        <v>Kmti9yukdt06d</v>
       </c>
       <c r="B1755" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67217,7 +67217,7 @@
     </row>
     <row r="1756" xml:space="preserve">
       <c r="A1756" t="str">
-        <v>Kmti9ur4w6m9q</v>
+        <v>Kmti9yukd7zza</v>
       </c>
       <c r="B1756" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67256,7 +67256,7 @@
     </row>
     <row r="1757">
       <c r="A1757" t="str">
-        <v>Kmti9ur4wcf8k</v>
+        <v>Kmti9yukdua60</v>
       </c>
       <c r="B1757" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67294,7 +67294,7 @@
     </row>
     <row r="1758" xml:space="preserve">
       <c r="A1758" t="str">
-        <v>Kmti9ur4w22af</v>
+        <v>Kmti9yukd6m0x</v>
       </c>
       <c r="B1758" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67333,7 +67333,7 @@
     </row>
     <row r="1759" xml:space="preserve">
       <c r="A1759" t="str">
-        <v>Kmti9ur4wj51y</v>
+        <v>Kmti9yukdhaia</v>
       </c>
       <c r="B1759" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67410,7 +67410,7 @@
     </row>
     <row r="1761">
       <c r="A1761" t="str">
-        <v>Kmti9ur4w6bsd</v>
+        <v>Kmti9yukdotfj</v>
       </c>
       <c r="B1761" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67448,7 +67448,7 @@
     </row>
     <row r="1762">
       <c r="A1762" t="str">
-        <v>Kmti9ur4wvk3w</v>
+        <v>Kmti9yukdqwgc</v>
       </c>
       <c r="B1762" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67486,7 +67486,7 @@
     </row>
     <row r="1763">
       <c r="A1763" t="str">
-        <v>Kmti9ur4wk3gq</v>
+        <v>Kmti9yukd9fk0</v>
       </c>
       <c r="B1763" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67524,7 +67524,7 @@
     </row>
     <row r="1764" xml:space="preserve">
       <c r="A1764" t="str">
-        <v>Kmti9ur4wk8k7</v>
+        <v>Kmti9yukd876c</v>
       </c>
       <c r="B1764" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67563,7 +67563,7 @@
     </row>
     <row r="1765" xml:space="preserve">
       <c r="A1765" t="str">
-        <v>Kmti9ur4wmvo6</v>
+        <v>Kmti9yukdhsac</v>
       </c>
       <c r="B1765" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67602,7 +67602,7 @@
     </row>
     <row r="1766">
       <c r="A1766" t="str">
-        <v>Kmti9ur4wtr9d</v>
+        <v>Kmti9yukdd1hm</v>
       </c>
       <c r="B1766" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67640,7 +67640,7 @@
     </row>
     <row r="1767" xml:space="preserve">
       <c r="A1767" t="str">
-        <v>Kmti9ur4wvqkx</v>
+        <v>Kmti9yukdfk38</v>
       </c>
       <c r="B1767" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67679,7 +67679,7 @@
     </row>
     <row r="1768" xml:space="preserve">
       <c r="A1768" t="str">
-        <v>Kmti9ur4w36a7</v>
+        <v>Kmti9yukdeysi</v>
       </c>
       <c r="B1768" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67718,7 +67718,7 @@
     </row>
     <row r="1769">
       <c r="A1769" t="str">
-        <v>Kmti9ur4w97xx</v>
+        <v>Kmti9yukd6dko</v>
       </c>
       <c r="B1769" t="str">
         <v>Analis Anggaran Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -67756,7 +67756,7 @@
     </row>
     <row r="1770">
       <c r="A1770" t="str">
-        <v>Kmti9ur4wx0i2</v>
+        <v>Kmti9yukdrkj3</v>
       </c>
       <c r="B1770" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67794,7 +67794,7 @@
     </row>
     <row r="1771">
       <c r="A1771" t="str">
-        <v>Kmti9ur4w2zp0</v>
+        <v>Kmti9yukdg2zo</v>
       </c>
       <c r="B1771" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -67832,7 +67832,7 @@
     </row>
     <row r="1772">
       <c r="A1772" t="str">
-        <v>Kmti9ur4w4209</v>
+        <v>Kmti9yukd5qt2</v>
       </c>
       <c r="B1772" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Ahli Muda</v>
@@ -67870,7 +67870,7 @@
     </row>
     <row r="1773">
       <c r="A1773" t="str">
-        <v>Kmti9ur4wcjvu</v>
+        <v>Kmti9yukdb432</v>
       </c>
       <c r="B1773" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -67908,7 +67908,7 @@
     </row>
     <row r="1774">
       <c r="A1774" t="str">
-        <v>Kmti9ur4waruh</v>
+        <v>Kmti9yukdvcur</v>
       </c>
       <c r="B1774" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67946,7 +67946,7 @@
     </row>
     <row r="1775">
       <c r="A1775" t="str">
-        <v>Kmti9ur4w38yj</v>
+        <v>Kmti9yukdzk8r</v>
       </c>
       <c r="B1775" t="str">
         <v>Pranata Keuangan APBN Mahir/Pengawas Keuangan Negara Mahir</v>
@@ -67984,7 +67984,7 @@
     </row>
     <row r="1776">
       <c r="A1776" t="str">
-        <v>Kmti9ur4wwwbj</v>
+        <v>Kmti9yukdjzl7</v>
       </c>
       <c r="B1776" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -68098,7 +68098,7 @@
     </row>
     <row r="1779">
       <c r="A1779" t="str">
-        <v>Kmti9ur4wz40y</v>
+        <v>Kmti9yukd2pmd</v>
       </c>
       <c r="B1779" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68136,7 +68136,7 @@
     </row>
     <row r="1780">
       <c r="A1780" t="str">
-        <v>Kmti9ur4w0yz3</v>
+        <v>Kmti9yukdptus</v>
       </c>
       <c r="B1780" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68174,7 +68174,7 @@
     </row>
     <row r="1781">
       <c r="A1781" t="str">
-        <v>Kmti9ur4w71dz</v>
+        <v>Kmti9yukd1j09</v>
       </c>
       <c r="B1781" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68250,7 +68250,7 @@
     </row>
     <row r="1783">
       <c r="A1783" t="str">
-        <v>Kmti9ur4w9naw</v>
+        <v>Kmti9yukdir23</v>
       </c>
       <c r="B1783" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68288,7 +68288,7 @@
     </row>
     <row r="1784">
       <c r="A1784" t="str">
-        <v>Kmti9ur4we2z9</v>
+        <v>Kmti9yukd7ymh</v>
       </c>
       <c r="B1784" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68326,7 +68326,7 @@
     </row>
     <row r="1785">
       <c r="A1785" t="str">
-        <v>Kmti9ur4wpjng</v>
+        <v>Kmti9yukd1zh1</v>
       </c>
       <c r="B1785" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68364,7 +68364,7 @@
     </row>
     <row r="1786">
       <c r="A1786" t="str">
-        <v>Kmti9ur4wojfv</v>
+        <v>Kmti9yukdbv0k</v>
       </c>
       <c r="B1786" t="str">
         <v>Penata Keprotokolan*</v>
@@ -68402,7 +68402,7 @@
     </row>
     <row r="1787">
       <c r="A1787" t="str">
-        <v>Kmti9ur4w7r4c</v>
+        <v>Kmti9yukd9si1</v>
       </c>
       <c r="B1787" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68440,7 +68440,7 @@
     </row>
     <row r="1788">
       <c r="A1788" t="str">
-        <v>Kmti9ur4wcr4p</v>
+        <v>Kmti9yukdlwj5</v>
       </c>
       <c r="B1788" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68478,7 +68478,7 @@
     </row>
     <row r="1789">
       <c r="A1789" t="str">
-        <v>Kmti9ur4w8u1q</v>
+        <v>Kmti9yukd70ag</v>
       </c>
       <c r="B1789" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68516,7 +68516,7 @@
     </row>
     <row r="1790">
       <c r="A1790" t="str">
-        <v>Kmti9ur4w3cxm</v>
+        <v>Kmti9yukd5w8m</v>
       </c>
       <c r="B1790" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68592,7 +68592,7 @@
     </row>
     <row r="1792">
       <c r="A1792" t="str">
-        <v>Kmti9ur4w0dwj</v>
+        <v>Kmti9yukd0wrn</v>
       </c>
       <c r="B1792" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68630,7 +68630,7 @@
     </row>
     <row r="1793">
       <c r="A1793" t="str">
-        <v>Kmti9ur4w6qi9</v>
+        <v>Kmti9yukdqmsb</v>
       </c>
       <c r="B1793" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68668,7 +68668,7 @@
     </row>
     <row r="1794">
       <c r="A1794" t="str">
-        <v>Kmti9ur4w0chm</v>
+        <v>Kmti9yukd0sfv</v>
       </c>
       <c r="B1794" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68706,7 +68706,7 @@
     </row>
     <row r="1795">
       <c r="A1795" t="str">
-        <v>Kmti9ur4wdscs</v>
+        <v>Kmti9yukdmve6</v>
       </c>
       <c r="B1795" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -68744,7 +68744,7 @@
     </row>
     <row r="1796">
       <c r="A1796" t="str">
-        <v>Kmti9ur4woxmr</v>
+        <v>Kmti9yukdl7jm</v>
       </c>
       <c r="B1796" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68782,7 +68782,7 @@
     </row>
     <row r="1797">
       <c r="A1797" t="str">
-        <v>Kmti9ur4w7rvn</v>
+        <v>Kmti9yukde0xl</v>
       </c>
       <c r="B1797" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68820,7 +68820,7 @@
     </row>
     <row r="1798">
       <c r="A1798" t="str">
-        <v>Kmti9ur4wat4t</v>
+        <v>Kmti9yukds4g5</v>
       </c>
       <c r="B1798" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68858,7 +68858,7 @@
     </row>
     <row r="1799">
       <c r="A1799" t="str">
-        <v>Kmti9ur4w2mzo</v>
+        <v>Kmti9yukd2c9l</v>
       </c>
       <c r="B1799" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68934,7 +68934,7 @@
     </row>
     <row r="1801">
       <c r="A1801" t="str">
-        <v>Kmti9ur4wbqah</v>
+        <v>Kmti9yukdbfr5</v>
       </c>
       <c r="B1801" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68972,7 +68972,7 @@
     </row>
     <row r="1802">
       <c r="A1802" t="str">
-        <v>Kmti9ur4wj2qk</v>
+        <v>Kmti9yukdtwzc</v>
       </c>
       <c r="B1802" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69010,7 +69010,7 @@
     </row>
     <row r="1803">
       <c r="A1803" t="str">
-        <v>Kmti9ur4wmdwe</v>
+        <v>Kmti9yukdtwi5</v>
       </c>
       <c r="B1803" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69048,7 +69048,7 @@
     </row>
     <row r="1804">
       <c r="A1804" t="str">
-        <v>Kmti9ur4w29sk</v>
+        <v>Kmti9yukdgvp4</v>
       </c>
       <c r="B1804" t="str">
         <v>Penata Keprotokolan*</v>
@@ -69086,7 +69086,7 @@
     </row>
     <row r="1805">
       <c r="A1805" t="str">
-        <v>Kmti9ur4whkuf</v>
+        <v>Kmti9yukdntuz</v>
       </c>
       <c r="B1805" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -69124,7 +69124,7 @@
     </row>
     <row r="1806">
       <c r="A1806" t="str">
-        <v>Kmti9ur4wzroy</v>
+        <v>Kmti9yukdtlp0</v>
       </c>
       <c r="B1806" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -69162,7 +69162,7 @@
     </row>
     <row r="1807">
       <c r="A1807" t="str">
-        <v>Kmti9ur4wznmj</v>
+        <v>Kmti9yukd7iki</v>
       </c>
       <c r="B1807" t="str">
         <v>Arsiparis Penyelia</v>
@@ -69200,7 +69200,7 @@
     </row>
     <row r="1808">
       <c r="A1808" t="str">
-        <v>Kmti9ur4wu309</v>
+        <v>Kmti9yukd7j9j</v>
       </c>
       <c r="B1808" t="str">
         <v>Arsiparis Mahir</v>
@@ -69238,7 +69238,7 @@
     </row>
     <row r="1809">
       <c r="A1809" t="str">
-        <v>Kmti9ur4wswo7</v>
+        <v>Kmti9yukdsrua</v>
       </c>
       <c r="B1809" t="str">
         <v>Arsiparis Terampil</v>
@@ -69276,7 +69276,7 @@
     </row>
     <row r="1810">
       <c r="A1810" t="str">
-        <v>Kmti9ur4w861c</v>
+        <v>Kmti9yukdu6x7</v>
       </c>
       <c r="B1810" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -69314,7 +69314,7 @@
     </row>
     <row r="1811">
       <c r="A1811" t="str">
-        <v>Kmti9ur4wndi6</v>
+        <v>Kmti9yukdxuwv</v>
       </c>
       <c r="B1811" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69352,7 +69352,7 @@
     </row>
     <row r="1812">
       <c r="A1812" t="str">
-        <v>Kmti9ur4w36g6</v>
+        <v>Kmti9yukdb1tw</v>
       </c>
       <c r="B1812" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -69390,7 +69390,7 @@
     </row>
     <row r="1813">
       <c r="A1813" t="str">
-        <v>Kmti9ur4wmeql</v>
+        <v>Kmti9yukddvq3</v>
       </c>
       <c r="B1813" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -69428,7 +69428,7 @@
     </row>
     <row r="1814">
       <c r="A1814" t="str">
-        <v>Kmti9ur4w2uak</v>
+        <v>Kmti9yukdz3ei</v>
       </c>
       <c r="B1814" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -69542,7 +69542,7 @@
     </row>
     <row r="1817">
       <c r="A1817" t="str">
-        <v>Kmti9ur4w5oi9</v>
+        <v>Kmti9yukdoadn</v>
       </c>
       <c r="B1817" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69580,7 +69580,7 @@
     </row>
     <row r="1818">
       <c r="A1818" t="str">
-        <v>Kmti9ur4wo3pc</v>
+        <v>Kmti9yukdaz20</v>
       </c>
       <c r="B1818" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69618,7 +69618,7 @@
     </row>
     <row r="1819">
       <c r="A1819" t="str">
-        <v>Kmti9ur4wulre</v>
+        <v>Kmti9yukdcd45</v>
       </c>
       <c r="B1819" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69656,7 +69656,7 @@
     </row>
     <row r="1820">
       <c r="A1820" t="str">
-        <v>Kmti9ur4w8to1</v>
+        <v>Kmti9yukd2xjx</v>
       </c>
       <c r="B1820" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69694,7 +69694,7 @@
     </row>
     <row r="1821">
       <c r="A1821" t="str">
-        <v>Kmti9ur4wgb3u</v>
+        <v>Kmti9yukdvgf1</v>
       </c>
       <c r="B1821" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69732,7 +69732,7 @@
     </row>
     <row r="1822">
       <c r="A1822" t="str">
-        <v>Kmti9ur4w8q9k</v>
+        <v>Kmti9yukdz9ez</v>
       </c>
       <c r="B1822" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -69808,7 +69808,7 @@
     </row>
     <row r="1824">
       <c r="A1824" t="str">
-        <v>Kmti9ur4w8rww</v>
+        <v>Kmti9yukdkg0u</v>
       </c>
       <c r="B1824" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69846,7 +69846,7 @@
     </row>
     <row r="1825">
       <c r="A1825" t="str">
-        <v>Kmti9ur4wemmu</v>
+        <v>Kmti9yukdiopv</v>
       </c>
       <c r="B1825" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69884,7 +69884,7 @@
     </row>
     <row r="1826">
       <c r="A1826" t="str">
-        <v>Kmti9ur4w4szd</v>
+        <v>Kmti9yukdum1c</v>
       </c>
       <c r="B1826" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69922,7 +69922,7 @@
     </row>
     <row r="1827">
       <c r="A1827" t="str">
-        <v>Kmti9ur4w4tch</v>
+        <v>Kmti9yukd8o94</v>
       </c>
       <c r="B1827" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69960,7 +69960,7 @@
     </row>
     <row r="1828">
       <c r="A1828" t="str">
-        <v>Kmti9ur4wexq8</v>
+        <v>Kmti9yukdqu4z</v>
       </c>
       <c r="B1828" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69998,7 +69998,7 @@
     </row>
     <row r="1829">
       <c r="A1829" t="str">
-        <v>Kmti9ur4wbdlv</v>
+        <v>Kmti9yukdefhz</v>
       </c>
       <c r="B1829" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70036,7 +70036,7 @@
     </row>
     <row r="1830">
       <c r="A1830" t="str">
-        <v>Kmti9ur4wvl7r</v>
+        <v>Kmti9yukd7cn7</v>
       </c>
       <c r="B1830" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70112,7 +70112,7 @@
     </row>
     <row r="1832">
       <c r="A1832" t="str">
-        <v>Kmti9ur4whhvi</v>
+        <v>Kmti9yukdf082</v>
       </c>
       <c r="B1832" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -70150,7 +70150,7 @@
     </row>
     <row r="1833">
       <c r="A1833" t="str">
-        <v>Kmti9ur4wpw39</v>
+        <v>Kmti9yukdnr6u</v>
       </c>
       <c r="B1833" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70188,7 +70188,7 @@
     </row>
     <row r="1834">
       <c r="A1834" t="str">
-        <v>Kmti9ur4wpktr</v>
+        <v>Kmti9yukd1kb5</v>
       </c>
       <c r="B1834" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70226,7 +70226,7 @@
     </row>
     <row r="1835">
       <c r="A1835" t="str">
-        <v>Kmti9ur4wwj5r</v>
+        <v>Kmti9yukdva2t</v>
       </c>
       <c r="B1835" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70264,7 +70264,7 @@
     </row>
     <row r="1836">
       <c r="A1836" t="str">
-        <v>Kmti9ur4wyem1</v>
+        <v>Kmti9yukdytm7</v>
       </c>
       <c r="B1836" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70302,7 +70302,7 @@
     </row>
     <row r="1837">
       <c r="A1837" t="str">
-        <v>Kmti9ur4w0fry</v>
+        <v>Kmti9yukdbeo2</v>
       </c>
       <c r="B1837" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70340,7 +70340,7 @@
     </row>
     <row r="1838">
       <c r="A1838" t="str">
-        <v>Kmti9ur4w7ww9</v>
+        <v>Kmti9yukdb3wl</v>
       </c>
       <c r="B1838" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70378,7 +70378,7 @@
     </row>
     <row r="1839">
       <c r="A1839" t="str">
-        <v>Kmti9ur4wsctc</v>
+        <v>Kmti9yukd4qwr</v>
       </c>
       <c r="B1839" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70416,7 +70416,7 @@
     </row>
     <row r="1840">
       <c r="A1840" t="str">
-        <v>Kmti9ur4w15nl</v>
+        <v>Kmti9yukdjmm3</v>
       </c>
       <c r="B1840" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70454,7 +70454,7 @@
     </row>
     <row r="1841">
       <c r="A1841" t="str">
-        <v>Kmti9ur4wuwo0</v>
+        <v>Kmti9yukdpbgy</v>
       </c>
       <c r="B1841" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70492,7 +70492,7 @@
     </row>
     <row r="1842">
       <c r="A1842" t="str">
-        <v>Kmti9ur4wexux</v>
+        <v>Kmti9yukdv0ch</v>
       </c>
       <c r="B1842" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70568,7 +70568,7 @@
     </row>
     <row r="1844">
       <c r="A1844" t="str">
-        <v>Kmti9ur4xv8k9</v>
+        <v>Kmti9yukdhmjh</v>
       </c>
       <c r="B1844" t="str">
         <v>Penata Layanan Operasional</v>
@@ -70606,7 +70606,7 @@
     </row>
     <row r="1845">
       <c r="A1845" t="str">
-        <v>Kmti9ur4xu5t3</v>
+        <v>Kmti9yukdgast</v>
       </c>
       <c r="B1845" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70644,7 +70644,7 @@
     </row>
     <row r="1846">
       <c r="A1846" t="str">
-        <v>Kmti9ur4xsnlc</v>
+        <v>Kmti9yukd50io</v>
       </c>
       <c r="B1846" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70682,7 +70682,7 @@
     </row>
     <row r="1847">
       <c r="A1847" t="str">
-        <v>Kmti9ur4xjff3</v>
+        <v>Kmti9yukdovi3</v>
       </c>
       <c r="B1847" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -70720,7 +70720,7 @@
     </row>
     <row r="1848">
       <c r="A1848" t="str">
-        <v>Kmti9ur4xd17d</v>
+        <v>Kmti9yukdvidh</v>
       </c>
       <c r="B1848" t="str">
         <v>Pranata Humas Ahli Pertama</v>
@@ -70758,7 +70758,7 @@
     </row>
     <row r="1849">
       <c r="A1849" t="str">
-        <v>Kmti9ur4xmeua</v>
+        <v>Kmti9yukdf8oe</v>
       </c>
       <c r="B1849" t="str">
         <v>Pranata Humas Penyelia</v>
@@ -70796,7 +70796,7 @@
     </row>
     <row r="1850">
       <c r="A1850" t="str">
-        <v>Kmti9ur4x3q4u</v>
+        <v>Kmti9yukdw37h</v>
       </c>
       <c r="B1850" t="str">
         <v>Pranata Humas Mahir</v>
@@ -70834,7 +70834,7 @@
     </row>
     <row r="1851">
       <c r="A1851" t="str">
-        <v>Kmti9ur4xu7ab</v>
+        <v>Kmti9yukdmias</v>
       </c>
       <c r="B1851" t="str">
         <v>Pranata Humas Terampil</v>
@@ -70872,7 +70872,7 @@
     </row>
     <row r="1852">
       <c r="A1852" t="str">
-        <v>Kmti9ur4x0zq8</v>
+        <v>Kmti9yukdc4qm</v>
       </c>
       <c r="B1852" t="str">
         <v>Pustakawan Ahli Muda</v>
@@ -70910,7 +70910,7 @@
     </row>
     <row r="1853">
       <c r="A1853" t="str">
-        <v>Kmti9ur4x8nrw</v>
+        <v>Kmti9yukdo9vl</v>
       </c>
       <c r="B1853" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -70948,7 +70948,7 @@
     </row>
     <row r="1854">
       <c r="A1854" t="str">
-        <v>Kmti9ur4xb31q</v>
+        <v>Kmti9yukdoge2</v>
       </c>
       <c r="B1854" t="str">
         <v>Pustakawan Penyelia</v>
@@ -70986,7 +70986,7 @@
     </row>
     <row r="1855">
       <c r="A1855" t="str">
-        <v>Kmti9ur4xjiks</v>
+        <v>Kmti9yukdodqd</v>
       </c>
       <c r="B1855" t="str">
         <v>Pustakawan Mahir</v>
@@ -71024,7 +71024,7 @@
     </row>
     <row r="1856">
       <c r="A1856" t="str">
-        <v>Kmti9ur4xhclh</v>
+        <v>Kmti9yukdzku7</v>
       </c>
       <c r="B1856" t="str">
         <v>Pustakawan Terampil</v>
@@ -71138,7 +71138,7 @@
     </row>
     <row r="1859">
       <c r="A1859" t="str">
-        <v>Kmti9ur4xwsxu</v>
+        <v>Kmti9yukdf6us</v>
       </c>
       <c r="B1859" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71176,7 +71176,7 @@
     </row>
     <row r="1860">
       <c r="A1860" t="str">
-        <v>Kmti9ur4xxkq6</v>
+        <v>Kmti9yukdzqya</v>
       </c>
       <c r="B1860" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71214,7 +71214,7 @@
     </row>
     <row r="1861">
       <c r="A1861" t="str">
-        <v>Kmti9ur4x9zdc</v>
+        <v>Kmti9yukd1tea</v>
       </c>
       <c r="B1861" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71252,7 +71252,7 @@
     </row>
     <row r="1862">
       <c r="A1862" t="str">
-        <v>Kmti9ur4xqe2r</v>
+        <v>Kmti9yukdnev6</v>
       </c>
       <c r="B1862" t="str">
         <v>Penata Keprotokolan*</v>
@@ -71366,7 +71366,7 @@
     </row>
     <row r="1865">
       <c r="A1865" t="str">
-        <v>Kmti9ur4xvwou</v>
+        <v>Kmti9yukd9qe0</v>
       </c>
       <c r="B1865" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71404,7 +71404,7 @@
     </row>
     <row r="1866">
       <c r="A1866" t="str">
-        <v>Kmti9ur4x5myr</v>
+        <v>Kmti9yukdk4nc</v>
       </c>
       <c r="B1866" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71442,7 +71442,7 @@
     </row>
     <row r="1867">
       <c r="A1867" t="str">
-        <v>Kmti9ur4xiw6j</v>
+        <v>Kmti9yukdr0g3</v>
       </c>
       <c r="B1867" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71518,7 +71518,7 @@
     </row>
     <row r="1869">
       <c r="A1869" t="str">
-        <v>Kmti9ur4xcmrp</v>
+        <v>Kmti9yukd9fw7</v>
       </c>
       <c r="B1869" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71556,7 +71556,7 @@
     </row>
     <row r="1870">
       <c r="A1870" t="str">
-        <v>Kmti9ur4xotay</v>
+        <v>Kmti9yukdij1c</v>
       </c>
       <c r="B1870" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71594,7 +71594,7 @@
     </row>
     <row r="1871">
       <c r="A1871" t="str">
-        <v>Kmti9ur4xf758</v>
+        <v>Kmti9yukd56qp</v>
       </c>
       <c r="B1871" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71632,7 +71632,7 @@
     </row>
     <row r="1872" xml:space="preserve">
       <c r="A1872" t="str">
-        <v>Kmti9ur4xl5sx</v>
+        <v>Kmti9yukdplf0</v>
       </c>
       <c r="B1872" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -71671,7 +71671,7 @@
     </row>
     <row r="1873" xml:space="preserve">
       <c r="A1873" t="str">
-        <v>Kmti9ur4x0lhb</v>
+        <v>Kmti9yukd35hi</v>
       </c>
       <c r="B1873" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -71710,7 +71710,7 @@
     </row>
     <row r="1874" xml:space="preserve">
       <c r="A1874" t="str">
-        <v>Kmti9ur4x7apn</v>
+        <v>Kmti9yukd9mox</v>
       </c>
       <c r="B1874" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -71749,7 +71749,7 @@
     </row>
     <row r="1875" xml:space="preserve">
       <c r="A1875" t="str">
-        <v>Kmti9ur4x78ia</v>
+        <v>Kmti9yukd8gtj</v>
       </c>
       <c r="B1875" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -71864,7 +71864,7 @@
     </row>
     <row r="1878">
       <c r="A1878" t="str">
-        <v>Kmti9ur4xw769</v>
+        <v>Kmti9yukd6ugj</v>
       </c>
       <c r="B1878" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71902,7 +71902,7 @@
     </row>
     <row r="1879">
       <c r="A1879" t="str">
-        <v>Kmti9ur4xg9v6</v>
+        <v>Kmti9yukdywdj</v>
       </c>
       <c r="B1879" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71940,7 +71940,7 @@
     </row>
     <row r="1880">
       <c r="A1880" t="str">
-        <v>Kmti9ur4x9g45</v>
+        <v>Kmti9yukdkt2q</v>
       </c>
       <c r="B1880" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71978,7 +71978,7 @@
     </row>
     <row r="1881">
       <c r="A1881" t="str">
-        <v>Kmti9ur4x63qh</v>
+        <v>Kmti9yukd37kp</v>
       </c>
       <c r="B1881" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72092,7 +72092,7 @@
     </row>
     <row r="1884">
       <c r="A1884" t="str">
-        <v>Kmti9ur4xzvwc</v>
+        <v>Kmti9yukdr0na</v>
       </c>
       <c r="B1884" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72130,7 +72130,7 @@
     </row>
     <row r="1885">
       <c r="A1885" t="str">
-        <v>Kmti9ur4xgy9k</v>
+        <v>Kmti9yukdj2f6</v>
       </c>
       <c r="B1885" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72168,7 +72168,7 @@
     </row>
     <row r="1886">
       <c r="A1886" t="str">
-        <v>Kmti9ur4xseh6</v>
+        <v>Kmti9yukdhk60</v>
       </c>
       <c r="B1886" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72244,7 +72244,7 @@
     </row>
     <row r="1888">
       <c r="A1888" t="str">
-        <v>Kmti9ur4xeazs</v>
+        <v>Kmti9yukddrak</v>
       </c>
       <c r="B1888" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72282,7 +72282,7 @@
     </row>
     <row r="1889">
       <c r="A1889" t="str">
-        <v>Kmti9ur4xoxms</v>
+        <v>Kmti9yukdsik3</v>
       </c>
       <c r="B1889" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72320,7 +72320,7 @@
     </row>
     <row r="1890">
       <c r="A1890" t="str">
-        <v>Kmti9ur4x7ddz</v>
+        <v>Kmti9yukd4q3k</v>
       </c>
       <c r="B1890" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72358,7 +72358,7 @@
     </row>
     <row r="1891" xml:space="preserve">
       <c r="A1891" t="str">
-        <v>Kmti9ur4xpf6b</v>
+        <v>Kmti9yukdbrn8</v>
       </c>
       <c r="B1891" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -72397,7 +72397,7 @@
     </row>
     <row r="1892" xml:space="preserve">
       <c r="A1892" t="str">
-        <v>Kmti9ur4xmal2</v>
+        <v>Kmti9yukd5h1h</v>
       </c>
       <c r="B1892" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -72436,7 +72436,7 @@
     </row>
     <row r="1893" xml:space="preserve">
       <c r="A1893" t="str">
-        <v>Kmti9ur4xn3nq</v>
+        <v>Kmti9yukddzuq</v>
       </c>
       <c r="B1893" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -72475,7 +72475,7 @@
     </row>
     <row r="1894" xml:space="preserve">
       <c r="A1894" t="str">
-        <v>Kmti9ur4xbuoy</v>
+        <v>Kmti9yukdu7z7</v>
       </c>
       <c r="B1894" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -72590,7 +72590,7 @@
     </row>
     <row r="1897">
       <c r="A1897" t="str">
-        <v>Kmti9ur4xo6wn</v>
+        <v>Kmti9yukdxyx2</v>
       </c>
       <c r="B1897" t="str">
         <v>Penata Layanan Operasional</v>
@@ -72628,7 +72628,7 @@
     </row>
     <row r="1898">
       <c r="A1898" t="str">
-        <v>Kmti9ur4xyqbd</v>
+        <v>Kmti9yukdjqee</v>
       </c>
       <c r="B1898" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72666,7 +72666,7 @@
     </row>
     <row r="1899">
       <c r="A1899" t="str">
-        <v>Kmti9ur4xsqan</v>
+        <v>Kmti9yukdad06</v>
       </c>
       <c r="B1899" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72704,7 +72704,7 @@
     </row>
     <row r="1900">
       <c r="A1900" t="str">
-        <v>Kmti9ur4x496h</v>
+        <v>Kmti9yukdgzir</v>
       </c>
       <c r="B1900" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72818,7 +72818,7 @@
     </row>
     <row r="1903">
       <c r="A1903" t="str">
-        <v>Kmti9ur4xcati</v>
+        <v>Kmti9yukdip56</v>
       </c>
       <c r="B1903" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72856,7 +72856,7 @@
     </row>
     <row r="1904">
       <c r="A1904" t="str">
-        <v>Kmti9ur4xb96v</v>
+        <v>Kmti9yukdlmdu</v>
       </c>
       <c r="B1904" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72894,7 +72894,7 @@
     </row>
     <row r="1905">
       <c r="A1905" t="str">
-        <v>Kmti9ur4x53v3</v>
+        <v>Kmti9yukdf555</v>
       </c>
       <c r="B1905" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72970,7 +72970,7 @@
     </row>
     <row r="1907">
       <c r="A1907" t="str">
-        <v>Kmti9ur4xd78h</v>
+        <v>Kmti9yukd7sdf</v>
       </c>
       <c r="B1907" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73008,7 +73008,7 @@
     </row>
     <row r="1908">
       <c r="A1908" t="str">
-        <v>Kmti9ur4xfmk9</v>
+        <v>Kmti9yukd4w3j</v>
       </c>
       <c r="B1908" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73046,7 +73046,7 @@
     </row>
     <row r="1909">
       <c r="A1909" t="str">
-        <v>Kmti9ur4xduud</v>
+        <v>Kmti9yukdyngy</v>
       </c>
       <c r="B1909" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73084,7 +73084,7 @@
     </row>
     <row r="1910" xml:space="preserve">
       <c r="A1910" t="str">
-        <v>Kmti9ur4x24xj</v>
+        <v>Kmti9yukdftgs</v>
       </c>
       <c r="B1910" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73123,7 +73123,7 @@
     </row>
     <row r="1911" xml:space="preserve">
       <c r="A1911" t="str">
-        <v>Kmti9ur4xkw50</v>
+        <v>Kmti9yukdka1c</v>
       </c>
       <c r="B1911" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73162,7 +73162,7 @@
     </row>
     <row r="1912" xml:space="preserve">
       <c r="A1912" t="str">
-        <v>Kmti9ur4x8ilm</v>
+        <v>Kmti9yukdlgby</v>
       </c>
       <c r="B1912" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73201,7 +73201,7 @@
     </row>
     <row r="1913" xml:space="preserve">
       <c r="A1913" t="str">
-        <v>Kmti9ur4xwf2a</v>
+        <v>Kmti9yukd65sw</v>
       </c>
       <c r="B1913" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73316,7 +73316,7 @@
     </row>
     <row r="1916">
       <c r="A1916" t="str">
-        <v>Kmti9ur4x0i53</v>
+        <v>Kmti9yukd3yfq</v>
       </c>
       <c r="B1916" t="str">
         <v>Penata Layanan Operasional</v>
@@ -73354,7 +73354,7 @@
     </row>
     <row r="1917">
       <c r="A1917" t="str">
-        <v>Kmti9ur4xe4p9</v>
+        <v>Kmti9yukd8265</v>
       </c>
       <c r="B1917" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73392,7 +73392,7 @@
     </row>
     <row r="1918">
       <c r="A1918" t="str">
-        <v>Kmti9ur4x8o65</v>
+        <v>Kmti9yukd8vm2</v>
       </c>
       <c r="B1918" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73430,7 +73430,7 @@
     </row>
     <row r="1919">
       <c r="A1919" t="str">
-        <v>Kmti9ur4xmf31</v>
+        <v>Kmti9yukdf5ep</v>
       </c>
       <c r="B1919" t="str">
         <v>Penata Keprotokolan*</v>
@@ -73544,7 +73544,7 @@
     </row>
     <row r="1922">
       <c r="A1922" t="str">
-        <v>Kmti9ur4xt9u2</v>
+        <v>Kmti9yukdbq33</v>
       </c>
       <c r="B1922" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73582,7 +73582,7 @@
     </row>
     <row r="1923">
       <c r="A1923" t="str">
-        <v>Kmti9ur4xv7uj</v>
+        <v>Kmti9yukd63dr</v>
       </c>
       <c r="B1923" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73620,7 +73620,7 @@
     </row>
     <row r="1924">
       <c r="A1924" t="str">
-        <v>Kmti9ur4xqr21</v>
+        <v>Kmti9yukdzfru</v>
       </c>
       <c r="B1924" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73696,7 +73696,7 @@
     </row>
     <row r="1926">
       <c r="A1926" t="str">
-        <v>Kmti9ur4xo381</v>
+        <v>Kmti9yukddm3x</v>
       </c>
       <c r="B1926" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73734,7 +73734,7 @@
     </row>
     <row r="1927">
       <c r="A1927" t="str">
-        <v>Kmti9ur4x2lw3</v>
+        <v>Kmti9yukd21x6</v>
       </c>
       <c r="B1927" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73772,7 +73772,7 @@
     </row>
     <row r="1928">
       <c r="A1928" t="str">
-        <v>Kmti9ur4xmhti</v>
+        <v>Kmti9yukd353p</v>
       </c>
       <c r="B1928" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73810,7 +73810,7 @@
     </row>
     <row r="1929" xml:space="preserve">
       <c r="A1929" t="str">
-        <v>Kmti9ur4xptu3</v>
+        <v>Kmti9yukdcr1w</v>
       </c>
       <c r="B1929" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73849,7 +73849,7 @@
     </row>
     <row r="1930" xml:space="preserve">
       <c r="A1930" t="str">
-        <v>Kmti9ur4xuqhr</v>
+        <v>Kmti9yukd9gxi</v>
       </c>
       <c r="B1930" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73888,7 +73888,7 @@
     </row>
     <row r="1931" xml:space="preserve">
       <c r="A1931" t="str">
-        <v>Kmti9ur4xploh</v>
+        <v>Kmti9yukdv3kv</v>
       </c>
       <c r="B1931" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73927,7 +73927,7 @@
     </row>
     <row r="1932" xml:space="preserve">
       <c r="A1932" t="str">
-        <v>Kmti9ur4xetvq</v>
+        <v>Kmti9yukddphs</v>
       </c>
       <c r="B1932" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73966,7 +73966,7 @@
     </row>
     <row r="1933" xml:space="preserve">
       <c r="A1933" t="str">
-        <v>Kmti9ur4xd0oo</v>
+        <v>Kmti9yukdf4zn</v>
       </c>
       <c r="B1933" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74005,7 +74005,7 @@
     </row>
     <row r="1934" xml:space="preserve">
       <c r="A1934" t="str">
-        <v>Kmti9ur4xe8s0</v>
+        <v>Kmti9yukdkbj4</v>
       </c>
       <c r="B1934" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74044,7 +74044,7 @@
     </row>
     <row r="1935" xml:space="preserve">
       <c r="A1935" t="str">
-        <v>Kmti9ur4xr54r</v>
+        <v>Kmti9yukdhcmi</v>
       </c>
       <c r="B1935" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -74159,7 +74159,7 @@
     </row>
     <row r="1938">
       <c r="A1938" t="str">
-        <v>Kmti9ur4x4u5x</v>
+        <v>Kmti9yukdjz19</v>
       </c>
       <c r="B1938" t="str">
         <v>Penata Layanan Operasional</v>
@@ -74197,7 +74197,7 @@
     </row>
     <row r="1939">
       <c r="A1939" t="str">
-        <v>Kmti9ur4xo6dj</v>
+        <v>Kmti9yukdazvu</v>
       </c>
       <c r="B1939" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74235,7 +74235,7 @@
     </row>
     <row r="1940">
       <c r="A1940" t="str">
-        <v>Kmti9ur4x4e0b</v>
+        <v>Kmti9yukdh97d</v>
       </c>
       <c r="B1940" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74273,7 +74273,7 @@
     </row>
     <row r="1941">
       <c r="A1941" t="str">
-        <v>Kmti9ur4xf9rg</v>
+        <v>Kmti9yukdg6wa</v>
       </c>
       <c r="B1941" t="str">
         <v>Penata Keprotokolan*</v>
@@ -74387,7 +74387,7 @@
     </row>
     <row r="1944">
       <c r="A1944" t="str">
-        <v>Kmti9ur4xrtba</v>
+        <v>Kmti9yukdmczk</v>
       </c>
       <c r="B1944" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74425,7 +74425,7 @@
     </row>
     <row r="1945">
       <c r="A1945" t="str">
-        <v>Kmti9ur4x0sor</v>
+        <v>Kmti9yukdud7o</v>
       </c>
       <c r="B1945" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74463,7 +74463,7 @@
     </row>
     <row r="1946">
       <c r="A1946" t="str">
-        <v>Kmti9ur4x7q0l</v>
+        <v>Kmti9yukdukpv</v>
       </c>
       <c r="B1946" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74539,7 +74539,7 @@
     </row>
     <row r="1948">
       <c r="A1948" t="str">
-        <v>Kmti9ur4xsur5</v>
+        <v>Kmti9yukdglp5</v>
       </c>
       <c r="B1948" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74577,7 +74577,7 @@
     </row>
     <row r="1949">
       <c r="A1949" t="str">
-        <v>Kmti9ur4xjt7c</v>
+        <v>Kmti9yukdsspg</v>
       </c>
       <c r="B1949" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74615,7 +74615,7 @@
     </row>
     <row r="1950">
       <c r="A1950" t="str">
-        <v>Kmti9ur4x34ip</v>
+        <v>Kmti9yukd6krl</v>
       </c>
       <c r="B1950" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74653,7 +74653,7 @@
     </row>
     <row r="1951" xml:space="preserve">
       <c r="A1951" t="str">
-        <v>Kmti9ur4xl3qy</v>
+        <v>Kmti9yukdn376</v>
       </c>
       <c r="B1951" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -74692,7 +74692,7 @@
     </row>
     <row r="1952" xml:space="preserve">
       <c r="A1952" t="str">
-        <v>Kmti9ur4xqt6i</v>
+        <v>Kmti9yukd3to2</v>
       </c>
       <c r="B1952" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -74731,7 +74731,7 @@
     </row>
     <row r="1953" xml:space="preserve">
       <c r="A1953" t="str">
-        <v>Kmti9ur4x6qtu</v>
+        <v>Kmti9yukd3rqh</v>
       </c>
       <c r="B1953" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -74770,7 +74770,7 @@
     </row>
     <row r="1954" xml:space="preserve">
       <c r="A1954" t="str">
-        <v>Kmti9ur4xy6az</v>
+        <v>Kmti9yukdtyvp</v>
       </c>
       <c r="B1954" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -74809,7 +74809,7 @@
     </row>
     <row r="1955" xml:space="preserve">
       <c r="A1955" t="str">
-        <v>Kmti9ur4xsu3m</v>
+        <v>Kmti9yukdfyug</v>
       </c>
       <c r="B1955" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74848,7 +74848,7 @@
     </row>
     <row r="1956" xml:space="preserve">
       <c r="A1956" t="str">
-        <v>Kmti9ur4xpz66</v>
+        <v>Kmti9yukdx29h</v>
       </c>
       <c r="B1956" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74887,7 +74887,7 @@
     </row>
     <row r="1957" xml:space="preserve">
       <c r="A1957" t="str">
-        <v>Kmti9ur4xo17f</v>
+        <v>Kmti9yukdur84</v>
       </c>
       <c r="B1957" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -75002,7 +75002,7 @@
     </row>
     <row r="1960">
       <c r="A1960" t="str">
-        <v>Kmti9ur4xy1bz</v>
+        <v>Kmti9yukdk10e</v>
       </c>
       <c r="B1960" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75040,7 +75040,7 @@
     </row>
     <row r="1961">
       <c r="A1961" t="str">
-        <v>Kmti9ur4xhczq</v>
+        <v>Kmti9yukdhon4</v>
       </c>
       <c r="B1961" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75078,7 +75078,7 @@
     </row>
     <row r="1962">
       <c r="A1962" t="str">
-        <v>Kmti9ur4x37l6</v>
+        <v>Kmti9yukd8ppu</v>
       </c>
       <c r="B1962" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75116,7 +75116,7 @@
     </row>
     <row r="1963">
       <c r="A1963" t="str">
-        <v>Kmti9ur4x995v</v>
+        <v>Kmti9yukdkow8</v>
       </c>
       <c r="B1963" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75230,7 +75230,7 @@
     </row>
     <row r="1966">
       <c r="A1966" t="str">
-        <v>Kmti9ur4xbkna</v>
+        <v>Kmti9yukd71if</v>
       </c>
       <c r="B1966" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75268,7 +75268,7 @@
     </row>
     <row r="1967">
       <c r="A1967" t="str">
-        <v>Kmti9ur4x9x2k</v>
+        <v>Kmti9yukdtm84</v>
       </c>
       <c r="B1967" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75306,7 +75306,7 @@
     </row>
     <row r="1968">
       <c r="A1968" t="str">
-        <v>Kmti9ur4xju5u</v>
+        <v>Kmti9yukdrwem</v>
       </c>
       <c r="B1968" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75382,7 +75382,7 @@
     </row>
     <row r="1970">
       <c r="A1970" t="str">
-        <v>Kmti9ur4xp7pq</v>
+        <v>Kmti9yukdsx8a</v>
       </c>
       <c r="B1970" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75420,7 +75420,7 @@
     </row>
     <row r="1971">
       <c r="A1971" t="str">
-        <v>Kmti9ur4x6jyn</v>
+        <v>Kmti9yukd51cd</v>
       </c>
       <c r="B1971" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75458,7 +75458,7 @@
     </row>
     <row r="1972">
       <c r="A1972" t="str">
-        <v>Kmti9ur4x59ht</v>
+        <v>Kmti9yukdt5l0</v>
       </c>
       <c r="B1972" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75496,7 +75496,7 @@
     </row>
     <row r="1973" xml:space="preserve">
       <c r="A1973" t="str">
-        <v>Kmti9ur4x26h1</v>
+        <v>Kmti9yukd6r7m</v>
       </c>
       <c r="B1973" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -75535,7 +75535,7 @@
     </row>
     <row r="1974" xml:space="preserve">
       <c r="A1974" t="str">
-        <v>Kmti9ur4xkh18</v>
+        <v>Kmti9yukdrxp3</v>
       </c>
       <c r="B1974" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -75574,7 +75574,7 @@
     </row>
     <row r="1975" xml:space="preserve">
       <c r="A1975" t="str">
-        <v>Kmti9ur4xgr8j</v>
+        <v>Kmti9yukdxxjr</v>
       </c>
       <c r="B1975" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -75613,7 +75613,7 @@
     </row>
     <row r="1976" xml:space="preserve">
       <c r="A1976" t="str">
-        <v>Kmti9ur4xg31o</v>
+        <v>Kmti9yukdgykc</v>
       </c>
       <c r="B1976" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -75728,7 +75728,7 @@
     </row>
     <row r="1979">
       <c r="A1979" t="str">
-        <v>Kmti9ur4xcrs9</v>
+        <v>Kmti9yukd7yaj</v>
       </c>
       <c r="B1979" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75766,7 +75766,7 @@
     </row>
     <row r="1980">
       <c r="A1980" t="str">
-        <v>Kmti9ur4x0oko</v>
+        <v>Kmti9yukd94ft</v>
       </c>
       <c r="B1980" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75804,7 +75804,7 @@
     </row>
     <row r="1981">
       <c r="A1981" t="str">
-        <v>Kmti9ur4xftjp</v>
+        <v>Kmti9yukdqgq2</v>
       </c>
       <c r="B1981" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75842,7 +75842,7 @@
     </row>
     <row r="1982">
       <c r="A1982" t="str">
-        <v>Kmti9ur4xb4xx</v>
+        <v>Kmti9yukda4jh</v>
       </c>
       <c r="B1982" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75956,7 +75956,7 @@
     </row>
     <row r="1985">
       <c r="A1985" t="str">
-        <v>Kmti9ur4xg6rl</v>
+        <v>Kmti9yukdop5p</v>
       </c>
       <c r="B1985" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75994,7 +75994,7 @@
     </row>
     <row r="1986">
       <c r="A1986" t="str">
-        <v>Kmti9ur4x6p36</v>
+        <v>Kmti9yukdn0ij</v>
       </c>
       <c r="B1986" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76032,7 +76032,7 @@
     </row>
     <row r="1987">
       <c r="A1987" t="str">
-        <v>Kmti9ur4xz420</v>
+        <v>Kmti9yukdj1tf</v>
       </c>
       <c r="B1987" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76108,7 +76108,7 @@
     </row>
     <row r="1989">
       <c r="A1989" t="str">
-        <v>Kmti9ur4xc5gk</v>
+        <v>Kmti9yukd6dm0</v>
       </c>
       <c r="B1989" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76146,7 +76146,7 @@
     </row>
     <row r="1990">
       <c r="A1990" t="str">
-        <v>Kmti9ur4xcvsq</v>
+        <v>Kmti9yukdpi0w</v>
       </c>
       <c r="B1990" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76184,7 +76184,7 @@
     </row>
     <row r="1991">
       <c r="A1991" t="str">
-        <v>Kmti9ur4xizlq</v>
+        <v>Kmti9yukdkhs9</v>
       </c>
       <c r="B1991" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76222,7 +76222,7 @@
     </row>
     <row r="1992" xml:space="preserve">
       <c r="A1992" t="str">
-        <v>Kmti9ur4xljvi</v>
+        <v>Kmti9yukdyo8h</v>
       </c>
       <c r="B1992" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76261,7 +76261,7 @@
     </row>
     <row r="1993" xml:space="preserve">
       <c r="A1993" t="str">
-        <v>Kmti9ur4xis1c</v>
+        <v>Kmti9yukd1jwm</v>
       </c>
       <c r="B1993" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -76300,7 +76300,7 @@
     </row>
     <row r="1994" xml:space="preserve">
       <c r="A1994" t="str">
-        <v>Kmti9ur4x7yay</v>
+        <v>Kmti9yukdsz3n</v>
       </c>
       <c r="B1994" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -76339,7 +76339,7 @@
     </row>
     <row r="1995" xml:space="preserve">
       <c r="A1995" t="str">
-        <v>Kmti9ur4x9yz6</v>
+        <v>Kmti9yukevvbo</v>
       </c>
       <c r="B1995" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -76454,7 +76454,7 @@
     </row>
     <row r="1998">
       <c r="A1998" t="str">
-        <v>Kmti9ur4xx3kg</v>
+        <v>Kmti9yuken0ok</v>
       </c>
       <c r="B1998" t="str">
         <v>Penata Layanan Operasional</v>
@@ -76492,7 +76492,7 @@
     </row>
     <row r="1999">
       <c r="A1999" t="str">
-        <v>Kmti9ur4xxb2n</v>
+        <v>Kmti9yukewwcg</v>
       </c>
       <c r="B1999" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76530,7 +76530,7 @@
     </row>
     <row r="2000">
       <c r="A2000" t="str">
-        <v>Kmti9ur4x09s3</v>
+        <v>Kmti9yuke55ge</v>
       </c>
       <c r="B2000" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76568,7 +76568,7 @@
     </row>
     <row r="2001">
       <c r="A2001" t="str">
-        <v>Kmti9ur4x75mn</v>
+        <v>Kmti9yukeeapn</v>
       </c>
       <c r="B2001" t="str">
         <v>Penata Keprotokolan*</v>
@@ -76682,7 +76682,7 @@
     </row>
     <row r="2004">
       <c r="A2004" t="str">
-        <v>Kmti9ur4xmvw4</v>
+        <v>Kmti9yukev16f</v>
       </c>
       <c r="B2004" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76720,7 +76720,7 @@
     </row>
     <row r="2005">
       <c r="A2005" t="str">
-        <v>Kmti9ur4x5m6n</v>
+        <v>Kmti9yuke203w</v>
       </c>
       <c r="B2005" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76758,7 +76758,7 @@
     </row>
     <row r="2006">
       <c r="A2006" t="str">
-        <v>Kmti9ur4xzt6b</v>
+        <v>Kmti9yuke9miy</v>
       </c>
       <c r="B2006" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76834,7 +76834,7 @@
     </row>
     <row r="2008">
       <c r="A2008" t="str">
-        <v>Kmti9ur4xye59</v>
+        <v>Kmti9yukenr18</v>
       </c>
       <c r="B2008" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76872,7 +76872,7 @@
     </row>
     <row r="2009">
       <c r="A2009" t="str">
-        <v>Kmti9ur4xigre</v>
+        <v>Kmti9yukextx7</v>
       </c>
       <c r="B2009" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76910,7 +76910,7 @@
     </row>
     <row r="2010">
       <c r="A2010" t="str">
-        <v>Kmti9ur4xk9ox</v>
+        <v>Kmti9yukecz84</v>
       </c>
       <c r="B2010" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76948,7 +76948,7 @@
     </row>
     <row r="2011" xml:space="preserve">
       <c r="A2011" t="str">
-        <v>Kmti9ur4xn3fy</v>
+        <v>Kmti9yuke757d</v>
       </c>
       <c r="B2011" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76987,7 +76987,7 @@
     </row>
     <row r="2012" xml:space="preserve">
       <c r="A2012" t="str">
-        <v>Kmti9ur4x8hzq</v>
+        <v>Kmti9yukeqj8g</v>
       </c>
       <c r="B2012" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77026,7 +77026,7 @@
     </row>
     <row r="2013" xml:space="preserve">
       <c r="A2013" t="str">
-        <v>Kmti9ur4xwtne</v>
+        <v>Kmti9yukehzdz</v>
       </c>
       <c r="B2013" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77065,7 +77065,7 @@
     </row>
     <row r="2014" xml:space="preserve">
       <c r="A2014" t="str">
-        <v>Kmti9ur4x1o9n</v>
+        <v>Kmti9yuke192p</v>
       </c>
       <c r="B2014" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77180,7 +77180,7 @@
     </row>
     <row r="2017">
       <c r="A2017" t="str">
-        <v>Kmti9ur4xyq81</v>
+        <v>Kmti9yukexnyw</v>
       </c>
       <c r="B2017" t="str">
         <v>Penata Layanan Operasional</v>
@@ -77218,7 +77218,7 @@
     </row>
     <row r="2018">
       <c r="A2018" t="str">
-        <v>Kmti9ur4xsg30</v>
+        <v>Kmti9yuke6wi6</v>
       </c>
       <c r="B2018" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77256,7 +77256,7 @@
     </row>
     <row r="2019">
       <c r="A2019" t="str">
-        <v>Kmti9ur4x6pgr</v>
+        <v>Kmti9yukez3al</v>
       </c>
       <c r="B2019" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77294,7 +77294,7 @@
     </row>
     <row r="2020">
       <c r="A2020" t="str">
-        <v>Kmti9ur4xdknd</v>
+        <v>Kmti9yukeol57</v>
       </c>
       <c r="B2020" t="str">
         <v>Penata Keprotokolan*</v>
@@ -77408,7 +77408,7 @@
     </row>
     <row r="2023">
       <c r="A2023" t="str">
-        <v>Kmti9ur4xyric</v>
+        <v>Kmti9yukegoow</v>
       </c>
       <c r="B2023" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77446,7 +77446,7 @@
     </row>
     <row r="2024">
       <c r="A2024" t="str">
-        <v>Kmti9ur4xz2h7</v>
+        <v>Kmti9yukekino</v>
       </c>
       <c r="B2024" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77484,7 +77484,7 @@
     </row>
     <row r="2025">
       <c r="A2025" t="str">
-        <v>Kmti9ur4xgxyz</v>
+        <v>Kmti9yuke7wyt</v>
       </c>
       <c r="B2025" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77560,7 +77560,7 @@
     </row>
     <row r="2027">
       <c r="A2027" t="str">
-        <v>Kmti9ur4xtjyc</v>
+        <v>Kmti9yukeiueo</v>
       </c>
       <c r="B2027" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77598,7 +77598,7 @@
     </row>
     <row r="2028">
       <c r="A2028" t="str">
-        <v>Kmti9ur4x0yea</v>
+        <v>Kmti9yukexcfr</v>
       </c>
       <c r="B2028" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77636,7 +77636,7 @@
     </row>
     <row r="2029">
       <c r="A2029" t="str">
-        <v>Kmti9ur4xfk37</v>
+        <v>Kmti9yukentw8</v>
       </c>
       <c r="B2029" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77674,7 +77674,7 @@
     </row>
     <row r="2030" xml:space="preserve">
       <c r="A2030" t="str">
-        <v>Kmti9ur4xl5p3</v>
+        <v>Kmti9yukef2w2</v>
       </c>
       <c r="B2030" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -77713,7 +77713,7 @@
     </row>
     <row r="2031" xml:space="preserve">
       <c r="A2031" t="str">
-        <v>Kmti9ur4x15by</v>
+        <v>Kmti9yuke32zg</v>
       </c>
       <c r="B2031" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77752,7 +77752,7 @@
     </row>
     <row r="2032" xml:space="preserve">
       <c r="A2032" t="str">
-        <v>Kmti9ur4xfk8s</v>
+        <v>Kmti9yukehiz7</v>
       </c>
       <c r="B2032" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77791,7 +77791,7 @@
     </row>
     <row r="2033" xml:space="preserve">
       <c r="A2033" t="str">
-        <v>Kmti9ur4xfzof</v>
+        <v>Kmti9yukejo44</v>
       </c>
       <c r="B2033" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77830,7 +77830,7 @@
     </row>
     <row r="2034">
       <c r="A2034" t="str">
-        <v>Kmti9ur4x7wvx</v>
+        <v>Kmti9yukexfff</v>
       </c>
       <c r="B2034" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -77868,7 +77868,7 @@
     </row>
     <row r="2035">
       <c r="A2035" t="str">
-        <v>Kmti9ur4xilqi</v>
+        <v>Kmti9yukepndc</v>
       </c>
       <c r="B2035" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -77944,7 +77944,7 @@
     </row>
     <row r="2037" xml:space="preserve">
       <c r="A2037" t="str">
-        <v>Kmti9ur4xy2at</v>
+        <v>Kmti9yukeaxlh</v>
       </c>
       <c r="B2037" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -77972,7 +77972,7 @@
         <v/>
       </c>
       <c r="J2037" t="str">
-        <v/>
+        <v>Jabatan Fungsional</v>
       </c>
       <c r="K2037" t="str">
         <v/>

--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -63909,7 +63909,7 @@
     </row>
     <row r="1669">
       <c r="A1669" t="str">
-        <v>Kmti9yukcofxe</v>
+        <v>Kmti9zgfv26p3</v>
       </c>
       <c r="B1669" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -63947,7 +63947,7 @@
     </row>
     <row r="1670">
       <c r="A1670" t="str">
-        <v>Kmti9yukcfsz7</v>
+        <v>Kmti9zgfvwyrb</v>
       </c>
       <c r="B1670" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -63985,7 +63985,7 @@
     </row>
     <row r="1671">
       <c r="A1671" t="str">
-        <v>Kmti9yukcf9iq</v>
+        <v>Kmti9zgfvtx00</v>
       </c>
       <c r="B1671" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64023,7 +64023,7 @@
     </row>
     <row r="1672">
       <c r="A1672" t="str">
-        <v>Kmti9yukc58uh</v>
+        <v>Kmti9zgfv4cbb</v>
       </c>
       <c r="B1672" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64061,7 +64061,7 @@
     </row>
     <row r="1673">
       <c r="A1673" t="str">
-        <v>Kmti9yukcfnao</v>
+        <v>Kmti9zgfv0cd5</v>
       </c>
       <c r="B1673" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64099,7 +64099,7 @@
     </row>
     <row r="1674">
       <c r="A1674" t="str">
-        <v>Kmti9yukc81rb</v>
+        <v>Kmti9zgfv45ja</v>
       </c>
       <c r="B1674" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64137,7 +64137,7 @@
     </row>
     <row r="1675">
       <c r="A1675" t="str">
-        <v>Kmti9yukcmk5n</v>
+        <v>Kmti9zgfv5dbr</v>
       </c>
       <c r="B1675" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64175,7 +64175,7 @@
     </row>
     <row r="1676">
       <c r="A1676" t="str">
-        <v>Kmti9yukctkgi</v>
+        <v>Kmti9zgfvpxse</v>
       </c>
       <c r="B1676" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64251,7 +64251,7 @@
     </row>
     <row r="1678">
       <c r="A1678" t="str">
-        <v>Kmti9yukcp0hn</v>
+        <v>Kmti9zgfvuuv7</v>
       </c>
       <c r="B1678" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64289,7 +64289,7 @@
     </row>
     <row r="1679">
       <c r="A1679" t="str">
-        <v>Kmti9yukcj4fo</v>
+        <v>Kmti9zgfvlrdk</v>
       </c>
       <c r="B1679" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64327,7 +64327,7 @@
     </row>
     <row r="1680">
       <c r="A1680" t="str">
-        <v>Kmti9yukc4zuf</v>
+        <v>Kmti9zgfvbsli</v>
       </c>
       <c r="B1680" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64365,7 +64365,7 @@
     </row>
     <row r="1681">
       <c r="A1681" t="str">
-        <v>Kmti9yukczuqw</v>
+        <v>Kmti9zgfv70po</v>
       </c>
       <c r="B1681" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64403,7 +64403,7 @@
     </row>
     <row r="1682">
       <c r="A1682" t="str">
-        <v>Kmti9yukc8u3w</v>
+        <v>Kmti9zgfveogu</v>
       </c>
       <c r="B1682" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64441,7 +64441,7 @@
     </row>
     <row r="1683">
       <c r="A1683" t="str">
-        <v>Kmti9yukckfny</v>
+        <v>Kmti9zgfvmgxf</v>
       </c>
       <c r="B1683" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64479,7 +64479,7 @@
     </row>
     <row r="1684">
       <c r="A1684" t="str">
-        <v>Kmti9yukcwern</v>
+        <v>Kmti9zgfvknli</v>
       </c>
       <c r="B1684" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64517,7 +64517,7 @@
     </row>
     <row r="1685">
       <c r="A1685" t="str">
-        <v>Kmti9yukck28r</v>
+        <v>Kmti9zgfvprvh</v>
       </c>
       <c r="B1685" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64593,7 +64593,7 @@
     </row>
     <row r="1687">
       <c r="A1687" t="str">
-        <v>Kmti9yukcd9l6</v>
+        <v>Kmti9zgfvbb3w</v>
       </c>
       <c r="B1687" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64631,7 +64631,7 @@
     </row>
     <row r="1688">
       <c r="A1688" t="str">
-        <v>Kmti9yukcrw7k</v>
+        <v>Kmti9zgfvdowe</v>
       </c>
       <c r="B1688" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64669,7 +64669,7 @@
     </row>
     <row r="1689">
       <c r="A1689" t="str">
-        <v>Kmti9yukc9eg8</v>
+        <v>Kmti9zgfvapml</v>
       </c>
       <c r="B1689" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64707,7 +64707,7 @@
     </row>
     <row r="1690">
       <c r="A1690" t="str">
-        <v>Kmti9yukckemr</v>
+        <v>Kmti9zgfv6noy</v>
       </c>
       <c r="B1690" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64745,7 +64745,7 @@
     </row>
     <row r="1691">
       <c r="A1691" t="str">
-        <v>Kmti9yukcky8f</v>
+        <v>Kmti9zgfvsrt3</v>
       </c>
       <c r="B1691" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64783,7 +64783,7 @@
     </row>
     <row r="1692">
       <c r="A1692" t="str">
-        <v>Kmti9yukc38w9</v>
+        <v>Kmti9zgfv7snw</v>
       </c>
       <c r="B1692" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64821,7 +64821,7 @@
     </row>
     <row r="1693">
       <c r="A1693" t="str">
-        <v>Kmti9yukcyfpi</v>
+        <v>Kmti9zgfvijxf</v>
       </c>
       <c r="B1693" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64859,7 +64859,7 @@
     </row>
     <row r="1694">
       <c r="A1694" t="str">
-        <v>Kmti9yukcourn</v>
+        <v>Kmti9zgfvq82j</v>
       </c>
       <c r="B1694" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64897,7 +64897,7 @@
     </row>
     <row r="1695">
       <c r="A1695" t="str">
-        <v>Kmti9yukcl2av</v>
+        <v>Kmti9zgfvy2bj</v>
       </c>
       <c r="B1695" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64935,7 +64935,7 @@
     </row>
     <row r="1696">
       <c r="A1696" t="str">
-        <v>Kmti9yukczj03</v>
+        <v>Kmti9zgfv3xh5</v>
       </c>
       <c r="B1696" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64973,7 +64973,7 @@
     </row>
     <row r="1697">
       <c r="A1697" t="str">
-        <v>Kmti9yukc6j0x</v>
+        <v>Kmti9zgfv676s</v>
       </c>
       <c r="B1697" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65087,7 +65087,7 @@
     </row>
     <row r="1700">
       <c r="A1700" t="str">
-        <v>Kmti9yukc1hrv</v>
+        <v>Kmti9zgfv4f31</v>
       </c>
       <c r="B1700" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65125,7 +65125,7 @@
     </row>
     <row r="1701">
       <c r="A1701" t="str">
-        <v>Kmti9yukc74ou</v>
+        <v>Kmti9zgfvaki2</v>
       </c>
       <c r="B1701" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65163,7 +65163,7 @@
     </row>
     <row r="1702">
       <c r="A1702" t="str">
-        <v>Kmti9yukcqe1f</v>
+        <v>Kmti9zgfvljfh</v>
       </c>
       <c r="B1702" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65201,7 +65201,7 @@
     </row>
     <row r="1703">
       <c r="A1703" t="str">
-        <v>Kmti9yukc1ni9</v>
+        <v>Kmti9zgfvbm7i</v>
       </c>
       <c r="B1703" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65239,7 +65239,7 @@
     </row>
     <row r="1704">
       <c r="A1704" t="str">
-        <v>Kmti9yukcau4s</v>
+        <v>Kmti9zgfvw9hy</v>
       </c>
       <c r="B1704" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65277,7 +65277,7 @@
     </row>
     <row r="1705">
       <c r="A1705" t="str">
-        <v>Kmti9yukcz88u</v>
+        <v>Kmti9zgfv2qcb</v>
       </c>
       <c r="B1705" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65315,7 +65315,7 @@
     </row>
     <row r="1706">
       <c r="A1706" t="str">
-        <v>Kmti9yukctog3</v>
+        <v>Kmti9zgfvd8mh</v>
       </c>
       <c r="B1706" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65353,7 +65353,7 @@
     </row>
     <row r="1707">
       <c r="A1707" t="str">
-        <v>Kmti9yukc0jz8</v>
+        <v>Kmti9zgfvc9si</v>
       </c>
       <c r="B1707" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65391,7 +65391,7 @@
     </row>
     <row r="1708">
       <c r="A1708" t="str">
-        <v>Kmti9yukc8mjr</v>
+        <v>Kmti9zgfvawm4</v>
       </c>
       <c r="B1708" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -65429,7 +65429,7 @@
     </row>
     <row r="1709">
       <c r="A1709" t="str">
-        <v>Kmti9yukc0x73</v>
+        <v>Kmti9zgfvu4kv</v>
       </c>
       <c r="B1709" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -65505,7 +65505,7 @@
     </row>
     <row r="1711">
       <c r="A1711" t="str">
-        <v>Kmti9yukchmug</v>
+        <v>Kmti9zgfvn91l</v>
       </c>
       <c r="B1711" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65543,7 +65543,7 @@
     </row>
     <row r="1712">
       <c r="A1712" t="str">
-        <v>Kmti9yukce7ib</v>
+        <v>Kmti9zgfvy7ll</v>
       </c>
       <c r="B1712" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65581,7 +65581,7 @@
     </row>
     <row r="1713">
       <c r="A1713" t="str">
-        <v>Kmti9yukcwch7</v>
+        <v>Kmti9zgfv3bkw</v>
       </c>
       <c r="B1713" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65619,7 +65619,7 @@
     </row>
     <row r="1714">
       <c r="A1714" t="str">
-        <v>Kmti9yukd5n45</v>
+        <v>Kmti9zgfvk58c</v>
       </c>
       <c r="B1714" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65657,7 +65657,7 @@
     </row>
     <row r="1715">
       <c r="A1715" t="str">
-        <v>Kmti9yukdbjt6</v>
+        <v>Kmti9zgfvg5e1</v>
       </c>
       <c r="B1715" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65695,7 +65695,7 @@
     </row>
     <row r="1716">
       <c r="A1716" t="str">
-        <v>Kmti9yukd8bkx</v>
+        <v>Kmti9zgfvk469</v>
       </c>
       <c r="B1716" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65733,7 +65733,7 @@
     </row>
     <row r="1717">
       <c r="A1717" t="str">
-        <v>Kmti9yukdr5rn</v>
+        <v>Kmti9zgfwkwkh</v>
       </c>
       <c r="B1717" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65771,7 +65771,7 @@
     </row>
     <row r="1718">
       <c r="A1718" t="str">
-        <v>Kmti9yukd68w6</v>
+        <v>Kmti9zgfwsx0u</v>
       </c>
       <c r="B1718" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65847,7 +65847,7 @@
     </row>
     <row r="1720">
       <c r="A1720" t="str">
-        <v>Kmti9yukdttf6</v>
+        <v>Kmti9zgfwr6bz</v>
       </c>
       <c r="B1720" t="str">
         <v>Penata Layanan Operasional</v>
@@ -65885,7 +65885,7 @@
     </row>
     <row r="1721">
       <c r="A1721" t="str">
-        <v>Kmti9yukdsgax</v>
+        <v>Kmti9zgfwgsxa</v>
       </c>
       <c r="B1721" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65923,7 +65923,7 @@
     </row>
     <row r="1722">
       <c r="A1722" t="str">
-        <v>Kmti9yukd1eo1</v>
+        <v>Kmti9zgfw4dul</v>
       </c>
       <c r="B1722" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65961,7 +65961,7 @@
     </row>
     <row r="1723">
       <c r="A1723" t="str">
-        <v>Kmti9yukdbiv0</v>
+        <v>Kmti9zgfwowkd</v>
       </c>
       <c r="B1723" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65999,7 +65999,7 @@
     </row>
     <row r="1724">
       <c r="A1724" t="str">
-        <v>Kmti9yukdtdrn</v>
+        <v>Kmti9zgfwsb26</v>
       </c>
       <c r="B1724" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66037,7 +66037,7 @@
     </row>
     <row r="1725">
       <c r="A1725" t="str">
-        <v>Kmti9yukd3t41</v>
+        <v>Kmti9zgfwaza4</v>
       </c>
       <c r="B1725" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66075,7 +66075,7 @@
     </row>
     <row r="1726">
       <c r="A1726" t="str">
-        <v>Kmti9yukd5ff9</v>
+        <v>Kmti9zgfwure0</v>
       </c>
       <c r="B1726" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66113,7 +66113,7 @@
     </row>
     <row r="1727">
       <c r="A1727" t="str">
-        <v>Kmti9yukd5ywk</v>
+        <v>Kmti9zgfwsb5n</v>
       </c>
       <c r="B1727" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66189,7 +66189,7 @@
     </row>
     <row r="1729">
       <c r="A1729" t="str">
-        <v>Kmti9yukd1qen</v>
+        <v>Kmti9zgfw36rk</v>
       </c>
       <c r="B1729" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66227,7 +66227,7 @@
     </row>
     <row r="1730">
       <c r="A1730" t="str">
-        <v>Kmti9yukdt9eg</v>
+        <v>Kmti9zgfw3xp6</v>
       </c>
       <c r="B1730" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66265,7 +66265,7 @@
     </row>
     <row r="1731">
       <c r="A1731" t="str">
-        <v>Kmti9yukdd73v</v>
+        <v>Kmti9zgfwfvik</v>
       </c>
       <c r="B1731" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66303,7 +66303,7 @@
     </row>
     <row r="1732">
       <c r="A1732" t="str">
-        <v>Kmti9yukdmgrp</v>
+        <v>Kmti9zgfw4593</v>
       </c>
       <c r="B1732" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66341,7 +66341,7 @@
     </row>
     <row r="1733">
       <c r="A1733" t="str">
-        <v>Kmti9yukd38cl</v>
+        <v>Kmti9zgfw4kki</v>
       </c>
       <c r="B1733" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66379,7 +66379,7 @@
     </row>
     <row r="1734">
       <c r="A1734" t="str">
-        <v>Kmti9yukd6vj8</v>
+        <v>Kmti9zgfw72q9</v>
       </c>
       <c r="B1734" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66417,7 +66417,7 @@
     </row>
     <row r="1735">
       <c r="A1735" t="str">
-        <v>Kmti9yukdcc39</v>
+        <v>Kmti9zgfw0hmg</v>
       </c>
       <c r="B1735" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66455,7 +66455,7 @@
     </row>
     <row r="1736">
       <c r="A1736" t="str">
-        <v>Kmti9yukd2qa4</v>
+        <v>Kmti9zgfw9jf7</v>
       </c>
       <c r="B1736" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66493,7 +66493,7 @@
     </row>
     <row r="1737">
       <c r="A1737" t="str">
-        <v>Kmti9yukdn227</v>
+        <v>Kmti9zgfw4y3j</v>
       </c>
       <c r="B1737" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66531,7 +66531,7 @@
     </row>
     <row r="1738">
       <c r="A1738" t="str">
-        <v>Kmti9yukdtavb</v>
+        <v>Kmti9zgfwto78</v>
       </c>
       <c r="B1738" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66569,7 +66569,7 @@
     </row>
     <row r="1739">
       <c r="A1739" t="str">
-        <v>Kmti9yukd06ri</v>
+        <v>Kmti9zgfw6xgk</v>
       </c>
       <c r="B1739" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66607,7 +66607,7 @@
     </row>
     <row r="1740">
       <c r="A1740" t="str">
-        <v>Kmti9yukd69i6</v>
+        <v>Kmti9zgfw57jm</v>
       </c>
       <c r="B1740" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66645,7 +66645,7 @@
     </row>
     <row r="1741">
       <c r="A1741" t="str">
-        <v>Kmti9yukdfab6</v>
+        <v>Kmti9zgfwlksp</v>
       </c>
       <c r="B1741" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66683,7 +66683,7 @@
     </row>
     <row r="1742">
       <c r="A1742" t="str">
-        <v>Kmti9yukdmc22</v>
+        <v>Kmti9zgfwiets</v>
       </c>
       <c r="B1742" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -66721,7 +66721,7 @@
     </row>
     <row r="1743">
       <c r="A1743" t="str">
-        <v>Kmti9yukdamse</v>
+        <v>Kmti9zgfwmd71</v>
       </c>
       <c r="B1743" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -66835,7 +66835,7 @@
     </row>
     <row r="1746">
       <c r="A1746" t="str">
-        <v>Kmti9yukduryf</v>
+        <v>Kmti9zgfwph3s</v>
       </c>
       <c r="B1746" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66873,7 +66873,7 @@
     </row>
     <row r="1747">
       <c r="A1747" t="str">
-        <v>Kmti9yukdo9fp</v>
+        <v>Kmti9zgfwkppc</v>
       </c>
       <c r="B1747" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66911,7 +66911,7 @@
     </row>
     <row r="1748">
       <c r="A1748" t="str">
-        <v>Kmti9yukdl6ik</v>
+        <v>Kmti9zgfw0cxv</v>
       </c>
       <c r="B1748" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66949,7 +66949,7 @@
     </row>
     <row r="1749" xml:space="preserve">
       <c r="A1749" t="str">
-        <v>Kmti9yukdfnw9</v>
+        <v>Kmti9zgfw6ykh</v>
       </c>
       <c r="B1749" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -66988,7 +66988,7 @@
     </row>
     <row r="1750">
       <c r="A1750" t="str">
-        <v>Kmti9yukdhnmb</v>
+        <v>Kmti9zgfwrkt3</v>
       </c>
       <c r="B1750" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67064,7 +67064,7 @@
     </row>
     <row r="1752">
       <c r="A1752" t="str">
-        <v>Kmti9yukdnord</v>
+        <v>Kmti9zgfw2txy</v>
       </c>
       <c r="B1752" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67102,7 +67102,7 @@
     </row>
     <row r="1753">
       <c r="A1753" t="str">
-        <v>Kmti9yukdayap</v>
+        <v>Kmti9zgfw3olu</v>
       </c>
       <c r="B1753" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67140,7 +67140,7 @@
     </row>
     <row r="1754">
       <c r="A1754" t="str">
-        <v>Kmti9yukdzmt5</v>
+        <v>Kmti9zgfwyrgw</v>
       </c>
       <c r="B1754" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67178,7 +67178,7 @@
     </row>
     <row r="1755" xml:space="preserve">
       <c r="A1755" t="str">
-        <v>Kmti9yukdt06d</v>
+        <v>Kmti9zgfw5xjt</v>
       </c>
       <c r="B1755" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67217,7 +67217,7 @@
     </row>
     <row r="1756" xml:space="preserve">
       <c r="A1756" t="str">
-        <v>Kmti9yukd7zza</v>
+        <v>Kmti9zgfwukt5</v>
       </c>
       <c r="B1756" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67256,7 +67256,7 @@
     </row>
     <row r="1757">
       <c r="A1757" t="str">
-        <v>Kmti9yukdua60</v>
+        <v>Kmti9zgfwffgf</v>
       </c>
       <c r="B1757" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67294,7 +67294,7 @@
     </row>
     <row r="1758" xml:space="preserve">
       <c r="A1758" t="str">
-        <v>Kmti9yukd6m0x</v>
+        <v>Kmti9zgfwfrt0</v>
       </c>
       <c r="B1758" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67333,7 +67333,7 @@
     </row>
     <row r="1759" xml:space="preserve">
       <c r="A1759" t="str">
-        <v>Kmti9yukdhaia</v>
+        <v>Kmti9zgfwqx35</v>
       </c>
       <c r="B1759" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67410,7 +67410,7 @@
     </row>
     <row r="1761">
       <c r="A1761" t="str">
-        <v>Kmti9yukdotfj</v>
+        <v>Kmti9zgfwp79t</v>
       </c>
       <c r="B1761" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67448,7 +67448,7 @@
     </row>
     <row r="1762">
       <c r="A1762" t="str">
-        <v>Kmti9yukdqwgc</v>
+        <v>Kmti9zgfw5w0d</v>
       </c>
       <c r="B1762" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67486,7 +67486,7 @@
     </row>
     <row r="1763">
       <c r="A1763" t="str">
-        <v>Kmti9yukd9fk0</v>
+        <v>Kmti9zgfwwc7b</v>
       </c>
       <c r="B1763" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67524,7 +67524,7 @@
     </row>
     <row r="1764" xml:space="preserve">
       <c r="A1764" t="str">
-        <v>Kmti9yukd876c</v>
+        <v>Kmti9zgfwgmis</v>
       </c>
       <c r="B1764" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67563,7 +67563,7 @@
     </row>
     <row r="1765" xml:space="preserve">
       <c r="A1765" t="str">
-        <v>Kmti9yukdhsac</v>
+        <v>Kmti9zgfwqfcn</v>
       </c>
       <c r="B1765" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67602,7 +67602,7 @@
     </row>
     <row r="1766">
       <c r="A1766" t="str">
-        <v>Kmti9yukdd1hm</v>
+        <v>Kmti9zgfw8fwd</v>
       </c>
       <c r="B1766" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67640,7 +67640,7 @@
     </row>
     <row r="1767" xml:space="preserve">
       <c r="A1767" t="str">
-        <v>Kmti9yukdfk38</v>
+        <v>Kmti9zgfw3a03</v>
       </c>
       <c r="B1767" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67679,7 +67679,7 @@
     </row>
     <row r="1768" xml:space="preserve">
       <c r="A1768" t="str">
-        <v>Kmti9yukdeysi</v>
+        <v>Kmti9zgfwnd9w</v>
       </c>
       <c r="B1768" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67718,7 +67718,7 @@
     </row>
     <row r="1769">
       <c r="A1769" t="str">
-        <v>Kmti9yukd6dko</v>
+        <v>Kmti9zgfwg7p6</v>
       </c>
       <c r="B1769" t="str">
         <v>Analis Anggaran Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -67756,7 +67756,7 @@
     </row>
     <row r="1770">
       <c r="A1770" t="str">
-        <v>Kmti9yukdrkj3</v>
+        <v>Kmti9zgfwlxww</v>
       </c>
       <c r="B1770" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67794,7 +67794,7 @@
     </row>
     <row r="1771">
       <c r="A1771" t="str">
-        <v>Kmti9yukdg2zo</v>
+        <v>Kmti9zgfweso7</v>
       </c>
       <c r="B1771" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -67832,7 +67832,7 @@
     </row>
     <row r="1772">
       <c r="A1772" t="str">
-        <v>Kmti9yukd5qt2</v>
+        <v>Kmti9zgfwya1b</v>
       </c>
       <c r="B1772" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Ahli Muda</v>
@@ -67870,7 +67870,7 @@
     </row>
     <row r="1773">
       <c r="A1773" t="str">
-        <v>Kmti9yukdb432</v>
+        <v>Kmti9zgfwol0w</v>
       </c>
       <c r="B1773" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -67908,7 +67908,7 @@
     </row>
     <row r="1774">
       <c r="A1774" t="str">
-        <v>Kmti9yukdvcur</v>
+        <v>Kmti9zgfw4mzw</v>
       </c>
       <c r="B1774" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67946,7 +67946,7 @@
     </row>
     <row r="1775">
       <c r="A1775" t="str">
-        <v>Kmti9yukdzk8r</v>
+        <v>Kmti9zgfwb5sn</v>
       </c>
       <c r="B1775" t="str">
         <v>Pranata Keuangan APBN Mahir/Pengawas Keuangan Negara Mahir</v>
@@ -67984,7 +67984,7 @@
     </row>
     <row r="1776">
       <c r="A1776" t="str">
-        <v>Kmti9yukdjzl7</v>
+        <v>Kmti9zgfw42g7</v>
       </c>
       <c r="B1776" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -68098,7 +68098,7 @@
     </row>
     <row r="1779">
       <c r="A1779" t="str">
-        <v>Kmti9yukd2pmd</v>
+        <v>Kmti9zgfwgvaq</v>
       </c>
       <c r="B1779" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68136,7 +68136,7 @@
     </row>
     <row r="1780">
       <c r="A1780" t="str">
-        <v>Kmti9yukdptus</v>
+        <v>Kmti9zgfw117s</v>
       </c>
       <c r="B1780" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68174,7 +68174,7 @@
     </row>
     <row r="1781">
       <c r="A1781" t="str">
-        <v>Kmti9yukd1j09</v>
+        <v>Kmti9zgfwc6hl</v>
       </c>
       <c r="B1781" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68250,7 +68250,7 @@
     </row>
     <row r="1783">
       <c r="A1783" t="str">
-        <v>Kmti9yukdir23</v>
+        <v>Kmti9zgfwprkg</v>
       </c>
       <c r="B1783" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68288,7 +68288,7 @@
     </row>
     <row r="1784">
       <c r="A1784" t="str">
-        <v>Kmti9yukd7ymh</v>
+        <v>Kmti9zgfwlhys</v>
       </c>
       <c r="B1784" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68326,7 +68326,7 @@
     </row>
     <row r="1785">
       <c r="A1785" t="str">
-        <v>Kmti9yukd1zh1</v>
+        <v>Kmti9zgfwkuna</v>
       </c>
       <c r="B1785" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68364,7 +68364,7 @@
     </row>
     <row r="1786">
       <c r="A1786" t="str">
-        <v>Kmti9yukdbv0k</v>
+        <v>Kmti9zgfwluh2</v>
       </c>
       <c r="B1786" t="str">
         <v>Penata Keprotokolan*</v>
@@ -68402,7 +68402,7 @@
     </row>
     <row r="1787">
       <c r="A1787" t="str">
-        <v>Kmti9yukd9si1</v>
+        <v>Kmti9zgfwg7ii</v>
       </c>
       <c r="B1787" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68440,7 +68440,7 @@
     </row>
     <row r="1788">
       <c r="A1788" t="str">
-        <v>Kmti9yukdlwj5</v>
+        <v>Kmti9zgfwzqqc</v>
       </c>
       <c r="B1788" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68478,7 +68478,7 @@
     </row>
     <row r="1789">
       <c r="A1789" t="str">
-        <v>Kmti9yukd70ag</v>
+        <v>Kmti9zgfwg8vo</v>
       </c>
       <c r="B1789" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68516,7 +68516,7 @@
     </row>
     <row r="1790">
       <c r="A1790" t="str">
-        <v>Kmti9yukd5w8m</v>
+        <v>Kmti9zgfw6kia</v>
       </c>
       <c r="B1790" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68592,7 +68592,7 @@
     </row>
     <row r="1792">
       <c r="A1792" t="str">
-        <v>Kmti9yukd0wrn</v>
+        <v>Kmti9zgfwvs7f</v>
       </c>
       <c r="B1792" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68630,7 +68630,7 @@
     </row>
     <row r="1793">
       <c r="A1793" t="str">
-        <v>Kmti9yukdqmsb</v>
+        <v>Kmti9zgfwinbd</v>
       </c>
       <c r="B1793" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68668,7 +68668,7 @@
     </row>
     <row r="1794">
       <c r="A1794" t="str">
-        <v>Kmti9yukd0sfv</v>
+        <v>Kmti9zgfwi2a5</v>
       </c>
       <c r="B1794" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68706,7 +68706,7 @@
     </row>
     <row r="1795">
       <c r="A1795" t="str">
-        <v>Kmti9yukdmve6</v>
+        <v>Kmti9zgfw1s7e</v>
       </c>
       <c r="B1795" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -68744,7 +68744,7 @@
     </row>
     <row r="1796">
       <c r="A1796" t="str">
-        <v>Kmti9yukdl7jm</v>
+        <v>Kmti9zgfwtdxj</v>
       </c>
       <c r="B1796" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68782,7 +68782,7 @@
     </row>
     <row r="1797">
       <c r="A1797" t="str">
-        <v>Kmti9yukde0xl</v>
+        <v>Kmti9zgfw2ch2</v>
       </c>
       <c r="B1797" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68820,7 +68820,7 @@
     </row>
     <row r="1798">
       <c r="A1798" t="str">
-        <v>Kmti9yukds4g5</v>
+        <v>Kmti9zgfwp942</v>
       </c>
       <c r="B1798" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68858,7 +68858,7 @@
     </row>
     <row r="1799">
       <c r="A1799" t="str">
-        <v>Kmti9yukd2c9l</v>
+        <v>Kmti9zgfw2ttx</v>
       </c>
       <c r="B1799" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68934,7 +68934,7 @@
     </row>
     <row r="1801">
       <c r="A1801" t="str">
-        <v>Kmti9yukdbfr5</v>
+        <v>Kmti9zgfw74gb</v>
       </c>
       <c r="B1801" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68972,7 +68972,7 @@
     </row>
     <row r="1802">
       <c r="A1802" t="str">
-        <v>Kmti9yukdtwzc</v>
+        <v>Kmti9zgfwbjjg</v>
       </c>
       <c r="B1802" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69010,7 +69010,7 @@
     </row>
     <row r="1803">
       <c r="A1803" t="str">
-        <v>Kmti9yukdtwi5</v>
+        <v>Kmti9zgfwrqwo</v>
       </c>
       <c r="B1803" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69048,7 +69048,7 @@
     </row>
     <row r="1804">
       <c r="A1804" t="str">
-        <v>Kmti9yukdgvp4</v>
+        <v>Kmti9zgfwhexu</v>
       </c>
       <c r="B1804" t="str">
         <v>Penata Keprotokolan*</v>
@@ -69086,7 +69086,7 @@
     </row>
     <row r="1805">
       <c r="A1805" t="str">
-        <v>Kmti9yukdntuz</v>
+        <v>Kmti9zgfwdna0</v>
       </c>
       <c r="B1805" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -69124,7 +69124,7 @@
     </row>
     <row r="1806">
       <c r="A1806" t="str">
-        <v>Kmti9yukdtlp0</v>
+        <v>Kmti9zgfwxez5</v>
       </c>
       <c r="B1806" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -69162,7 +69162,7 @@
     </row>
     <row r="1807">
       <c r="A1807" t="str">
-        <v>Kmti9yukd7iki</v>
+        <v>Kmti9zgfwy5z6</v>
       </c>
       <c r="B1807" t="str">
         <v>Arsiparis Penyelia</v>
@@ -69200,7 +69200,7 @@
     </row>
     <row r="1808">
       <c r="A1808" t="str">
-        <v>Kmti9yukd7j9j</v>
+        <v>Kmti9zgfw5cy1</v>
       </c>
       <c r="B1808" t="str">
         <v>Arsiparis Mahir</v>
@@ -69238,7 +69238,7 @@
     </row>
     <row r="1809">
       <c r="A1809" t="str">
-        <v>Kmti9yukdsrua</v>
+        <v>Kmti9zgfweff0</v>
       </c>
       <c r="B1809" t="str">
         <v>Arsiparis Terampil</v>
@@ -69276,7 +69276,7 @@
     </row>
     <row r="1810">
       <c r="A1810" t="str">
-        <v>Kmti9yukdu6x7</v>
+        <v>Kmti9zgfwfxcr</v>
       </c>
       <c r="B1810" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -69314,7 +69314,7 @@
     </row>
     <row r="1811">
       <c r="A1811" t="str">
-        <v>Kmti9yukdxuwv</v>
+        <v>Kmti9zgfwj2pm</v>
       </c>
       <c r="B1811" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69352,7 +69352,7 @@
     </row>
     <row r="1812">
       <c r="A1812" t="str">
-        <v>Kmti9yukdb1tw</v>
+        <v>Kmti9zgfwe8ra</v>
       </c>
       <c r="B1812" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -69390,7 +69390,7 @@
     </row>
     <row r="1813">
       <c r="A1813" t="str">
-        <v>Kmti9yukddvq3</v>
+        <v>Kmti9zgfwaj0c</v>
       </c>
       <c r="B1813" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -69428,7 +69428,7 @@
     </row>
     <row r="1814">
       <c r="A1814" t="str">
-        <v>Kmti9yukdz3ei</v>
+        <v>Kmti9zgfwvo49</v>
       </c>
       <c r="B1814" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -69542,7 +69542,7 @@
     </row>
     <row r="1817">
       <c r="A1817" t="str">
-        <v>Kmti9yukdoadn</v>
+        <v>Kmti9zgfwjqwo</v>
       </c>
       <c r="B1817" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69580,7 +69580,7 @@
     </row>
     <row r="1818">
       <c r="A1818" t="str">
-        <v>Kmti9yukdaz20</v>
+        <v>Kmti9zgfwem78</v>
       </c>
       <c r="B1818" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69618,7 +69618,7 @@
     </row>
     <row r="1819">
       <c r="A1819" t="str">
-        <v>Kmti9yukdcd45</v>
+        <v>Kmti9zgfw48hj</v>
       </c>
       <c r="B1819" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69656,7 +69656,7 @@
     </row>
     <row r="1820">
       <c r="A1820" t="str">
-        <v>Kmti9yukd2xjx</v>
+        <v>Kmti9zgfwyiy6</v>
       </c>
       <c r="B1820" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69694,7 +69694,7 @@
     </row>
     <row r="1821">
       <c r="A1821" t="str">
-        <v>Kmti9yukdvgf1</v>
+        <v>Kmti9zgfw4rmo</v>
       </c>
       <c r="B1821" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69732,7 +69732,7 @@
     </row>
     <row r="1822">
       <c r="A1822" t="str">
-        <v>Kmti9yukdz9ez</v>
+        <v>Kmti9zgfwsdmd</v>
       </c>
       <c r="B1822" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -69808,7 +69808,7 @@
     </row>
     <row r="1824">
       <c r="A1824" t="str">
-        <v>Kmti9yukdkg0u</v>
+        <v>Kmti9zgfwhaic</v>
       </c>
       <c r="B1824" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69846,7 +69846,7 @@
     </row>
     <row r="1825">
       <c r="A1825" t="str">
-        <v>Kmti9yukdiopv</v>
+        <v>Kmti9zgfwz66l</v>
       </c>
       <c r="B1825" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69884,7 +69884,7 @@
     </row>
     <row r="1826">
       <c r="A1826" t="str">
-        <v>Kmti9yukdum1c</v>
+        <v>Kmti9zgfw2y2o</v>
       </c>
       <c r="B1826" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69922,7 +69922,7 @@
     </row>
     <row r="1827">
       <c r="A1827" t="str">
-        <v>Kmti9yukd8o94</v>
+        <v>Kmti9zgfwldzg</v>
       </c>
       <c r="B1827" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69960,7 +69960,7 @@
     </row>
     <row r="1828">
       <c r="A1828" t="str">
-        <v>Kmti9yukdqu4z</v>
+        <v>Kmti9zgfwln2m</v>
       </c>
       <c r="B1828" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69998,7 +69998,7 @@
     </row>
     <row r="1829">
       <c r="A1829" t="str">
-        <v>Kmti9yukdefhz</v>
+        <v>Kmti9zgfw4fjz</v>
       </c>
       <c r="B1829" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70036,7 +70036,7 @@
     </row>
     <row r="1830">
       <c r="A1830" t="str">
-        <v>Kmti9yukd7cn7</v>
+        <v>Kmti9zgfwrcj7</v>
       </c>
       <c r="B1830" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70112,7 +70112,7 @@
     </row>
     <row r="1832">
       <c r="A1832" t="str">
-        <v>Kmti9yukdf082</v>
+        <v>Kmti9zgfwwsyh</v>
       </c>
       <c r="B1832" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -70150,7 +70150,7 @@
     </row>
     <row r="1833">
       <c r="A1833" t="str">
-        <v>Kmti9yukdnr6u</v>
+        <v>Kmti9zgfwtkvi</v>
       </c>
       <c r="B1833" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70188,7 +70188,7 @@
     </row>
     <row r="1834">
       <c r="A1834" t="str">
-        <v>Kmti9yukd1kb5</v>
+        <v>Kmti9zgfwv418</v>
       </c>
       <c r="B1834" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70226,7 +70226,7 @@
     </row>
     <row r="1835">
       <c r="A1835" t="str">
-        <v>Kmti9yukdva2t</v>
+        <v>Kmti9zgfw5nyi</v>
       </c>
       <c r="B1835" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70264,7 +70264,7 @@
     </row>
     <row r="1836">
       <c r="A1836" t="str">
-        <v>Kmti9yukdytm7</v>
+        <v>Kmti9zgfw36v4</v>
       </c>
       <c r="B1836" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70302,7 +70302,7 @@
     </row>
     <row r="1837">
       <c r="A1837" t="str">
-        <v>Kmti9yukdbeo2</v>
+        <v>Kmti9zgfwrhj9</v>
       </c>
       <c r="B1837" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70340,7 +70340,7 @@
     </row>
     <row r="1838">
       <c r="A1838" t="str">
-        <v>Kmti9yukdb3wl</v>
+        <v>Kmti9zgfw9p5y</v>
       </c>
       <c r="B1838" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70378,7 +70378,7 @@
     </row>
     <row r="1839">
       <c r="A1839" t="str">
-        <v>Kmti9yukd4qwr</v>
+        <v>Kmti9zgfw7yh8</v>
       </c>
       <c r="B1839" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70416,7 +70416,7 @@
     </row>
     <row r="1840">
       <c r="A1840" t="str">
-        <v>Kmti9yukdjmm3</v>
+        <v>Kmti9zgfwytqd</v>
       </c>
       <c r="B1840" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70454,7 +70454,7 @@
     </row>
     <row r="1841">
       <c r="A1841" t="str">
-        <v>Kmti9yukdpbgy</v>
+        <v>Kmti9zgfwidk1</v>
       </c>
       <c r="B1841" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70492,7 +70492,7 @@
     </row>
     <row r="1842">
       <c r="A1842" t="str">
-        <v>Kmti9yukdv0ch</v>
+        <v>Kmti9zgfw5qi3</v>
       </c>
       <c r="B1842" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70568,7 +70568,7 @@
     </row>
     <row r="1844">
       <c r="A1844" t="str">
-        <v>Kmti9yukdhmjh</v>
+        <v>Kmti9zgfw7bm4</v>
       </c>
       <c r="B1844" t="str">
         <v>Penata Layanan Operasional</v>
@@ -70606,7 +70606,7 @@
     </row>
     <row r="1845">
       <c r="A1845" t="str">
-        <v>Kmti9yukdgast</v>
+        <v>Kmti9zgfwsvbt</v>
       </c>
       <c r="B1845" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70644,7 +70644,7 @@
     </row>
     <row r="1846">
       <c r="A1846" t="str">
-        <v>Kmti9yukd50io</v>
+        <v>Kmti9zgfwg9f7</v>
       </c>
       <c r="B1846" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70682,7 +70682,7 @@
     </row>
     <row r="1847">
       <c r="A1847" t="str">
-        <v>Kmti9yukdovi3</v>
+        <v>Kmti9zgfwwt6t</v>
       </c>
       <c r="B1847" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -70720,7 +70720,7 @@
     </row>
     <row r="1848">
       <c r="A1848" t="str">
-        <v>Kmti9yukdvidh</v>
+        <v>Kmti9zgfwv7iq</v>
       </c>
       <c r="B1848" t="str">
         <v>Pranata Humas Ahli Pertama</v>
@@ -70758,7 +70758,7 @@
     </row>
     <row r="1849">
       <c r="A1849" t="str">
-        <v>Kmti9yukdf8oe</v>
+        <v>Kmti9zgfwdkza</v>
       </c>
       <c r="B1849" t="str">
         <v>Pranata Humas Penyelia</v>
@@ -70796,7 +70796,7 @@
     </row>
     <row r="1850">
       <c r="A1850" t="str">
-        <v>Kmti9yukdw37h</v>
+        <v>Kmti9zgfwko74</v>
       </c>
       <c r="B1850" t="str">
         <v>Pranata Humas Mahir</v>
@@ -70834,7 +70834,7 @@
     </row>
     <row r="1851">
       <c r="A1851" t="str">
-        <v>Kmti9yukdmias</v>
+        <v>Kmti9zgfwifm5</v>
       </c>
       <c r="B1851" t="str">
         <v>Pranata Humas Terampil</v>
@@ -70872,7 +70872,7 @@
     </row>
     <row r="1852">
       <c r="A1852" t="str">
-        <v>Kmti9yukdc4qm</v>
+        <v>Kmti9zgfw8us7</v>
       </c>
       <c r="B1852" t="str">
         <v>Pustakawan Ahli Muda</v>
@@ -70910,7 +70910,7 @@
     </row>
     <row r="1853">
       <c r="A1853" t="str">
-        <v>Kmti9yukdo9vl</v>
+        <v>Kmti9zgfwbumm</v>
       </c>
       <c r="B1853" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -70948,7 +70948,7 @@
     </row>
     <row r="1854">
       <c r="A1854" t="str">
-        <v>Kmti9yukdoge2</v>
+        <v>Kmti9zgfw2iij</v>
       </c>
       <c r="B1854" t="str">
         <v>Pustakawan Penyelia</v>
@@ -70986,7 +70986,7 @@
     </row>
     <row r="1855">
       <c r="A1855" t="str">
-        <v>Kmti9yukdodqd</v>
+        <v>Kmti9zgfwyyps</v>
       </c>
       <c r="B1855" t="str">
         <v>Pustakawan Mahir</v>
@@ -71024,7 +71024,7 @@
     </row>
     <row r="1856">
       <c r="A1856" t="str">
-        <v>Kmti9yukdzku7</v>
+        <v>Kmti9zgfwjo3x</v>
       </c>
       <c r="B1856" t="str">
         <v>Pustakawan Terampil</v>
@@ -71138,7 +71138,7 @@
     </row>
     <row r="1859">
       <c r="A1859" t="str">
-        <v>Kmti9yukdf6us</v>
+        <v>Kmti9zgfw0xyq</v>
       </c>
       <c r="B1859" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71176,7 +71176,7 @@
     </row>
     <row r="1860">
       <c r="A1860" t="str">
-        <v>Kmti9yukdzqya</v>
+        <v>Kmti9zgfwe6ho</v>
       </c>
       <c r="B1860" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71214,7 +71214,7 @@
     </row>
     <row r="1861">
       <c r="A1861" t="str">
-        <v>Kmti9yukd1tea</v>
+        <v>Kmti9zgfwfgw6</v>
       </c>
       <c r="B1861" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71252,7 +71252,7 @@
     </row>
     <row r="1862">
       <c r="A1862" t="str">
-        <v>Kmti9yukdnev6</v>
+        <v>Kmti9zgfwla25</v>
       </c>
       <c r="B1862" t="str">
         <v>Penata Keprotokolan*</v>
@@ -71366,7 +71366,7 @@
     </row>
     <row r="1865">
       <c r="A1865" t="str">
-        <v>Kmti9yukd9qe0</v>
+        <v>Kmti9zgfw2nin</v>
       </c>
       <c r="B1865" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71404,7 +71404,7 @@
     </row>
     <row r="1866">
       <c r="A1866" t="str">
-        <v>Kmti9yukdk4nc</v>
+        <v>Kmti9zgfw7zit</v>
       </c>
       <c r="B1866" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71442,7 +71442,7 @@
     </row>
     <row r="1867">
       <c r="A1867" t="str">
-        <v>Kmti9yukdr0g3</v>
+        <v>Kmti9zgfwii39</v>
       </c>
       <c r="B1867" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71518,7 +71518,7 @@
     </row>
     <row r="1869">
       <c r="A1869" t="str">
-        <v>Kmti9yukd9fw7</v>
+        <v>Kmti9zgfwzuwq</v>
       </c>
       <c r="B1869" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71556,7 +71556,7 @@
     </row>
     <row r="1870">
       <c r="A1870" t="str">
-        <v>Kmti9yukdij1c</v>
+        <v>Kmti9zgfwlnqc</v>
       </c>
       <c r="B1870" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71594,7 +71594,7 @@
     </row>
     <row r="1871">
       <c r="A1871" t="str">
-        <v>Kmti9yukd56qp</v>
+        <v>Kmti9zgfwp5sv</v>
       </c>
       <c r="B1871" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71632,7 +71632,7 @@
     </row>
     <row r="1872" xml:space="preserve">
       <c r="A1872" t="str">
-        <v>Kmti9yukdplf0</v>
+        <v>Kmti9zgfw0ds4</v>
       </c>
       <c r="B1872" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -71671,7 +71671,7 @@
     </row>
     <row r="1873" xml:space="preserve">
       <c r="A1873" t="str">
-        <v>Kmti9yukd35hi</v>
+        <v>Kmti9zgfwa6fc</v>
       </c>
       <c r="B1873" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -71710,7 +71710,7 @@
     </row>
     <row r="1874" xml:space="preserve">
       <c r="A1874" t="str">
-        <v>Kmti9yukd9mox</v>
+        <v>Kmti9zgfwajv1</v>
       </c>
       <c r="B1874" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -71749,7 +71749,7 @@
     </row>
     <row r="1875" xml:space="preserve">
       <c r="A1875" t="str">
-        <v>Kmti9yukd8gtj</v>
+        <v>Kmti9zgfwc10z</v>
       </c>
       <c r="B1875" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -71864,7 +71864,7 @@
     </row>
     <row r="1878">
       <c r="A1878" t="str">
-        <v>Kmti9yukd6ugj</v>
+        <v>Kmti9zgfwygzd</v>
       </c>
       <c r="B1878" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71902,7 +71902,7 @@
     </row>
     <row r="1879">
       <c r="A1879" t="str">
-        <v>Kmti9yukdywdj</v>
+        <v>Kmti9zgfwoltt</v>
       </c>
       <c r="B1879" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71940,7 +71940,7 @@
     </row>
     <row r="1880">
       <c r="A1880" t="str">
-        <v>Kmti9yukdkt2q</v>
+        <v>Kmti9zgfwqkai</v>
       </c>
       <c r="B1880" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71978,7 +71978,7 @@
     </row>
     <row r="1881">
       <c r="A1881" t="str">
-        <v>Kmti9yukd37kp</v>
+        <v>Kmti9zgfwypfl</v>
       </c>
       <c r="B1881" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72092,7 +72092,7 @@
     </row>
     <row r="1884">
       <c r="A1884" t="str">
-        <v>Kmti9yukdr0na</v>
+        <v>Kmti9zgfwhczd</v>
       </c>
       <c r="B1884" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72130,7 +72130,7 @@
     </row>
     <row r="1885">
       <c r="A1885" t="str">
-        <v>Kmti9yukdj2f6</v>
+        <v>Kmti9zgfw7qoi</v>
       </c>
       <c r="B1885" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72168,7 +72168,7 @@
     </row>
     <row r="1886">
       <c r="A1886" t="str">
-        <v>Kmti9yukdhk60</v>
+        <v>Kmti9zgfwb0ne</v>
       </c>
       <c r="B1886" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72244,7 +72244,7 @@
     </row>
     <row r="1888">
       <c r="A1888" t="str">
-        <v>Kmti9yukddrak</v>
+        <v>Kmti9zgfwonwb</v>
       </c>
       <c r="B1888" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72282,7 +72282,7 @@
     </row>
     <row r="1889">
       <c r="A1889" t="str">
-        <v>Kmti9yukdsik3</v>
+        <v>Kmti9zgfwmcx1</v>
       </c>
       <c r="B1889" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72320,7 +72320,7 @@
     </row>
     <row r="1890">
       <c r="A1890" t="str">
-        <v>Kmti9yukd4q3k</v>
+        <v>Kmti9zgfwvgey</v>
       </c>
       <c r="B1890" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72358,7 +72358,7 @@
     </row>
     <row r="1891" xml:space="preserve">
       <c r="A1891" t="str">
-        <v>Kmti9yukdbrn8</v>
+        <v>Kmti9zgfwhsjl</v>
       </c>
       <c r="B1891" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -72397,7 +72397,7 @@
     </row>
     <row r="1892" xml:space="preserve">
       <c r="A1892" t="str">
-        <v>Kmti9yukd5h1h</v>
+        <v>Kmti9zgfwz45u</v>
       </c>
       <c r="B1892" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -72436,7 +72436,7 @@
     </row>
     <row r="1893" xml:space="preserve">
       <c r="A1893" t="str">
-        <v>Kmti9yukddzuq</v>
+        <v>Kmti9zgfwkdjf</v>
       </c>
       <c r="B1893" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -72475,7 +72475,7 @@
     </row>
     <row r="1894" xml:space="preserve">
       <c r="A1894" t="str">
-        <v>Kmti9yukdu7z7</v>
+        <v>Kmti9zgfwqky1</v>
       </c>
       <c r="B1894" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -72590,7 +72590,7 @@
     </row>
     <row r="1897">
       <c r="A1897" t="str">
-        <v>Kmti9yukdxyx2</v>
+        <v>Kmti9zgfwdg9m</v>
       </c>
       <c r="B1897" t="str">
         <v>Penata Layanan Operasional</v>
@@ -72628,7 +72628,7 @@
     </row>
     <row r="1898">
       <c r="A1898" t="str">
-        <v>Kmti9yukdjqee</v>
+        <v>Kmti9zgfw93o7</v>
       </c>
       <c r="B1898" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72666,7 +72666,7 @@
     </row>
     <row r="1899">
       <c r="A1899" t="str">
-        <v>Kmti9yukdad06</v>
+        <v>Kmti9zgfw3rvs</v>
       </c>
       <c r="B1899" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72704,7 +72704,7 @@
     </row>
     <row r="1900">
       <c r="A1900" t="str">
-        <v>Kmti9yukdgzir</v>
+        <v>Kmti9zgfwaiyz</v>
       </c>
       <c r="B1900" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72818,7 +72818,7 @@
     </row>
     <row r="1903">
       <c r="A1903" t="str">
-        <v>Kmti9yukdip56</v>
+        <v>Kmti9zgfwqae2</v>
       </c>
       <c r="B1903" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72856,7 +72856,7 @@
     </row>
     <row r="1904">
       <c r="A1904" t="str">
-        <v>Kmti9yukdlmdu</v>
+        <v>Kmti9zgfwd4z6</v>
       </c>
       <c r="B1904" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72894,7 +72894,7 @@
     </row>
     <row r="1905">
       <c r="A1905" t="str">
-        <v>Kmti9yukdf555</v>
+        <v>Kmti9zgfw2ujl</v>
       </c>
       <c r="B1905" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72970,7 +72970,7 @@
     </row>
     <row r="1907">
       <c r="A1907" t="str">
-        <v>Kmti9yukd7sdf</v>
+        <v>Kmti9zgfw9m04</v>
       </c>
       <c r="B1907" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73008,7 +73008,7 @@
     </row>
     <row r="1908">
       <c r="A1908" t="str">
-        <v>Kmti9yukd4w3j</v>
+        <v>Kmti9zgfwx768</v>
       </c>
       <c r="B1908" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73046,7 +73046,7 @@
     </row>
     <row r="1909">
       <c r="A1909" t="str">
-        <v>Kmti9yukdyngy</v>
+        <v>Kmti9zgfwvkwj</v>
       </c>
       <c r="B1909" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73084,7 +73084,7 @@
     </row>
     <row r="1910" xml:space="preserve">
       <c r="A1910" t="str">
-        <v>Kmti9yukdftgs</v>
+        <v>Kmti9zgfw6b8v</v>
       </c>
       <c r="B1910" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73123,7 +73123,7 @@
     </row>
     <row r="1911" xml:space="preserve">
       <c r="A1911" t="str">
-        <v>Kmti9yukdka1c</v>
+        <v>Kmti9zgfwsy1c</v>
       </c>
       <c r="B1911" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73162,7 +73162,7 @@
     </row>
     <row r="1912" xml:space="preserve">
       <c r="A1912" t="str">
-        <v>Kmti9yukdlgby</v>
+        <v>Kmti9zgfw5kvp</v>
       </c>
       <c r="B1912" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73201,7 +73201,7 @@
     </row>
     <row r="1913" xml:space="preserve">
       <c r="A1913" t="str">
-        <v>Kmti9yukd65sw</v>
+        <v>Kmti9zgfwz84e</v>
       </c>
       <c r="B1913" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73316,7 +73316,7 @@
     </row>
     <row r="1916">
       <c r="A1916" t="str">
-        <v>Kmti9yukd3yfq</v>
+        <v>Kmti9zgfwbw3m</v>
       </c>
       <c r="B1916" t="str">
         <v>Penata Layanan Operasional</v>
@@ -73354,7 +73354,7 @@
     </row>
     <row r="1917">
       <c r="A1917" t="str">
-        <v>Kmti9yukd8265</v>
+        <v>Kmti9zgfwkfny</v>
       </c>
       <c r="B1917" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73392,7 +73392,7 @@
     </row>
     <row r="1918">
       <c r="A1918" t="str">
-        <v>Kmti9yukd8vm2</v>
+        <v>Kmti9zgfwcyo6</v>
       </c>
       <c r="B1918" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73430,7 +73430,7 @@
     </row>
     <row r="1919">
       <c r="A1919" t="str">
-        <v>Kmti9yukdf5ep</v>
+        <v>Kmti9zgfw0tnz</v>
       </c>
       <c r="B1919" t="str">
         <v>Penata Keprotokolan*</v>
@@ -73544,7 +73544,7 @@
     </row>
     <row r="1922">
       <c r="A1922" t="str">
-        <v>Kmti9yukdbq33</v>
+        <v>Kmti9zgfwltys</v>
       </c>
       <c r="B1922" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73582,7 +73582,7 @@
     </row>
     <row r="1923">
       <c r="A1923" t="str">
-        <v>Kmti9yukd63dr</v>
+        <v>Kmti9zgfwlv3o</v>
       </c>
       <c r="B1923" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73620,7 +73620,7 @@
     </row>
     <row r="1924">
       <c r="A1924" t="str">
-        <v>Kmti9yukdzfru</v>
+        <v>Kmti9zgfwjioh</v>
       </c>
       <c r="B1924" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73696,7 +73696,7 @@
     </row>
     <row r="1926">
       <c r="A1926" t="str">
-        <v>Kmti9yukddm3x</v>
+        <v>Kmti9zgfw06pe</v>
       </c>
       <c r="B1926" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73734,7 +73734,7 @@
     </row>
     <row r="1927">
       <c r="A1927" t="str">
-        <v>Kmti9yukd21x6</v>
+        <v>Kmti9zgfwuj6q</v>
       </c>
       <c r="B1927" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73772,7 +73772,7 @@
     </row>
     <row r="1928">
       <c r="A1928" t="str">
-        <v>Kmti9yukd353p</v>
+        <v>Kmti9zgfw033o</v>
       </c>
       <c r="B1928" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73810,7 +73810,7 @@
     </row>
     <row r="1929" xml:space="preserve">
       <c r="A1929" t="str">
-        <v>Kmti9yukdcr1w</v>
+        <v>Kmti9zgfwjjey</v>
       </c>
       <c r="B1929" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73849,7 +73849,7 @@
     </row>
     <row r="1930" xml:space="preserve">
       <c r="A1930" t="str">
-        <v>Kmti9yukd9gxi</v>
+        <v>Kmti9zgfwnnpn</v>
       </c>
       <c r="B1930" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73888,7 +73888,7 @@
     </row>
     <row r="1931" xml:space="preserve">
       <c r="A1931" t="str">
-        <v>Kmti9yukdv3kv</v>
+        <v>Kmti9zgfw6gap</v>
       </c>
       <c r="B1931" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73927,7 +73927,7 @@
     </row>
     <row r="1932" xml:space="preserve">
       <c r="A1932" t="str">
-        <v>Kmti9yukddphs</v>
+        <v>Kmti9zgfwoabt</v>
       </c>
       <c r="B1932" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73966,7 +73966,7 @@
     </row>
     <row r="1933" xml:space="preserve">
       <c r="A1933" t="str">
-        <v>Kmti9yukdf4zn</v>
+        <v>Kmti9zgfww5t6</v>
       </c>
       <c r="B1933" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74005,7 +74005,7 @@
     </row>
     <row r="1934" xml:space="preserve">
       <c r="A1934" t="str">
-        <v>Kmti9yukdkbj4</v>
+        <v>Kmti9zgfwyfcf</v>
       </c>
       <c r="B1934" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74044,7 +74044,7 @@
     </row>
     <row r="1935" xml:space="preserve">
       <c r="A1935" t="str">
-        <v>Kmti9yukdhcmi</v>
+        <v>Kmti9zgfw2bzn</v>
       </c>
       <c r="B1935" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -74159,7 +74159,7 @@
     </row>
     <row r="1938">
       <c r="A1938" t="str">
-        <v>Kmti9yukdjz19</v>
+        <v>Kmti9zgfwe6jk</v>
       </c>
       <c r="B1938" t="str">
         <v>Penata Layanan Operasional</v>
@@ -74197,7 +74197,7 @@
     </row>
     <row r="1939">
       <c r="A1939" t="str">
-        <v>Kmti9yukdazvu</v>
+        <v>Kmti9zgfwnr3v</v>
       </c>
       <c r="B1939" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74235,7 +74235,7 @@
     </row>
     <row r="1940">
       <c r="A1940" t="str">
-        <v>Kmti9yukdh97d</v>
+        <v>Kmti9zgfw1j05</v>
       </c>
       <c r="B1940" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74273,7 +74273,7 @@
     </row>
     <row r="1941">
       <c r="A1941" t="str">
-        <v>Kmti9yukdg6wa</v>
+        <v>Kmti9zgfw5rbq</v>
       </c>
       <c r="B1941" t="str">
         <v>Penata Keprotokolan*</v>
@@ -74387,7 +74387,7 @@
     </row>
     <row r="1944">
       <c r="A1944" t="str">
-        <v>Kmti9yukdmczk</v>
+        <v>Kmti9zgfwfb0h</v>
       </c>
       <c r="B1944" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74425,7 +74425,7 @@
     </row>
     <row r="1945">
       <c r="A1945" t="str">
-        <v>Kmti9yukdud7o</v>
+        <v>Kmti9zgfw1aqi</v>
       </c>
       <c r="B1945" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74463,7 +74463,7 @@
     </row>
     <row r="1946">
       <c r="A1946" t="str">
-        <v>Kmti9yukdukpv</v>
+        <v>Kmti9zgfwxvsl</v>
       </c>
       <c r="B1946" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74539,7 +74539,7 @@
     </row>
     <row r="1948">
       <c r="A1948" t="str">
-        <v>Kmti9yukdglp5</v>
+        <v>Kmti9zgfwixeo</v>
       </c>
       <c r="B1948" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74577,7 +74577,7 @@
     </row>
     <row r="1949">
       <c r="A1949" t="str">
-        <v>Kmti9yukdsspg</v>
+        <v>Kmti9zgfwztsm</v>
       </c>
       <c r="B1949" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74615,7 +74615,7 @@
     </row>
     <row r="1950">
       <c r="A1950" t="str">
-        <v>Kmti9yukd6krl</v>
+        <v>Kmti9zgfwjky0</v>
       </c>
       <c r="B1950" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74653,7 +74653,7 @@
     </row>
     <row r="1951" xml:space="preserve">
       <c r="A1951" t="str">
-        <v>Kmti9yukdn376</v>
+        <v>Kmti9zgfwql8b</v>
       </c>
       <c r="B1951" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -74692,7 +74692,7 @@
     </row>
     <row r="1952" xml:space="preserve">
       <c r="A1952" t="str">
-        <v>Kmti9yukd3to2</v>
+        <v>Kmti9zgfwb0ad</v>
       </c>
       <c r="B1952" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -74731,7 +74731,7 @@
     </row>
     <row r="1953" xml:space="preserve">
       <c r="A1953" t="str">
-        <v>Kmti9yukd3rqh</v>
+        <v>Kmti9zgfwr31d</v>
       </c>
       <c r="B1953" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -74770,7 +74770,7 @@
     </row>
     <row r="1954" xml:space="preserve">
       <c r="A1954" t="str">
-        <v>Kmti9yukdtyvp</v>
+        <v>Kmti9zgfwr8in</v>
       </c>
       <c r="B1954" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -74809,7 +74809,7 @@
     </row>
     <row r="1955" xml:space="preserve">
       <c r="A1955" t="str">
-        <v>Kmti9yukdfyug</v>
+        <v>Kmti9zgfwtaz2</v>
       </c>
       <c r="B1955" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74848,7 +74848,7 @@
     </row>
     <row r="1956" xml:space="preserve">
       <c r="A1956" t="str">
-        <v>Kmti9yukdx29h</v>
+        <v>Kmti9zgfwqbyo</v>
       </c>
       <c r="B1956" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74887,7 +74887,7 @@
     </row>
     <row r="1957" xml:space="preserve">
       <c r="A1957" t="str">
-        <v>Kmti9yukdur84</v>
+        <v>Kmti9zgfw8hv9</v>
       </c>
       <c r="B1957" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -75002,7 +75002,7 @@
     </row>
     <row r="1960">
       <c r="A1960" t="str">
-        <v>Kmti9yukdk10e</v>
+        <v>Kmti9zgfwct15</v>
       </c>
       <c r="B1960" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75040,7 +75040,7 @@
     </row>
     <row r="1961">
       <c r="A1961" t="str">
-        <v>Kmti9yukdhon4</v>
+        <v>Kmti9zgfwa9hm</v>
       </c>
       <c r="B1961" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75078,7 +75078,7 @@
     </row>
     <row r="1962">
       <c r="A1962" t="str">
-        <v>Kmti9yukd8ppu</v>
+        <v>Kmti9zgfwlm30</v>
       </c>
       <c r="B1962" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75116,7 +75116,7 @@
     </row>
     <row r="1963">
       <c r="A1963" t="str">
-        <v>Kmti9yukdkow8</v>
+        <v>Kmti9zgfwqbvg</v>
       </c>
       <c r="B1963" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75230,7 +75230,7 @@
     </row>
     <row r="1966">
       <c r="A1966" t="str">
-        <v>Kmti9yukd71if</v>
+        <v>Kmti9zgfws9sa</v>
       </c>
       <c r="B1966" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75268,7 +75268,7 @@
     </row>
     <row r="1967">
       <c r="A1967" t="str">
-        <v>Kmti9yukdtm84</v>
+        <v>Kmti9zgfwash5</v>
       </c>
       <c r="B1967" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75306,7 +75306,7 @@
     </row>
     <row r="1968">
       <c r="A1968" t="str">
-        <v>Kmti9yukdrwem</v>
+        <v>Kmti9zgfwquo0</v>
       </c>
       <c r="B1968" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75382,7 +75382,7 @@
     </row>
     <row r="1970">
       <c r="A1970" t="str">
-        <v>Kmti9yukdsx8a</v>
+        <v>Kmti9zgfwup3i</v>
       </c>
       <c r="B1970" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75420,7 +75420,7 @@
     </row>
     <row r="1971">
       <c r="A1971" t="str">
-        <v>Kmti9yukd51cd</v>
+        <v>Kmti9zgfwef5s</v>
       </c>
       <c r="B1971" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75458,7 +75458,7 @@
     </row>
     <row r="1972">
       <c r="A1972" t="str">
-        <v>Kmti9yukdt5l0</v>
+        <v>Kmti9zgfwwtwu</v>
       </c>
       <c r="B1972" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75496,7 +75496,7 @@
     </row>
     <row r="1973" xml:space="preserve">
       <c r="A1973" t="str">
-        <v>Kmti9yukd6r7m</v>
+        <v>Kmti9zgfw75iy</v>
       </c>
       <c r="B1973" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -75535,7 +75535,7 @@
     </row>
     <row r="1974" xml:space="preserve">
       <c r="A1974" t="str">
-        <v>Kmti9yukdrxp3</v>
+        <v>Kmti9zgfwt3u7</v>
       </c>
       <c r="B1974" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -75574,7 +75574,7 @@
     </row>
     <row r="1975" xml:space="preserve">
       <c r="A1975" t="str">
-        <v>Kmti9yukdxxjr</v>
+        <v>Kmti9zgfwetaa</v>
       </c>
       <c r="B1975" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -75613,7 +75613,7 @@
     </row>
     <row r="1976" xml:space="preserve">
       <c r="A1976" t="str">
-        <v>Kmti9yukdgykc</v>
+        <v>Kmti9zgfwckqd</v>
       </c>
       <c r="B1976" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -75728,7 +75728,7 @@
     </row>
     <row r="1979">
       <c r="A1979" t="str">
-        <v>Kmti9yukd7yaj</v>
+        <v>Kmti9zgfwvci0</v>
       </c>
       <c r="B1979" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75766,7 +75766,7 @@
     </row>
     <row r="1980">
       <c r="A1980" t="str">
-        <v>Kmti9yukd94ft</v>
+        <v>Kmti9zgfw7psj</v>
       </c>
       <c r="B1980" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75804,7 +75804,7 @@
     </row>
     <row r="1981">
       <c r="A1981" t="str">
-        <v>Kmti9yukdqgq2</v>
+        <v>Kmti9zgfw0gqv</v>
       </c>
       <c r="B1981" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75842,7 +75842,7 @@
     </row>
     <row r="1982">
       <c r="A1982" t="str">
-        <v>Kmti9yukda4jh</v>
+        <v>Kmti9zgfw1kr2</v>
       </c>
       <c r="B1982" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75956,7 +75956,7 @@
     </row>
     <row r="1985">
       <c r="A1985" t="str">
-        <v>Kmti9yukdop5p</v>
+        <v>Kmti9zgfwryyh</v>
       </c>
       <c r="B1985" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75994,7 +75994,7 @@
     </row>
     <row r="1986">
       <c r="A1986" t="str">
-        <v>Kmti9yukdn0ij</v>
+        <v>Kmti9zgfwff1h</v>
       </c>
       <c r="B1986" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76032,7 +76032,7 @@
     </row>
     <row r="1987">
       <c r="A1987" t="str">
-        <v>Kmti9yukdj1tf</v>
+        <v>Kmti9zgfw6v3w</v>
       </c>
       <c r="B1987" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76108,7 +76108,7 @@
     </row>
     <row r="1989">
       <c r="A1989" t="str">
-        <v>Kmti9yukd6dm0</v>
+        <v>Kmti9zgfw9zoj</v>
       </c>
       <c r="B1989" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76146,7 +76146,7 @@
     </row>
     <row r="1990">
       <c r="A1990" t="str">
-        <v>Kmti9yukdpi0w</v>
+        <v>Kmti9zgfwyso0</v>
       </c>
       <c r="B1990" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76184,7 +76184,7 @@
     </row>
     <row r="1991">
       <c r="A1991" t="str">
-        <v>Kmti9yukdkhs9</v>
+        <v>Kmti9zgfwugsv</v>
       </c>
       <c r="B1991" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76222,7 +76222,7 @@
     </row>
     <row r="1992" xml:space="preserve">
       <c r="A1992" t="str">
-        <v>Kmti9yukdyo8h</v>
+        <v>Kmti9zgfw6fhy</v>
       </c>
       <c r="B1992" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76261,7 +76261,7 @@
     </row>
     <row r="1993" xml:space="preserve">
       <c r="A1993" t="str">
-        <v>Kmti9yukd1jwm</v>
+        <v>Kmti9zgfwexxz</v>
       </c>
       <c r="B1993" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -76300,7 +76300,7 @@
     </row>
     <row r="1994" xml:space="preserve">
       <c r="A1994" t="str">
-        <v>Kmti9yukdsz3n</v>
+        <v>Kmti9zgfwx8ig</v>
       </c>
       <c r="B1994" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -76339,7 +76339,7 @@
     </row>
     <row r="1995" xml:space="preserve">
       <c r="A1995" t="str">
-        <v>Kmti9yukevvbo</v>
+        <v>Kmti9zgfwt7iw</v>
       </c>
       <c r="B1995" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -76454,7 +76454,7 @@
     </row>
     <row r="1998">
       <c r="A1998" t="str">
-        <v>Kmti9yuken0ok</v>
+        <v>Kmti9zgfw4cxt</v>
       </c>
       <c r="B1998" t="str">
         <v>Penata Layanan Operasional</v>
@@ -76492,7 +76492,7 @@
     </row>
     <row r="1999">
       <c r="A1999" t="str">
-        <v>Kmti9yukewwcg</v>
+        <v>Kmti9zgfwxx46</v>
       </c>
       <c r="B1999" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76530,7 +76530,7 @@
     </row>
     <row r="2000">
       <c r="A2000" t="str">
-        <v>Kmti9yuke55ge</v>
+        <v>Kmti9zgfwdx4b</v>
       </c>
       <c r="B2000" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76568,7 +76568,7 @@
     </row>
     <row r="2001">
       <c r="A2001" t="str">
-        <v>Kmti9yukeeapn</v>
+        <v>Kmti9zgfwuima</v>
       </c>
       <c r="B2001" t="str">
         <v>Penata Keprotokolan*</v>
@@ -76682,7 +76682,7 @@
     </row>
     <row r="2004">
       <c r="A2004" t="str">
-        <v>Kmti9yukev16f</v>
+        <v>Kmti9zgfwtjyt</v>
       </c>
       <c r="B2004" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76720,7 +76720,7 @@
     </row>
     <row r="2005">
       <c r="A2005" t="str">
-        <v>Kmti9yuke203w</v>
+        <v>Kmti9zgfx25jb</v>
       </c>
       <c r="B2005" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76758,7 +76758,7 @@
     </row>
     <row r="2006">
       <c r="A2006" t="str">
-        <v>Kmti9yuke9miy</v>
+        <v>Kmti9zgfxvr5x</v>
       </c>
       <c r="B2006" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76834,7 +76834,7 @@
     </row>
     <row r="2008">
       <c r="A2008" t="str">
-        <v>Kmti9yukenr18</v>
+        <v>Kmti9zgfx60nq</v>
       </c>
       <c r="B2008" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76872,7 +76872,7 @@
     </row>
     <row r="2009">
       <c r="A2009" t="str">
-        <v>Kmti9yukextx7</v>
+        <v>Kmti9zgfx5fvs</v>
       </c>
       <c r="B2009" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76910,7 +76910,7 @@
     </row>
     <row r="2010">
       <c r="A2010" t="str">
-        <v>Kmti9yukecz84</v>
+        <v>Kmti9zgfx8g5q</v>
       </c>
       <c r="B2010" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76948,7 +76948,7 @@
     </row>
     <row r="2011" xml:space="preserve">
       <c r="A2011" t="str">
-        <v>Kmti9yuke757d</v>
+        <v>Kmti9zgfxshjn</v>
       </c>
       <c r="B2011" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76987,7 +76987,7 @@
     </row>
     <row r="2012" xml:space="preserve">
       <c r="A2012" t="str">
-        <v>Kmti9yukeqj8g</v>
+        <v>Kmti9zgfxrkcb</v>
       </c>
       <c r="B2012" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77026,7 +77026,7 @@
     </row>
     <row r="2013" xml:space="preserve">
       <c r="A2013" t="str">
-        <v>Kmti9yukehzdz</v>
+        <v>Kmti9zgfx1osk</v>
       </c>
       <c r="B2013" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77065,7 +77065,7 @@
     </row>
     <row r="2014" xml:space="preserve">
       <c r="A2014" t="str">
-        <v>Kmti9yuke192p</v>
+        <v>Kmti9zgfx01sb</v>
       </c>
       <c r="B2014" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77180,7 +77180,7 @@
     </row>
     <row r="2017">
       <c r="A2017" t="str">
-        <v>Kmti9yukexnyw</v>
+        <v>Kmti9zgfxxidv</v>
       </c>
       <c r="B2017" t="str">
         <v>Penata Layanan Operasional</v>
@@ -77218,7 +77218,7 @@
     </row>
     <row r="2018">
       <c r="A2018" t="str">
-        <v>Kmti9yuke6wi6</v>
+        <v>Kmti9zgfxnyrh</v>
       </c>
       <c r="B2018" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77256,7 +77256,7 @@
     </row>
     <row r="2019">
       <c r="A2019" t="str">
-        <v>Kmti9yukez3al</v>
+        <v>Kmti9zgfxvb34</v>
       </c>
       <c r="B2019" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77294,7 +77294,7 @@
     </row>
     <row r="2020">
       <c r="A2020" t="str">
-        <v>Kmti9yukeol57</v>
+        <v>Kmti9zgfxoj9b</v>
       </c>
       <c r="B2020" t="str">
         <v>Penata Keprotokolan*</v>
@@ -77408,7 +77408,7 @@
     </row>
     <row r="2023">
       <c r="A2023" t="str">
-        <v>Kmti9yukegoow</v>
+        <v>Kmti9zgfxkbvv</v>
       </c>
       <c r="B2023" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77446,7 +77446,7 @@
     </row>
     <row r="2024">
       <c r="A2024" t="str">
-        <v>Kmti9yukekino</v>
+        <v>Kmti9zgfxhm06</v>
       </c>
       <c r="B2024" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77484,7 +77484,7 @@
     </row>
     <row r="2025">
       <c r="A2025" t="str">
-        <v>Kmti9yuke7wyt</v>
+        <v>Kmti9zgfx63dk</v>
       </c>
       <c r="B2025" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77560,7 +77560,7 @@
     </row>
     <row r="2027">
       <c r="A2027" t="str">
-        <v>Kmti9yukeiueo</v>
+        <v>Kmti9zgfxupom</v>
       </c>
       <c r="B2027" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77598,7 +77598,7 @@
     </row>
     <row r="2028">
       <c r="A2028" t="str">
-        <v>Kmti9yukexcfr</v>
+        <v>Kmti9zgfxovu8</v>
       </c>
       <c r="B2028" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77636,7 +77636,7 @@
     </row>
     <row r="2029">
       <c r="A2029" t="str">
-        <v>Kmti9yukentw8</v>
+        <v>Kmti9zgfxwy6o</v>
       </c>
       <c r="B2029" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77674,7 +77674,7 @@
     </row>
     <row r="2030" xml:space="preserve">
       <c r="A2030" t="str">
-        <v>Kmti9yukef2w2</v>
+        <v>Kmti9zgfxflrx</v>
       </c>
       <c r="B2030" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -77713,7 +77713,7 @@
     </row>
     <row r="2031" xml:space="preserve">
       <c r="A2031" t="str">
-        <v>Kmti9yuke32zg</v>
+        <v>Kmti9zgfxc1b3</v>
       </c>
       <c r="B2031" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77752,7 +77752,7 @@
     </row>
     <row r="2032" xml:space="preserve">
       <c r="A2032" t="str">
-        <v>Kmti9yukehiz7</v>
+        <v>Kmti9zgfxt41q</v>
       </c>
       <c r="B2032" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77791,7 +77791,7 @@
     </row>
     <row r="2033" xml:space="preserve">
       <c r="A2033" t="str">
-        <v>Kmti9yukejo44</v>
+        <v>Kmti9zgfxiwy8</v>
       </c>
       <c r="B2033" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77830,7 +77830,7 @@
     </row>
     <row r="2034">
       <c r="A2034" t="str">
-        <v>Kmti9yukexfff</v>
+        <v>Kmti9zgfxmdk5</v>
       </c>
       <c r="B2034" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -77868,7 +77868,7 @@
     </row>
     <row r="2035">
       <c r="A2035" t="str">
-        <v>Kmti9yukepndc</v>
+        <v>Kmti9zgfxvt2x</v>
       </c>
       <c r="B2035" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -77944,7 +77944,7 @@
     </row>
     <row r="2037" xml:space="preserve">
       <c r="A2037" t="str">
-        <v>Kmti9yukeaxlh</v>
+        <v>Kmti9zgfxcf89</v>
       </c>
       <c r="B2037" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_

--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -63909,7 +63909,7 @@
     </row>
     <row r="1669">
       <c r="A1669" t="str">
-        <v>Kmti9zgfv26p3</v>
+        <v>Kmtia02g5jawg</v>
       </c>
       <c r="B1669" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -63947,7 +63947,7 @@
     </row>
     <row r="1670">
       <c r="A1670" t="str">
-        <v>Kmti9zgfvwyrb</v>
+        <v>Kmtia02g5naro</v>
       </c>
       <c r="B1670" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -63985,7 +63985,7 @@
     </row>
     <row r="1671">
       <c r="A1671" t="str">
-        <v>Kmti9zgfvtx00</v>
+        <v>Kmtia02g5i9oq</v>
       </c>
       <c r="B1671" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64023,7 +64023,7 @@
     </row>
     <row r="1672">
       <c r="A1672" t="str">
-        <v>Kmti9zgfv4cbb</v>
+        <v>Kmtia02g5tdaw</v>
       </c>
       <c r="B1672" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64061,7 +64061,7 @@
     </row>
     <row r="1673">
       <c r="A1673" t="str">
-        <v>Kmti9zgfv0cd5</v>
+        <v>Kmtia02g5n2em</v>
       </c>
       <c r="B1673" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64099,7 +64099,7 @@
     </row>
     <row r="1674">
       <c r="A1674" t="str">
-        <v>Kmti9zgfv45ja</v>
+        <v>Kmtia02g5dqvc</v>
       </c>
       <c r="B1674" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64137,7 +64137,7 @@
     </row>
     <row r="1675">
       <c r="A1675" t="str">
-        <v>Kmti9zgfv5dbr</v>
+        <v>Kmtia02g58etg</v>
       </c>
       <c r="B1675" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64175,7 +64175,7 @@
     </row>
     <row r="1676">
       <c r="A1676" t="str">
-        <v>Kmti9zgfvpxse</v>
+        <v>Kmtia02g5p8rj</v>
       </c>
       <c r="B1676" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64251,7 +64251,7 @@
     </row>
     <row r="1678">
       <c r="A1678" t="str">
-        <v>Kmti9zgfvuuv7</v>
+        <v>Kmtia02g5b6su</v>
       </c>
       <c r="B1678" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64289,7 +64289,7 @@
     </row>
     <row r="1679">
       <c r="A1679" t="str">
-        <v>Kmti9zgfvlrdk</v>
+        <v>Kmtia02g5fh5r</v>
       </c>
       <c r="B1679" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64327,7 +64327,7 @@
     </row>
     <row r="1680">
       <c r="A1680" t="str">
-        <v>Kmti9zgfvbsli</v>
+        <v>Kmtia02g5kbtf</v>
       </c>
       <c r="B1680" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64365,7 +64365,7 @@
     </row>
     <row r="1681">
       <c r="A1681" t="str">
-        <v>Kmti9zgfv70po</v>
+        <v>Kmtia02g51e7e</v>
       </c>
       <c r="B1681" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64403,7 +64403,7 @@
     </row>
     <row r="1682">
       <c r="A1682" t="str">
-        <v>Kmti9zgfveogu</v>
+        <v>Kmtia02g5377n</v>
       </c>
       <c r="B1682" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64441,7 +64441,7 @@
     </row>
     <row r="1683">
       <c r="A1683" t="str">
-        <v>Kmti9zgfvmgxf</v>
+        <v>Kmtia02g5j4jj</v>
       </c>
       <c r="B1683" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64479,7 +64479,7 @@
     </row>
     <row r="1684">
       <c r="A1684" t="str">
-        <v>Kmti9zgfvknli</v>
+        <v>Kmtia02g5kjjt</v>
       </c>
       <c r="B1684" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64517,7 +64517,7 @@
     </row>
     <row r="1685">
       <c r="A1685" t="str">
-        <v>Kmti9zgfvprvh</v>
+        <v>Kmtia02g5qh5e</v>
       </c>
       <c r="B1685" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64593,7 +64593,7 @@
     </row>
     <row r="1687">
       <c r="A1687" t="str">
-        <v>Kmti9zgfvbb3w</v>
+        <v>Kmtia02g5dfjp</v>
       </c>
       <c r="B1687" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64631,7 +64631,7 @@
     </row>
     <row r="1688">
       <c r="A1688" t="str">
-        <v>Kmti9zgfvdowe</v>
+        <v>Kmtia02g5dmi3</v>
       </c>
       <c r="B1688" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64669,7 +64669,7 @@
     </row>
     <row r="1689">
       <c r="A1689" t="str">
-        <v>Kmti9zgfvapml</v>
+        <v>Kmtia02g5h0s5</v>
       </c>
       <c r="B1689" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64707,7 +64707,7 @@
     </row>
     <row r="1690">
       <c r="A1690" t="str">
-        <v>Kmti9zgfv6noy</v>
+        <v>Kmtia02g5fbah</v>
       </c>
       <c r="B1690" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64745,7 +64745,7 @@
     </row>
     <row r="1691">
       <c r="A1691" t="str">
-        <v>Kmti9zgfvsrt3</v>
+        <v>Kmtia02g5kh36</v>
       </c>
       <c r="B1691" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64783,7 +64783,7 @@
     </row>
     <row r="1692">
       <c r="A1692" t="str">
-        <v>Kmti9zgfv7snw</v>
+        <v>Kmtia02g5xi3y</v>
       </c>
       <c r="B1692" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64821,7 +64821,7 @@
     </row>
     <row r="1693">
       <c r="A1693" t="str">
-        <v>Kmti9zgfvijxf</v>
+        <v>Kmtia02g5nhoc</v>
       </c>
       <c r="B1693" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64859,7 +64859,7 @@
     </row>
     <row r="1694">
       <c r="A1694" t="str">
-        <v>Kmti9zgfvq82j</v>
+        <v>Kmtia02g54eq6</v>
       </c>
       <c r="B1694" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64897,7 +64897,7 @@
     </row>
     <row r="1695">
       <c r="A1695" t="str">
-        <v>Kmti9zgfvy2bj</v>
+        <v>Kmtia02g5vltc</v>
       </c>
       <c r="B1695" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64935,7 +64935,7 @@
     </row>
     <row r="1696">
       <c r="A1696" t="str">
-        <v>Kmti9zgfv3xh5</v>
+        <v>Kmtia02g505c3</v>
       </c>
       <c r="B1696" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64973,7 +64973,7 @@
     </row>
     <row r="1697">
       <c r="A1697" t="str">
-        <v>Kmti9zgfv676s</v>
+        <v>Kmtia02g5vo6a</v>
       </c>
       <c r="B1697" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65087,7 +65087,7 @@
     </row>
     <row r="1700">
       <c r="A1700" t="str">
-        <v>Kmti9zgfv4f31</v>
+        <v>Kmtia02g555dj</v>
       </c>
       <c r="B1700" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65125,7 +65125,7 @@
     </row>
     <row r="1701">
       <c r="A1701" t="str">
-        <v>Kmti9zgfvaki2</v>
+        <v>Kmtia02g5gq2n</v>
       </c>
       <c r="B1701" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65163,7 +65163,7 @@
     </row>
     <row r="1702">
       <c r="A1702" t="str">
-        <v>Kmti9zgfvljfh</v>
+        <v>Kmtia02g56jm2</v>
       </c>
       <c r="B1702" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65201,7 +65201,7 @@
     </row>
     <row r="1703">
       <c r="A1703" t="str">
-        <v>Kmti9zgfvbm7i</v>
+        <v>Kmtia02g5ys50</v>
       </c>
       <c r="B1703" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65239,7 +65239,7 @@
     </row>
     <row r="1704">
       <c r="A1704" t="str">
-        <v>Kmti9zgfvw9hy</v>
+        <v>Kmtia02g59s2o</v>
       </c>
       <c r="B1704" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65277,7 +65277,7 @@
     </row>
     <row r="1705">
       <c r="A1705" t="str">
-        <v>Kmti9zgfv2qcb</v>
+        <v>Kmtia02g5ezsf</v>
       </c>
       <c r="B1705" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65315,7 +65315,7 @@
     </row>
     <row r="1706">
       <c r="A1706" t="str">
-        <v>Kmti9zgfvd8mh</v>
+        <v>Kmtia02g54416</v>
       </c>
       <c r="B1706" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65353,7 +65353,7 @@
     </row>
     <row r="1707">
       <c r="A1707" t="str">
-        <v>Kmti9zgfvc9si</v>
+        <v>Kmtia02g5m43x</v>
       </c>
       <c r="B1707" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65391,7 +65391,7 @@
     </row>
     <row r="1708">
       <c r="A1708" t="str">
-        <v>Kmti9zgfvawm4</v>
+        <v>Kmtia02g58zdp</v>
       </c>
       <c r="B1708" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -65429,7 +65429,7 @@
     </row>
     <row r="1709">
       <c r="A1709" t="str">
-        <v>Kmti9zgfvu4kv</v>
+        <v>Kmtia02g5um0d</v>
       </c>
       <c r="B1709" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -65505,7 +65505,7 @@
     </row>
     <row r="1711">
       <c r="A1711" t="str">
-        <v>Kmti9zgfvn91l</v>
+        <v>Kmtia02g5dtlp</v>
       </c>
       <c r="B1711" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65543,7 +65543,7 @@
     </row>
     <row r="1712">
       <c r="A1712" t="str">
-        <v>Kmti9zgfvy7ll</v>
+        <v>Kmtia02g5ug8c</v>
       </c>
       <c r="B1712" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65581,7 +65581,7 @@
     </row>
     <row r="1713">
       <c r="A1713" t="str">
-        <v>Kmti9zgfv3bkw</v>
+        <v>Kmtia02g5azkf</v>
       </c>
       <c r="B1713" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65619,7 +65619,7 @@
     </row>
     <row r="1714">
       <c r="A1714" t="str">
-        <v>Kmti9zgfvk58c</v>
+        <v>Kmtia02g5a723</v>
       </c>
       <c r="B1714" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65657,7 +65657,7 @@
     </row>
     <row r="1715">
       <c r="A1715" t="str">
-        <v>Kmti9zgfvg5e1</v>
+        <v>Kmtia02g5570l</v>
       </c>
       <c r="B1715" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65695,7 +65695,7 @@
     </row>
     <row r="1716">
       <c r="A1716" t="str">
-        <v>Kmti9zgfvk469</v>
+        <v>Kmtia02g5474m</v>
       </c>
       <c r="B1716" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65733,7 +65733,7 @@
     </row>
     <row r="1717">
       <c r="A1717" t="str">
-        <v>Kmti9zgfwkwkh</v>
+        <v>Kmtia02g535lj</v>
       </c>
       <c r="B1717" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65771,7 +65771,7 @@
     </row>
     <row r="1718">
       <c r="A1718" t="str">
-        <v>Kmti9zgfwsx0u</v>
+        <v>Kmtia02g58dyt</v>
       </c>
       <c r="B1718" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65847,7 +65847,7 @@
     </row>
     <row r="1720">
       <c r="A1720" t="str">
-        <v>Kmti9zgfwr6bz</v>
+        <v>Kmtia02g5g8of</v>
       </c>
       <c r="B1720" t="str">
         <v>Penata Layanan Operasional</v>
@@ -65885,7 +65885,7 @@
     </row>
     <row r="1721">
       <c r="A1721" t="str">
-        <v>Kmti9zgfwgsxa</v>
+        <v>Kmtia02g57dow</v>
       </c>
       <c r="B1721" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65923,7 +65923,7 @@
     </row>
     <row r="1722">
       <c r="A1722" t="str">
-        <v>Kmti9zgfw4dul</v>
+        <v>Kmtia02g5v18i</v>
       </c>
       <c r="B1722" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65961,7 +65961,7 @@
     </row>
     <row r="1723">
       <c r="A1723" t="str">
-        <v>Kmti9zgfwowkd</v>
+        <v>Kmtia02g52jmt</v>
       </c>
       <c r="B1723" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65999,7 +65999,7 @@
     </row>
     <row r="1724">
       <c r="A1724" t="str">
-        <v>Kmti9zgfwsb26</v>
+        <v>Kmtia02g5ews8</v>
       </c>
       <c r="B1724" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66037,7 +66037,7 @@
     </row>
     <row r="1725">
       <c r="A1725" t="str">
-        <v>Kmti9zgfwaza4</v>
+        <v>Kmtia02g5cesx</v>
       </c>
       <c r="B1725" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66075,7 +66075,7 @@
     </row>
     <row r="1726">
       <c r="A1726" t="str">
-        <v>Kmti9zgfwure0</v>
+        <v>Kmtia02g5n8zw</v>
       </c>
       <c r="B1726" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66113,7 +66113,7 @@
     </row>
     <row r="1727">
       <c r="A1727" t="str">
-        <v>Kmti9zgfwsb5n</v>
+        <v>Kmtia02g552t4</v>
       </c>
       <c r="B1727" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66189,7 +66189,7 @@
     </row>
     <row r="1729">
       <c r="A1729" t="str">
-        <v>Kmti9zgfw36rk</v>
+        <v>Kmtia02g504v6</v>
       </c>
       <c r="B1729" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66227,7 +66227,7 @@
     </row>
     <row r="1730">
       <c r="A1730" t="str">
-        <v>Kmti9zgfw3xp6</v>
+        <v>Kmtia02g5brv4</v>
       </c>
       <c r="B1730" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66265,7 +66265,7 @@
     </row>
     <row r="1731">
       <c r="A1731" t="str">
-        <v>Kmti9zgfwfvik</v>
+        <v>Kmtia02g5gq6m</v>
       </c>
       <c r="B1731" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66303,7 +66303,7 @@
     </row>
     <row r="1732">
       <c r="A1732" t="str">
-        <v>Kmti9zgfw4593</v>
+        <v>Kmtia02g5v3hn</v>
       </c>
       <c r="B1732" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66341,7 +66341,7 @@
     </row>
     <row r="1733">
       <c r="A1733" t="str">
-        <v>Kmti9zgfw4kki</v>
+        <v>Kmtia02g5sieb</v>
       </c>
       <c r="B1733" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66379,7 +66379,7 @@
     </row>
     <row r="1734">
       <c r="A1734" t="str">
-        <v>Kmti9zgfw72q9</v>
+        <v>Kmtia02g5lvtj</v>
       </c>
       <c r="B1734" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66417,7 +66417,7 @@
     </row>
     <row r="1735">
       <c r="A1735" t="str">
-        <v>Kmti9zgfw0hmg</v>
+        <v>Kmtia02g5r2ur</v>
       </c>
       <c r="B1735" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66455,7 +66455,7 @@
     </row>
     <row r="1736">
       <c r="A1736" t="str">
-        <v>Kmti9zgfw9jf7</v>
+        <v>Kmtia02g5oaqr</v>
       </c>
       <c r="B1736" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66493,7 +66493,7 @@
     </row>
     <row r="1737">
       <c r="A1737" t="str">
-        <v>Kmti9zgfw4y3j</v>
+        <v>Kmtia02g5n333</v>
       </c>
       <c r="B1737" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66531,7 +66531,7 @@
     </row>
     <row r="1738">
       <c r="A1738" t="str">
-        <v>Kmti9zgfwto78</v>
+        <v>Kmtia02g57e65</v>
       </c>
       <c r="B1738" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66569,7 +66569,7 @@
     </row>
     <row r="1739">
       <c r="A1739" t="str">
-        <v>Kmti9zgfw6xgk</v>
+        <v>Kmtia02g5c10j</v>
       </c>
       <c r="B1739" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66607,7 +66607,7 @@
     </row>
     <row r="1740">
       <c r="A1740" t="str">
-        <v>Kmti9zgfw57jm</v>
+        <v>Kmtia02g57618</v>
       </c>
       <c r="B1740" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66645,7 +66645,7 @@
     </row>
     <row r="1741">
       <c r="A1741" t="str">
-        <v>Kmti9zgfwlksp</v>
+        <v>Kmtia02g5bfnx</v>
       </c>
       <c r="B1741" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66683,7 +66683,7 @@
     </row>
     <row r="1742">
       <c r="A1742" t="str">
-        <v>Kmti9zgfwiets</v>
+        <v>Kmtia02g5og4z</v>
       </c>
       <c r="B1742" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -66721,7 +66721,7 @@
     </row>
     <row r="1743">
       <c r="A1743" t="str">
-        <v>Kmti9zgfwmd71</v>
+        <v>Kmtia02g57n1z</v>
       </c>
       <c r="B1743" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -66835,7 +66835,7 @@
     </row>
     <row r="1746">
       <c r="A1746" t="str">
-        <v>Kmti9zgfwph3s</v>
+        <v>Kmtia02g5uor5</v>
       </c>
       <c r="B1746" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66873,7 +66873,7 @@
     </row>
     <row r="1747">
       <c r="A1747" t="str">
-        <v>Kmti9zgfwkppc</v>
+        <v>Kmtia02g5kucy</v>
       </c>
       <c r="B1747" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66911,7 +66911,7 @@
     </row>
     <row r="1748">
       <c r="A1748" t="str">
-        <v>Kmti9zgfw0cxv</v>
+        <v>Kmtia02g5quiy</v>
       </c>
       <c r="B1748" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66949,7 +66949,7 @@
     </row>
     <row r="1749" xml:space="preserve">
       <c r="A1749" t="str">
-        <v>Kmti9zgfw6ykh</v>
+        <v>Kmtia02g5rqqv</v>
       </c>
       <c r="B1749" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -66988,7 +66988,7 @@
     </row>
     <row r="1750">
       <c r="A1750" t="str">
-        <v>Kmti9zgfwrkt3</v>
+        <v>Kmtia02g5y05f</v>
       </c>
       <c r="B1750" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67064,7 +67064,7 @@
     </row>
     <row r="1752">
       <c r="A1752" t="str">
-        <v>Kmti9zgfw2txy</v>
+        <v>Kmtia02g5mc4x</v>
       </c>
       <c r="B1752" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67102,7 +67102,7 @@
     </row>
     <row r="1753">
       <c r="A1753" t="str">
-        <v>Kmti9zgfw3olu</v>
+        <v>Kmtia02g5ooyp</v>
       </c>
       <c r="B1753" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67140,7 +67140,7 @@
     </row>
     <row r="1754">
       <c r="A1754" t="str">
-        <v>Kmti9zgfwyrgw</v>
+        <v>Kmtia02g5f59f</v>
       </c>
       <c r="B1754" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67178,7 +67178,7 @@
     </row>
     <row r="1755" xml:space="preserve">
       <c r="A1755" t="str">
-        <v>Kmti9zgfw5xjt</v>
+        <v>Kmtia02g5ie9e</v>
       </c>
       <c r="B1755" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67217,7 +67217,7 @@
     </row>
     <row r="1756" xml:space="preserve">
       <c r="A1756" t="str">
-        <v>Kmti9zgfwukt5</v>
+        <v>Kmtia02g50k5a</v>
       </c>
       <c r="B1756" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67256,7 +67256,7 @@
     </row>
     <row r="1757">
       <c r="A1757" t="str">
-        <v>Kmti9zgfwffgf</v>
+        <v>Kmtia02g5qac8</v>
       </c>
       <c r="B1757" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67294,7 +67294,7 @@
     </row>
     <row r="1758" xml:space="preserve">
       <c r="A1758" t="str">
-        <v>Kmti9zgfwfrt0</v>
+        <v>Kmtia02g5hnhr</v>
       </c>
       <c r="B1758" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67333,7 +67333,7 @@
     </row>
     <row r="1759" xml:space="preserve">
       <c r="A1759" t="str">
-        <v>Kmti9zgfwqx35</v>
+        <v>Kmtia02g5ow1a</v>
       </c>
       <c r="B1759" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67410,7 +67410,7 @@
     </row>
     <row r="1761">
       <c r="A1761" t="str">
-        <v>Kmti9zgfwp79t</v>
+        <v>Kmtia02g504rl</v>
       </c>
       <c r="B1761" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67448,7 +67448,7 @@
     </row>
     <row r="1762">
       <c r="A1762" t="str">
-        <v>Kmti9zgfw5w0d</v>
+        <v>Kmtia02g5z7ob</v>
       </c>
       <c r="B1762" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67486,7 +67486,7 @@
     </row>
     <row r="1763">
       <c r="A1763" t="str">
-        <v>Kmti9zgfwwc7b</v>
+        <v>Kmtia02g56yb1</v>
       </c>
       <c r="B1763" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67524,7 +67524,7 @@
     </row>
     <row r="1764" xml:space="preserve">
       <c r="A1764" t="str">
-        <v>Kmti9zgfwgmis</v>
+        <v>Kmtia02g5l8u6</v>
       </c>
       <c r="B1764" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67563,7 +67563,7 @@
     </row>
     <row r="1765" xml:space="preserve">
       <c r="A1765" t="str">
-        <v>Kmti9zgfwqfcn</v>
+        <v>Kmtia02g5y7sd</v>
       </c>
       <c r="B1765" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67602,7 +67602,7 @@
     </row>
     <row r="1766">
       <c r="A1766" t="str">
-        <v>Kmti9zgfw8fwd</v>
+        <v>Kmtia02g5iaic</v>
       </c>
       <c r="B1766" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67640,7 +67640,7 @@
     </row>
     <row r="1767" xml:space="preserve">
       <c r="A1767" t="str">
-        <v>Kmti9zgfw3a03</v>
+        <v>Kmtia02g59bdb</v>
       </c>
       <c r="B1767" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67679,7 +67679,7 @@
     </row>
     <row r="1768" xml:space="preserve">
       <c r="A1768" t="str">
-        <v>Kmti9zgfwnd9w</v>
+        <v>Kmtia02g5jhar</v>
       </c>
       <c r="B1768" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67718,7 +67718,7 @@
     </row>
     <row r="1769">
       <c r="A1769" t="str">
-        <v>Kmti9zgfwg7p6</v>
+        <v>Kmtia02g5otlq</v>
       </c>
       <c r="B1769" t="str">
         <v>Analis Anggaran Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -67756,7 +67756,7 @@
     </row>
     <row r="1770">
       <c r="A1770" t="str">
-        <v>Kmti9zgfwlxww</v>
+        <v>Kmtia02g50c5p</v>
       </c>
       <c r="B1770" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67794,7 +67794,7 @@
     </row>
     <row r="1771">
       <c r="A1771" t="str">
-        <v>Kmti9zgfweso7</v>
+        <v>Kmtia02g5fxu8</v>
       </c>
       <c r="B1771" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -67832,7 +67832,7 @@
     </row>
     <row r="1772">
       <c r="A1772" t="str">
-        <v>Kmti9zgfwya1b</v>
+        <v>Kmtia02g51840</v>
       </c>
       <c r="B1772" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Ahli Muda</v>
@@ -67870,7 +67870,7 @@
     </row>
     <row r="1773">
       <c r="A1773" t="str">
-        <v>Kmti9zgfwol0w</v>
+        <v>Kmtia02g54482</v>
       </c>
       <c r="B1773" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -67908,7 +67908,7 @@
     </row>
     <row r="1774">
       <c r="A1774" t="str">
-        <v>Kmti9zgfw4mzw</v>
+        <v>Kmtia02g5x7dm</v>
       </c>
       <c r="B1774" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67946,7 +67946,7 @@
     </row>
     <row r="1775">
       <c r="A1775" t="str">
-        <v>Kmti9zgfwb5sn</v>
+        <v>Kmtia02g56c0k</v>
       </c>
       <c r="B1775" t="str">
         <v>Pranata Keuangan APBN Mahir/Pengawas Keuangan Negara Mahir</v>
@@ -67984,7 +67984,7 @@
     </row>
     <row r="1776">
       <c r="A1776" t="str">
-        <v>Kmti9zgfw42g7</v>
+        <v>Kmtia02g57l4j</v>
       </c>
       <c r="B1776" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -68098,7 +68098,7 @@
     </row>
     <row r="1779">
       <c r="A1779" t="str">
-        <v>Kmti9zgfwgvaq</v>
+        <v>Kmtia02g5ijsg</v>
       </c>
       <c r="B1779" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68136,7 +68136,7 @@
     </row>
     <row r="1780">
       <c r="A1780" t="str">
-        <v>Kmti9zgfw117s</v>
+        <v>Kmtia02g5q6zy</v>
       </c>
       <c r="B1780" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68174,7 +68174,7 @@
     </row>
     <row r="1781">
       <c r="A1781" t="str">
-        <v>Kmti9zgfwc6hl</v>
+        <v>Kmtia02g51nq2</v>
       </c>
       <c r="B1781" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68250,7 +68250,7 @@
     </row>
     <row r="1783">
       <c r="A1783" t="str">
-        <v>Kmti9zgfwprkg</v>
+        <v>Kmtia02g5mcdz</v>
       </c>
       <c r="B1783" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68288,7 +68288,7 @@
     </row>
     <row r="1784">
       <c r="A1784" t="str">
-        <v>Kmti9zgfwlhys</v>
+        <v>Kmtia02g57aq0</v>
       </c>
       <c r="B1784" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68326,7 +68326,7 @@
     </row>
     <row r="1785">
       <c r="A1785" t="str">
-        <v>Kmti9zgfwkuna</v>
+        <v>Kmtia02g548bq</v>
       </c>
       <c r="B1785" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68364,7 +68364,7 @@
     </row>
     <row r="1786">
       <c r="A1786" t="str">
-        <v>Kmti9zgfwluh2</v>
+        <v>Kmtia02g5em6c</v>
       </c>
       <c r="B1786" t="str">
         <v>Penata Keprotokolan*</v>
@@ -68402,7 +68402,7 @@
     </row>
     <row r="1787">
       <c r="A1787" t="str">
-        <v>Kmti9zgfwg7ii</v>
+        <v>Kmtia02g5wbt0</v>
       </c>
       <c r="B1787" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68440,7 +68440,7 @@
     </row>
     <row r="1788">
       <c r="A1788" t="str">
-        <v>Kmti9zgfwzqqc</v>
+        <v>Kmtia02g5tsuz</v>
       </c>
       <c r="B1788" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68478,7 +68478,7 @@
     </row>
     <row r="1789">
       <c r="A1789" t="str">
-        <v>Kmti9zgfwg8vo</v>
+        <v>Kmtia02g5zee5</v>
       </c>
       <c r="B1789" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68516,7 +68516,7 @@
     </row>
     <row r="1790">
       <c r="A1790" t="str">
-        <v>Kmti9zgfw6kia</v>
+        <v>Kmtia02g5bzk7</v>
       </c>
       <c r="B1790" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68592,7 +68592,7 @@
     </row>
     <row r="1792">
       <c r="A1792" t="str">
-        <v>Kmti9zgfwvs7f</v>
+        <v>Kmtia02g5q7o3</v>
       </c>
       <c r="B1792" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68630,7 +68630,7 @@
     </row>
     <row r="1793">
       <c r="A1793" t="str">
-        <v>Kmti9zgfwinbd</v>
+        <v>Kmtia02g5t885</v>
       </c>
       <c r="B1793" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68668,7 +68668,7 @@
     </row>
     <row r="1794">
       <c r="A1794" t="str">
-        <v>Kmti9zgfwi2a5</v>
+        <v>Kmtia02g541cu</v>
       </c>
       <c r="B1794" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68706,7 +68706,7 @@
     </row>
     <row r="1795">
       <c r="A1795" t="str">
-        <v>Kmti9zgfw1s7e</v>
+        <v>Kmtia02g57jxa</v>
       </c>
       <c r="B1795" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -68744,7 +68744,7 @@
     </row>
     <row r="1796">
       <c r="A1796" t="str">
-        <v>Kmti9zgfwtdxj</v>
+        <v>Kmtia02g5wphh</v>
       </c>
       <c r="B1796" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68782,7 +68782,7 @@
     </row>
     <row r="1797">
       <c r="A1797" t="str">
-        <v>Kmti9zgfw2ch2</v>
+        <v>Kmtia02g5f8fz</v>
       </c>
       <c r="B1797" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68820,7 +68820,7 @@
     </row>
     <row r="1798">
       <c r="A1798" t="str">
-        <v>Kmti9zgfwp942</v>
+        <v>Kmtia02g5hyc0</v>
       </c>
       <c r="B1798" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68858,7 +68858,7 @@
     </row>
     <row r="1799">
       <c r="A1799" t="str">
-        <v>Kmti9zgfw2ttx</v>
+        <v>Kmtia02g5lelq</v>
       </c>
       <c r="B1799" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68934,7 +68934,7 @@
     </row>
     <row r="1801">
       <c r="A1801" t="str">
-        <v>Kmti9zgfw74gb</v>
+        <v>Kmtia02g5i80r</v>
       </c>
       <c r="B1801" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68972,7 +68972,7 @@
     </row>
     <row r="1802">
       <c r="A1802" t="str">
-        <v>Kmti9zgfwbjjg</v>
+        <v>Kmtia02g5mz8o</v>
       </c>
       <c r="B1802" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69010,7 +69010,7 @@
     </row>
     <row r="1803">
       <c r="A1803" t="str">
-        <v>Kmti9zgfwrqwo</v>
+        <v>Kmtia02g59ck3</v>
       </c>
       <c r="B1803" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69048,7 +69048,7 @@
     </row>
     <row r="1804">
       <c r="A1804" t="str">
-        <v>Kmti9zgfwhexu</v>
+        <v>Kmtia02g5851z</v>
       </c>
       <c r="B1804" t="str">
         <v>Penata Keprotokolan*</v>
@@ -69086,7 +69086,7 @@
     </row>
     <row r="1805">
       <c r="A1805" t="str">
-        <v>Kmti9zgfwdna0</v>
+        <v>Kmtia02g528yh</v>
       </c>
       <c r="B1805" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -69124,7 +69124,7 @@
     </row>
     <row r="1806">
       <c r="A1806" t="str">
-        <v>Kmti9zgfwxez5</v>
+        <v>Kmtia02g5g3cc</v>
       </c>
       <c r="B1806" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -69162,7 +69162,7 @@
     </row>
     <row r="1807">
       <c r="A1807" t="str">
-        <v>Kmti9zgfwy5z6</v>
+        <v>Kmtia02g5qi08</v>
       </c>
       <c r="B1807" t="str">
         <v>Arsiparis Penyelia</v>
@@ -69200,7 +69200,7 @@
     </row>
     <row r="1808">
       <c r="A1808" t="str">
-        <v>Kmti9zgfw5cy1</v>
+        <v>Kmtia02g5tf66</v>
       </c>
       <c r="B1808" t="str">
         <v>Arsiparis Mahir</v>
@@ -69238,7 +69238,7 @@
     </row>
     <row r="1809">
       <c r="A1809" t="str">
-        <v>Kmti9zgfweff0</v>
+        <v>Kmtia02g5en5p</v>
       </c>
       <c r="B1809" t="str">
         <v>Arsiparis Terampil</v>
@@ -69276,7 +69276,7 @@
     </row>
     <row r="1810">
       <c r="A1810" t="str">
-        <v>Kmti9zgfwfxcr</v>
+        <v>Kmtia02g54v75</v>
       </c>
       <c r="B1810" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -69314,7 +69314,7 @@
     </row>
     <row r="1811">
       <c r="A1811" t="str">
-        <v>Kmti9zgfwj2pm</v>
+        <v>Kmtia02g59puy</v>
       </c>
       <c r="B1811" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69352,7 +69352,7 @@
     </row>
     <row r="1812">
       <c r="A1812" t="str">
-        <v>Kmti9zgfwe8ra</v>
+        <v>Kmtia02g5y4cv</v>
       </c>
       <c r="B1812" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -69390,7 +69390,7 @@
     </row>
     <row r="1813">
       <c r="A1813" t="str">
-        <v>Kmti9zgfwaj0c</v>
+        <v>Kmtia02g5vd0v</v>
       </c>
       <c r="B1813" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -69428,7 +69428,7 @@
     </row>
     <row r="1814">
       <c r="A1814" t="str">
-        <v>Kmti9zgfwvo49</v>
+        <v>Kmtia02g5u2cs</v>
       </c>
       <c r="B1814" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -69542,7 +69542,7 @@
     </row>
     <row r="1817">
       <c r="A1817" t="str">
-        <v>Kmti9zgfwjqwo</v>
+        <v>Kmtia02g5fwmp</v>
       </c>
       <c r="B1817" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69580,7 +69580,7 @@
     </row>
     <row r="1818">
       <c r="A1818" t="str">
-        <v>Kmti9zgfwem78</v>
+        <v>Kmtia02g5mhs7</v>
       </c>
       <c r="B1818" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69618,7 +69618,7 @@
     </row>
     <row r="1819">
       <c r="A1819" t="str">
-        <v>Kmti9zgfw48hj</v>
+        <v>Kmtia02g58hq9</v>
       </c>
       <c r="B1819" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69656,7 +69656,7 @@
     </row>
     <row r="1820">
       <c r="A1820" t="str">
-        <v>Kmti9zgfwyiy6</v>
+        <v>Kmtia02g5ucy1</v>
       </c>
       <c r="B1820" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69694,7 +69694,7 @@
     </row>
     <row r="1821">
       <c r="A1821" t="str">
-        <v>Kmti9zgfw4rmo</v>
+        <v>Kmtia02g57urv</v>
       </c>
       <c r="B1821" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69732,7 +69732,7 @@
     </row>
     <row r="1822">
       <c r="A1822" t="str">
-        <v>Kmti9zgfwsdmd</v>
+        <v>Kmtia02g570vk</v>
       </c>
       <c r="B1822" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -69808,7 +69808,7 @@
     </row>
     <row r="1824">
       <c r="A1824" t="str">
-        <v>Kmti9zgfwhaic</v>
+        <v>Kmtia02g5dgnc</v>
       </c>
       <c r="B1824" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69846,7 +69846,7 @@
     </row>
     <row r="1825">
       <c r="A1825" t="str">
-        <v>Kmti9zgfwz66l</v>
+        <v>Kmtia02g51x9j</v>
       </c>
       <c r="B1825" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69884,7 +69884,7 @@
     </row>
     <row r="1826">
       <c r="A1826" t="str">
-        <v>Kmti9zgfw2y2o</v>
+        <v>Kmtia02g58aiv</v>
       </c>
       <c r="B1826" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69922,7 +69922,7 @@
     </row>
     <row r="1827">
       <c r="A1827" t="str">
-        <v>Kmti9zgfwldzg</v>
+        <v>Kmtia02g5094l</v>
       </c>
       <c r="B1827" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69960,7 +69960,7 @@
     </row>
     <row r="1828">
       <c r="A1828" t="str">
-        <v>Kmti9zgfwln2m</v>
+        <v>Kmtia02g5d1t4</v>
       </c>
       <c r="B1828" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69998,7 +69998,7 @@
     </row>
     <row r="1829">
       <c r="A1829" t="str">
-        <v>Kmti9zgfw4fjz</v>
+        <v>Kmtia02g57duk</v>
       </c>
       <c r="B1829" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70036,7 +70036,7 @@
     </row>
     <row r="1830">
       <c r="A1830" t="str">
-        <v>Kmti9zgfwrcj7</v>
+        <v>Kmtia02g5awdb</v>
       </c>
       <c r="B1830" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70112,7 +70112,7 @@
     </row>
     <row r="1832">
       <c r="A1832" t="str">
-        <v>Kmti9zgfwwsyh</v>
+        <v>Kmtia02g506h5</v>
       </c>
       <c r="B1832" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -70150,7 +70150,7 @@
     </row>
     <row r="1833">
       <c r="A1833" t="str">
-        <v>Kmti9zgfwtkvi</v>
+        <v>Kmtia02g5tgav</v>
       </c>
       <c r="B1833" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70188,7 +70188,7 @@
     </row>
     <row r="1834">
       <c r="A1834" t="str">
-        <v>Kmti9zgfwv418</v>
+        <v>Kmtia02g53yk1</v>
       </c>
       <c r="B1834" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70226,7 +70226,7 @@
     </row>
     <row r="1835">
       <c r="A1835" t="str">
-        <v>Kmti9zgfw5nyi</v>
+        <v>Kmtia02g5bnta</v>
       </c>
       <c r="B1835" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70264,7 +70264,7 @@
     </row>
     <row r="1836">
       <c r="A1836" t="str">
-        <v>Kmti9zgfw36v4</v>
+        <v>Kmtia02g50mv0</v>
       </c>
       <c r="B1836" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70302,7 +70302,7 @@
     </row>
     <row r="1837">
       <c r="A1837" t="str">
-        <v>Kmti9zgfwrhj9</v>
+        <v>Kmtia02g5en1j</v>
       </c>
       <c r="B1837" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70340,7 +70340,7 @@
     </row>
     <row r="1838">
       <c r="A1838" t="str">
-        <v>Kmti9zgfw9p5y</v>
+        <v>Kmtia02g5wgv9</v>
       </c>
       <c r="B1838" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70378,7 +70378,7 @@
     </row>
     <row r="1839">
       <c r="A1839" t="str">
-        <v>Kmti9zgfw7yh8</v>
+        <v>Kmtia02g52l3u</v>
       </c>
       <c r="B1839" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70416,7 +70416,7 @@
     </row>
     <row r="1840">
       <c r="A1840" t="str">
-        <v>Kmti9zgfwytqd</v>
+        <v>Kmtia02g5sr20</v>
       </c>
       <c r="B1840" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70454,7 +70454,7 @@
     </row>
     <row r="1841">
       <c r="A1841" t="str">
-        <v>Kmti9zgfwidk1</v>
+        <v>Kmtia02g59eyb</v>
       </c>
       <c r="B1841" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70492,7 +70492,7 @@
     </row>
     <row r="1842">
       <c r="A1842" t="str">
-        <v>Kmti9zgfw5qi3</v>
+        <v>Kmtia02g5y8fb</v>
       </c>
       <c r="B1842" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70568,7 +70568,7 @@
     </row>
     <row r="1844">
       <c r="A1844" t="str">
-        <v>Kmti9zgfw7bm4</v>
+        <v>Kmtia02g5mx3q</v>
       </c>
       <c r="B1844" t="str">
         <v>Penata Layanan Operasional</v>
@@ -70606,7 +70606,7 @@
     </row>
     <row r="1845">
       <c r="A1845" t="str">
-        <v>Kmti9zgfwsvbt</v>
+        <v>Kmtia02g5gv4c</v>
       </c>
       <c r="B1845" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70644,7 +70644,7 @@
     </row>
     <row r="1846">
       <c r="A1846" t="str">
-        <v>Kmti9zgfwg9f7</v>
+        <v>Kmtia02g5mlx1</v>
       </c>
       <c r="B1846" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70682,7 +70682,7 @@
     </row>
     <row r="1847">
       <c r="A1847" t="str">
-        <v>Kmti9zgfwwt6t</v>
+        <v>Kmtia02g52bdq</v>
       </c>
       <c r="B1847" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -70720,7 +70720,7 @@
     </row>
     <row r="1848">
       <c r="A1848" t="str">
-        <v>Kmti9zgfwv7iq</v>
+        <v>Kmtia02g5seaj</v>
       </c>
       <c r="B1848" t="str">
         <v>Pranata Humas Ahli Pertama</v>
@@ -70758,7 +70758,7 @@
     </row>
     <row r="1849">
       <c r="A1849" t="str">
-        <v>Kmti9zgfwdkza</v>
+        <v>Kmtia02g5blr7</v>
       </c>
       <c r="B1849" t="str">
         <v>Pranata Humas Penyelia</v>
@@ -70796,7 +70796,7 @@
     </row>
     <row r="1850">
       <c r="A1850" t="str">
-        <v>Kmti9zgfwko74</v>
+        <v>Kmtia02g5p73l</v>
       </c>
       <c r="B1850" t="str">
         <v>Pranata Humas Mahir</v>
@@ -70834,7 +70834,7 @@
     </row>
     <row r="1851">
       <c r="A1851" t="str">
-        <v>Kmti9zgfwifm5</v>
+        <v>Kmtia02g5zppp</v>
       </c>
       <c r="B1851" t="str">
         <v>Pranata Humas Terampil</v>
@@ -70872,7 +70872,7 @@
     </row>
     <row r="1852">
       <c r="A1852" t="str">
-        <v>Kmti9zgfw8us7</v>
+        <v>Kmtia02g5evqm</v>
       </c>
       <c r="B1852" t="str">
         <v>Pustakawan Ahli Muda</v>
@@ -70910,7 +70910,7 @@
     </row>
     <row r="1853">
       <c r="A1853" t="str">
-        <v>Kmti9zgfwbumm</v>
+        <v>Kmtia02g5sk81</v>
       </c>
       <c r="B1853" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -70948,7 +70948,7 @@
     </row>
     <row r="1854">
       <c r="A1854" t="str">
-        <v>Kmti9zgfw2iij</v>
+        <v>Kmtia02g5847t</v>
       </c>
       <c r="B1854" t="str">
         <v>Pustakawan Penyelia</v>
@@ -70986,7 +70986,7 @@
     </row>
     <row r="1855">
       <c r="A1855" t="str">
-        <v>Kmti9zgfwyyps</v>
+        <v>Kmtia02g5esxu</v>
       </c>
       <c r="B1855" t="str">
         <v>Pustakawan Mahir</v>
@@ -71024,7 +71024,7 @@
     </row>
     <row r="1856">
       <c r="A1856" t="str">
-        <v>Kmti9zgfwjo3x</v>
+        <v>Kmtia02g5xv9d</v>
       </c>
       <c r="B1856" t="str">
         <v>Pustakawan Terampil</v>
@@ -71138,7 +71138,7 @@
     </row>
     <row r="1859">
       <c r="A1859" t="str">
-        <v>Kmti9zgfw0xyq</v>
+        <v>Kmtia02g5751t</v>
       </c>
       <c r="B1859" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71176,7 +71176,7 @@
     </row>
     <row r="1860">
       <c r="A1860" t="str">
-        <v>Kmti9zgfwe6ho</v>
+        <v>Kmtia02g5n6is</v>
       </c>
       <c r="B1860" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71214,7 +71214,7 @@
     </row>
     <row r="1861">
       <c r="A1861" t="str">
-        <v>Kmti9zgfwfgw6</v>
+        <v>Kmtia02g5jo1h</v>
       </c>
       <c r="B1861" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71252,7 +71252,7 @@
     </row>
     <row r="1862">
       <c r="A1862" t="str">
-        <v>Kmti9zgfwla25</v>
+        <v>Kmtia02g5fhzw</v>
       </c>
       <c r="B1862" t="str">
         <v>Penata Keprotokolan*</v>
@@ -71366,7 +71366,7 @@
     </row>
     <row r="1865">
       <c r="A1865" t="str">
-        <v>Kmti9zgfw2nin</v>
+        <v>Kmtia02g52apj</v>
       </c>
       <c r="B1865" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71404,7 +71404,7 @@
     </row>
     <row r="1866">
       <c r="A1866" t="str">
-        <v>Kmti9zgfw7zit</v>
+        <v>Kmtia02g51nt1</v>
       </c>
       <c r="B1866" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71442,7 +71442,7 @@
     </row>
     <row r="1867">
       <c r="A1867" t="str">
-        <v>Kmti9zgfwii39</v>
+        <v>Kmtia02g543v3</v>
       </c>
       <c r="B1867" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71518,7 +71518,7 @@
     </row>
     <row r="1869">
       <c r="A1869" t="str">
-        <v>Kmti9zgfwzuwq</v>
+        <v>Kmtia02g5ufdv</v>
       </c>
       <c r="B1869" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71556,7 +71556,7 @@
     </row>
     <row r="1870">
       <c r="A1870" t="str">
-        <v>Kmti9zgfwlnqc</v>
+        <v>Kmtia02g5h0pq</v>
       </c>
       <c r="B1870" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71594,7 +71594,7 @@
     </row>
     <row r="1871">
       <c r="A1871" t="str">
-        <v>Kmti9zgfwp5sv</v>
+        <v>Kmtia02g52i5g</v>
       </c>
       <c r="B1871" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71632,7 +71632,7 @@
     </row>
     <row r="1872" xml:space="preserve">
       <c r="A1872" t="str">
-        <v>Kmti9zgfw0ds4</v>
+        <v>Kmtia02g5arra</v>
       </c>
       <c r="B1872" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -71671,7 +71671,7 @@
     </row>
     <row r="1873" xml:space="preserve">
       <c r="A1873" t="str">
-        <v>Kmti9zgfwa6fc</v>
+        <v>Kmtia02g5vqpj</v>
       </c>
       <c r="B1873" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -71710,7 +71710,7 @@
     </row>
     <row r="1874" xml:space="preserve">
       <c r="A1874" t="str">
-        <v>Kmti9zgfwajv1</v>
+        <v>Kmtia02g5dw28</v>
       </c>
       <c r="B1874" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -71749,7 +71749,7 @@
     </row>
     <row r="1875" xml:space="preserve">
       <c r="A1875" t="str">
-        <v>Kmti9zgfwc10z</v>
+        <v>Kmtia02g50kef</v>
       </c>
       <c r="B1875" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -71864,7 +71864,7 @@
     </row>
     <row r="1878">
       <c r="A1878" t="str">
-        <v>Kmti9zgfwygzd</v>
+        <v>Kmtia02g5xkth</v>
       </c>
       <c r="B1878" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71902,7 +71902,7 @@
     </row>
     <row r="1879">
       <c r="A1879" t="str">
-        <v>Kmti9zgfwoltt</v>
+        <v>Kmtia02g5w1p4</v>
       </c>
       <c r="B1879" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71940,7 +71940,7 @@
     </row>
     <row r="1880">
       <c r="A1880" t="str">
-        <v>Kmti9zgfwqkai</v>
+        <v>Kmtia02g5emrb</v>
       </c>
       <c r="B1880" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71978,7 +71978,7 @@
     </row>
     <row r="1881">
       <c r="A1881" t="str">
-        <v>Kmti9zgfwypfl</v>
+        <v>Kmtia02g5jwg2</v>
       </c>
       <c r="B1881" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72092,7 +72092,7 @@
     </row>
     <row r="1884">
       <c r="A1884" t="str">
-        <v>Kmti9zgfwhczd</v>
+        <v>Kmtia02g5rr92</v>
       </c>
       <c r="B1884" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72130,7 +72130,7 @@
     </row>
     <row r="1885">
       <c r="A1885" t="str">
-        <v>Kmti9zgfw7qoi</v>
+        <v>Kmtia02g5z6a2</v>
       </c>
       <c r="B1885" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72168,7 +72168,7 @@
     </row>
     <row r="1886">
       <c r="A1886" t="str">
-        <v>Kmti9zgfwb0ne</v>
+        <v>Kmtia02g5c1v6</v>
       </c>
       <c r="B1886" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72244,7 +72244,7 @@
     </row>
     <row r="1888">
       <c r="A1888" t="str">
-        <v>Kmti9zgfwonwb</v>
+        <v>Kmtia02g5yd27</v>
       </c>
       <c r="B1888" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72282,7 +72282,7 @@
     </row>
     <row r="1889">
       <c r="A1889" t="str">
-        <v>Kmti9zgfwmcx1</v>
+        <v>Kmtia02g5sdjj</v>
       </c>
       <c r="B1889" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72320,7 +72320,7 @@
     </row>
     <row r="1890">
       <c r="A1890" t="str">
-        <v>Kmti9zgfwvgey</v>
+        <v>Kmtia02g5rlp6</v>
       </c>
       <c r="B1890" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72358,7 +72358,7 @@
     </row>
     <row r="1891" xml:space="preserve">
       <c r="A1891" t="str">
-        <v>Kmti9zgfwhsjl</v>
+        <v>Kmtia02g5gw3m</v>
       </c>
       <c r="B1891" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -72397,7 +72397,7 @@
     </row>
     <row r="1892" xml:space="preserve">
       <c r="A1892" t="str">
-        <v>Kmti9zgfwz45u</v>
+        <v>Kmtia02g5ycyf</v>
       </c>
       <c r="B1892" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -72436,7 +72436,7 @@
     </row>
     <row r="1893" xml:space="preserve">
       <c r="A1893" t="str">
-        <v>Kmti9zgfwkdjf</v>
+        <v>Kmtia02g5xp44</v>
       </c>
       <c r="B1893" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -72475,7 +72475,7 @@
     </row>
     <row r="1894" xml:space="preserve">
       <c r="A1894" t="str">
-        <v>Kmti9zgfwqky1</v>
+        <v>Kmtia02g5po7x</v>
       </c>
       <c r="B1894" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -72590,7 +72590,7 @@
     </row>
     <row r="1897">
       <c r="A1897" t="str">
-        <v>Kmti9zgfwdg9m</v>
+        <v>Kmtia02g5jnvm</v>
       </c>
       <c r="B1897" t="str">
         <v>Penata Layanan Operasional</v>
@@ -72628,7 +72628,7 @@
     </row>
     <row r="1898">
       <c r="A1898" t="str">
-        <v>Kmti9zgfw93o7</v>
+        <v>Kmtia02g5tu8l</v>
       </c>
       <c r="B1898" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72666,7 +72666,7 @@
     </row>
     <row r="1899">
       <c r="A1899" t="str">
-        <v>Kmti9zgfw3rvs</v>
+        <v>Kmtia02g59zte</v>
       </c>
       <c r="B1899" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72704,7 +72704,7 @@
     </row>
     <row r="1900">
       <c r="A1900" t="str">
-        <v>Kmti9zgfwaiyz</v>
+        <v>Kmtia02g54rf9</v>
       </c>
       <c r="B1900" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72818,7 +72818,7 @@
     </row>
     <row r="1903">
       <c r="A1903" t="str">
-        <v>Kmti9zgfwqae2</v>
+        <v>Kmtia02g5eucu</v>
       </c>
       <c r="B1903" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72856,7 +72856,7 @@
     </row>
     <row r="1904">
       <c r="A1904" t="str">
-        <v>Kmti9zgfwd4z6</v>
+        <v>Kmtia02g5xv40</v>
       </c>
       <c r="B1904" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72894,7 +72894,7 @@
     </row>
     <row r="1905">
       <c r="A1905" t="str">
-        <v>Kmti9zgfw2ujl</v>
+        <v>Kmtia02g5tio4</v>
       </c>
       <c r="B1905" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72970,7 +72970,7 @@
     </row>
     <row r="1907">
       <c r="A1907" t="str">
-        <v>Kmti9zgfw9m04</v>
+        <v>Kmtia02g52b6t</v>
       </c>
       <c r="B1907" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73008,7 +73008,7 @@
     </row>
     <row r="1908">
       <c r="A1908" t="str">
-        <v>Kmti9zgfwx768</v>
+        <v>Kmtia02g5xi3c</v>
       </c>
       <c r="B1908" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73046,7 +73046,7 @@
     </row>
     <row r="1909">
       <c r="A1909" t="str">
-        <v>Kmti9zgfwvkwj</v>
+        <v>Kmtia02g5ju1t</v>
       </c>
       <c r="B1909" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73084,7 +73084,7 @@
     </row>
     <row r="1910" xml:space="preserve">
       <c r="A1910" t="str">
-        <v>Kmti9zgfw6b8v</v>
+        <v>Kmtia02g5j8e4</v>
       </c>
       <c r="B1910" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73123,7 +73123,7 @@
     </row>
     <row r="1911" xml:space="preserve">
       <c r="A1911" t="str">
-        <v>Kmti9zgfwsy1c</v>
+        <v>Kmtia02g5lo7f</v>
       </c>
       <c r="B1911" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73162,7 +73162,7 @@
     </row>
     <row r="1912" xml:space="preserve">
       <c r="A1912" t="str">
-        <v>Kmti9zgfw5kvp</v>
+        <v>Kmtia02g54w5v</v>
       </c>
       <c r="B1912" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73201,7 +73201,7 @@
     </row>
     <row r="1913" xml:space="preserve">
       <c r="A1913" t="str">
-        <v>Kmti9zgfwz84e</v>
+        <v>Kmtia02g5tsmj</v>
       </c>
       <c r="B1913" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73316,7 +73316,7 @@
     </row>
     <row r="1916">
       <c r="A1916" t="str">
-        <v>Kmti9zgfwbw3m</v>
+        <v>Kmtia02g67x9r</v>
       </c>
       <c r="B1916" t="str">
         <v>Penata Layanan Operasional</v>
@@ -73354,7 +73354,7 @@
     </row>
     <row r="1917">
       <c r="A1917" t="str">
-        <v>Kmti9zgfwkfny</v>
+        <v>Kmtia02g6l4mu</v>
       </c>
       <c r="B1917" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73392,7 +73392,7 @@
     </row>
     <row r="1918">
       <c r="A1918" t="str">
-        <v>Kmti9zgfwcyo6</v>
+        <v>Kmtia02g6fhzw</v>
       </c>
       <c r="B1918" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73430,7 +73430,7 @@
     </row>
     <row r="1919">
       <c r="A1919" t="str">
-        <v>Kmti9zgfw0tnz</v>
+        <v>Kmtia02g6xz2g</v>
       </c>
       <c r="B1919" t="str">
         <v>Penata Keprotokolan*</v>
@@ -73544,7 +73544,7 @@
     </row>
     <row r="1922">
       <c r="A1922" t="str">
-        <v>Kmti9zgfwltys</v>
+        <v>Kmtia02g6mfnb</v>
       </c>
       <c r="B1922" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73582,7 +73582,7 @@
     </row>
     <row r="1923">
       <c r="A1923" t="str">
-        <v>Kmti9zgfwlv3o</v>
+        <v>Kmtia02g6sda7</v>
       </c>
       <c r="B1923" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73620,7 +73620,7 @@
     </row>
     <row r="1924">
       <c r="A1924" t="str">
-        <v>Kmti9zgfwjioh</v>
+        <v>Kmtia02g6m9u1</v>
       </c>
       <c r="B1924" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73696,7 +73696,7 @@
     </row>
     <row r="1926">
       <c r="A1926" t="str">
-        <v>Kmti9zgfw06pe</v>
+        <v>Kmtia02g6uvuq</v>
       </c>
       <c r="B1926" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73734,7 +73734,7 @@
     </row>
     <row r="1927">
       <c r="A1927" t="str">
-        <v>Kmti9zgfwuj6q</v>
+        <v>Kmtia02g65myt</v>
       </c>
       <c r="B1927" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73772,7 +73772,7 @@
     </row>
     <row r="1928">
       <c r="A1928" t="str">
-        <v>Kmti9zgfw033o</v>
+        <v>Kmtia02g6oiwu</v>
       </c>
       <c r="B1928" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73810,7 +73810,7 @@
     </row>
     <row r="1929" xml:space="preserve">
       <c r="A1929" t="str">
-        <v>Kmti9zgfwjjey</v>
+        <v>Kmtia02g6s09i</v>
       </c>
       <c r="B1929" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73849,7 +73849,7 @@
     </row>
     <row r="1930" xml:space="preserve">
       <c r="A1930" t="str">
-        <v>Kmti9zgfwnnpn</v>
+        <v>Kmtia02g6x36c</v>
       </c>
       <c r="B1930" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73888,7 +73888,7 @@
     </row>
     <row r="1931" xml:space="preserve">
       <c r="A1931" t="str">
-        <v>Kmti9zgfw6gap</v>
+        <v>Kmtia02g6x3zw</v>
       </c>
       <c r="B1931" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73927,7 +73927,7 @@
     </row>
     <row r="1932" xml:space="preserve">
       <c r="A1932" t="str">
-        <v>Kmti9zgfwoabt</v>
+        <v>Kmtia02g6iuxz</v>
       </c>
       <c r="B1932" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73966,7 +73966,7 @@
     </row>
     <row r="1933" xml:space="preserve">
       <c r="A1933" t="str">
-        <v>Kmti9zgfww5t6</v>
+        <v>Kmtia02g6rzrv</v>
       </c>
       <c r="B1933" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74005,7 +74005,7 @@
     </row>
     <row r="1934" xml:space="preserve">
       <c r="A1934" t="str">
-        <v>Kmti9zgfwyfcf</v>
+        <v>Kmtia02g68m2x</v>
       </c>
       <c r="B1934" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74044,7 +74044,7 @@
     </row>
     <row r="1935" xml:space="preserve">
       <c r="A1935" t="str">
-        <v>Kmti9zgfw2bzn</v>
+        <v>Kmtia02g6b66o</v>
       </c>
       <c r="B1935" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -74159,7 +74159,7 @@
     </row>
     <row r="1938">
       <c r="A1938" t="str">
-        <v>Kmti9zgfwe6jk</v>
+        <v>Kmtia02g6ix1r</v>
       </c>
       <c r="B1938" t="str">
         <v>Penata Layanan Operasional</v>
@@ -74197,7 +74197,7 @@
     </row>
     <row r="1939">
       <c r="A1939" t="str">
-        <v>Kmti9zgfwnr3v</v>
+        <v>Kmtia02g6bevy</v>
       </c>
       <c r="B1939" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74235,7 +74235,7 @@
     </row>
     <row r="1940">
       <c r="A1940" t="str">
-        <v>Kmti9zgfw1j05</v>
+        <v>Kmtia02g6gfob</v>
       </c>
       <c r="B1940" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74273,7 +74273,7 @@
     </row>
     <row r="1941">
       <c r="A1941" t="str">
-        <v>Kmti9zgfw5rbq</v>
+        <v>Kmtia02g69792</v>
       </c>
       <c r="B1941" t="str">
         <v>Penata Keprotokolan*</v>
@@ -74387,7 +74387,7 @@
     </row>
     <row r="1944">
       <c r="A1944" t="str">
-        <v>Kmti9zgfwfb0h</v>
+        <v>Kmtia02g634r5</v>
       </c>
       <c r="B1944" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74425,7 +74425,7 @@
     </row>
     <row r="1945">
       <c r="A1945" t="str">
-        <v>Kmti9zgfw1aqi</v>
+        <v>Kmtia02g69to5</v>
       </c>
       <c r="B1945" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74463,7 +74463,7 @@
     </row>
     <row r="1946">
       <c r="A1946" t="str">
-        <v>Kmti9zgfwxvsl</v>
+        <v>Kmtia02g6j9iw</v>
       </c>
       <c r="B1946" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74539,7 +74539,7 @@
     </row>
     <row r="1948">
       <c r="A1948" t="str">
-        <v>Kmti9zgfwixeo</v>
+        <v>Kmtia02g6yxsa</v>
       </c>
       <c r="B1948" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74577,7 +74577,7 @@
     </row>
     <row r="1949">
       <c r="A1949" t="str">
-        <v>Kmti9zgfwztsm</v>
+        <v>Kmtia02g6c24a</v>
       </c>
       <c r="B1949" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74615,7 +74615,7 @@
     </row>
     <row r="1950">
       <c r="A1950" t="str">
-        <v>Kmti9zgfwjky0</v>
+        <v>Kmtia02g6uyjx</v>
       </c>
       <c r="B1950" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74653,7 +74653,7 @@
     </row>
     <row r="1951" xml:space="preserve">
       <c r="A1951" t="str">
-        <v>Kmti9zgfwql8b</v>
+        <v>Kmtia02g60w4t</v>
       </c>
       <c r="B1951" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -74692,7 +74692,7 @@
     </row>
     <row r="1952" xml:space="preserve">
       <c r="A1952" t="str">
-        <v>Kmti9zgfwb0ad</v>
+        <v>Kmtia02g6jo7p</v>
       </c>
       <c r="B1952" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -74731,7 +74731,7 @@
     </row>
     <row r="1953" xml:space="preserve">
       <c r="A1953" t="str">
-        <v>Kmti9zgfwr31d</v>
+        <v>Kmtia02g6zxp9</v>
       </c>
       <c r="B1953" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -74770,7 +74770,7 @@
     </row>
     <row r="1954" xml:space="preserve">
       <c r="A1954" t="str">
-        <v>Kmti9zgfwr8in</v>
+        <v>Kmtia02g64hhx</v>
       </c>
       <c r="B1954" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -74809,7 +74809,7 @@
     </row>
     <row r="1955" xml:space="preserve">
       <c r="A1955" t="str">
-        <v>Kmti9zgfwtaz2</v>
+        <v>Kmtia02g6vv0j</v>
       </c>
       <c r="B1955" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74848,7 +74848,7 @@
     </row>
     <row r="1956" xml:space="preserve">
       <c r="A1956" t="str">
-        <v>Kmti9zgfwqbyo</v>
+        <v>Kmtia02g6i9p7</v>
       </c>
       <c r="B1956" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74887,7 +74887,7 @@
     </row>
     <row r="1957" xml:space="preserve">
       <c r="A1957" t="str">
-        <v>Kmti9zgfw8hv9</v>
+        <v>Kmtia02g6t9dv</v>
       </c>
       <c r="B1957" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -75002,7 +75002,7 @@
     </row>
     <row r="1960">
       <c r="A1960" t="str">
-        <v>Kmti9zgfwct15</v>
+        <v>Kmtia02g6fz4z</v>
       </c>
       <c r="B1960" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75040,7 +75040,7 @@
     </row>
     <row r="1961">
       <c r="A1961" t="str">
-        <v>Kmti9zgfwa9hm</v>
+        <v>Kmtia02g66nrd</v>
       </c>
       <c r="B1961" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75078,7 +75078,7 @@
     </row>
     <row r="1962">
       <c r="A1962" t="str">
-        <v>Kmti9zgfwlm30</v>
+        <v>Kmtia02g6jop0</v>
       </c>
       <c r="B1962" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75116,7 +75116,7 @@
     </row>
     <row r="1963">
       <c r="A1963" t="str">
-        <v>Kmti9zgfwqbvg</v>
+        <v>Kmtia02g6klnl</v>
       </c>
       <c r="B1963" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75230,7 +75230,7 @@
     </row>
     <row r="1966">
       <c r="A1966" t="str">
-        <v>Kmti9zgfws9sa</v>
+        <v>Kmtia02g6ov06</v>
       </c>
       <c r="B1966" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75268,7 +75268,7 @@
     </row>
     <row r="1967">
       <c r="A1967" t="str">
-        <v>Kmti9zgfwash5</v>
+        <v>Kmtia02g6yv4s</v>
       </c>
       <c r="B1967" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75306,7 +75306,7 @@
     </row>
     <row r="1968">
       <c r="A1968" t="str">
-        <v>Kmti9zgfwquo0</v>
+        <v>Kmtia02g6kky4</v>
       </c>
       <c r="B1968" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75382,7 +75382,7 @@
     </row>
     <row r="1970">
       <c r="A1970" t="str">
-        <v>Kmti9zgfwup3i</v>
+        <v>Kmtia02g6cqkx</v>
       </c>
       <c r="B1970" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75420,7 +75420,7 @@
     </row>
     <row r="1971">
       <c r="A1971" t="str">
-        <v>Kmti9zgfwef5s</v>
+        <v>Kmtia02g6q0vj</v>
       </c>
       <c r="B1971" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75458,7 +75458,7 @@
     </row>
     <row r="1972">
       <c r="A1972" t="str">
-        <v>Kmti9zgfwwtwu</v>
+        <v>Kmtia02g6mn3p</v>
       </c>
       <c r="B1972" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75496,7 +75496,7 @@
     </row>
     <row r="1973" xml:space="preserve">
       <c r="A1973" t="str">
-        <v>Kmti9zgfw75iy</v>
+        <v>Kmtia02g6gtj3</v>
       </c>
       <c r="B1973" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -75535,7 +75535,7 @@
     </row>
     <row r="1974" xml:space="preserve">
       <c r="A1974" t="str">
-        <v>Kmti9zgfwt3u7</v>
+        <v>Kmtia02g61exi</v>
       </c>
       <c r="B1974" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -75574,7 +75574,7 @@
     </row>
     <row r="1975" xml:space="preserve">
       <c r="A1975" t="str">
-        <v>Kmti9zgfwetaa</v>
+        <v>Kmtia02g6dxfe</v>
       </c>
       <c r="B1975" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -75613,7 +75613,7 @@
     </row>
     <row r="1976" xml:space="preserve">
       <c r="A1976" t="str">
-        <v>Kmti9zgfwckqd</v>
+        <v>Kmtia02g6ubih</v>
       </c>
       <c r="B1976" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -75728,7 +75728,7 @@
     </row>
     <row r="1979">
       <c r="A1979" t="str">
-        <v>Kmti9zgfwvci0</v>
+        <v>Kmtia02g6t1vj</v>
       </c>
       <c r="B1979" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75766,7 +75766,7 @@
     </row>
     <row r="1980">
       <c r="A1980" t="str">
-        <v>Kmti9zgfw7psj</v>
+        <v>Kmtia02g6vjq0</v>
       </c>
       <c r="B1980" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75804,7 +75804,7 @@
     </row>
     <row r="1981">
       <c r="A1981" t="str">
-        <v>Kmti9zgfw0gqv</v>
+        <v>Kmtia02g6o1h4</v>
       </c>
       <c r="B1981" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75842,7 +75842,7 @@
     </row>
     <row r="1982">
       <c r="A1982" t="str">
-        <v>Kmti9zgfw1kr2</v>
+        <v>Kmtia02g6ufxj</v>
       </c>
       <c r="B1982" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75956,7 +75956,7 @@
     </row>
     <row r="1985">
       <c r="A1985" t="str">
-        <v>Kmti9zgfwryyh</v>
+        <v>Kmtia02g6eqwo</v>
       </c>
       <c r="B1985" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75994,7 +75994,7 @@
     </row>
     <row r="1986">
       <c r="A1986" t="str">
-        <v>Kmti9zgfwff1h</v>
+        <v>Kmtia02g656ap</v>
       </c>
       <c r="B1986" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76032,7 +76032,7 @@
     </row>
     <row r="1987">
       <c r="A1987" t="str">
-        <v>Kmti9zgfw6v3w</v>
+        <v>Kmtia02g62ruv</v>
       </c>
       <c r="B1987" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76108,7 +76108,7 @@
     </row>
     <row r="1989">
       <c r="A1989" t="str">
-        <v>Kmti9zgfw9zoj</v>
+        <v>Kmtia02g6f242</v>
       </c>
       <c r="B1989" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76146,7 +76146,7 @@
     </row>
     <row r="1990">
       <c r="A1990" t="str">
-        <v>Kmti9zgfwyso0</v>
+        <v>Kmtia02g6bh6y</v>
       </c>
       <c r="B1990" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76184,7 +76184,7 @@
     </row>
     <row r="1991">
       <c r="A1991" t="str">
-        <v>Kmti9zgfwugsv</v>
+        <v>Kmtia02g6tcdt</v>
       </c>
       <c r="B1991" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76222,7 +76222,7 @@
     </row>
     <row r="1992" xml:space="preserve">
       <c r="A1992" t="str">
-        <v>Kmti9zgfw6fhy</v>
+        <v>Kmtia02g6qn01</v>
       </c>
       <c r="B1992" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76261,7 +76261,7 @@
     </row>
     <row r="1993" xml:space="preserve">
       <c r="A1993" t="str">
-        <v>Kmti9zgfwexxz</v>
+        <v>Kmtia02g690ph</v>
       </c>
       <c r="B1993" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -76300,7 +76300,7 @@
     </row>
     <row r="1994" xml:space="preserve">
       <c r="A1994" t="str">
-        <v>Kmti9zgfwx8ig</v>
+        <v>Kmtia02g63qre</v>
       </c>
       <c r="B1994" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -76339,7 +76339,7 @@
     </row>
     <row r="1995" xml:space="preserve">
       <c r="A1995" t="str">
-        <v>Kmti9zgfwt7iw</v>
+        <v>Kmtia02g69f8a</v>
       </c>
       <c r="B1995" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -76454,7 +76454,7 @@
     </row>
     <row r="1998">
       <c r="A1998" t="str">
-        <v>Kmti9zgfw4cxt</v>
+        <v>Kmtia02g66bb0</v>
       </c>
       <c r="B1998" t="str">
         <v>Penata Layanan Operasional</v>
@@ -76492,7 +76492,7 @@
     </row>
     <row r="1999">
       <c r="A1999" t="str">
-        <v>Kmti9zgfwxx46</v>
+        <v>Kmtia02g6cgaj</v>
       </c>
       <c r="B1999" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76530,7 +76530,7 @@
     </row>
     <row r="2000">
       <c r="A2000" t="str">
-        <v>Kmti9zgfwdx4b</v>
+        <v>Kmtia02g6wnsc</v>
       </c>
       <c r="B2000" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76568,7 +76568,7 @@
     </row>
     <row r="2001">
       <c r="A2001" t="str">
-        <v>Kmti9zgfwuima</v>
+        <v>Kmtia02g6wqz2</v>
       </c>
       <c r="B2001" t="str">
         <v>Penata Keprotokolan*</v>
@@ -76682,7 +76682,7 @@
     </row>
     <row r="2004">
       <c r="A2004" t="str">
-        <v>Kmti9zgfwtjyt</v>
+        <v>Kmtia02g6vn1p</v>
       </c>
       <c r="B2004" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76720,7 +76720,7 @@
     </row>
     <row r="2005">
       <c r="A2005" t="str">
-        <v>Kmti9zgfx25jb</v>
+        <v>Kmtia02g6lyqk</v>
       </c>
       <c r="B2005" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76758,7 +76758,7 @@
     </row>
     <row r="2006">
       <c r="A2006" t="str">
-        <v>Kmti9zgfxvr5x</v>
+        <v>Kmtia02g67sbl</v>
       </c>
       <c r="B2006" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76834,7 +76834,7 @@
     </row>
     <row r="2008">
       <c r="A2008" t="str">
-        <v>Kmti9zgfx60nq</v>
+        <v>Kmtia02g6wg95</v>
       </c>
       <c r="B2008" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76872,7 +76872,7 @@
     </row>
     <row r="2009">
       <c r="A2009" t="str">
-        <v>Kmti9zgfx5fvs</v>
+        <v>Kmtia02g6tyo0</v>
       </c>
       <c r="B2009" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76910,7 +76910,7 @@
     </row>
     <row r="2010">
       <c r="A2010" t="str">
-        <v>Kmti9zgfx8g5q</v>
+        <v>Kmtia02g6j3y3</v>
       </c>
       <c r="B2010" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76948,7 +76948,7 @@
     </row>
     <row r="2011" xml:space="preserve">
       <c r="A2011" t="str">
-        <v>Kmti9zgfxshjn</v>
+        <v>Kmtia02g6ftgs</v>
       </c>
       <c r="B2011" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76987,7 +76987,7 @@
     </row>
     <row r="2012" xml:space="preserve">
       <c r="A2012" t="str">
-        <v>Kmti9zgfxrkcb</v>
+        <v>Kmtia02g6iwfs</v>
       </c>
       <c r="B2012" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77026,7 +77026,7 @@
     </row>
     <row r="2013" xml:space="preserve">
       <c r="A2013" t="str">
-        <v>Kmti9zgfx1osk</v>
+        <v>Kmtia02g6ij3d</v>
       </c>
       <c r="B2013" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77065,7 +77065,7 @@
     </row>
     <row r="2014" xml:space="preserve">
       <c r="A2014" t="str">
-        <v>Kmti9zgfx01sb</v>
+        <v>Kmtia02g61wcy</v>
       </c>
       <c r="B2014" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77180,7 +77180,7 @@
     </row>
     <row r="2017">
       <c r="A2017" t="str">
-        <v>Kmti9zgfxxidv</v>
+        <v>Kmtia02g6jmi4</v>
       </c>
       <c r="B2017" t="str">
         <v>Penata Layanan Operasional</v>
@@ -77218,7 +77218,7 @@
     </row>
     <row r="2018">
       <c r="A2018" t="str">
-        <v>Kmti9zgfxnyrh</v>
+        <v>Kmtia02g6ivzc</v>
       </c>
       <c r="B2018" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77256,7 +77256,7 @@
     </row>
     <row r="2019">
       <c r="A2019" t="str">
-        <v>Kmti9zgfxvb34</v>
+        <v>Kmtia02g65mjt</v>
       </c>
       <c r="B2019" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77294,7 +77294,7 @@
     </row>
     <row r="2020">
       <c r="A2020" t="str">
-        <v>Kmti9zgfxoj9b</v>
+        <v>Kmtia02g6f6p9</v>
       </c>
       <c r="B2020" t="str">
         <v>Penata Keprotokolan*</v>
@@ -77408,7 +77408,7 @@
     </row>
     <row r="2023">
       <c r="A2023" t="str">
-        <v>Kmti9zgfxkbvv</v>
+        <v>Kmtia02g65q8m</v>
       </c>
       <c r="B2023" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77446,7 +77446,7 @@
     </row>
     <row r="2024">
       <c r="A2024" t="str">
-        <v>Kmti9zgfxhm06</v>
+        <v>Kmtia02g62e4f</v>
       </c>
       <c r="B2024" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77484,7 +77484,7 @@
     </row>
     <row r="2025">
       <c r="A2025" t="str">
-        <v>Kmti9zgfx63dk</v>
+        <v>Kmtia02g6azc8</v>
       </c>
       <c r="B2025" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77560,7 +77560,7 @@
     </row>
     <row r="2027">
       <c r="A2027" t="str">
-        <v>Kmti9zgfxupom</v>
+        <v>Kmtia02g6w5gk</v>
       </c>
       <c r="B2027" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77598,7 +77598,7 @@
     </row>
     <row r="2028">
       <c r="A2028" t="str">
-        <v>Kmti9zgfxovu8</v>
+        <v>Kmtia02g6on0i</v>
       </c>
       <c r="B2028" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77636,7 +77636,7 @@
     </row>
     <row r="2029">
       <c r="A2029" t="str">
-        <v>Kmti9zgfxwy6o</v>
+        <v>Kmtia02g6f17q</v>
       </c>
       <c r="B2029" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77674,7 +77674,7 @@
     </row>
     <row r="2030" xml:space="preserve">
       <c r="A2030" t="str">
-        <v>Kmti9zgfxflrx</v>
+        <v>Kmtia02g6202h</v>
       </c>
       <c r="B2030" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -77713,7 +77713,7 @@
     </row>
     <row r="2031" xml:space="preserve">
       <c r="A2031" t="str">
-        <v>Kmti9zgfxc1b3</v>
+        <v>Kmtia02g6cj3j</v>
       </c>
       <c r="B2031" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77752,7 +77752,7 @@
     </row>
     <row r="2032" xml:space="preserve">
       <c r="A2032" t="str">
-        <v>Kmti9zgfxt41q</v>
+        <v>Kmtia02g6cz8d</v>
       </c>
       <c r="B2032" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77791,7 +77791,7 @@
     </row>
     <row r="2033" xml:space="preserve">
       <c r="A2033" t="str">
-        <v>Kmti9zgfxiwy8</v>
+        <v>Kmtia02g6wjtm</v>
       </c>
       <c r="B2033" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77830,7 +77830,7 @@
     </row>
     <row r="2034">
       <c r="A2034" t="str">
-        <v>Kmti9zgfxmdk5</v>
+        <v>Kmtia02g68p82</v>
       </c>
       <c r="B2034" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -77868,7 +77868,7 @@
     </row>
     <row r="2035">
       <c r="A2035" t="str">
-        <v>Kmti9zgfxvt2x</v>
+        <v>Kmtia02g6mn0u</v>
       </c>
       <c r="B2035" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -77944,7 +77944,7 @@
     </row>
     <row r="2037" xml:space="preserve">
       <c r="A2037" t="str">
-        <v>Kmti9zgfxcf89</v>
+        <v>Kmtia02g6u0rs</v>
       </c>
       <c r="B2037" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_

--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -63909,7 +63909,7 @@
     </row>
     <row r="1669">
       <c r="A1669" t="str">
-        <v>Kmtia02g5jawg</v>
+        <v>Kmti9zgfv26p3</v>
       </c>
       <c r="B1669" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -63947,7 +63947,7 @@
     </row>
     <row r="1670">
       <c r="A1670" t="str">
-        <v>Kmtia02g5naro</v>
+        <v>Kmti9zgfvwyrb</v>
       </c>
       <c r="B1670" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -63985,7 +63985,7 @@
     </row>
     <row r="1671">
       <c r="A1671" t="str">
-        <v>Kmtia02g5i9oq</v>
+        <v>Kmti9zgfvtx00</v>
       </c>
       <c r="B1671" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64023,7 +64023,7 @@
     </row>
     <row r="1672">
       <c r="A1672" t="str">
-        <v>Kmtia02g5tdaw</v>
+        <v>Kmti9zgfv4cbb</v>
       </c>
       <c r="B1672" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64061,7 +64061,7 @@
     </row>
     <row r="1673">
       <c r="A1673" t="str">
-        <v>Kmtia02g5n2em</v>
+        <v>Kmti9zgfv0cd5</v>
       </c>
       <c r="B1673" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64099,7 +64099,7 @@
     </row>
     <row r="1674">
       <c r="A1674" t="str">
-        <v>Kmtia02g5dqvc</v>
+        <v>Kmti9zgfv45ja</v>
       </c>
       <c r="B1674" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64137,7 +64137,7 @@
     </row>
     <row r="1675">
       <c r="A1675" t="str">
-        <v>Kmtia02g58etg</v>
+        <v>Kmti9zgfv5dbr</v>
       </c>
       <c r="B1675" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64175,7 +64175,7 @@
     </row>
     <row r="1676">
       <c r="A1676" t="str">
-        <v>Kmtia02g5p8rj</v>
+        <v>Kmti9zgfvpxse</v>
       </c>
       <c r="B1676" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64251,7 +64251,7 @@
     </row>
     <row r="1678">
       <c r="A1678" t="str">
-        <v>Kmtia02g5b6su</v>
+        <v>Kmti9zgfvuuv7</v>
       </c>
       <c r="B1678" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64289,7 +64289,7 @@
     </row>
     <row r="1679">
       <c r="A1679" t="str">
-        <v>Kmtia02g5fh5r</v>
+        <v>Kmti9zgfvlrdk</v>
       </c>
       <c r="B1679" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64327,7 +64327,7 @@
     </row>
     <row r="1680">
       <c r="A1680" t="str">
-        <v>Kmtia02g5kbtf</v>
+        <v>Kmti9zgfvbsli</v>
       </c>
       <c r="B1680" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64365,7 +64365,7 @@
     </row>
     <row r="1681">
       <c r="A1681" t="str">
-        <v>Kmtia02g51e7e</v>
+        <v>Kmti9zgfv70po</v>
       </c>
       <c r="B1681" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64403,7 +64403,7 @@
     </row>
     <row r="1682">
       <c r="A1682" t="str">
-        <v>Kmtia02g5377n</v>
+        <v>Kmti9zgfveogu</v>
       </c>
       <c r="B1682" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64441,7 +64441,7 @@
     </row>
     <row r="1683">
       <c r="A1683" t="str">
-        <v>Kmtia02g5j4jj</v>
+        <v>Kmti9zgfvmgxf</v>
       </c>
       <c r="B1683" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64479,7 +64479,7 @@
     </row>
     <row r="1684">
       <c r="A1684" t="str">
-        <v>Kmtia02g5kjjt</v>
+        <v>Kmti9zgfvknli</v>
       </c>
       <c r="B1684" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64517,7 +64517,7 @@
     </row>
     <row r="1685">
       <c r="A1685" t="str">
-        <v>Kmtia02g5qh5e</v>
+        <v>Kmti9zgfvprvh</v>
       </c>
       <c r="B1685" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64593,7 +64593,7 @@
     </row>
     <row r="1687">
       <c r="A1687" t="str">
-        <v>Kmtia02g5dfjp</v>
+        <v>Kmti9zgfvbb3w</v>
       </c>
       <c r="B1687" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -64631,7 +64631,7 @@
     </row>
     <row r="1688">
       <c r="A1688" t="str">
-        <v>Kmtia02g5dmi3</v>
+        <v>Kmti9zgfvdowe</v>
       </c>
       <c r="B1688" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -64669,7 +64669,7 @@
     </row>
     <row r="1689">
       <c r="A1689" t="str">
-        <v>Kmtia02g5h0s5</v>
+        <v>Kmti9zgfvapml</v>
       </c>
       <c r="B1689" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -64707,7 +64707,7 @@
     </row>
     <row r="1690">
       <c r="A1690" t="str">
-        <v>Kmtia02g5fbah</v>
+        <v>Kmti9zgfv6noy</v>
       </c>
       <c r="B1690" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -64745,7 +64745,7 @@
     </row>
     <row r="1691">
       <c r="A1691" t="str">
-        <v>Kmtia02g5kh36</v>
+        <v>Kmti9zgfvsrt3</v>
       </c>
       <c r="B1691" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -64783,7 +64783,7 @@
     </row>
     <row r="1692">
       <c r="A1692" t="str">
-        <v>Kmtia02g5xi3y</v>
+        <v>Kmti9zgfv7snw</v>
       </c>
       <c r="B1692" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64821,7 +64821,7 @@
     </row>
     <row r="1693">
       <c r="A1693" t="str">
-        <v>Kmtia02g5nhoc</v>
+        <v>Kmti9zgfvijxf</v>
       </c>
       <c r="B1693" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64859,7 +64859,7 @@
     </row>
     <row r="1694">
       <c r="A1694" t="str">
-        <v>Kmtia02g54eq6</v>
+        <v>Kmti9zgfvq82j</v>
       </c>
       <c r="B1694" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -64897,7 +64897,7 @@
     </row>
     <row r="1695">
       <c r="A1695" t="str">
-        <v>Kmtia02g5vltc</v>
+        <v>Kmti9zgfvy2bj</v>
       </c>
       <c r="B1695" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -64935,7 +64935,7 @@
     </row>
     <row r="1696">
       <c r="A1696" t="str">
-        <v>Kmtia02g505c3</v>
+        <v>Kmti9zgfv3xh5</v>
       </c>
       <c r="B1696" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -64973,7 +64973,7 @@
     </row>
     <row r="1697">
       <c r="A1697" t="str">
-        <v>Kmtia02g5vo6a</v>
+        <v>Kmti9zgfv676s</v>
       </c>
       <c r="B1697" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65087,7 +65087,7 @@
     </row>
     <row r="1700">
       <c r="A1700" t="str">
-        <v>Kmtia02g555dj</v>
+        <v>Kmti9zgfv4f31</v>
       </c>
       <c r="B1700" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65125,7 +65125,7 @@
     </row>
     <row r="1701">
       <c r="A1701" t="str">
-        <v>Kmtia02g5gq2n</v>
+        <v>Kmti9zgfvaki2</v>
       </c>
       <c r="B1701" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65163,7 +65163,7 @@
     </row>
     <row r="1702">
       <c r="A1702" t="str">
-        <v>Kmtia02g56jm2</v>
+        <v>Kmti9zgfvljfh</v>
       </c>
       <c r="B1702" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65201,7 +65201,7 @@
     </row>
     <row r="1703">
       <c r="A1703" t="str">
-        <v>Kmtia02g5ys50</v>
+        <v>Kmti9zgfvbm7i</v>
       </c>
       <c r="B1703" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65239,7 +65239,7 @@
     </row>
     <row r="1704">
       <c r="A1704" t="str">
-        <v>Kmtia02g59s2o</v>
+        <v>Kmti9zgfvw9hy</v>
       </c>
       <c r="B1704" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65277,7 +65277,7 @@
     </row>
     <row r="1705">
       <c r="A1705" t="str">
-        <v>Kmtia02g5ezsf</v>
+        <v>Kmti9zgfv2qcb</v>
       </c>
       <c r="B1705" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65315,7 +65315,7 @@
     </row>
     <row r="1706">
       <c r="A1706" t="str">
-        <v>Kmtia02g54416</v>
+        <v>Kmti9zgfvd8mh</v>
       </c>
       <c r="B1706" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65353,7 +65353,7 @@
     </row>
     <row r="1707">
       <c r="A1707" t="str">
-        <v>Kmtia02g5m43x</v>
+        <v>Kmti9zgfvc9si</v>
       </c>
       <c r="B1707" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65391,7 +65391,7 @@
     </row>
     <row r="1708">
       <c r="A1708" t="str">
-        <v>Kmtia02g58zdp</v>
+        <v>Kmti9zgfvawm4</v>
       </c>
       <c r="B1708" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -65429,7 +65429,7 @@
     </row>
     <row r="1709">
       <c r="A1709" t="str">
-        <v>Kmtia02g5um0d</v>
+        <v>Kmti9zgfvu4kv</v>
       </c>
       <c r="B1709" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -65505,7 +65505,7 @@
     </row>
     <row r="1711">
       <c r="A1711" t="str">
-        <v>Kmtia02g5dtlp</v>
+        <v>Kmti9zgfvn91l</v>
       </c>
       <c r="B1711" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -65543,7 +65543,7 @@
     </row>
     <row r="1712">
       <c r="A1712" t="str">
-        <v>Kmtia02g5ug8c</v>
+        <v>Kmti9zgfvy7ll</v>
       </c>
       <c r="B1712" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65581,7 +65581,7 @@
     </row>
     <row r="1713">
       <c r="A1713" t="str">
-        <v>Kmtia02g5azkf</v>
+        <v>Kmti9zgfv3bkw</v>
       </c>
       <c r="B1713" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65619,7 +65619,7 @@
     </row>
     <row r="1714">
       <c r="A1714" t="str">
-        <v>Kmtia02g5a723</v>
+        <v>Kmti9zgfvk58c</v>
       </c>
       <c r="B1714" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65657,7 +65657,7 @@
     </row>
     <row r="1715">
       <c r="A1715" t="str">
-        <v>Kmtia02g5570l</v>
+        <v>Kmti9zgfvg5e1</v>
       </c>
       <c r="B1715" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -65695,7 +65695,7 @@
     </row>
     <row r="1716">
       <c r="A1716" t="str">
-        <v>Kmtia02g5474m</v>
+        <v>Kmti9zgfvk469</v>
       </c>
       <c r="B1716" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -65733,7 +65733,7 @@
     </row>
     <row r="1717">
       <c r="A1717" t="str">
-        <v>Kmtia02g535lj</v>
+        <v>Kmti9zgfwkwkh</v>
       </c>
       <c r="B1717" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -65771,7 +65771,7 @@
     </row>
     <row r="1718">
       <c r="A1718" t="str">
-        <v>Kmtia02g58dyt</v>
+        <v>Kmti9zgfwsx0u</v>
       </c>
       <c r="B1718" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -65847,7 +65847,7 @@
     </row>
     <row r="1720">
       <c r="A1720" t="str">
-        <v>Kmtia02g5g8of</v>
+        <v>Kmti9zgfwr6bz</v>
       </c>
       <c r="B1720" t="str">
         <v>Penata Layanan Operasional</v>
@@ -65885,7 +65885,7 @@
     </row>
     <row r="1721">
       <c r="A1721" t="str">
-        <v>Kmtia02g57dow</v>
+        <v>Kmti9zgfwgsxa</v>
       </c>
       <c r="B1721" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -65923,7 +65923,7 @@
     </row>
     <row r="1722">
       <c r="A1722" t="str">
-        <v>Kmtia02g5v18i</v>
+        <v>Kmti9zgfw4dul</v>
       </c>
       <c r="B1722" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -65961,7 +65961,7 @@
     </row>
     <row r="1723">
       <c r="A1723" t="str">
-        <v>Kmtia02g52jmt</v>
+        <v>Kmti9zgfwowkd</v>
       </c>
       <c r="B1723" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -65999,7 +65999,7 @@
     </row>
     <row r="1724">
       <c r="A1724" t="str">
-        <v>Kmtia02g5ews8</v>
+        <v>Kmti9zgfwsb26</v>
       </c>
       <c r="B1724" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66037,7 +66037,7 @@
     </row>
     <row r="1725">
       <c r="A1725" t="str">
-        <v>Kmtia02g5cesx</v>
+        <v>Kmti9zgfwaza4</v>
       </c>
       <c r="B1725" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66075,7 +66075,7 @@
     </row>
     <row r="1726">
       <c r="A1726" t="str">
-        <v>Kmtia02g5n8zw</v>
+        <v>Kmti9zgfwure0</v>
       </c>
       <c r="B1726" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66113,7 +66113,7 @@
     </row>
     <row r="1727">
       <c r="A1727" t="str">
-        <v>Kmtia02g552t4</v>
+        <v>Kmti9zgfwsb5n</v>
       </c>
       <c r="B1727" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66189,7 +66189,7 @@
     </row>
     <row r="1729">
       <c r="A1729" t="str">
-        <v>Kmtia02g504v6</v>
+        <v>Kmti9zgfw36rk</v>
       </c>
       <c r="B1729" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66227,7 +66227,7 @@
     </row>
     <row r="1730">
       <c r="A1730" t="str">
-        <v>Kmtia02g5brv4</v>
+        <v>Kmti9zgfw3xp6</v>
       </c>
       <c r="B1730" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66265,7 +66265,7 @@
     </row>
     <row r="1731">
       <c r="A1731" t="str">
-        <v>Kmtia02g5gq6m</v>
+        <v>Kmti9zgfwfvik</v>
       </c>
       <c r="B1731" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66303,7 +66303,7 @@
     </row>
     <row r="1732">
       <c r="A1732" t="str">
-        <v>Kmtia02g5v3hn</v>
+        <v>Kmti9zgfw4593</v>
       </c>
       <c r="B1732" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66341,7 +66341,7 @@
     </row>
     <row r="1733">
       <c r="A1733" t="str">
-        <v>Kmtia02g5sieb</v>
+        <v>Kmti9zgfw4kki</v>
       </c>
       <c r="B1733" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66379,7 +66379,7 @@
     </row>
     <row r="1734">
       <c r="A1734" t="str">
-        <v>Kmtia02g5lvtj</v>
+        <v>Kmti9zgfw72q9</v>
       </c>
       <c r="B1734" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66417,7 +66417,7 @@
     </row>
     <row r="1735">
       <c r="A1735" t="str">
-        <v>Kmtia02g5r2ur</v>
+        <v>Kmti9zgfw0hmg</v>
       </c>
       <c r="B1735" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66455,7 +66455,7 @@
     </row>
     <row r="1736">
       <c r="A1736" t="str">
-        <v>Kmtia02g5oaqr</v>
+        <v>Kmti9zgfw9jf7</v>
       </c>
       <c r="B1736" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66493,7 +66493,7 @@
     </row>
     <row r="1737">
       <c r="A1737" t="str">
-        <v>Kmtia02g5n333</v>
+        <v>Kmti9zgfw4y3j</v>
       </c>
       <c r="B1737" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -66531,7 +66531,7 @@
     </row>
     <row r="1738">
       <c r="A1738" t="str">
-        <v>Kmtia02g57e65</v>
+        <v>Kmti9zgfwto78</v>
       </c>
       <c r="B1738" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -66569,7 +66569,7 @@
     </row>
     <row r="1739">
       <c r="A1739" t="str">
-        <v>Kmtia02g5c10j</v>
+        <v>Kmti9zgfw6xgk</v>
       </c>
       <c r="B1739" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -66607,7 +66607,7 @@
     </row>
     <row r="1740">
       <c r="A1740" t="str">
-        <v>Kmtia02g57618</v>
+        <v>Kmti9zgfw57jm</v>
       </c>
       <c r="B1740" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -66645,7 +66645,7 @@
     </row>
     <row r="1741">
       <c r="A1741" t="str">
-        <v>Kmtia02g5bfnx</v>
+        <v>Kmti9zgfwlksp</v>
       </c>
       <c r="B1741" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -66683,7 +66683,7 @@
     </row>
     <row r="1742">
       <c r="A1742" t="str">
-        <v>Kmtia02g5og4z</v>
+        <v>Kmti9zgfwiets</v>
       </c>
       <c r="B1742" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -66721,7 +66721,7 @@
     </row>
     <row r="1743">
       <c r="A1743" t="str">
-        <v>Kmtia02g57n1z</v>
+        <v>Kmti9zgfwmd71</v>
       </c>
       <c r="B1743" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -66835,7 +66835,7 @@
     </row>
     <row r="1746">
       <c r="A1746" t="str">
-        <v>Kmtia02g5uor5</v>
+        <v>Kmti9zgfwph3s</v>
       </c>
       <c r="B1746" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -66873,7 +66873,7 @@
     </row>
     <row r="1747">
       <c r="A1747" t="str">
-        <v>Kmtia02g5kucy</v>
+        <v>Kmti9zgfwkppc</v>
       </c>
       <c r="B1747" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -66911,7 +66911,7 @@
     </row>
     <row r="1748">
       <c r="A1748" t="str">
-        <v>Kmtia02g5quiy</v>
+        <v>Kmti9zgfw0cxv</v>
       </c>
       <c r="B1748" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -66949,7 +66949,7 @@
     </row>
     <row r="1749" xml:space="preserve">
       <c r="A1749" t="str">
-        <v>Kmtia02g5rqqv</v>
+        <v>Kmti9zgfw6ykh</v>
       </c>
       <c r="B1749" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -66988,7 +66988,7 @@
     </row>
     <row r="1750">
       <c r="A1750" t="str">
-        <v>Kmtia02g5y05f</v>
+        <v>Kmti9zgfwrkt3</v>
       </c>
       <c r="B1750" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67064,7 +67064,7 @@
     </row>
     <row r="1752">
       <c r="A1752" t="str">
-        <v>Kmtia02g5mc4x</v>
+        <v>Kmti9zgfw2txy</v>
       </c>
       <c r="B1752" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67102,7 +67102,7 @@
     </row>
     <row r="1753">
       <c r="A1753" t="str">
-        <v>Kmtia02g5ooyp</v>
+        <v>Kmti9zgfw3olu</v>
       </c>
       <c r="B1753" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67140,7 +67140,7 @@
     </row>
     <row r="1754">
       <c r="A1754" t="str">
-        <v>Kmtia02g5f59f</v>
+        <v>Kmti9zgfwyrgw</v>
       </c>
       <c r="B1754" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67178,7 +67178,7 @@
     </row>
     <row r="1755" xml:space="preserve">
       <c r="A1755" t="str">
-        <v>Kmtia02g5ie9e</v>
+        <v>Kmti9zgfw5xjt</v>
       </c>
       <c r="B1755" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67217,7 +67217,7 @@
     </row>
     <row r="1756" xml:space="preserve">
       <c r="A1756" t="str">
-        <v>Kmtia02g50k5a</v>
+        <v>Kmti9zgfwukt5</v>
       </c>
       <c r="B1756" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67256,7 +67256,7 @@
     </row>
     <row r="1757">
       <c r="A1757" t="str">
-        <v>Kmtia02g5qac8</v>
+        <v>Kmti9zgfwffgf</v>
       </c>
       <c r="B1757" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67294,7 +67294,7 @@
     </row>
     <row r="1758" xml:space="preserve">
       <c r="A1758" t="str">
-        <v>Kmtia02g5hnhr</v>
+        <v>Kmti9zgfwfrt0</v>
       </c>
       <c r="B1758" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67333,7 +67333,7 @@
     </row>
     <row r="1759" xml:space="preserve">
       <c r="A1759" t="str">
-        <v>Kmtia02g5ow1a</v>
+        <v>Kmti9zgfwqx35</v>
       </c>
       <c r="B1759" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67410,7 +67410,7 @@
     </row>
     <row r="1761">
       <c r="A1761" t="str">
-        <v>Kmtia02g504rl</v>
+        <v>Kmti9zgfwp79t</v>
       </c>
       <c r="B1761" t="str">
         <v>Penata Layanan Operasional</v>
@@ -67448,7 +67448,7 @@
     </row>
     <row r="1762">
       <c r="A1762" t="str">
-        <v>Kmtia02g5z7ob</v>
+        <v>Kmti9zgfw5w0d</v>
       </c>
       <c r="B1762" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -67486,7 +67486,7 @@
     </row>
     <row r="1763">
       <c r="A1763" t="str">
-        <v>Kmtia02g56yb1</v>
+        <v>Kmti9zgfwwc7b</v>
       </c>
       <c r="B1763" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -67524,7 +67524,7 @@
     </row>
     <row r="1764" xml:space="preserve">
       <c r="A1764" t="str">
-        <v>Kmtia02g5l8u6</v>
+        <v>Kmti9zgfwgmis</v>
       </c>
       <c r="B1764" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -67563,7 +67563,7 @@
     </row>
     <row r="1765" xml:space="preserve">
       <c r="A1765" t="str">
-        <v>Kmtia02g5y7sd</v>
+        <v>Kmti9zgfwqfcn</v>
       </c>
       <c r="B1765" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -67602,7 +67602,7 @@
     </row>
     <row r="1766">
       <c r="A1766" t="str">
-        <v>Kmtia02g5iaic</v>
+        <v>Kmti9zgfw8fwd</v>
       </c>
       <c r="B1766" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67640,7 +67640,7 @@
     </row>
     <row r="1767" xml:space="preserve">
       <c r="A1767" t="str">
-        <v>Kmtia02g59bdb</v>
+        <v>Kmti9zgfw3a03</v>
       </c>
       <c r="B1767" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Mahir/_x000d_
@@ -67679,7 +67679,7 @@
     </row>
     <row r="1768" xml:space="preserve">
       <c r="A1768" t="str">
-        <v>Kmtia02g5jhar</v>
+        <v>Kmti9zgfwnd9w</v>
       </c>
       <c r="B1768" t="str" xml:space="preserve">
         <v xml:space="preserve">Pranata Keuangan APBN Terampil/_x000d_
@@ -67718,7 +67718,7 @@
     </row>
     <row r="1769">
       <c r="A1769" t="str">
-        <v>Kmtia02g5otlq</v>
+        <v>Kmti9zgfwg7p6</v>
       </c>
       <c r="B1769" t="str">
         <v>Analis Anggaran Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -67756,7 +67756,7 @@
     </row>
     <row r="1770">
       <c r="A1770" t="str">
-        <v>Kmtia02g50c5p</v>
+        <v>Kmti9zgfwlxww</v>
       </c>
       <c r="B1770" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -67794,7 +67794,7 @@
     </row>
     <row r="1771">
       <c r="A1771" t="str">
-        <v>Kmtia02g5fxu8</v>
+        <v>Kmti9zgfweso7</v>
       </c>
       <c r="B1771" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -67832,7 +67832,7 @@
     </row>
     <row r="1772">
       <c r="A1772" t="str">
-        <v>Kmtia02g51840</v>
+        <v>Kmti9zgfwya1b</v>
       </c>
       <c r="B1772" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Ahli Muda</v>
@@ -67870,7 +67870,7 @@
     </row>
     <row r="1773">
       <c r="A1773" t="str">
-        <v>Kmtia02g54482</v>
+        <v>Kmti9zgfwol0w</v>
       </c>
       <c r="B1773" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -67908,7 +67908,7 @@
     </row>
     <row r="1774">
       <c r="A1774" t="str">
-        <v>Kmtia02g5x7dm</v>
+        <v>Kmti9zgfw4mzw</v>
       </c>
       <c r="B1774" t="str">
         <v>Pranata Keuangan APBN Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -67946,7 +67946,7 @@
     </row>
     <row r="1775">
       <c r="A1775" t="str">
-        <v>Kmtia02g56c0k</v>
+        <v>Kmti9zgfwb5sn</v>
       </c>
       <c r="B1775" t="str">
         <v>Pranata Keuangan APBN Mahir/Pengawas Keuangan Negara Mahir</v>
@@ -67984,7 +67984,7 @@
     </row>
     <row r="1776">
       <c r="A1776" t="str">
-        <v>Kmtia02g57l4j</v>
+        <v>Kmti9zgfw42g7</v>
       </c>
       <c r="B1776" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -68098,7 +68098,7 @@
     </row>
     <row r="1779">
       <c r="A1779" t="str">
-        <v>Kmtia02g5ijsg</v>
+        <v>Kmti9zgfwgvaq</v>
       </c>
       <c r="B1779" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68136,7 +68136,7 @@
     </row>
     <row r="1780">
       <c r="A1780" t="str">
-        <v>Kmtia02g5q6zy</v>
+        <v>Kmti9zgfw117s</v>
       </c>
       <c r="B1780" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68174,7 +68174,7 @@
     </row>
     <row r="1781">
       <c r="A1781" t="str">
-        <v>Kmtia02g51nq2</v>
+        <v>Kmti9zgfwc6hl</v>
       </c>
       <c r="B1781" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68250,7 +68250,7 @@
     </row>
     <row r="1783">
       <c r="A1783" t="str">
-        <v>Kmtia02g5mcdz</v>
+        <v>Kmti9zgfwprkg</v>
       </c>
       <c r="B1783" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68288,7 +68288,7 @@
     </row>
     <row r="1784">
       <c r="A1784" t="str">
-        <v>Kmtia02g57aq0</v>
+        <v>Kmti9zgfwlhys</v>
       </c>
       <c r="B1784" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68326,7 +68326,7 @@
     </row>
     <row r="1785">
       <c r="A1785" t="str">
-        <v>Kmtia02g548bq</v>
+        <v>Kmti9zgfwkuna</v>
       </c>
       <c r="B1785" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68364,7 +68364,7 @@
     </row>
     <row r="1786">
       <c r="A1786" t="str">
-        <v>Kmtia02g5em6c</v>
+        <v>Kmti9zgfwluh2</v>
       </c>
       <c r="B1786" t="str">
         <v>Penata Keprotokolan*</v>
@@ -68402,7 +68402,7 @@
     </row>
     <row r="1787">
       <c r="A1787" t="str">
-        <v>Kmtia02g5wbt0</v>
+        <v>Kmti9zgfwg7ii</v>
       </c>
       <c r="B1787" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68440,7 +68440,7 @@
     </row>
     <row r="1788">
       <c r="A1788" t="str">
-        <v>Kmtia02g5tsuz</v>
+        <v>Kmti9zgfwzqqc</v>
       </c>
       <c r="B1788" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68478,7 +68478,7 @@
     </row>
     <row r="1789">
       <c r="A1789" t="str">
-        <v>Kmtia02g5zee5</v>
+        <v>Kmti9zgfwg8vo</v>
       </c>
       <c r="B1789" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68516,7 +68516,7 @@
     </row>
     <row r="1790">
       <c r="A1790" t="str">
-        <v>Kmtia02g5bzk7</v>
+        <v>Kmti9zgfw6kia</v>
       </c>
       <c r="B1790" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68592,7 +68592,7 @@
     </row>
     <row r="1792">
       <c r="A1792" t="str">
-        <v>Kmtia02g5q7o3</v>
+        <v>Kmti9zgfwvs7f</v>
       </c>
       <c r="B1792" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68630,7 +68630,7 @@
     </row>
     <row r="1793">
       <c r="A1793" t="str">
-        <v>Kmtia02g5t885</v>
+        <v>Kmti9zgfwinbd</v>
       </c>
       <c r="B1793" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -68668,7 +68668,7 @@
     </row>
     <row r="1794">
       <c r="A1794" t="str">
-        <v>Kmtia02g541cu</v>
+        <v>Kmti9zgfwi2a5</v>
       </c>
       <c r="B1794" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -68706,7 +68706,7 @@
     </row>
     <row r="1795">
       <c r="A1795" t="str">
-        <v>Kmtia02g57jxa</v>
+        <v>Kmti9zgfw1s7e</v>
       </c>
       <c r="B1795" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -68744,7 +68744,7 @@
     </row>
     <row r="1796">
       <c r="A1796" t="str">
-        <v>Kmtia02g5wphh</v>
+        <v>Kmti9zgfwtdxj</v>
       </c>
       <c r="B1796" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -68782,7 +68782,7 @@
     </row>
     <row r="1797">
       <c r="A1797" t="str">
-        <v>Kmtia02g5f8fz</v>
+        <v>Kmti9zgfw2ch2</v>
       </c>
       <c r="B1797" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -68820,7 +68820,7 @@
     </row>
     <row r="1798">
       <c r="A1798" t="str">
-        <v>Kmtia02g5hyc0</v>
+        <v>Kmti9zgfwp942</v>
       </c>
       <c r="B1798" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -68858,7 +68858,7 @@
     </row>
     <row r="1799">
       <c r="A1799" t="str">
-        <v>Kmtia02g5lelq</v>
+        <v>Kmti9zgfw2ttx</v>
       </c>
       <c r="B1799" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -68934,7 +68934,7 @@
     </row>
     <row r="1801">
       <c r="A1801" t="str">
-        <v>Kmtia02g5i80r</v>
+        <v>Kmti9zgfw74gb</v>
       </c>
       <c r="B1801" t="str">
         <v>Penata Layanan Operasional</v>
@@ -68972,7 +68972,7 @@
     </row>
     <row r="1802">
       <c r="A1802" t="str">
-        <v>Kmtia02g5mz8o</v>
+        <v>Kmti9zgfwbjjg</v>
       </c>
       <c r="B1802" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69010,7 +69010,7 @@
     </row>
     <row r="1803">
       <c r="A1803" t="str">
-        <v>Kmtia02g59ck3</v>
+        <v>Kmti9zgfwrqwo</v>
       </c>
       <c r="B1803" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69048,7 +69048,7 @@
     </row>
     <row r="1804">
       <c r="A1804" t="str">
-        <v>Kmtia02g5851z</v>
+        <v>Kmti9zgfwhexu</v>
       </c>
       <c r="B1804" t="str">
         <v>Penata Keprotokolan*</v>
@@ -69086,7 +69086,7 @@
     </row>
     <row r="1805">
       <c r="A1805" t="str">
-        <v>Kmtia02g528yh</v>
+        <v>Kmti9zgfwdna0</v>
       </c>
       <c r="B1805" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -69124,7 +69124,7 @@
     </row>
     <row r="1806">
       <c r="A1806" t="str">
-        <v>Kmtia02g5g3cc</v>
+        <v>Kmti9zgfwxez5</v>
       </c>
       <c r="B1806" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -69162,7 +69162,7 @@
     </row>
     <row r="1807">
       <c r="A1807" t="str">
-        <v>Kmtia02g5qi08</v>
+        <v>Kmti9zgfwy5z6</v>
       </c>
       <c r="B1807" t="str">
         <v>Arsiparis Penyelia</v>
@@ -69200,7 +69200,7 @@
     </row>
     <row r="1808">
       <c r="A1808" t="str">
-        <v>Kmtia02g5tf66</v>
+        <v>Kmti9zgfw5cy1</v>
       </c>
       <c r="B1808" t="str">
         <v>Arsiparis Mahir</v>
@@ -69238,7 +69238,7 @@
     </row>
     <row r="1809">
       <c r="A1809" t="str">
-        <v>Kmtia02g5en5p</v>
+        <v>Kmti9zgfweff0</v>
       </c>
       <c r="B1809" t="str">
         <v>Arsiparis Terampil</v>
@@ -69276,7 +69276,7 @@
     </row>
     <row r="1810">
       <c r="A1810" t="str">
-        <v>Kmtia02g54v75</v>
+        <v>Kmti9zgfwfxcr</v>
       </c>
       <c r="B1810" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -69314,7 +69314,7 @@
     </row>
     <row r="1811">
       <c r="A1811" t="str">
-        <v>Kmtia02g59puy</v>
+        <v>Kmti9zgfwj2pm</v>
       </c>
       <c r="B1811" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69352,7 +69352,7 @@
     </row>
     <row r="1812">
       <c r="A1812" t="str">
-        <v>Kmtia02g5y4cv</v>
+        <v>Kmti9zgfwe8ra</v>
       </c>
       <c r="B1812" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -69390,7 +69390,7 @@
     </row>
     <row r="1813">
       <c r="A1813" t="str">
-        <v>Kmtia02g5vd0v</v>
+        <v>Kmti9zgfwaj0c</v>
       </c>
       <c r="B1813" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -69428,7 +69428,7 @@
     </row>
     <row r="1814">
       <c r="A1814" t="str">
-        <v>Kmtia02g5u2cs</v>
+        <v>Kmti9zgfwvo49</v>
       </c>
       <c r="B1814" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -69542,7 +69542,7 @@
     </row>
     <row r="1817">
       <c r="A1817" t="str">
-        <v>Kmtia02g5fwmp</v>
+        <v>Kmti9zgfwjqwo</v>
       </c>
       <c r="B1817" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69580,7 +69580,7 @@
     </row>
     <row r="1818">
       <c r="A1818" t="str">
-        <v>Kmtia02g5mhs7</v>
+        <v>Kmti9zgfwem78</v>
       </c>
       <c r="B1818" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69618,7 +69618,7 @@
     </row>
     <row r="1819">
       <c r="A1819" t="str">
-        <v>Kmtia02g58hq9</v>
+        <v>Kmti9zgfw48hj</v>
       </c>
       <c r="B1819" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69656,7 +69656,7 @@
     </row>
     <row r="1820">
       <c r="A1820" t="str">
-        <v>Kmtia02g5ucy1</v>
+        <v>Kmti9zgfwyiy6</v>
       </c>
       <c r="B1820" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69694,7 +69694,7 @@
     </row>
     <row r="1821">
       <c r="A1821" t="str">
-        <v>Kmtia02g57urv</v>
+        <v>Kmti9zgfw4rmo</v>
       </c>
       <c r="B1821" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69732,7 +69732,7 @@
     </row>
     <row r="1822">
       <c r="A1822" t="str">
-        <v>Kmtia02g570vk</v>
+        <v>Kmti9zgfwsdmd</v>
       </c>
       <c r="B1822" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -69808,7 +69808,7 @@
     </row>
     <row r="1824">
       <c r="A1824" t="str">
-        <v>Kmtia02g5dgnc</v>
+        <v>Kmti9zgfwhaic</v>
       </c>
       <c r="B1824" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -69846,7 +69846,7 @@
     </row>
     <row r="1825">
       <c r="A1825" t="str">
-        <v>Kmtia02g51x9j</v>
+        <v>Kmti9zgfwz66l</v>
       </c>
       <c r="B1825" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -69884,7 +69884,7 @@
     </row>
     <row r="1826">
       <c r="A1826" t="str">
-        <v>Kmtia02g58aiv</v>
+        <v>Kmti9zgfw2y2o</v>
       </c>
       <c r="B1826" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -69922,7 +69922,7 @@
     </row>
     <row r="1827">
       <c r="A1827" t="str">
-        <v>Kmtia02g5094l</v>
+        <v>Kmti9zgfwldzg</v>
       </c>
       <c r="B1827" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -69960,7 +69960,7 @@
     </row>
     <row r="1828">
       <c r="A1828" t="str">
-        <v>Kmtia02g5d1t4</v>
+        <v>Kmti9zgfwln2m</v>
       </c>
       <c r="B1828" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -69998,7 +69998,7 @@
     </row>
     <row r="1829">
       <c r="A1829" t="str">
-        <v>Kmtia02g57duk</v>
+        <v>Kmti9zgfw4fjz</v>
       </c>
       <c r="B1829" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70036,7 +70036,7 @@
     </row>
     <row r="1830">
       <c r="A1830" t="str">
-        <v>Kmtia02g5awdb</v>
+        <v>Kmti9zgfwrcj7</v>
       </c>
       <c r="B1830" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70112,7 +70112,7 @@
     </row>
     <row r="1832">
       <c r="A1832" t="str">
-        <v>Kmtia02g506h5</v>
+        <v>Kmti9zgfwwsyh</v>
       </c>
       <c r="B1832" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -70150,7 +70150,7 @@
     </row>
     <row r="1833">
       <c r="A1833" t="str">
-        <v>Kmtia02g5tgav</v>
+        <v>Kmti9zgfwtkvi</v>
       </c>
       <c r="B1833" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70188,7 +70188,7 @@
     </row>
     <row r="1834">
       <c r="A1834" t="str">
-        <v>Kmtia02g53yk1</v>
+        <v>Kmti9zgfwv418</v>
       </c>
       <c r="B1834" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70226,7 +70226,7 @@
     </row>
     <row r="1835">
       <c r="A1835" t="str">
-        <v>Kmtia02g5bnta</v>
+        <v>Kmti9zgfw5nyi</v>
       </c>
       <c r="B1835" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70264,7 +70264,7 @@
     </row>
     <row r="1836">
       <c r="A1836" t="str">
-        <v>Kmtia02g50mv0</v>
+        <v>Kmti9zgfw36v4</v>
       </c>
       <c r="B1836" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70302,7 +70302,7 @@
     </row>
     <row r="1837">
       <c r="A1837" t="str">
-        <v>Kmtia02g5en1j</v>
+        <v>Kmti9zgfwrhj9</v>
       </c>
       <c r="B1837" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70340,7 +70340,7 @@
     </row>
     <row r="1838">
       <c r="A1838" t="str">
-        <v>Kmtia02g5wgv9</v>
+        <v>Kmti9zgfw9p5y</v>
       </c>
       <c r="B1838" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70378,7 +70378,7 @@
     </row>
     <row r="1839">
       <c r="A1839" t="str">
-        <v>Kmtia02g52l3u</v>
+        <v>Kmti9zgfw7yh8</v>
       </c>
       <c r="B1839" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -70416,7 +70416,7 @@
     </row>
     <row r="1840">
       <c r="A1840" t="str">
-        <v>Kmtia02g5sr20</v>
+        <v>Kmti9zgfwytqd</v>
       </c>
       <c r="B1840" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -70454,7 +70454,7 @@
     </row>
     <row r="1841">
       <c r="A1841" t="str">
-        <v>Kmtia02g59eyb</v>
+        <v>Kmti9zgfwidk1</v>
       </c>
       <c r="B1841" t="str">
         <v xml:space="preserve">Pengawas Keuangan Negara Mahir </v>
@@ -70492,7 +70492,7 @@
     </row>
     <row r="1842">
       <c r="A1842" t="str">
-        <v>Kmtia02g5y8fb</v>
+        <v>Kmti9zgfw5qi3</v>
       </c>
       <c r="B1842" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -70568,7 +70568,7 @@
     </row>
     <row r="1844">
       <c r="A1844" t="str">
-        <v>Kmtia02g5mx3q</v>
+        <v>Kmti9zgfw7bm4</v>
       </c>
       <c r="B1844" t="str">
         <v>Penata Layanan Operasional</v>
@@ -70606,7 +70606,7 @@
     </row>
     <row r="1845">
       <c r="A1845" t="str">
-        <v>Kmtia02g5gv4c</v>
+        <v>Kmti9zgfwsvbt</v>
       </c>
       <c r="B1845" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -70644,7 +70644,7 @@
     </row>
     <row r="1846">
       <c r="A1846" t="str">
-        <v>Kmtia02g5mlx1</v>
+        <v>Kmti9zgfwg9f7</v>
       </c>
       <c r="B1846" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -70682,7 +70682,7 @@
     </row>
     <row r="1847">
       <c r="A1847" t="str">
-        <v>Kmtia02g52bdq</v>
+        <v>Kmti9zgfwwt6t</v>
       </c>
       <c r="B1847" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -70720,7 +70720,7 @@
     </row>
     <row r="1848">
       <c r="A1848" t="str">
-        <v>Kmtia02g5seaj</v>
+        <v>Kmti9zgfwv7iq</v>
       </c>
       <c r="B1848" t="str">
         <v>Pranata Humas Ahli Pertama</v>
@@ -70758,7 +70758,7 @@
     </row>
     <row r="1849">
       <c r="A1849" t="str">
-        <v>Kmtia02g5blr7</v>
+        <v>Kmti9zgfwdkza</v>
       </c>
       <c r="B1849" t="str">
         <v>Pranata Humas Penyelia</v>
@@ -70796,7 +70796,7 @@
     </row>
     <row r="1850">
       <c r="A1850" t="str">
-        <v>Kmtia02g5p73l</v>
+        <v>Kmti9zgfwko74</v>
       </c>
       <c r="B1850" t="str">
         <v>Pranata Humas Mahir</v>
@@ -70834,7 +70834,7 @@
     </row>
     <row r="1851">
       <c r="A1851" t="str">
-        <v>Kmtia02g5zppp</v>
+        <v>Kmti9zgfwifm5</v>
       </c>
       <c r="B1851" t="str">
         <v>Pranata Humas Terampil</v>
@@ -70872,7 +70872,7 @@
     </row>
     <row r="1852">
       <c r="A1852" t="str">
-        <v>Kmtia02g5evqm</v>
+        <v>Kmti9zgfw8us7</v>
       </c>
       <c r="B1852" t="str">
         <v>Pustakawan Ahli Muda</v>
@@ -70910,7 +70910,7 @@
     </row>
     <row r="1853">
       <c r="A1853" t="str">
-        <v>Kmtia02g5sk81</v>
+        <v>Kmti9zgfwbumm</v>
       </c>
       <c r="B1853" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -70948,7 +70948,7 @@
     </row>
     <row r="1854">
       <c r="A1854" t="str">
-        <v>Kmtia02g5847t</v>
+        <v>Kmti9zgfw2iij</v>
       </c>
       <c r="B1854" t="str">
         <v>Pustakawan Penyelia</v>
@@ -70986,7 +70986,7 @@
     </row>
     <row r="1855">
       <c r="A1855" t="str">
-        <v>Kmtia02g5esxu</v>
+        <v>Kmti9zgfwyyps</v>
       </c>
       <c r="B1855" t="str">
         <v>Pustakawan Mahir</v>
@@ -71024,7 +71024,7 @@
     </row>
     <row r="1856">
       <c r="A1856" t="str">
-        <v>Kmtia02g5xv9d</v>
+        <v>Kmti9zgfwjo3x</v>
       </c>
       <c r="B1856" t="str">
         <v>Pustakawan Terampil</v>
@@ -71138,7 +71138,7 @@
     </row>
     <row r="1859">
       <c r="A1859" t="str">
-        <v>Kmtia02g5751t</v>
+        <v>Kmti9zgfw0xyq</v>
       </c>
       <c r="B1859" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71176,7 +71176,7 @@
     </row>
     <row r="1860">
       <c r="A1860" t="str">
-        <v>Kmtia02g5n6is</v>
+        <v>Kmti9zgfwe6ho</v>
       </c>
       <c r="B1860" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71214,7 +71214,7 @@
     </row>
     <row r="1861">
       <c r="A1861" t="str">
-        <v>Kmtia02g5jo1h</v>
+        <v>Kmti9zgfwfgw6</v>
       </c>
       <c r="B1861" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71252,7 +71252,7 @@
     </row>
     <row r="1862">
       <c r="A1862" t="str">
-        <v>Kmtia02g5fhzw</v>
+        <v>Kmti9zgfwla25</v>
       </c>
       <c r="B1862" t="str">
         <v>Penata Keprotokolan*</v>
@@ -71366,7 +71366,7 @@
     </row>
     <row r="1865">
       <c r="A1865" t="str">
-        <v>Kmtia02g52apj</v>
+        <v>Kmti9zgfw2nin</v>
       </c>
       <c r="B1865" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71404,7 +71404,7 @@
     </row>
     <row r="1866">
       <c r="A1866" t="str">
-        <v>Kmtia02g51nt1</v>
+        <v>Kmti9zgfw7zit</v>
       </c>
       <c r="B1866" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71442,7 +71442,7 @@
     </row>
     <row r="1867">
       <c r="A1867" t="str">
-        <v>Kmtia02g543v3</v>
+        <v>Kmti9zgfwii39</v>
       </c>
       <c r="B1867" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71518,7 +71518,7 @@
     </row>
     <row r="1869">
       <c r="A1869" t="str">
-        <v>Kmtia02g5ufdv</v>
+        <v>Kmti9zgfwzuwq</v>
       </c>
       <c r="B1869" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -71556,7 +71556,7 @@
     </row>
     <row r="1870">
       <c r="A1870" t="str">
-        <v>Kmtia02g5h0pq</v>
+        <v>Kmti9zgfwlnqc</v>
       </c>
       <c r="B1870" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71594,7 +71594,7 @@
     </row>
     <row r="1871">
       <c r="A1871" t="str">
-        <v>Kmtia02g52i5g</v>
+        <v>Kmti9zgfwp5sv</v>
       </c>
       <c r="B1871" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71632,7 +71632,7 @@
     </row>
     <row r="1872" xml:space="preserve">
       <c r="A1872" t="str">
-        <v>Kmtia02g5arra</v>
+        <v>Kmti9zgfw0ds4</v>
       </c>
       <c r="B1872" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -71671,7 +71671,7 @@
     </row>
     <row r="1873" xml:space="preserve">
       <c r="A1873" t="str">
-        <v>Kmtia02g5vqpj</v>
+        <v>Kmti9zgfwa6fc</v>
       </c>
       <c r="B1873" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -71710,7 +71710,7 @@
     </row>
     <row r="1874" xml:space="preserve">
       <c r="A1874" t="str">
-        <v>Kmtia02g5dw28</v>
+        <v>Kmti9zgfwajv1</v>
       </c>
       <c r="B1874" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -71749,7 +71749,7 @@
     </row>
     <row r="1875" xml:space="preserve">
       <c r="A1875" t="str">
-        <v>Kmtia02g50kef</v>
+        <v>Kmti9zgfwc10z</v>
       </c>
       <c r="B1875" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -71864,7 +71864,7 @@
     </row>
     <row r="1878">
       <c r="A1878" t="str">
-        <v>Kmtia02g5xkth</v>
+        <v>Kmti9zgfwygzd</v>
       </c>
       <c r="B1878" t="str">
         <v>Penata Layanan Operasional</v>
@@ -71902,7 +71902,7 @@
     </row>
     <row r="1879">
       <c r="A1879" t="str">
-        <v>Kmtia02g5w1p4</v>
+        <v>Kmti9zgfwoltt</v>
       </c>
       <c r="B1879" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -71940,7 +71940,7 @@
     </row>
     <row r="1880">
       <c r="A1880" t="str">
-        <v>Kmtia02g5emrb</v>
+        <v>Kmti9zgfwqkai</v>
       </c>
       <c r="B1880" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -71978,7 +71978,7 @@
     </row>
     <row r="1881">
       <c r="A1881" t="str">
-        <v>Kmtia02g5jwg2</v>
+        <v>Kmti9zgfwypfl</v>
       </c>
       <c r="B1881" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72092,7 +72092,7 @@
     </row>
     <row r="1884">
       <c r="A1884" t="str">
-        <v>Kmtia02g5rr92</v>
+        <v>Kmti9zgfwhczd</v>
       </c>
       <c r="B1884" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72130,7 +72130,7 @@
     </row>
     <row r="1885">
       <c r="A1885" t="str">
-        <v>Kmtia02g5z6a2</v>
+        <v>Kmti9zgfw7qoi</v>
       </c>
       <c r="B1885" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72168,7 +72168,7 @@
     </row>
     <row r="1886">
       <c r="A1886" t="str">
-        <v>Kmtia02g5c1v6</v>
+        <v>Kmti9zgfwb0ne</v>
       </c>
       <c r="B1886" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72244,7 +72244,7 @@
     </row>
     <row r="1888">
       <c r="A1888" t="str">
-        <v>Kmtia02g5yd27</v>
+        <v>Kmti9zgfwonwb</v>
       </c>
       <c r="B1888" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72282,7 +72282,7 @@
     </row>
     <row r="1889">
       <c r="A1889" t="str">
-        <v>Kmtia02g5sdjj</v>
+        <v>Kmti9zgfwmcx1</v>
       </c>
       <c r="B1889" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72320,7 +72320,7 @@
     </row>
     <row r="1890">
       <c r="A1890" t="str">
-        <v>Kmtia02g5rlp6</v>
+        <v>Kmti9zgfwvgey</v>
       </c>
       <c r="B1890" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72358,7 +72358,7 @@
     </row>
     <row r="1891" xml:space="preserve">
       <c r="A1891" t="str">
-        <v>Kmtia02g5gw3m</v>
+        <v>Kmti9zgfwhsjl</v>
       </c>
       <c r="B1891" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -72397,7 +72397,7 @@
     </row>
     <row r="1892" xml:space="preserve">
       <c r="A1892" t="str">
-        <v>Kmtia02g5ycyf</v>
+        <v>Kmti9zgfwz45u</v>
       </c>
       <c r="B1892" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -72436,7 +72436,7 @@
     </row>
     <row r="1893" xml:space="preserve">
       <c r="A1893" t="str">
-        <v>Kmtia02g5xp44</v>
+        <v>Kmti9zgfwkdjf</v>
       </c>
       <c r="B1893" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -72475,7 +72475,7 @@
     </row>
     <row r="1894" xml:space="preserve">
       <c r="A1894" t="str">
-        <v>Kmtia02g5po7x</v>
+        <v>Kmti9zgfwqky1</v>
       </c>
       <c r="B1894" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -72590,7 +72590,7 @@
     </row>
     <row r="1897">
       <c r="A1897" t="str">
-        <v>Kmtia02g5jnvm</v>
+        <v>Kmti9zgfwdg9m</v>
       </c>
       <c r="B1897" t="str">
         <v>Penata Layanan Operasional</v>
@@ -72628,7 +72628,7 @@
     </row>
     <row r="1898">
       <c r="A1898" t="str">
-        <v>Kmtia02g5tu8l</v>
+        <v>Kmti9zgfw93o7</v>
       </c>
       <c r="B1898" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72666,7 +72666,7 @@
     </row>
     <row r="1899">
       <c r="A1899" t="str">
-        <v>Kmtia02g59zte</v>
+        <v>Kmti9zgfw3rvs</v>
       </c>
       <c r="B1899" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72704,7 +72704,7 @@
     </row>
     <row r="1900">
       <c r="A1900" t="str">
-        <v>Kmtia02g54rf9</v>
+        <v>Kmti9zgfwaiyz</v>
       </c>
       <c r="B1900" t="str">
         <v>Penata Keprotokolan*</v>
@@ -72818,7 +72818,7 @@
     </row>
     <row r="1903">
       <c r="A1903" t="str">
-        <v>Kmtia02g5eucu</v>
+        <v>Kmti9zgfwqae2</v>
       </c>
       <c r="B1903" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -72856,7 +72856,7 @@
     </row>
     <row r="1904">
       <c r="A1904" t="str">
-        <v>Kmtia02g5xv40</v>
+        <v>Kmti9zgfwd4z6</v>
       </c>
       <c r="B1904" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -72894,7 +72894,7 @@
     </row>
     <row r="1905">
       <c r="A1905" t="str">
-        <v>Kmtia02g5tio4</v>
+        <v>Kmti9zgfw2ujl</v>
       </c>
       <c r="B1905" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -72970,7 +72970,7 @@
     </row>
     <row r="1907">
       <c r="A1907" t="str">
-        <v>Kmtia02g52b6t</v>
+        <v>Kmti9zgfw9m04</v>
       </c>
       <c r="B1907" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73008,7 +73008,7 @@
     </row>
     <row r="1908">
       <c r="A1908" t="str">
-        <v>Kmtia02g5xi3c</v>
+        <v>Kmti9zgfwx768</v>
       </c>
       <c r="B1908" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73046,7 +73046,7 @@
     </row>
     <row r="1909">
       <c r="A1909" t="str">
-        <v>Kmtia02g5ju1t</v>
+        <v>Kmti9zgfwvkwj</v>
       </c>
       <c r="B1909" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73084,7 +73084,7 @@
     </row>
     <row r="1910" xml:space="preserve">
       <c r="A1910" t="str">
-        <v>Kmtia02g5j8e4</v>
+        <v>Kmti9zgfw6b8v</v>
       </c>
       <c r="B1910" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73123,7 +73123,7 @@
     </row>
     <row r="1911" xml:space="preserve">
       <c r="A1911" t="str">
-        <v>Kmtia02g5lo7f</v>
+        <v>Kmti9zgfwsy1c</v>
       </c>
       <c r="B1911" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73162,7 +73162,7 @@
     </row>
     <row r="1912" xml:space="preserve">
       <c r="A1912" t="str">
-        <v>Kmtia02g54w5v</v>
+        <v>Kmti9zgfw5kvp</v>
       </c>
       <c r="B1912" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73201,7 +73201,7 @@
     </row>
     <row r="1913" xml:space="preserve">
       <c r="A1913" t="str">
-        <v>Kmtia02g5tsmj</v>
+        <v>Kmti9zgfwz84e</v>
       </c>
       <c r="B1913" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73316,7 +73316,7 @@
     </row>
     <row r="1916">
       <c r="A1916" t="str">
-        <v>Kmtia02g67x9r</v>
+        <v>Kmti9zgfwbw3m</v>
       </c>
       <c r="B1916" t="str">
         <v>Penata Layanan Operasional</v>
@@ -73354,7 +73354,7 @@
     </row>
     <row r="1917">
       <c r="A1917" t="str">
-        <v>Kmtia02g6l4mu</v>
+        <v>Kmti9zgfwkfny</v>
       </c>
       <c r="B1917" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73392,7 +73392,7 @@
     </row>
     <row r="1918">
       <c r="A1918" t="str">
-        <v>Kmtia02g6fhzw</v>
+        <v>Kmti9zgfwcyo6</v>
       </c>
       <c r="B1918" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73430,7 +73430,7 @@
     </row>
     <row r="1919">
       <c r="A1919" t="str">
-        <v>Kmtia02g6xz2g</v>
+        <v>Kmti9zgfw0tnz</v>
       </c>
       <c r="B1919" t="str">
         <v>Penata Keprotokolan*</v>
@@ -73544,7 +73544,7 @@
     </row>
     <row r="1922">
       <c r="A1922" t="str">
-        <v>Kmtia02g6mfnb</v>
+        <v>Kmti9zgfwltys</v>
       </c>
       <c r="B1922" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73582,7 +73582,7 @@
     </row>
     <row r="1923">
       <c r="A1923" t="str">
-        <v>Kmtia02g6sda7</v>
+        <v>Kmti9zgfwlv3o</v>
       </c>
       <c r="B1923" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73620,7 +73620,7 @@
     </row>
     <row r="1924">
       <c r="A1924" t="str">
-        <v>Kmtia02g6m9u1</v>
+        <v>Kmti9zgfwjioh</v>
       </c>
       <c r="B1924" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73696,7 +73696,7 @@
     </row>
     <row r="1926">
       <c r="A1926" t="str">
-        <v>Kmtia02g6uvuq</v>
+        <v>Kmti9zgfw06pe</v>
       </c>
       <c r="B1926" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -73734,7 +73734,7 @@
     </row>
     <row r="1927">
       <c r="A1927" t="str">
-        <v>Kmtia02g65myt</v>
+        <v>Kmti9zgfwuj6q</v>
       </c>
       <c r="B1927" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -73772,7 +73772,7 @@
     </row>
     <row r="1928">
       <c r="A1928" t="str">
-        <v>Kmtia02g6oiwu</v>
+        <v>Kmti9zgfw033o</v>
       </c>
       <c r="B1928" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -73810,7 +73810,7 @@
     </row>
     <row r="1929" xml:space="preserve">
       <c r="A1929" t="str">
-        <v>Kmtia02g6s09i</v>
+        <v>Kmti9zgfwjjey</v>
       </c>
       <c r="B1929" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -73849,7 +73849,7 @@
     </row>
     <row r="1930" xml:space="preserve">
       <c r="A1930" t="str">
-        <v>Kmtia02g6x36c</v>
+        <v>Kmti9zgfwnnpn</v>
       </c>
       <c r="B1930" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -73888,7 +73888,7 @@
     </row>
     <row r="1931" xml:space="preserve">
       <c r="A1931" t="str">
-        <v>Kmtia02g6x3zw</v>
+        <v>Kmti9zgfw6gap</v>
       </c>
       <c r="B1931" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -73927,7 +73927,7 @@
     </row>
     <row r="1932" xml:space="preserve">
       <c r="A1932" t="str">
-        <v>Kmtia02g6iuxz</v>
+        <v>Kmti9zgfwoabt</v>
       </c>
       <c r="B1932" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -73966,7 +73966,7 @@
     </row>
     <row r="1933" xml:space="preserve">
       <c r="A1933" t="str">
-        <v>Kmtia02g6rzrv</v>
+        <v>Kmti9zgfww5t6</v>
       </c>
       <c r="B1933" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74005,7 +74005,7 @@
     </row>
     <row r="1934" xml:space="preserve">
       <c r="A1934" t="str">
-        <v>Kmtia02g68m2x</v>
+        <v>Kmti9zgfwyfcf</v>
       </c>
       <c r="B1934" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74044,7 +74044,7 @@
     </row>
     <row r="1935" xml:space="preserve">
       <c r="A1935" t="str">
-        <v>Kmtia02g6b66o</v>
+        <v>Kmti9zgfw2bzn</v>
       </c>
       <c r="B1935" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -74159,7 +74159,7 @@
     </row>
     <row r="1938">
       <c r="A1938" t="str">
-        <v>Kmtia02g6ix1r</v>
+        <v>Kmti9zgfwe6jk</v>
       </c>
       <c r="B1938" t="str">
         <v>Penata Layanan Operasional</v>
@@ -74197,7 +74197,7 @@
     </row>
     <row r="1939">
       <c r="A1939" t="str">
-        <v>Kmtia02g6bevy</v>
+        <v>Kmti9zgfwnr3v</v>
       </c>
       <c r="B1939" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74235,7 +74235,7 @@
     </row>
     <row r="1940">
       <c r="A1940" t="str">
-        <v>Kmtia02g6gfob</v>
+        <v>Kmti9zgfw1j05</v>
       </c>
       <c r="B1940" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74273,7 +74273,7 @@
     </row>
     <row r="1941">
       <c r="A1941" t="str">
-        <v>Kmtia02g69792</v>
+        <v>Kmti9zgfw5rbq</v>
       </c>
       <c r="B1941" t="str">
         <v>Penata Keprotokolan*</v>
@@ -74387,7 +74387,7 @@
     </row>
     <row r="1944">
       <c r="A1944" t="str">
-        <v>Kmtia02g634r5</v>
+        <v>Kmti9zgfwfb0h</v>
       </c>
       <c r="B1944" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74425,7 +74425,7 @@
     </row>
     <row r="1945">
       <c r="A1945" t="str">
-        <v>Kmtia02g69to5</v>
+        <v>Kmti9zgfw1aqi</v>
       </c>
       <c r="B1945" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74463,7 +74463,7 @@
     </row>
     <row r="1946">
       <c r="A1946" t="str">
-        <v>Kmtia02g6j9iw</v>
+        <v>Kmti9zgfwxvsl</v>
       </c>
       <c r="B1946" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74539,7 +74539,7 @@
     </row>
     <row r="1948">
       <c r="A1948" t="str">
-        <v>Kmtia02g6yxsa</v>
+        <v>Kmti9zgfwixeo</v>
       </c>
       <c r="B1948" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -74577,7 +74577,7 @@
     </row>
     <row r="1949">
       <c r="A1949" t="str">
-        <v>Kmtia02g6c24a</v>
+        <v>Kmti9zgfwztsm</v>
       </c>
       <c r="B1949" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -74615,7 +74615,7 @@
     </row>
     <row r="1950">
       <c r="A1950" t="str">
-        <v>Kmtia02g6uyjx</v>
+        <v>Kmti9zgfwjky0</v>
       </c>
       <c r="B1950" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -74653,7 +74653,7 @@
     </row>
     <row r="1951" xml:space="preserve">
       <c r="A1951" t="str">
-        <v>Kmtia02g60w4t</v>
+        <v>Kmti9zgfwql8b</v>
       </c>
       <c r="B1951" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -74692,7 +74692,7 @@
     </row>
     <row r="1952" xml:space="preserve">
       <c r="A1952" t="str">
-        <v>Kmtia02g6jo7p</v>
+        <v>Kmti9zgfwb0ad</v>
       </c>
       <c r="B1952" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -74731,7 +74731,7 @@
     </row>
     <row r="1953" xml:space="preserve">
       <c r="A1953" t="str">
-        <v>Kmtia02g6zxp9</v>
+        <v>Kmti9zgfwr31d</v>
       </c>
       <c r="B1953" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -74770,7 +74770,7 @@
     </row>
     <row r="1954" xml:space="preserve">
       <c r="A1954" t="str">
-        <v>Kmtia02g64hhx</v>
+        <v>Kmti9zgfwr8in</v>
       </c>
       <c r="B1954" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -74809,7 +74809,7 @@
     </row>
     <row r="1955" xml:space="preserve">
       <c r="A1955" t="str">
-        <v>Kmtia02g6vv0j</v>
+        <v>Kmti9zgfwtaz2</v>
       </c>
       <c r="B1955" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Madya/_x000d_
@@ -74848,7 +74848,7 @@
     </row>
     <row r="1956" xml:space="preserve">
       <c r="A1956" t="str">
-        <v>Kmtia02g6i9p7</v>
+        <v>Kmti9zgfwqbyo</v>
       </c>
       <c r="B1956" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Muda/_x000d_
@@ -74887,7 +74887,7 @@
     </row>
     <row r="1957" xml:space="preserve">
       <c r="A1957" t="str">
-        <v>Kmtia02g6t9dv</v>
+        <v>Kmti9zgfw8hv9</v>
       </c>
       <c r="B1957" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Pengelolaan Keuangan APBN Ahli Pertama/_x000d_
@@ -75002,7 +75002,7 @@
     </row>
     <row r="1960">
       <c r="A1960" t="str">
-        <v>Kmtia02g6fz4z</v>
+        <v>Kmti9zgfwct15</v>
       </c>
       <c r="B1960" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75040,7 +75040,7 @@
     </row>
     <row r="1961">
       <c r="A1961" t="str">
-        <v>Kmtia02g66nrd</v>
+        <v>Kmti9zgfwa9hm</v>
       </c>
       <c r="B1961" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75078,7 +75078,7 @@
     </row>
     <row r="1962">
       <c r="A1962" t="str">
-        <v>Kmtia02g6jop0</v>
+        <v>Kmti9zgfwlm30</v>
       </c>
       <c r="B1962" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75116,7 +75116,7 @@
     </row>
     <row r="1963">
       <c r="A1963" t="str">
-        <v>Kmtia02g6klnl</v>
+        <v>Kmti9zgfwqbvg</v>
       </c>
       <c r="B1963" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75230,7 +75230,7 @@
     </row>
     <row r="1966">
       <c r="A1966" t="str">
-        <v>Kmtia02g6ov06</v>
+        <v>Kmti9zgfws9sa</v>
       </c>
       <c r="B1966" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75268,7 +75268,7 @@
     </row>
     <row r="1967">
       <c r="A1967" t="str">
-        <v>Kmtia02g6yv4s</v>
+        <v>Kmti9zgfwash5</v>
       </c>
       <c r="B1967" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75306,7 +75306,7 @@
     </row>
     <row r="1968">
       <c r="A1968" t="str">
-        <v>Kmtia02g6kky4</v>
+        <v>Kmti9zgfwquo0</v>
       </c>
       <c r="B1968" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75382,7 +75382,7 @@
     </row>
     <row r="1970">
       <c r="A1970" t="str">
-        <v>Kmtia02g6cqkx</v>
+        <v>Kmti9zgfwup3i</v>
       </c>
       <c r="B1970" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75420,7 +75420,7 @@
     </row>
     <row r="1971">
       <c r="A1971" t="str">
-        <v>Kmtia02g6q0vj</v>
+        <v>Kmti9zgfwef5s</v>
       </c>
       <c r="B1971" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75458,7 +75458,7 @@
     </row>
     <row r="1972">
       <c r="A1972" t="str">
-        <v>Kmtia02g6mn3p</v>
+        <v>Kmti9zgfwwtwu</v>
       </c>
       <c r="B1972" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75496,7 +75496,7 @@
     </row>
     <row r="1973" xml:space="preserve">
       <c r="A1973" t="str">
-        <v>Kmtia02g6gtj3</v>
+        <v>Kmti9zgfw75iy</v>
       </c>
       <c r="B1973" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -75535,7 +75535,7 @@
     </row>
     <row r="1974" xml:space="preserve">
       <c r="A1974" t="str">
-        <v>Kmtia02g61exi</v>
+        <v>Kmti9zgfwt3u7</v>
       </c>
       <c r="B1974" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -75574,7 +75574,7 @@
     </row>
     <row r="1975" xml:space="preserve">
       <c r="A1975" t="str">
-        <v>Kmtia02g6dxfe</v>
+        <v>Kmti9zgfwetaa</v>
       </c>
       <c r="B1975" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -75613,7 +75613,7 @@
     </row>
     <row r="1976" xml:space="preserve">
       <c r="A1976" t="str">
-        <v>Kmtia02g6ubih</v>
+        <v>Kmti9zgfwckqd</v>
       </c>
       <c r="B1976" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -75728,7 +75728,7 @@
     </row>
     <row r="1979">
       <c r="A1979" t="str">
-        <v>Kmtia02g6t1vj</v>
+        <v>Kmti9zgfwvci0</v>
       </c>
       <c r="B1979" t="str">
         <v>Penata Layanan Operasional</v>
@@ -75766,7 +75766,7 @@
     </row>
     <row r="1980">
       <c r="A1980" t="str">
-        <v>Kmtia02g6vjq0</v>
+        <v>Kmti9zgfw7psj</v>
       </c>
       <c r="B1980" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -75804,7 +75804,7 @@
     </row>
     <row r="1981">
       <c r="A1981" t="str">
-        <v>Kmtia02g6o1h4</v>
+        <v>Kmti9zgfw0gqv</v>
       </c>
       <c r="B1981" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -75842,7 +75842,7 @@
     </row>
     <row r="1982">
       <c r="A1982" t="str">
-        <v>Kmtia02g6ufxj</v>
+        <v>Kmti9zgfw1kr2</v>
       </c>
       <c r="B1982" t="str">
         <v>Penata Keprotokolan*</v>
@@ -75956,7 +75956,7 @@
     </row>
     <row r="1985">
       <c r="A1985" t="str">
-        <v>Kmtia02g6eqwo</v>
+        <v>Kmti9zgfwryyh</v>
       </c>
       <c r="B1985" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -75994,7 +75994,7 @@
     </row>
     <row r="1986">
       <c r="A1986" t="str">
-        <v>Kmtia02g656ap</v>
+        <v>Kmti9zgfwff1h</v>
       </c>
       <c r="B1986" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76032,7 +76032,7 @@
     </row>
     <row r="1987">
       <c r="A1987" t="str">
-        <v>Kmtia02g62ruv</v>
+        <v>Kmti9zgfw6v3w</v>
       </c>
       <c r="B1987" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76108,7 +76108,7 @@
     </row>
     <row r="1989">
       <c r="A1989" t="str">
-        <v>Kmtia02g6f242</v>
+        <v>Kmti9zgfw9zoj</v>
       </c>
       <c r="B1989" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76146,7 +76146,7 @@
     </row>
     <row r="1990">
       <c r="A1990" t="str">
-        <v>Kmtia02g6bh6y</v>
+        <v>Kmti9zgfwyso0</v>
       </c>
       <c r="B1990" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76184,7 +76184,7 @@
     </row>
     <row r="1991">
       <c r="A1991" t="str">
-        <v>Kmtia02g6tcdt</v>
+        <v>Kmti9zgfwugsv</v>
       </c>
       <c r="B1991" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76222,7 +76222,7 @@
     </row>
     <row r="1992" xml:space="preserve">
       <c r="A1992" t="str">
-        <v>Kmtia02g6qn01</v>
+        <v>Kmti9zgfw6fhy</v>
       </c>
       <c r="B1992" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76261,7 +76261,7 @@
     </row>
     <row r="1993" xml:space="preserve">
       <c r="A1993" t="str">
-        <v>Kmtia02g690ph</v>
+        <v>Kmti9zgfwexxz</v>
       </c>
       <c r="B1993" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -76300,7 +76300,7 @@
     </row>
     <row r="1994" xml:space="preserve">
       <c r="A1994" t="str">
-        <v>Kmtia02g63qre</v>
+        <v>Kmti9zgfwx8ig</v>
       </c>
       <c r="B1994" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -76339,7 +76339,7 @@
     </row>
     <row r="1995" xml:space="preserve">
       <c r="A1995" t="str">
-        <v>Kmtia02g69f8a</v>
+        <v>Kmti9zgfwt7iw</v>
       </c>
       <c r="B1995" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -76454,7 +76454,7 @@
     </row>
     <row r="1998">
       <c r="A1998" t="str">
-        <v>Kmtia02g66bb0</v>
+        <v>Kmti9zgfw4cxt</v>
       </c>
       <c r="B1998" t="str">
         <v>Penata Layanan Operasional</v>
@@ -76492,7 +76492,7 @@
     </row>
     <row r="1999">
       <c r="A1999" t="str">
-        <v>Kmtia02g6cgaj</v>
+        <v>Kmti9zgfwxx46</v>
       </c>
       <c r="B1999" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76530,7 +76530,7 @@
     </row>
     <row r="2000">
       <c r="A2000" t="str">
-        <v>Kmtia02g6wnsc</v>
+        <v>Kmti9zgfwdx4b</v>
       </c>
       <c r="B2000" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76568,7 +76568,7 @@
     </row>
     <row r="2001">
       <c r="A2001" t="str">
-        <v>Kmtia02g6wqz2</v>
+        <v>Kmti9zgfwuima</v>
       </c>
       <c r="B2001" t="str">
         <v>Penata Keprotokolan*</v>
@@ -76682,7 +76682,7 @@
     </row>
     <row r="2004">
       <c r="A2004" t="str">
-        <v>Kmtia02g6vn1p</v>
+        <v>Kmti9zgfwtjyt</v>
       </c>
       <c r="B2004" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76720,7 +76720,7 @@
     </row>
     <row r="2005">
       <c r="A2005" t="str">
-        <v>Kmtia02g6lyqk</v>
+        <v>Kmti9zgfx25jb</v>
       </c>
       <c r="B2005" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76758,7 +76758,7 @@
     </row>
     <row r="2006">
       <c r="A2006" t="str">
-        <v>Kmtia02g67sbl</v>
+        <v>Kmti9zgfxvr5x</v>
       </c>
       <c r="B2006" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76834,7 +76834,7 @@
     </row>
     <row r="2008">
       <c r="A2008" t="str">
-        <v>Kmtia02g6wg95</v>
+        <v>Kmti9zgfx60nq</v>
       </c>
       <c r="B2008" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -76872,7 +76872,7 @@
     </row>
     <row r="2009">
       <c r="A2009" t="str">
-        <v>Kmtia02g6tyo0</v>
+        <v>Kmti9zgfx5fvs</v>
       </c>
       <c r="B2009" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -76910,7 +76910,7 @@
     </row>
     <row r="2010">
       <c r="A2010" t="str">
-        <v>Kmtia02g6j3y3</v>
+        <v>Kmti9zgfx8g5q</v>
       </c>
       <c r="B2010" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -76948,7 +76948,7 @@
     </row>
     <row r="2011" xml:space="preserve">
       <c r="A2011" t="str">
-        <v>Kmtia02g6ftgs</v>
+        <v>Kmti9zgfxshjn</v>
       </c>
       <c r="B2011" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -76987,7 +76987,7 @@
     </row>
     <row r="2012" xml:space="preserve">
       <c r="A2012" t="str">
-        <v>Kmtia02g6iwfs</v>
+        <v>Kmti9zgfxrkcb</v>
       </c>
       <c r="B2012" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77026,7 +77026,7 @@
     </row>
     <row r="2013" xml:space="preserve">
       <c r="A2013" t="str">
-        <v>Kmtia02g6ij3d</v>
+        <v>Kmti9zgfx1osk</v>
       </c>
       <c r="B2013" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77065,7 +77065,7 @@
     </row>
     <row r="2014" xml:space="preserve">
       <c r="A2014" t="str">
-        <v>Kmtia02g61wcy</v>
+        <v>Kmti9zgfx01sb</v>
       </c>
       <c r="B2014" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77180,7 +77180,7 @@
     </row>
     <row r="2017">
       <c r="A2017" t="str">
-        <v>Kmtia02g6jmi4</v>
+        <v>Kmti9zgfxxidv</v>
       </c>
       <c r="B2017" t="str">
         <v>Penata Layanan Operasional</v>
@@ -77218,7 +77218,7 @@
     </row>
     <row r="2018">
       <c r="A2018" t="str">
-        <v>Kmtia02g6ivzc</v>
+        <v>Kmti9zgfxnyrh</v>
       </c>
       <c r="B2018" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77256,7 +77256,7 @@
     </row>
     <row r="2019">
       <c r="A2019" t="str">
-        <v>Kmtia02g65mjt</v>
+        <v>Kmti9zgfxvb34</v>
       </c>
       <c r="B2019" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77294,7 +77294,7 @@
     </row>
     <row r="2020">
       <c r="A2020" t="str">
-        <v>Kmtia02g6f6p9</v>
+        <v>Kmti9zgfxoj9b</v>
       </c>
       <c r="B2020" t="str">
         <v>Penata Keprotokolan*</v>
@@ -77408,7 +77408,7 @@
     </row>
     <row r="2023">
       <c r="A2023" t="str">
-        <v>Kmtia02g65q8m</v>
+        <v>Kmti9zgfxkbvv</v>
       </c>
       <c r="B2023" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77446,7 +77446,7 @@
     </row>
     <row r="2024">
       <c r="A2024" t="str">
-        <v>Kmtia02g62e4f</v>
+        <v>Kmti9zgfxhm06</v>
       </c>
       <c r="B2024" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77484,7 +77484,7 @@
     </row>
     <row r="2025">
       <c r="A2025" t="str">
-        <v>Kmtia02g6azc8</v>
+        <v>Kmti9zgfx63dk</v>
       </c>
       <c r="B2025" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77560,7 +77560,7 @@
     </row>
     <row r="2027">
       <c r="A2027" t="str">
-        <v>Kmtia02g6w5gk</v>
+        <v>Kmti9zgfxupom</v>
       </c>
       <c r="B2027" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -77598,7 +77598,7 @@
     </row>
     <row r="2028">
       <c r="A2028" t="str">
-        <v>Kmtia02g6on0i</v>
+        <v>Kmti9zgfxovu8</v>
       </c>
       <c r="B2028" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -77636,7 +77636,7 @@
     </row>
     <row r="2029">
       <c r="A2029" t="str">
-        <v>Kmtia02g6f17q</v>
+        <v>Kmti9zgfxwy6o</v>
       </c>
       <c r="B2029" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -77674,7 +77674,7 @@
     </row>
     <row r="2030" xml:space="preserve">
       <c r="A2030" t="str">
-        <v>Kmtia02g6202h</v>
+        <v>Kmti9zgfxflrx</v>
       </c>
       <c r="B2030" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_
@@ -77713,7 +77713,7 @@
     </row>
     <row r="2031" xml:space="preserve">
       <c r="A2031" t="str">
-        <v>Kmtia02g6cj3j</v>
+        <v>Kmti9zgfxc1b3</v>
       </c>
       <c r="B2031" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Madya/_x000d_
@@ -77752,7 +77752,7 @@
     </row>
     <row r="2032" xml:space="preserve">
       <c r="A2032" t="str">
-        <v>Kmtia02g6cz8d</v>
+        <v>Kmti9zgfxt41q</v>
       </c>
       <c r="B2032" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Muda/_x000d_
@@ -77791,7 +77791,7 @@
     </row>
     <row r="2033" xml:space="preserve">
       <c r="A2033" t="str">
-        <v>Kmtia02g6wjtm</v>
+        <v>Kmti9zgfxiwy8</v>
       </c>
       <c r="B2033" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Pertama/_x000d_
@@ -77830,7 +77830,7 @@
     </row>
     <row r="2034">
       <c r="A2034" t="str">
-        <v>Kmtia02g68p82</v>
+        <v>Kmti9zgfxmdk5</v>
       </c>
       <c r="B2034" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -77868,7 +77868,7 @@
     </row>
     <row r="2035">
       <c r="A2035" t="str">
-        <v>Kmtia02g6mn0u</v>
+        <v>Kmti9zgfxvt2x</v>
       </c>
       <c r="B2035" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -77944,7 +77944,7 @@
     </row>
     <row r="2037" xml:space="preserve">
       <c r="A2037" t="str">
-        <v>Kmtia02g6u0rs</v>
+        <v>Kmti9zgfxcf89</v>
       </c>
       <c r="B2037" t="str" xml:space="preserve">
         <v xml:space="preserve">Analis Anggaran Ahli Utama/_x000d_

--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -78173,7 +78173,7 @@
     </row>
     <row r="2043">
       <c r="A2043" t="str">
-        <v>Kmtsf9qqm3bh5</v>
+        <v>Kmtsfe5v8mzkd</v>
       </c>
       <c r="B2043" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78211,7 +78211,7 @@
     </row>
     <row r="2044">
       <c r="A2044" t="str">
-        <v>Kmtsf9qqn8d8c</v>
+        <v>Kmtsfe5v8d6as</v>
       </c>
       <c r="B2044" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78249,7 +78249,7 @@
     </row>
     <row r="2045">
       <c r="A2045" t="str">
-        <v>Kmtsf9qqniwpe</v>
+        <v>Kmtsfe5v8hr92</v>
       </c>
       <c r="B2045" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78325,7 +78325,7 @@
     </row>
     <row r="2047">
       <c r="A2047" t="str">
-        <v>Kmtsf9qqnpgkt</v>
+        <v>Kmtsfe5v8vmfh</v>
       </c>
       <c r="B2047" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78363,7 +78363,7 @@
     </row>
     <row r="2048">
       <c r="A2048" t="str">
-        <v>Kmtsf9qqn87k8</v>
+        <v>Kmtsfe5v8b2do</v>
       </c>
       <c r="B2048" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78401,7 +78401,7 @@
     </row>
     <row r="2049">
       <c r="A2049" t="str">
-        <v>Kmtsf9qqny9a7</v>
+        <v>Kmtsfe5v85ety</v>
       </c>
       <c r="B2049" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78477,7 +78477,7 @@
     </row>
     <row r="2051">
       <c r="A2051" t="str">
-        <v>Kmtsf9qqnyorv</v>
+        <v>Kmtsfe5v81xu0</v>
       </c>
       <c r="B2051" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78515,7 +78515,7 @@
     </row>
     <row r="2052">
       <c r="A2052" t="str">
-        <v>Kmtsf9qqn03do</v>
+        <v>Kmtsfe5v8rmlx</v>
       </c>
       <c r="B2052" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78553,7 +78553,7 @@
     </row>
     <row r="2053">
       <c r="A2053" t="str">
-        <v>Kmtsf9qqn4pbk</v>
+        <v>Kmtsfe5v8326o</v>
       </c>
       <c r="B2053" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78591,7 +78591,7 @@
     </row>
     <row r="2054">
       <c r="A2054" t="str">
-        <v>Kmtsf9qqna6i2</v>
+        <v>Kmtsfe5v8tizf</v>
       </c>
       <c r="B2054" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -78629,7 +78629,7 @@
     </row>
     <row r="2055">
       <c r="A2055" t="str">
-        <v>Kmtsf9qqngbbq</v>
+        <v>Kmtsfe5v8x19f</v>
       </c>
       <c r="B2055" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -78667,7 +78667,7 @@
     </row>
     <row r="2056">
       <c r="A2056" t="str">
-        <v>Kmtsf9qqng3w5</v>
+        <v>Kmtsfe5v819a6</v>
       </c>
       <c r="B2056" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -78705,7 +78705,7 @@
     </row>
     <row r="2057">
       <c r="A2057" t="str">
-        <v>Kmtsf9qqn721n</v>
+        <v>Kmtsfe5v8w77y</v>
       </c>
       <c r="B2057" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -78743,7 +78743,7 @@
     </row>
     <row r="2058">
       <c r="A2058" t="str">
-        <v>Kmtsf9qqnku9y</v>
+        <v>Kmtsfe5v8fs1z</v>
       </c>
       <c r="B2058" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -78857,7 +78857,7 @@
     </row>
     <row r="2061">
       <c r="A2061" t="str">
-        <v>Kmtsf9qqnktfp</v>
+        <v>Kmtsfe5v8lo3c</v>
       </c>
       <c r="B2061" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78895,7 +78895,7 @@
     </row>
     <row r="2062">
       <c r="A2062" t="str">
-        <v>Kmtsf9qqnkajz</v>
+        <v>Kmtsfe5v8vudv</v>
       </c>
       <c r="B2062" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78933,7 +78933,7 @@
     </row>
     <row r="2063">
       <c r="A2063" t="str">
-        <v>Kmtsf9qqnsi0v</v>
+        <v>Kmtsfe5v83wp5</v>
       </c>
       <c r="B2063" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79009,7 +79009,7 @@
     </row>
     <row r="2065">
       <c r="A2065" t="str">
-        <v>Kmtsf9qqnnket</v>
+        <v>Kmtsfe5v8acs9</v>
       </c>
       <c r="B2065" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79047,7 +79047,7 @@
     </row>
     <row r="2066">
       <c r="A2066" t="str">
-        <v>Kmtsf9qqn4uen</v>
+        <v>Kmtsfe5v8yu26</v>
       </c>
       <c r="B2066" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79085,7 +79085,7 @@
     </row>
     <row r="2067">
       <c r="A2067" t="str">
-        <v>Kmtsf9qqnnpwg</v>
+        <v>Kmtsfe5v8bvfg</v>
       </c>
       <c r="B2067" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79161,7 +79161,7 @@
     </row>
     <row r="2069">
       <c r="A2069" t="str">
-        <v>Kmtsf9qqna2d9</v>
+        <v>Kmtsfe5v8jn0i</v>
       </c>
       <c r="B2069" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79199,7 +79199,7 @@
     </row>
     <row r="2070">
       <c r="A2070" t="str">
-        <v>Kmtsf9qqng4mi</v>
+        <v>Kmtsfe5v8jnkm</v>
       </c>
       <c r="B2070" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79237,7 +79237,7 @@
     </row>
     <row r="2071">
       <c r="A2071" t="str">
-        <v>Kmtsf9qqnu37e</v>
+        <v>Kmtsfe5v8witz</v>
       </c>
       <c r="B2071" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79313,7 +79313,7 @@
     </row>
     <row r="2073">
       <c r="A2073" t="str">
-        <v>Kmtsf9qqnqluu</v>
+        <v>Kmtsfe5v8c5aq</v>
       </c>
       <c r="B2073" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79351,7 +79351,7 @@
     </row>
     <row r="2074">
       <c r="A2074" t="str">
-        <v>Kmtsf9qqnwmi3</v>
+        <v>Kmtsfe5v8q665</v>
       </c>
       <c r="B2074" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79389,7 +79389,7 @@
     </row>
     <row r="2075">
       <c r="A2075" t="str">
-        <v>Kmtsf9qqnflee</v>
+        <v>Kmtsfe5v81bg8</v>
       </c>
       <c r="B2075" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79427,7 +79427,7 @@
     </row>
     <row r="2076">
       <c r="A2076" t="str">
-        <v>Kmtsf9qqnvq40</v>
+        <v>Kmtsfe5v83ri4</v>
       </c>
       <c r="B2076" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -79465,7 +79465,7 @@
     </row>
     <row r="2077">
       <c r="A2077" t="str">
-        <v>Kmtsf9qqn3767</v>
+        <v>Kmtsfe5v8sk5i</v>
       </c>
       <c r="B2077" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -79503,7 +79503,7 @@
     </row>
     <row r="2078">
       <c r="A2078" t="str">
-        <v>Kmtsf9qqnwcdg</v>
+        <v>Kmtsfe5v8xnb0</v>
       </c>
       <c r="B2078" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -79541,7 +79541,7 @@
     </row>
     <row r="2079">
       <c r="A2079" t="str">
-        <v>Kmtsf9qqnlyc8</v>
+        <v>Kmtsfe5v81lvy</v>
       </c>
       <c r="B2079" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -79579,7 +79579,7 @@
     </row>
     <row r="2080">
       <c r="A2080" t="str">
-        <v>Kmtsf9qqnyn0a</v>
+        <v>Kmtsfe5v8cflq</v>
       </c>
       <c r="B2080" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -79617,7 +79617,7 @@
     </row>
     <row r="2081">
       <c r="A2081" t="str">
-        <v>Kmtsf9qqnrbqj</v>
+        <v>Kmtsfe5v82ep4</v>
       </c>
       <c r="B2081" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -79655,7 +79655,7 @@
     </row>
     <row r="2082">
       <c r="A2082" t="str">
-        <v>Kmtsf9qqnt49q</v>
+        <v>Kmtsfe5v89bg7</v>
       </c>
       <c r="B2082" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -79769,7 +79769,7 @@
     </row>
     <row r="2085">
       <c r="A2085" t="str">
-        <v>Kmtsf9qqn3k9j</v>
+        <v>Kmtsfe5v8gik7</v>
       </c>
       <c r="B2085" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79807,7 +79807,7 @@
     </row>
     <row r="2086">
       <c r="A2086" t="str">
-        <v>Kmtsf9qqnux1w</v>
+        <v>Kmtsfe5v83ceh</v>
       </c>
       <c r="B2086" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79845,7 +79845,7 @@
     </row>
     <row r="2087">
       <c r="A2087" t="str">
-        <v>Kmtsf9qqn2j0x</v>
+        <v>Kmtsfe5v8dovt</v>
       </c>
       <c r="B2087" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79921,7 +79921,7 @@
     </row>
     <row r="2089">
       <c r="A2089" t="str">
-        <v>Kmtsf9qqnepbo</v>
+        <v>Kmtsfe5v8vk84</v>
       </c>
       <c r="B2089" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79959,7 +79959,7 @@
     </row>
     <row r="2090">
       <c r="A2090" t="str">
-        <v>Kmtsf9qqntcev</v>
+        <v>Kmtsfe5v8ddw8</v>
       </c>
       <c r="B2090" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79997,7 +79997,7 @@
     </row>
     <row r="2091">
       <c r="A2091" t="str">
-        <v>Kmtsf9qqn3ds8</v>
+        <v>Kmtsfe5v8xd02</v>
       </c>
       <c r="B2091" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80073,7 +80073,7 @@
     </row>
     <row r="2093">
       <c r="A2093" t="str">
-        <v>Kmtsf9qqnuhkn</v>
+        <v>Kmtsfe5v8mkep</v>
       </c>
       <c r="B2093" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80111,7 +80111,7 @@
     </row>
     <row r="2094">
       <c r="A2094" t="str">
-        <v>Kmtsf9qqn6ti8</v>
+        <v>Kmtsfe5v8d31g</v>
       </c>
       <c r="B2094" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80149,7 +80149,7 @@
     </row>
     <row r="2095">
       <c r="A2095" t="str">
-        <v>Kmtsf9qqn8loi</v>
+        <v>Kmtsfe5v8amew</v>
       </c>
       <c r="B2095" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80187,7 +80187,7 @@
     </row>
     <row r="2096">
       <c r="A2096" t="str">
-        <v>Kmtsf9qqn42qd</v>
+        <v>Kmtsfe5v8pf1u</v>
       </c>
       <c r="B2096" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -80225,7 +80225,7 @@
     </row>
     <row r="2097">
       <c r="A2097" t="str">
-        <v>Kmtsf9qqnx979</v>
+        <v>Kmtsfe5v80hbj</v>
       </c>
       <c r="B2097" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Muda</v>
@@ -80263,7 +80263,7 @@
     </row>
     <row r="2098">
       <c r="A2098" t="str">
-        <v>Kmtsf9qqn0wzz</v>
+        <v>Kmtsfe5v86pvo</v>
       </c>
       <c r="B2098" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -80301,7 +80301,7 @@
     </row>
     <row r="2099">
       <c r="A2099" t="str">
-        <v>Kmtsf9qqny2y8</v>
+        <v>Kmtsfe5v8wnhh</v>
       </c>
       <c r="B2099" t="str">
         <v>Pranata Keuangan APBN Penyelia/Pengawas Keuangan Negara Penyelia</v>
@@ -80339,7 +80339,7 @@
     </row>
     <row r="2100">
       <c r="A2100" t="str">
-        <v>Kmtsf9qqngdh9</v>
+        <v>Kmtsfe5v8ng5f</v>
       </c>
       <c r="B2100" t="str">
         <v>Pranata Keuangan APBN Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -80377,7 +80377,7 @@
     </row>
     <row r="2101">
       <c r="A2101" t="str">
-        <v>Kmtsf9qqnan1o</v>
+        <v>Kmtsfe5v8m7su</v>
       </c>
       <c r="B2101" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -80415,7 +80415,7 @@
     </row>
     <row r="2102">
       <c r="A2102" t="str">
-        <v>Kmtsf9qqn0tzh</v>
+        <v>Kmtsfe5v8ow8t</v>
       </c>
       <c r="B2102" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -80453,7 +80453,7 @@
     </row>
     <row r="2103">
       <c r="A2103" t="str">
-        <v>Kmtsf9qqn9blm</v>
+        <v>Kmtsfe5v88y1b</v>
       </c>
       <c r="B2103" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -80491,7 +80491,7 @@
     </row>
     <row r="2104">
       <c r="A2104" t="str">
-        <v>Kmtsf9qqnkjjg</v>
+        <v>Kmtsfe5v8pd2v</v>
       </c>
       <c r="B2104" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -80529,7 +80529,7 @@
     </row>
     <row r="2105">
       <c r="A2105" t="str">
-        <v>Kmtsf9qqnyd12</v>
+        <v>Kmtsfe5v8dtby</v>
       </c>
       <c r="B2105" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -80567,7 +80567,7 @@
     </row>
     <row r="2106">
       <c r="A2106" t="str">
-        <v>Kmtsf9qqnegrj</v>
+        <v>Kmtsfe5v8sipx</v>
       </c>
       <c r="B2106" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -80681,7 +80681,7 @@
     </row>
     <row r="2109">
       <c r="A2109" t="str">
-        <v>Kmtsf9qqnuv3l</v>
+        <v>Kmtsfe5v81zox</v>
       </c>
       <c r="B2109" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80719,7 +80719,7 @@
     </row>
     <row r="2110">
       <c r="A2110" t="str">
-        <v>Kmtsf9qqn5y4p</v>
+        <v>Kmtsfe5v8uixu</v>
       </c>
       <c r="B2110" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80757,7 +80757,7 @@
     </row>
     <row r="2111">
       <c r="A2111" t="str">
-        <v>Kmtsf9qqnujk5</v>
+        <v>Kmtsfe5v8fmog</v>
       </c>
       <c r="B2111" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80833,7 +80833,7 @@
     </row>
     <row r="2113">
       <c r="A2113" t="str">
-        <v>Kmtsf9qqn94l9</v>
+        <v>Kmtsfe5v8ecvd</v>
       </c>
       <c r="B2113" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80871,7 +80871,7 @@
     </row>
     <row r="2114">
       <c r="A2114" t="str">
-        <v>Kmtsf9qqnd8cb</v>
+        <v>Kmtsfe5v8dv9u</v>
       </c>
       <c r="B2114" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80909,7 +80909,7 @@
     </row>
     <row r="2115">
       <c r="A2115" t="str">
-        <v>Kmtsf9qqnc6y9</v>
+        <v>Kmtsfe5v8i25b</v>
       </c>
       <c r="B2115" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80985,7 +80985,7 @@
     </row>
     <row r="2117">
       <c r="A2117" t="str">
-        <v>Kmtsf9qqn3pgq</v>
+        <v>Kmtsfe5v8fxri</v>
       </c>
       <c r="B2117" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -81023,7 +81023,7 @@
     </row>
     <row r="2118">
       <c r="A2118" t="str">
-        <v>Kmtsf9qqnpvq6</v>
+        <v>Kmtsfe5v8o8jm</v>
       </c>
       <c r="B2118" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81061,7 +81061,7 @@
     </row>
     <row r="2119">
       <c r="A2119" t="str">
-        <v>Kmtsf9qqnilkw</v>
+        <v>Kmtsfe5v81b3f</v>
       </c>
       <c r="B2119" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81099,7 +81099,7 @@
     </row>
     <row r="2120">
       <c r="A2120" t="str">
-        <v>Kmtsf9qqn6ren</v>
+        <v>Kmtsfe5v8tw2v</v>
       </c>
       <c r="B2120" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -81137,7 +81137,7 @@
     </row>
     <row r="2121">
       <c r="A2121" t="str">
-        <v>Kmtsf9qqnqfsj</v>
+        <v>Kmtsfe5v8oker</v>
       </c>
       <c r="B2121" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -81175,7 +81175,7 @@
     </row>
     <row r="2122">
       <c r="A2122" t="str">
-        <v>Kmtsf9qqnawna</v>
+        <v>Kmtsfe5v8p9y8</v>
       </c>
       <c r="B2122" t="str">
         <v>Pengawas Keuangan Negara Mahir</v>
@@ -81213,7 +81213,7 @@
     </row>
     <row r="2123">
       <c r="A2123" t="str">
-        <v>Kmtsf9qqnrrar</v>
+        <v>Kmtsfe5v8hrbt</v>
       </c>
       <c r="B2123" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -81327,7 +81327,7 @@
     </row>
     <row r="2126">
       <c r="A2126" t="str">
-        <v>Kmtsf9qqnord5</v>
+        <v>Kmtsfe5v82orl</v>
       </c>
       <c r="B2126" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81365,7 +81365,7 @@
     </row>
     <row r="2127">
       <c r="A2127" t="str">
-        <v>Kmtsf9qqnc2so</v>
+        <v>Kmtsfe5v8ab4a</v>
       </c>
       <c r="B2127" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81403,7 +81403,7 @@
     </row>
     <row r="2128">
       <c r="A2128" t="str">
-        <v>Kmtsf9qqnd697</v>
+        <v>Kmtsfe5v8gbpv</v>
       </c>
       <c r="B2128" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81441,7 +81441,7 @@
     </row>
     <row r="2129">
       <c r="A2129" t="str">
-        <v>Kmtsf9qqnr6ej</v>
+        <v>Kmtsfe5v89qo8</v>
       </c>
       <c r="B2129" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81517,7 +81517,7 @@
     </row>
     <row r="2131">
       <c r="A2131" t="str">
-        <v>Kmtsf9qqnnmkn</v>
+        <v>Kmtsfe5v8i89l</v>
       </c>
       <c r="B2131" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81555,7 +81555,7 @@
     </row>
     <row r="2132">
       <c r="A2132" t="str">
-        <v>Kmtsf9qqn3h4y</v>
+        <v>Kmtsfe5v8q9zq</v>
       </c>
       <c r="B2132" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81593,7 +81593,7 @@
     </row>
     <row r="2133">
       <c r="A2133" t="str">
-        <v>Kmtsf9qqneu99</v>
+        <v>Kmtsfe5v86rz7</v>
       </c>
       <c r="B2133" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81631,7 +81631,7 @@
     </row>
     <row r="2134">
       <c r="A2134" t="str">
-        <v>Kmtsf9qqnrqc9</v>
+        <v>Kmtsfe5v8jkep</v>
       </c>
       <c r="B2134" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81707,7 +81707,7 @@
     </row>
     <row r="2136">
       <c r="A2136" t="str">
-        <v>Kmtsf9qqnhg0s</v>
+        <v>Kmtsfe5v89l4a</v>
       </c>
       <c r="B2136" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81745,7 +81745,7 @@
     </row>
     <row r="2137">
       <c r="A2137" t="str">
-        <v>Kmtsf9qqndrp1</v>
+        <v>Kmtsfe5v8nu4a</v>
       </c>
       <c r="B2137" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81783,7 +81783,7 @@
     </row>
     <row r="2138">
       <c r="A2138" t="str">
-        <v>Kmtsf9qqnagyz</v>
+        <v>Kmtsfe5v8qgna</v>
       </c>
       <c r="B2138" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81821,7 +81821,7 @@
     </row>
     <row r="2139">
       <c r="A2139" t="str">
-        <v>Kmtsf9qqnewc9</v>
+        <v>Kmtsfe5v8wrs6</v>
       </c>
       <c r="B2139" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -81859,7 +81859,7 @@
     </row>
     <row r="2140">
       <c r="A2140" t="str">
-        <v>Kmtsf9qqn9d58</v>
+        <v>Kmtsfe5v84gh7</v>
       </c>
       <c r="B2140" t="str">
         <v>Pengawas Keuangan Negara Pertama</v>
@@ -81897,7 +81897,7 @@
     </row>
     <row r="2141">
       <c r="A2141" t="str">
-        <v>Kmtsf9qqnbkg9</v>
+        <v>Kmtsfe5v8u317</v>
       </c>
       <c r="B2141" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -81935,7 +81935,7 @@
     </row>
     <row r="2142">
       <c r="A2142" t="str">
-        <v>Kmtsf9qqni3s2</v>
+        <v>Kmtsfe5v8fxig</v>
       </c>
       <c r="B2142" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -81973,7 +81973,7 @@
     </row>
     <row r="2143">
       <c r="A2143" t="str">
-        <v>Kmtsf9qqnxmb1</v>
+        <v>Kmtsfe5v8ugr8</v>
       </c>
       <c r="B2143" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -82011,7 +82011,7 @@
     </row>
     <row r="2144">
       <c r="A2144" t="str">
-        <v>Kmtsf9qqn7w0f</v>
+        <v>Kmtsfe5v80onf</v>
       </c>
       <c r="B2144" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -82049,7 +82049,7 @@
     </row>
     <row r="2145">
       <c r="A2145" t="str">
-        <v>Kmtsf9qqndop0</v>
+        <v>Kmtsfe5v8kiu0</v>
       </c>
       <c r="B2145" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -82087,7 +82087,7 @@
     </row>
     <row r="2146">
       <c r="A2146" t="str">
-        <v>Kmtsf9qqnxyk9</v>
+        <v>Kmtsfe5v8jfto</v>
       </c>
       <c r="B2146" t="str">
         <v>Arsiparis Penyelia</v>
@@ -82125,7 +82125,7 @@
     </row>
     <row r="2147">
       <c r="A2147" t="str">
-        <v>Kmtsf9qqniy57</v>
+        <v>Kmtsfe5v8k1gn</v>
       </c>
       <c r="B2147" t="str">
         <v>Arsiparis Mahir</v>
@@ -82163,7 +82163,7 @@
     </row>
     <row r="2148">
       <c r="A2148" t="str">
-        <v>Kmtsf9qqnknw9</v>
+        <v>Kmtsfe5v8emoj</v>
       </c>
       <c r="B2148" t="str">
         <v>Arsiparis Terampil</v>
@@ -82277,7 +82277,7 @@
     </row>
     <row r="2151">
       <c r="A2151" t="str">
-        <v>Kmtsf9qqn5dzk</v>
+        <v>Kmtsfe5v80wr1</v>
       </c>
       <c r="B2151" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -82315,7 +82315,7 @@
     </row>
     <row r="2152">
       <c r="A2152" t="str">
-        <v>Kmtsf9qqnl1ed</v>
+        <v>Kmtsfe5v8tt8d</v>
       </c>
       <c r="B2152" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82353,7 +82353,7 @@
     </row>
     <row r="2153">
       <c r="A2153" t="str">
-        <v>Kmtsf9qqnbuw7</v>
+        <v>Kmtsfe5v8rrwd</v>
       </c>
       <c r="B2153" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82391,7 +82391,7 @@
     </row>
     <row r="2154">
       <c r="A2154" t="str">
-        <v>Kmtsf9qqn5p0d</v>
+        <v>Kmtsfe5v8hyi5</v>
       </c>
       <c r="B2154" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82429,7 +82429,7 @@
     </row>
     <row r="2155">
       <c r="A2155" t="str">
-        <v>Kmtsf9qqns3be</v>
+        <v>Kmtsfe5v88dj9</v>
       </c>
       <c r="B2155" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82467,7 +82467,7 @@
     </row>
     <row r="2156">
       <c r="A2156" t="str">
-        <v>Kmtsf9qqnyzwb</v>
+        <v>Kmtsfe5v8wy3f</v>
       </c>
       <c r="B2156" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82505,7 +82505,7 @@
     </row>
     <row r="2157">
       <c r="A2157" t="str">
-        <v>Kmtsf9qqnvrhv</v>
+        <v>Kmtsfe5v88e9o</v>
       </c>
       <c r="B2157" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82581,7 +82581,7 @@
     </row>
     <row r="2159">
       <c r="A2159" t="str">
-        <v>Kmtsf9qqnyigo</v>
+        <v>Kmtsfe5v8041b</v>
       </c>
       <c r="B2159" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82619,7 +82619,7 @@
     </row>
     <row r="2160">
       <c r="A2160" t="str">
-        <v>Kmtsf9qqn3nfn</v>
+        <v>Kmtsfe5v8mphb</v>
       </c>
       <c r="B2160" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82657,7 +82657,7 @@
     </row>
     <row r="2161">
       <c r="A2161" t="str">
-        <v>Kmtsf9qqnv946</v>
+        <v>Kmtsfe5v8r77b</v>
       </c>
       <c r="B2161" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82695,7 +82695,7 @@
     </row>
     <row r="2162">
       <c r="A2162" t="str">
-        <v>Kmtsf9qqn7ni0</v>
+        <v>Kmtsfe5v8aapa</v>
       </c>
       <c r="B2162" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82733,7 +82733,7 @@
     </row>
     <row r="2163">
       <c r="A2163" t="str">
-        <v>Kmtsf9qqnpbis</v>
+        <v>Kmtsfe5v8nr54</v>
       </c>
       <c r="B2163" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82771,7 +82771,7 @@
     </row>
     <row r="2164">
       <c r="A2164" t="str">
-        <v>Kmtsf9qqn50ry</v>
+        <v>Kmtsfe5v8nyqy</v>
       </c>
       <c r="B2164" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82809,7 +82809,7 @@
     </row>
     <row r="2165">
       <c r="A2165" t="str">
-        <v>Kmtsf9qqngwi6</v>
+        <v>Kmtsfe5v8xkl5</v>
       </c>
       <c r="B2165" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82885,7 +82885,7 @@
     </row>
     <row r="2167">
       <c r="A2167" t="str">
-        <v>Kmtsf9qqndglc</v>
+        <v>Kmtsfe5v853h0</v>
       </c>
       <c r="B2167" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82923,7 +82923,7 @@
     </row>
     <row r="2168">
       <c r="A2168" t="str">
-        <v>Kmtsf9qqnfkha</v>
+        <v>Kmtsfe5v80tor</v>
       </c>
       <c r="B2168" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82961,7 +82961,7 @@
     </row>
     <row r="2169">
       <c r="A2169" t="str">
-        <v>Kmtsf9qqnhnjp</v>
+        <v>Kmtsfe5v8nzzr</v>
       </c>
       <c r="B2169" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82999,7 +82999,7 @@
     </row>
     <row r="2170">
       <c r="A2170" t="str">
-        <v>Kmtsf9qqnqzsi</v>
+        <v>Kmtsfe5v8hlv4</v>
       </c>
       <c r="B2170" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83037,7 +83037,7 @@
     </row>
     <row r="2171">
       <c r="A2171" t="str">
-        <v>Kmtsf9qqnjclo</v>
+        <v>Kmtsfe5v8rthy</v>
       </c>
       <c r="B2171" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83075,7 +83075,7 @@
     </row>
     <row r="2172">
       <c r="A2172" t="str">
-        <v>Kmtsf9qqnntmf</v>
+        <v>Kmtsfe5v883wy</v>
       </c>
       <c r="B2172" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83113,7 +83113,7 @@
     </row>
     <row r="2173">
       <c r="A2173" t="str">
-        <v>Kmtsf9qqn4x8d</v>
+        <v>Kmtsfe5v8pt35</v>
       </c>
       <c r="B2173" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83151,7 +83151,7 @@
     </row>
     <row r="2174">
       <c r="A2174" t="str">
-        <v>Kmtsf9qqn1tgf</v>
+        <v>Kmtsfe5v8z2d6</v>
       </c>
       <c r="B2174" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -83189,7 +83189,7 @@
     </row>
     <row r="2175">
       <c r="A2175" t="str">
-        <v>Kmtsf9qqn7qky</v>
+        <v>Kmtsfe5v8qp4l</v>
       </c>
       <c r="B2175" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83227,7 +83227,7 @@
     </row>
     <row r="2176">
       <c r="A2176" t="str">
-        <v>Kmtsf9qqn24d5</v>
+        <v>Kmtsfe5v88ewg</v>
       </c>
       <c r="B2176" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83265,7 +83265,7 @@
     </row>
     <row r="2177">
       <c r="A2177" t="str">
-        <v>Kmtsf9qqnran8</v>
+        <v>Kmtsfe5v9amqw</v>
       </c>
       <c r="B2177" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83303,7 +83303,7 @@
     </row>
     <row r="2178">
       <c r="A2178" t="str">
-        <v>Kmtsf9qqnwe05</v>
+        <v>Kmtsfe5v9r1pa</v>
       </c>
       <c r="B2178" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83341,7 +83341,7 @@
     </row>
     <row r="2179">
       <c r="A2179" t="str">
-        <v>Kmtsf9qqnsqhm</v>
+        <v>Kmtsfe5v9adqk</v>
       </c>
       <c r="B2179" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -83379,7 +83379,7 @@
     </row>
     <row r="2180">
       <c r="A2180" t="str">
-        <v>Kmtsf9qqnydd2</v>
+        <v>Kmtsfe5v9kyj6</v>
       </c>
       <c r="B2180" t="str">
         <v>Asisten Perpustakaan Penyelia</v>
@@ -83417,7 +83417,7 @@
     </row>
     <row r="2181">
       <c r="A2181" t="str">
-        <v>Kmtsf9qqnohj5</v>
+        <v>Kmtsfe5v9uw97</v>
       </c>
       <c r="B2181" t="str">
         <v>Asisten Perpustakaan Mahir</v>
@@ -83455,7 +83455,7 @@
     </row>
     <row r="2182">
       <c r="A2182" t="str">
-        <v>Kmtsf9qqn9esb</v>
+        <v>Kmtsfe5v9slp0</v>
       </c>
       <c r="B2182" t="str">
         <v>Asisten Perpustakaan Terampil</v>
@@ -83493,7 +83493,7 @@
     </row>
     <row r="2183">
       <c r="A2183" t="str">
-        <v>Kmtsf9qqnoiqc</v>
+        <v>Kmtsfe5v91but</v>
       </c>
       <c r="B2183" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -83531,7 +83531,7 @@
     </row>
     <row r="2184">
       <c r="A2184" t="str">
-        <v>Kmtsf9qqnq7mg</v>
+        <v>Kmtsfe5v9uh59</v>
       </c>
       <c r="B2184" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -83569,7 +83569,7 @@
     </row>
     <row r="2185">
       <c r="A2185" t="str">
-        <v>Kmtsf9qqn18u8</v>
+        <v>Kmtsfe5v9tvxu</v>
       </c>
       <c r="B2185" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -83683,7 +83683,7 @@
     </row>
     <row r="2188">
       <c r="A2188" t="str">
-        <v>Kmtsf9qqnwrdj</v>
+        <v>Kmtsfe5v9s0cd</v>
       </c>
       <c r="B2188" t="str">
         <v>Penata Layanan Operasional</v>
@@ -83721,7 +83721,7 @@
     </row>
     <row r="2189">
       <c r="A2189" t="str">
-        <v>Kmtsf9qqnnml4</v>
+        <v>Kmtsfe5v9hx4e</v>
       </c>
       <c r="B2189" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83759,7 +83759,7 @@
     </row>
     <row r="2190">
       <c r="A2190" t="str">
-        <v>Kmtsf9qqna5m8</v>
+        <v>Kmtsfe5v9pfd9</v>
       </c>
       <c r="B2190" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -83797,7 +83797,7 @@
     </row>
     <row r="2191">
       <c r="A2191" t="str">
-        <v>Kmtsf9qqnp1lt</v>
+        <v>Kmtsfe5v9hocs</v>
       </c>
       <c r="B2191" t="str">
         <v>Penata Keprotokolan*</v>
@@ -83911,7 +83911,7 @@
     </row>
     <row r="2194">
       <c r="A2194" t="str">
-        <v>Kmtsf9qqnzyz6</v>
+        <v>Kmtsfe5v96pf7</v>
       </c>
       <c r="B2194" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -83949,7 +83949,7 @@
     </row>
     <row r="2195">
       <c r="A2195" t="str">
-        <v>Kmtsf9qqnbq89</v>
+        <v>Kmtsfe5v9rlzj</v>
       </c>
       <c r="B2195" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83987,7 +83987,7 @@
     </row>
     <row r="2196">
       <c r="A2196" t="str">
-        <v>Kmtsf9qqnfop0</v>
+        <v>Kmtsfe5v92g1u</v>
       </c>
       <c r="B2196" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84063,7 +84063,7 @@
     </row>
     <row r="2198">
       <c r="A2198" t="str">
-        <v>Kmtsf9qqny2l1</v>
+        <v>Kmtsfe5v9wp83</v>
       </c>
       <c r="B2198" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84101,7 +84101,7 @@
     </row>
     <row r="2199">
       <c r="A2199" t="str">
-        <v>Kmtsf9qqni9v4</v>
+        <v>Kmtsfe5v92buh</v>
       </c>
       <c r="B2199" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84139,7 +84139,7 @@
     </row>
     <row r="2200">
       <c r="A2200" t="str">
-        <v>Kmtsf9qqnkqbo</v>
+        <v>Kmtsfe5v9joc8</v>
       </c>
       <c r="B2200" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84177,7 +84177,7 @@
     </row>
     <row r="2201">
       <c r="A2201" t="str">
-        <v>Kmtsf9qqntuhj</v>
+        <v>Kmtsfe5v9cz21</v>
       </c>
       <c r="B2201" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84215,7 +84215,7 @@
     </row>
     <row r="2202">
       <c r="A2202" t="str">
-        <v>Kmtsf9qqnj2w0</v>
+        <v>Kmtsfe5v99dy9</v>
       </c>
       <c r="B2202" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84253,7 +84253,7 @@
     </row>
     <row r="2203">
       <c r="A2203" t="str">
-        <v>Kmtsf9qqnkqj8</v>
+        <v>Kmtsfe5v9hwh9</v>
       </c>
       <c r="B2203" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -84291,7 +84291,7 @@
     </row>
     <row r="2204">
       <c r="A2204" t="str">
-        <v>Kmtsf9qqnlkdp</v>
+        <v>Kmtsfe5v913ar</v>
       </c>
       <c r="B2204" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -84405,7 +84405,7 @@
     </row>
     <row r="2207">
       <c r="A2207" t="str">
-        <v>Kmtsf9qqnzfkc</v>
+        <v>Kmtsfe5v9mfhv</v>
       </c>
       <c r="B2207" t="str">
         <v>Penata Layanan Operasional</v>
@@ -84443,7 +84443,7 @@
     </row>
     <row r="2208">
       <c r="A2208" t="str">
-        <v>Kmtsf9qqn82k5</v>
+        <v>Kmtsfe5v9mhm3</v>
       </c>
       <c r="B2208" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84481,7 +84481,7 @@
     </row>
     <row r="2209">
       <c r="A2209" t="str">
-        <v>Kmtsf9qqnc9oq</v>
+        <v>Kmtsfe5v98z2i</v>
       </c>
       <c r="B2209" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84519,7 +84519,7 @@
     </row>
     <row r="2210">
       <c r="A2210" t="str">
-        <v>Kmtsf9qqnbgb8</v>
+        <v>Kmtsfe5v9f4bq</v>
       </c>
       <c r="B2210" t="str">
         <v>Penata Keprotokolan*</v>
@@ -84633,7 +84633,7 @@
     </row>
     <row r="2213">
       <c r="A2213" t="str">
-        <v>Kmtsf9qqnbwq4</v>
+        <v>Kmtsfe5v93xnx</v>
       </c>
       <c r="B2213" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84671,7 +84671,7 @@
     </row>
     <row r="2214">
       <c r="A2214" t="str">
-        <v>Kmtsf9qqn1lk4</v>
+        <v>Kmtsfe5v9jvvb</v>
       </c>
       <c r="B2214" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84709,7 +84709,7 @@
     </row>
     <row r="2215">
       <c r="A2215" t="str">
-        <v>Kmtsf9qqnm7jz</v>
+        <v>Kmtsfe5v9zj48</v>
       </c>
       <c r="B2215" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84785,7 +84785,7 @@
     </row>
     <row r="2217">
       <c r="A2217" t="str">
-        <v>Kmtsf9qqocvdc</v>
+        <v>Kmtsfe5v9mfid</v>
       </c>
       <c r="B2217" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84823,7 +84823,7 @@
     </row>
     <row r="2218">
       <c r="A2218" t="str">
-        <v>Kmtsf9qqop8sh</v>
+        <v>Kmtsfe5v9lb0l</v>
       </c>
       <c r="B2218" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84861,7 +84861,7 @@
     </row>
     <row r="2219">
       <c r="A2219" t="str">
-        <v>Kmtsf9qqovtat</v>
+        <v>Kmtsfe5v92355</v>
       </c>
       <c r="B2219" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84899,7 +84899,7 @@
     </row>
     <row r="2220">
       <c r="A2220" t="str">
-        <v>Kmtsf9qqogmcg</v>
+        <v>Kmtsfe5v9s3fp</v>
       </c>
       <c r="B2220" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84937,7 +84937,7 @@
     </row>
     <row r="2221">
       <c r="A2221" t="str">
-        <v>Kmtsf9qqo3j6s</v>
+        <v>Kmtsfe5v94ywz</v>
       </c>
       <c r="B2221" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84975,7 +84975,7 @@
     </row>
     <row r="2222">
       <c r="A2222" t="str">
-        <v>Kmtsf9qqog80f</v>
+        <v>Kmtsfe5v9q16m</v>
       </c>
       <c r="B2222" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85013,7 +85013,7 @@
     </row>
     <row r="2223">
       <c r="A2223" t="str">
-        <v>Kmtsf9qqohurq</v>
+        <v>Kmtsfe5v9w3ms</v>
       </c>
       <c r="B2223" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85127,7 +85127,7 @@
     </row>
     <row r="2226">
       <c r="A2226" t="str">
-        <v>Kmtsf9qqo3a8q</v>
+        <v>Kmtsfe5v92xar</v>
       </c>
       <c r="B2226" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85165,7 +85165,7 @@
     </row>
     <row r="2227">
       <c r="A2227" t="str">
-        <v>Kmtsf9qqoxvaz</v>
+        <v>Kmtsfe5v99a1y</v>
       </c>
       <c r="B2227" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85203,7 +85203,7 @@
     </row>
     <row r="2228">
       <c r="A2228" t="str">
-        <v>Kmtsf9qqopwzp</v>
+        <v>Kmtsfe5v93nbt</v>
       </c>
       <c r="B2228" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85241,7 +85241,7 @@
     </row>
     <row r="2229">
       <c r="A2229" t="str">
-        <v>Kmtsf9qqo3jy0</v>
+        <v>Kmtsfe5v95kzu</v>
       </c>
       <c r="B2229" t="str">
         <v>Penata Keprotokolan*</v>
@@ -85355,7 +85355,7 @@
     </row>
     <row r="2232">
       <c r="A2232" t="str">
-        <v>Kmtsf9qqocv9x</v>
+        <v>Kmtsfe5v91k6y</v>
       </c>
       <c r="B2232" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85393,7 +85393,7 @@
     </row>
     <row r="2233">
       <c r="A2233" t="str">
-        <v>Kmtsf9qqohpkd</v>
+        <v>Kmtsfe5v9da34</v>
       </c>
       <c r="B2233" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85431,7 +85431,7 @@
     </row>
     <row r="2234">
       <c r="A2234" t="str">
-        <v>Kmtsf9qqob7mh</v>
+        <v>Kmtsfe5v9brgz</v>
       </c>
       <c r="B2234" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85507,7 +85507,7 @@
     </row>
     <row r="2236">
       <c r="A2236" t="str">
-        <v>Kmtsf9qqout90</v>
+        <v>Kmtsfe5v9nsqh</v>
       </c>
       <c r="B2236" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85545,7 +85545,7 @@
     </row>
     <row r="2237">
       <c r="A2237" t="str">
-        <v>Kmtsf9qqom46w</v>
+        <v>Kmtsfe5v9ybmw</v>
       </c>
       <c r="B2237" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85583,7 +85583,7 @@
     </row>
     <row r="2238">
       <c r="A2238" t="str">
-        <v>Kmtsf9qqoj415</v>
+        <v>Kmtsfe5v94mkh</v>
       </c>
       <c r="B2238" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85621,7 +85621,7 @@
     </row>
     <row r="2239">
       <c r="A2239" t="str">
-        <v>Kmtsf9qqo41ua</v>
+        <v>Kmtsfe5v9jycm</v>
       </c>
       <c r="B2239" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -85659,7 +85659,7 @@
     </row>
     <row r="2240">
       <c r="A2240" t="str">
-        <v>Kmtsf9qqocfj7</v>
+        <v>Kmtsfe5v9zz26</v>
       </c>
       <c r="B2240" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -85697,7 +85697,7 @@
     </row>
     <row r="2241">
       <c r="A2241" t="str">
-        <v>Kmtsf9qqoax6o</v>
+        <v>Kmtsfe5v9ae5a</v>
       </c>
       <c r="B2241" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85735,7 +85735,7 @@
     </row>
     <row r="2242">
       <c r="A2242" t="str">
-        <v>Kmtsf9qqols4i</v>
+        <v>Kmtsfe5v966sv</v>
       </c>
       <c r="B2242" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85849,7 +85849,7 @@
     </row>
     <row r="2245">
       <c r="A2245" t="str">
-        <v>Kmtsf9qqoyojk</v>
+        <v>Kmtsfe5v9wzir</v>
       </c>
       <c r="B2245" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85887,7 +85887,7 @@
     </row>
     <row r="2246">
       <c r="A2246" t="str">
-        <v>Kmtsf9qqotg2x</v>
+        <v>Kmtsfe5v95bth</v>
       </c>
       <c r="B2246" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85925,7 +85925,7 @@
     </row>
     <row r="2247">
       <c r="A2247" t="str">
-        <v>Kmtsf9qqo50c2</v>
+        <v>Kmtsfe5v9c02g</v>
       </c>
       <c r="B2247" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85963,7 +85963,7 @@
     </row>
     <row r="2248">
       <c r="A2248" t="str">
-        <v>Kmtsf9qqorzb3</v>
+        <v>Kmtsfe5v9fkjb</v>
       </c>
       <c r="B2248" t="str">
         <v>Penata Keprotokolan*</v>
@@ -86039,7 +86039,7 @@
     </row>
     <row r="2250">
       <c r="A2250" t="str">
-        <v>Kmtsf9qqol7gx</v>
+        <v>Kmtsfe5v90v2g</v>
       </c>
       <c r="B2250" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86077,7 +86077,7 @@
     </row>
     <row r="2251">
       <c r="A2251" t="str">
-        <v>Kmtsf9qqo8yvt</v>
+        <v>Kmtsfe5v9uke2</v>
       </c>
       <c r="B2251" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86115,7 +86115,7 @@
     </row>
     <row r="2252">
       <c r="A2252" t="str">
-        <v>Kmtsf9qqowx9y</v>
+        <v>Kmtsfe5v9cdok</v>
       </c>
       <c r="B2252" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86153,7 +86153,7 @@
     </row>
     <row r="2253">
       <c r="A2253" t="str">
-        <v>Kmtsf9qqo7lds</v>
+        <v>Kmtsfe5v9mok3</v>
       </c>
       <c r="B2253" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86191,7 +86191,7 @@
     </row>
     <row r="2254">
       <c r="A2254" t="str">
-        <v>Kmtsf9qqolybg</v>
+        <v>Kmtsfe5v9rwxq</v>
       </c>
       <c r="B2254" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86305,7 +86305,7 @@
     </row>
     <row r="2257">
       <c r="A2257" t="str">
-        <v>Kmtsf9qqo9b3x</v>
+        <v>Kmtsfe5v9xy11</v>
       </c>
       <c r="B2257" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86343,7 +86343,7 @@
     </row>
     <row r="2258">
       <c r="A2258" t="str">
-        <v>Kmtsf9qqo506c</v>
+        <v>Kmtsfe5v9ln21</v>
       </c>
       <c r="B2258" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86381,7 +86381,7 @@
     </row>
     <row r="2259">
       <c r="A2259" t="str">
-        <v>Kmtsf9qqohcu3</v>
+        <v>Kmtsfe5v9311b</v>
       </c>
       <c r="B2259" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86457,7 +86457,7 @@
     </row>
     <row r="2261">
       <c r="A2261" t="str">
-        <v>Kmtsf9qqod19g</v>
+        <v>Kmtsfe5v9eyhm</v>
       </c>
       <c r="B2261" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86495,7 +86495,7 @@
     </row>
     <row r="2262">
       <c r="A2262" t="str">
-        <v>Kmtsf9qqos0j2</v>
+        <v>Kmtsfe5v9lum0</v>
       </c>
       <c r="B2262" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86533,7 +86533,7 @@
     </row>
     <row r="2263">
       <c r="A2263" t="str">
-        <v>Kmtsf9qqok5iz</v>
+        <v>Kmtsfe5v9v3e8</v>
       </c>
       <c r="B2263" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86571,7 +86571,7 @@
     </row>
     <row r="2264">
       <c r="A2264" t="str">
-        <v>Kmtsf9qqos1jg</v>
+        <v>Kmtsfe5v9wuda</v>
       </c>
       <c r="B2264" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -86609,7 +86609,7 @@
     </row>
     <row r="2265">
       <c r="A2265" t="str">
-        <v>Kmtsf9qqouxid</v>
+        <v>Kmtsfe5v9k5ry</v>
       </c>
       <c r="B2265" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -86647,7 +86647,7 @@
     </row>
     <row r="2266">
       <c r="A2266" t="str">
-        <v>Kmtsf9qqow430</v>
+        <v>Kmtsfe5v985dd</v>
       </c>
       <c r="B2266" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86685,7 +86685,7 @@
     </row>
     <row r="2267">
       <c r="A2267" t="str">
-        <v>Kmtsf9qqodbyv</v>
+        <v>Kmtsfe5v9c1fc</v>
       </c>
       <c r="B2267" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86799,7 +86799,7 @@
     </row>
     <row r="2270">
       <c r="A2270" t="str">
-        <v>Kmtsf9qqokt5j</v>
+        <v>Kmtsfe5v97jmt</v>
       </c>
       <c r="B2270" t="str">
         <v>Penata Layanan Operasional</v>
@@ -86837,7 +86837,7 @@
     </row>
     <row r="2271">
       <c r="A2271" t="str">
-        <v>Kmtsf9qqo66d4</v>
+        <v>Kmtsfe5v9k41b</v>
       </c>
       <c r="B2271" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86875,7 +86875,7 @@
     </row>
     <row r="2272">
       <c r="A2272" t="str">
-        <v>Kmtsf9qqowgh6</v>
+        <v>Kmtsfe5v9xugh</v>
       </c>
       <c r="B2272" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86913,7 +86913,7 @@
     </row>
     <row r="2273">
       <c r="A2273" t="str">
-        <v>Kmtsf9qqoz5oe</v>
+        <v>Kmtsfe5v9993n</v>
       </c>
       <c r="B2273" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87027,7 +87027,7 @@
     </row>
     <row r="2276">
       <c r="A2276" t="str">
-        <v>Kmtsf9qqoo9m4</v>
+        <v>Kmtsfe5v9ssf1</v>
       </c>
       <c r="B2276" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87065,7 +87065,7 @@
     </row>
     <row r="2277">
       <c r="A2277" t="str">
-        <v>Kmtsf9qqo8u7o</v>
+        <v>Kmtsfe5v9crr8</v>
       </c>
       <c r="B2277" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87103,7 +87103,7 @@
     </row>
     <row r="2278">
       <c r="A2278" t="str">
-        <v>Kmtsf9qqodhyb</v>
+        <v>Kmtsfe5v9z6z7</v>
       </c>
       <c r="B2278" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87179,7 +87179,7 @@
     </row>
     <row r="2280">
       <c r="A2280" t="str">
-        <v>Kmtsf9qqo6onu</v>
+        <v>Kmtsfe5v9042i</v>
       </c>
       <c r="B2280" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87217,7 +87217,7 @@
     </row>
     <row r="2281">
       <c r="A2281" t="str">
-        <v>Kmtsf9qqogldk</v>
+        <v>Kmtsfe5v9h5p8</v>
       </c>
       <c r="B2281" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87255,7 +87255,7 @@
     </row>
     <row r="2282">
       <c r="A2282" t="str">
-        <v>Kmtsf9qqoile1</v>
+        <v>Kmtsfe5v9zky1</v>
       </c>
       <c r="B2282" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87293,7 +87293,7 @@
     </row>
     <row r="2283">
       <c r="A2283" t="str">
-        <v>Kmtsf9qqopz71</v>
+        <v>Kmtsfe5v91gxr</v>
       </c>
       <c r="B2283" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -87331,7 +87331,7 @@
     </row>
     <row r="2284">
       <c r="A2284" t="str">
-        <v>Kmtsf9qqo1pfv</v>
+        <v>Kmtsfe5v99xkf</v>
       </c>
       <c r="B2284" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -87369,7 +87369,7 @@
     </row>
     <row r="2285">
       <c r="A2285" t="str">
-        <v>Kmtsf9qqorj7s</v>
+        <v>Kmtsfe5v9v6b9</v>
       </c>
       <c r="B2285" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -87407,7 +87407,7 @@
     </row>
     <row r="2286">
       <c r="A2286" t="str">
-        <v>Kmtsf9qqocppl</v>
+        <v>Kmtsfe5v9lqii</v>
       </c>
       <c r="B2286" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -87521,7 +87521,7 @@
     </row>
     <row r="2289">
       <c r="A2289" t="str">
-        <v>Kmtsf9qqoe55s</v>
+        <v>Kmtsfe5v9y4i7</v>
       </c>
       <c r="B2289" t="str">
         <v>Penata Layanan Operasional</v>
@@ -87559,7 +87559,7 @@
     </row>
     <row r="2290">
       <c r="A2290" t="str">
-        <v>Kmtsf9qqoyejp</v>
+        <v>Kmtsfe5v94leq</v>
       </c>
       <c r="B2290" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87597,7 +87597,7 @@
     </row>
     <row r="2291">
       <c r="A2291" t="str">
-        <v>Kmtsf9qqoes82</v>
+        <v>Kmtsfe5v9ulrq</v>
       </c>
       <c r="B2291" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87635,7 +87635,7 @@
     </row>
     <row r="2292">
       <c r="A2292" t="str">
-        <v>Kmtsf9qqou5hf</v>
+        <v>Kmtsfe5v91z68</v>
       </c>
       <c r="B2292" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87749,7 +87749,7 @@
     </row>
     <row r="2295">
       <c r="A2295" t="str">
-        <v>Kmtsf9qqobndi</v>
+        <v>Kmtsfe5v9d9x9</v>
       </c>
       <c r="B2295" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87787,7 +87787,7 @@
     </row>
     <row r="2296">
       <c r="A2296" t="str">
-        <v>Kmtsf9qqo6mvy</v>
+        <v>Kmtsfe5v9hr8k</v>
       </c>
       <c r="B2296" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87825,7 +87825,7 @@
     </row>
     <row r="2297">
       <c r="A2297" t="str">
-        <v>Kmtsf9qqohk8e</v>
+        <v>Kmtsfe5v9jfms</v>
       </c>
       <c r="B2297" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87901,7 +87901,7 @@
     </row>
     <row r="2299">
       <c r="A2299" t="str">
-        <v>Kmtsf9qqo1c0h</v>
+        <v>Kmtsfe5v9ns8v</v>
       </c>
       <c r="B2299" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87939,7 +87939,7 @@
     </row>
     <row r="2300">
       <c r="A2300" t="str">
-        <v>Kmtsf9qqo2nhc</v>
+        <v>Kmtsfe5v95pn5</v>
       </c>
       <c r="B2300" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87977,7 +87977,7 @@
     </row>
     <row r="2301">
       <c r="A2301" t="str">
-        <v>Kmtsf9qqorvlt</v>
+        <v>Kmtsfe5v9v573</v>
       </c>
       <c r="B2301" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88015,7 +88015,7 @@
     </row>
     <row r="2302">
       <c r="A2302" t="str">
-        <v>Kmtsf9qqov52u</v>
+        <v>Kmtsfe5v91fwe</v>
       </c>
       <c r="B2302" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -88053,7 +88053,7 @@
     </row>
     <row r="2303">
       <c r="A2303" t="str">
-        <v>Kmtsf9qqolxd2</v>
+        <v>Kmtsfe5v9wyxy</v>
       </c>
       <c r="B2303" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -88091,7 +88091,7 @@
     </row>
     <row r="2304">
       <c r="A2304" t="str">
-        <v>Kmtsf9qqod2d2</v>
+        <v>Kmtsfe5v9b0wr</v>
       </c>
       <c r="B2304" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -88129,7 +88129,7 @@
     </row>
     <row r="2305">
       <c r="A2305" t="str">
-        <v>Kmtsf9qqopp8f</v>
+        <v>Kmtsfe5v9wh3l</v>
       </c>
       <c r="B2305" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -88243,7 +88243,7 @@
     </row>
     <row r="2308">
       <c r="A2308" t="str">
-        <v>Kmtsf9qqodxu9</v>
+        <v>Kmtsfe5v9x908</v>
       </c>
       <c r="B2308" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88281,7 +88281,7 @@
     </row>
     <row r="2309">
       <c r="A2309" t="str">
-        <v>Kmtsf9qqoslxu</v>
+        <v>Kmtsfe5v9drxf</v>
       </c>
       <c r="B2309" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88319,7 +88319,7 @@
     </row>
     <row r="2310">
       <c r="A2310" t="str">
-        <v>Kmtsf9qqo6bdo</v>
+        <v>Kmtsfe5v9fad5</v>
       </c>
       <c r="B2310" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88357,7 +88357,7 @@
     </row>
     <row r="2311">
       <c r="A2311" t="str">
-        <v>Kmtsf9qqog1ya</v>
+        <v>Kmtsfe5v9i5e2</v>
       </c>
       <c r="B2311" t="str">
         <v>Penata Keprotokolan*</v>
@@ -88471,7 +88471,7 @@
     </row>
     <row r="2314">
       <c r="A2314" t="str">
-        <v>Kmtsf9qqo7h4x</v>
+        <v>Kmtsfe5v99cwm</v>
       </c>
       <c r="B2314" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88509,7 +88509,7 @@
     </row>
     <row r="2315">
       <c r="A2315" t="str">
-        <v>Kmtsf9qqox04h</v>
+        <v>Kmtsfe5v9s9yx</v>
       </c>
       <c r="B2315" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88547,7 +88547,7 @@
     </row>
     <row r="2316">
       <c r="A2316" t="str">
-        <v>Kmtsf9qqo8qlx</v>
+        <v>Kmtsfe5v999xz</v>
       </c>
       <c r="B2316" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88623,7 +88623,7 @@
     </row>
     <row r="2318">
       <c r="A2318" t="str">
-        <v>Kmtsf9qqotjpn</v>
+        <v>Kmtsfe5v9bhns</v>
       </c>
       <c r="B2318" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88661,7 +88661,7 @@
     </row>
     <row r="2319">
       <c r="A2319" t="str">
-        <v>Kmtsf9qqonjkr</v>
+        <v>Kmtsfe5v93t5d</v>
       </c>
       <c r="B2319" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88699,7 +88699,7 @@
     </row>
     <row r="2320">
       <c r="A2320" t="str">
-        <v>Kmtsf9qqos5pd</v>
+        <v>Kmtsfe5v9g4ij</v>
       </c>
       <c r="B2320" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88775,7 +88775,7 @@
     </row>
     <row r="2322">
       <c r="A2322" t="str">
-        <v>Kmtsf9qqokbb0</v>
+        <v>Kmtsfe5v9jp41</v>
       </c>
       <c r="B2322" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88813,7 +88813,7 @@
     </row>
     <row r="2323">
       <c r="A2323" t="str">
-        <v>Kmtsf9qqo29q6</v>
+        <v>Kmtsfe5v945z6</v>
       </c>
       <c r="B2323" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88851,7 +88851,7 @@
     </row>
     <row r="2324">
       <c r="A2324" t="str">
-        <v>Kmtsf9qqompye</v>
+        <v>Kmtsfe5v9zjcg</v>
       </c>
       <c r="B2324" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88927,7 +88927,7 @@
     </row>
     <row r="2326">
       <c r="A2326" t="str">
-        <v>Kmtsf9qqoaz4l</v>
+        <v>Kmtsfe5v9j750</v>
       </c>
       <c r="B2326" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88965,7 +88965,7 @@
     </row>
     <row r="2327">
       <c r="A2327" t="str">
-        <v>Kmtsf9qqoh3ys</v>
+        <v>Kmtsfe5v9a5e8</v>
       </c>
       <c r="B2327" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89003,7 +89003,7 @@
     </row>
     <row r="2328">
       <c r="A2328" t="str">
-        <v>Kmtsf9qqodvt9</v>
+        <v>Kmtsfe5v9k5ll</v>
       </c>
       <c r="B2328" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89117,7 +89117,7 @@
     </row>
     <row r="2331">
       <c r="A2331" t="str">
-        <v>Kmtsf9qqo1i5u</v>
+        <v>Kmtsfe5v9nilm</v>
       </c>
       <c r="B2331" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89155,7 +89155,7 @@
     </row>
     <row r="2332">
       <c r="A2332" t="str">
-        <v>Kmtsf9qqofacz</v>
+        <v>Kmtsfe5v9iisu</v>
       </c>
       <c r="B2332" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89193,7 +89193,7 @@
     </row>
     <row r="2333">
       <c r="A2333" t="str">
-        <v>Kmtsf9qqoikua</v>
+        <v>Kmtsfe5v94acl</v>
       </c>
       <c r="B2333" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89269,7 +89269,7 @@
     </row>
     <row r="2335">
       <c r="A2335" t="str">
-        <v>Kmtsf9qqokuv5</v>
+        <v>Kmtsfe5v9kney</v>
       </c>
       <c r="B2335" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89307,7 +89307,7 @@
     </row>
     <row r="2336">
       <c r="A2336" t="str">
-        <v>Kmtsf9qqo6eaa</v>
+        <v>Kmtsfe5v9n3l1</v>
       </c>
       <c r="B2336" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89345,7 +89345,7 @@
     </row>
     <row r="2337">
       <c r="A2337" t="str">
-        <v>Kmtsf9qqo6fi3</v>
+        <v>Kmtsfe5v9kns1</v>
       </c>
       <c r="B2337" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89383,7 +89383,7 @@
     </row>
     <row r="2338">
       <c r="A2338" t="str">
-        <v>Kmtsf9qqo1zob</v>
+        <v>Kmtsfe5v9vsai</v>
       </c>
       <c r="B2338" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -89421,7 +89421,7 @@
     </row>
     <row r="2339">
       <c r="A2339" t="str">
-        <v>Kmtsf9qqooap1</v>
+        <v>Kmtsfe5v9c4wi</v>
       </c>
       <c r="B2339" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -89459,7 +89459,7 @@
     </row>
     <row r="2340">
       <c r="A2340" t="str">
-        <v>Kmtsf9qqovgmw</v>
+        <v>Kmtsfe5v92zzk</v>
       </c>
       <c r="B2340" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -89497,7 +89497,7 @@
     </row>
     <row r="2341">
       <c r="A2341" t="str">
-        <v>Kmtsf9qqoq32i</v>
+        <v>Kmtsfe5v9ne1h</v>
       </c>
       <c r="B2341" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -89611,7 +89611,7 @@
     </row>
     <row r="2344">
       <c r="A2344" t="str">
-        <v>Kmtsf9qqogfjv</v>
+        <v>Kmtsfe5v9f5yo</v>
       </c>
       <c r="B2344" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89649,7 +89649,7 @@
     </row>
     <row r="2345">
       <c r="A2345" t="str">
-        <v>Kmtsf9qqo2g33</v>
+        <v>Kmtsfe5v951nz</v>
       </c>
       <c r="B2345" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89687,7 +89687,7 @@
     </row>
     <row r="2346">
       <c r="A2346" t="str">
-        <v>Kmtsf9qqoz67z</v>
+        <v>Kmtsfe5v9yuzx</v>
       </c>
       <c r="B2346" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89801,7 +89801,7 @@
     </row>
     <row r="2349">
       <c r="A2349" t="str">
-        <v>Kmtsf9qqo27gx</v>
+        <v>Kmtsfe5v9y8sc</v>
       </c>
       <c r="B2349" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89839,7 +89839,7 @@
     </row>
     <row r="2350">
       <c r="A2350" t="str">
-        <v>Kmtsf9qqo9vvv</v>
+        <v>Kmtsfe5v9how0</v>
       </c>
       <c r="B2350" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89877,7 +89877,7 @@
     </row>
     <row r="2351">
       <c r="A2351" t="str">
-        <v>Kmtsf9qqonhd1</v>
+        <v>Kmtsfe5v95ug8</v>
       </c>
       <c r="B2351" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89953,7 +89953,7 @@
     </row>
     <row r="2353">
       <c r="A2353" t="str">
-        <v>Kmtsf9qqo0dj2</v>
+        <v>Kmtsfe5v9xbna</v>
       </c>
       <c r="B2353" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89991,7 +89991,7 @@
     </row>
     <row r="2354">
       <c r="A2354" t="str">
-        <v>Kmtsf9qqo1qlr</v>
+        <v>Kmtsfe5v9xvsa</v>
       </c>
       <c r="B2354" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90029,7 +90029,7 @@
     </row>
     <row r="2355">
       <c r="A2355" t="str">
-        <v>Kmtsf9qqo8azs</v>
+        <v>Kmtsfe5v9l3j5</v>
       </c>
       <c r="B2355" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90067,7 +90067,7 @@
     </row>
     <row r="2356">
       <c r="A2356" t="str">
-        <v>Kmtsf9qqoujbh</v>
+        <v>Kmtsfe5v925ho</v>
       </c>
       <c r="B2356" t="str">
         <v>Penata Keprotokolan*</v>
@@ -90143,7 +90143,7 @@
     </row>
     <row r="2358">
       <c r="A2358" t="str">
-        <v>Kmtsf9qqomfnb</v>
+        <v>Kmtsfe5v9w9n4</v>
       </c>
       <c r="B2358" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90181,7 +90181,7 @@
     </row>
     <row r="2359">
       <c r="A2359" t="str">
-        <v>Kmtsf9qqojllg</v>
+        <v>Kmtsfe5v9mm8q</v>
       </c>
       <c r="B2359" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90219,7 +90219,7 @@
     </row>
     <row r="2360">
       <c r="A2360" t="str">
-        <v>Kmtsf9qqoa46o</v>
+        <v>Kmtsfe5v96yvy</v>
       </c>
       <c r="B2360" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90333,7 +90333,7 @@
     </row>
     <row r="2363">
       <c r="A2363" t="str">
-        <v>Kmtsf9qqo7fs3</v>
+        <v>Kmtsfe5v9cjcg</v>
       </c>
       <c r="B2363" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90371,7 +90371,7 @@
     </row>
     <row r="2364">
       <c r="A2364" t="str">
-        <v>Kmtsf9qqo4q7y</v>
+        <v>Kmtsfe5v92znu</v>
       </c>
       <c r="B2364" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90409,7 +90409,7 @@
     </row>
     <row r="2365">
       <c r="A2365" t="str">
-        <v>Kmtsf9qqo8ntf</v>
+        <v>Kmtsfe5vaqt2n</v>
       </c>
       <c r="B2365" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90485,7 +90485,7 @@
     </row>
     <row r="2367">
       <c r="A2367" t="str">
-        <v>Kmtsf9qqospeb</v>
+        <v>Kmtsfe5va2mhp</v>
       </c>
       <c r="B2367" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90523,7 +90523,7 @@
     </row>
     <row r="2368">
       <c r="A2368" t="str">
-        <v>Kmtsf9qqo8kph</v>
+        <v>Kmtsfe5va6kym</v>
       </c>
       <c r="B2368" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90561,7 +90561,7 @@
     </row>
     <row r="2369">
       <c r="A2369" t="str">
-        <v>Kmtsf9qqoe2w4</v>
+        <v>Kmtsfe5vaw4tl</v>
       </c>
       <c r="B2369" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90637,7 +90637,7 @@
     </row>
     <row r="2371">
       <c r="A2371" t="str">
-        <v>Kmtsf9qqopcan</v>
+        <v>Kmtsfe5vaqs5d</v>
       </c>
       <c r="B2371" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90675,7 +90675,7 @@
     </row>
     <row r="2372">
       <c r="A2372" t="str">
-        <v>Kmtsf9qqotzxw</v>
+        <v>Kmtsfe5vas8vj</v>
       </c>
       <c r="B2372" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90713,7 +90713,7 @@
     </row>
     <row r="2373">
       <c r="A2373" t="str">
-        <v>Kmtsf9qqo9cz7</v>
+        <v>Kmtsfe5va7kl9</v>
       </c>
       <c r="B2373" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90789,7 +90789,7 @@
     </row>
     <row r="2375">
       <c r="A2375" t="str">
-        <v>Kmtsf9qqoi8qs</v>
+        <v>Kmtsfe5va0862</v>
       </c>
       <c r="B2375" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90827,7 +90827,7 @@
     </row>
     <row r="2376">
       <c r="A2376" t="str">
-        <v>Kmtsf9qqo8509</v>
+        <v>Kmtsfe5va40rc</v>
       </c>
       <c r="B2376" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90865,7 +90865,7 @@
     </row>
     <row r="2377">
       <c r="A2377" t="str">
-        <v>Kmtsf9qqouruy</v>
+        <v>Kmtsfe5vaiv18</v>
       </c>
       <c r="B2377" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90903,7 +90903,7 @@
     </row>
     <row r="2378">
       <c r="A2378" t="str">
-        <v>Kmtsf9qqorj7g</v>
+        <v>Kmtsfe5vadrxi</v>
       </c>
       <c r="B2378" t="str">
         <v xml:space="preserve">Analis Pembiayaan Risiko dan Keuangan/ Analis Keuangan Negara Ahli Utama									</v>

--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -78173,7 +78173,7 @@
     </row>
     <row r="2043">
       <c r="A2043" t="str">
-        <v>Kmtsfe5v8mzkd</v>
+        <v>Kmtsferhmr99w</v>
       </c>
       <c r="B2043" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78211,7 +78211,7 @@
     </row>
     <row r="2044">
       <c r="A2044" t="str">
-        <v>Kmtsfe5v8d6as</v>
+        <v>Kmtsferhmqbib</v>
       </c>
       <c r="B2044" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78249,7 +78249,7 @@
     </row>
     <row r="2045">
       <c r="A2045" t="str">
-        <v>Kmtsfe5v8hr92</v>
+        <v>Kmtsferhmxfzj</v>
       </c>
       <c r="B2045" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78325,7 +78325,7 @@
     </row>
     <row r="2047">
       <c r="A2047" t="str">
-        <v>Kmtsfe5v8vmfh</v>
+        <v>Kmtsferhm25g3</v>
       </c>
       <c r="B2047" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78363,7 +78363,7 @@
     </row>
     <row r="2048">
       <c r="A2048" t="str">
-        <v>Kmtsfe5v8b2do</v>
+        <v>Kmtsferhm9ouv</v>
       </c>
       <c r="B2048" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78401,7 +78401,7 @@
     </row>
     <row r="2049">
       <c r="A2049" t="str">
-        <v>Kmtsfe5v85ety</v>
+        <v>Kmtsferhmlcv8</v>
       </c>
       <c r="B2049" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78477,7 +78477,7 @@
     </row>
     <row r="2051">
       <c r="A2051" t="str">
-        <v>Kmtsfe5v81xu0</v>
+        <v>Kmtsferhmkg6a</v>
       </c>
       <c r="B2051" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78515,7 +78515,7 @@
     </row>
     <row r="2052">
       <c r="A2052" t="str">
-        <v>Kmtsfe5v8rmlx</v>
+        <v>Kmtsferhmzdy4</v>
       </c>
       <c r="B2052" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78553,7 +78553,7 @@
     </row>
     <row r="2053">
       <c r="A2053" t="str">
-        <v>Kmtsfe5v8326o</v>
+        <v>Kmtsferhml8en</v>
       </c>
       <c r="B2053" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78591,7 +78591,7 @@
     </row>
     <row r="2054">
       <c r="A2054" t="str">
-        <v>Kmtsfe5v8tizf</v>
+        <v>Kmtsferhmrrvm</v>
       </c>
       <c r="B2054" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -78629,7 +78629,7 @@
     </row>
     <row r="2055">
       <c r="A2055" t="str">
-        <v>Kmtsfe5v8x19f</v>
+        <v>Kmtsferhm7epw</v>
       </c>
       <c r="B2055" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -78667,7 +78667,7 @@
     </row>
     <row r="2056">
       <c r="A2056" t="str">
-        <v>Kmtsfe5v819a6</v>
+        <v>Kmtsferhm91bq</v>
       </c>
       <c r="B2056" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -78705,7 +78705,7 @@
     </row>
     <row r="2057">
       <c r="A2057" t="str">
-        <v>Kmtsfe5v8w77y</v>
+        <v>Kmtsferhmxn6k</v>
       </c>
       <c r="B2057" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -78743,7 +78743,7 @@
     </row>
     <row r="2058">
       <c r="A2058" t="str">
-        <v>Kmtsfe5v8fs1z</v>
+        <v>Kmtsferhmuccz</v>
       </c>
       <c r="B2058" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -78857,7 +78857,7 @@
     </row>
     <row r="2061">
       <c r="A2061" t="str">
-        <v>Kmtsfe5v8lo3c</v>
+        <v>Kmtsferhm1kkq</v>
       </c>
       <c r="B2061" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78895,7 +78895,7 @@
     </row>
     <row r="2062">
       <c r="A2062" t="str">
-        <v>Kmtsfe5v8vudv</v>
+        <v>Kmtsferhmoj64</v>
       </c>
       <c r="B2062" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78933,7 +78933,7 @@
     </row>
     <row r="2063">
       <c r="A2063" t="str">
-        <v>Kmtsfe5v83wp5</v>
+        <v>Kmtsferhm8l4y</v>
       </c>
       <c r="B2063" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79009,7 +79009,7 @@
     </row>
     <row r="2065">
       <c r="A2065" t="str">
-        <v>Kmtsfe5v8acs9</v>
+        <v>Kmtsferhms2ct</v>
       </c>
       <c r="B2065" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79047,7 +79047,7 @@
     </row>
     <row r="2066">
       <c r="A2066" t="str">
-        <v>Kmtsfe5v8yu26</v>
+        <v>Kmtsferhmoifl</v>
       </c>
       <c r="B2066" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79085,7 +79085,7 @@
     </row>
     <row r="2067">
       <c r="A2067" t="str">
-        <v>Kmtsfe5v8bvfg</v>
+        <v>Kmtsferhm8bs4</v>
       </c>
       <c r="B2067" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79161,7 +79161,7 @@
     </row>
     <row r="2069">
       <c r="A2069" t="str">
-        <v>Kmtsfe5v8jn0i</v>
+        <v>Kmtsferhmg27y</v>
       </c>
       <c r="B2069" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79199,7 +79199,7 @@
     </row>
     <row r="2070">
       <c r="A2070" t="str">
-        <v>Kmtsfe5v8jnkm</v>
+        <v>Kmtsferhm8goy</v>
       </c>
       <c r="B2070" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79237,7 +79237,7 @@
     </row>
     <row r="2071">
       <c r="A2071" t="str">
-        <v>Kmtsfe5v8witz</v>
+        <v>Kmtsferhmmo90</v>
       </c>
       <c r="B2071" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79313,7 +79313,7 @@
     </row>
     <row r="2073">
       <c r="A2073" t="str">
-        <v>Kmtsfe5v8c5aq</v>
+        <v>Kmtsferhmstrm</v>
       </c>
       <c r="B2073" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79351,7 +79351,7 @@
     </row>
     <row r="2074">
       <c r="A2074" t="str">
-        <v>Kmtsfe5v8q665</v>
+        <v>Kmtsferhm45jj</v>
       </c>
       <c r="B2074" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79389,7 +79389,7 @@
     </row>
     <row r="2075">
       <c r="A2075" t="str">
-        <v>Kmtsfe5v81bg8</v>
+        <v>Kmtsferhmi9fs</v>
       </c>
       <c r="B2075" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79427,7 +79427,7 @@
     </row>
     <row r="2076">
       <c r="A2076" t="str">
-        <v>Kmtsfe5v83ri4</v>
+        <v>Kmtsferhmfvxk</v>
       </c>
       <c r="B2076" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -79465,7 +79465,7 @@
     </row>
     <row r="2077">
       <c r="A2077" t="str">
-        <v>Kmtsfe5v8sk5i</v>
+        <v>Kmtsferhmhica</v>
       </c>
       <c r="B2077" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -79503,7 +79503,7 @@
     </row>
     <row r="2078">
       <c r="A2078" t="str">
-        <v>Kmtsfe5v8xnb0</v>
+        <v>Kmtsferhmcsgx</v>
       </c>
       <c r="B2078" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -79541,7 +79541,7 @@
     </row>
     <row r="2079">
       <c r="A2079" t="str">
-        <v>Kmtsfe5v81lvy</v>
+        <v>Kmtsferhmd9ze</v>
       </c>
       <c r="B2079" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -79579,7 +79579,7 @@
     </row>
     <row r="2080">
       <c r="A2080" t="str">
-        <v>Kmtsfe5v8cflq</v>
+        <v>Kmtsferhm2l86</v>
       </c>
       <c r="B2080" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -79617,7 +79617,7 @@
     </row>
     <row r="2081">
       <c r="A2081" t="str">
-        <v>Kmtsfe5v82ep4</v>
+        <v>Kmtsferhmk7cv</v>
       </c>
       <c r="B2081" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -79655,7 +79655,7 @@
     </row>
     <row r="2082">
       <c r="A2082" t="str">
-        <v>Kmtsfe5v89bg7</v>
+        <v>Kmtsferhmvx99</v>
       </c>
       <c r="B2082" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -79769,7 +79769,7 @@
     </row>
     <row r="2085">
       <c r="A2085" t="str">
-        <v>Kmtsfe5v8gik7</v>
+        <v>Kmtsferhmj8hz</v>
       </c>
       <c r="B2085" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79807,7 +79807,7 @@
     </row>
     <row r="2086">
       <c r="A2086" t="str">
-        <v>Kmtsfe5v83ceh</v>
+        <v>Kmtsferhm7eo7</v>
       </c>
       <c r="B2086" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79845,7 +79845,7 @@
     </row>
     <row r="2087">
       <c r="A2087" t="str">
-        <v>Kmtsfe5v8dovt</v>
+        <v>Kmtsferhmcds3</v>
       </c>
       <c r="B2087" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79921,7 +79921,7 @@
     </row>
     <row r="2089">
       <c r="A2089" t="str">
-        <v>Kmtsfe5v8vk84</v>
+        <v>Kmtsferhmn81g</v>
       </c>
       <c r="B2089" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79959,7 +79959,7 @@
     </row>
     <row r="2090">
       <c r="A2090" t="str">
-        <v>Kmtsfe5v8ddw8</v>
+        <v>Kmtsferhmf254</v>
       </c>
       <c r="B2090" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79997,7 +79997,7 @@
     </row>
     <row r="2091">
       <c r="A2091" t="str">
-        <v>Kmtsfe5v8xd02</v>
+        <v>Kmtsferhmigo8</v>
       </c>
       <c r="B2091" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80073,7 +80073,7 @@
     </row>
     <row r="2093">
       <c r="A2093" t="str">
-        <v>Kmtsfe5v8mkep</v>
+        <v>Kmtsferhmtuqw</v>
       </c>
       <c r="B2093" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80111,7 +80111,7 @@
     </row>
     <row r="2094">
       <c r="A2094" t="str">
-        <v>Kmtsfe5v8d31g</v>
+        <v>Kmtsferhm741k</v>
       </c>
       <c r="B2094" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80149,7 +80149,7 @@
     </row>
     <row r="2095">
       <c r="A2095" t="str">
-        <v>Kmtsfe5v8amew</v>
+        <v>Kmtsferhmahsr</v>
       </c>
       <c r="B2095" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80187,7 +80187,7 @@
     </row>
     <row r="2096">
       <c r="A2096" t="str">
-        <v>Kmtsfe5v8pf1u</v>
+        <v>Kmtsferhmecnl</v>
       </c>
       <c r="B2096" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -80225,7 +80225,7 @@
     </row>
     <row r="2097">
       <c r="A2097" t="str">
-        <v>Kmtsfe5v80hbj</v>
+        <v>Kmtsferhmxi92</v>
       </c>
       <c r="B2097" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Muda</v>
@@ -80263,7 +80263,7 @@
     </row>
     <row r="2098">
       <c r="A2098" t="str">
-        <v>Kmtsfe5v86pvo</v>
+        <v>Kmtsferhm0onl</v>
       </c>
       <c r="B2098" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -80301,7 +80301,7 @@
     </row>
     <row r="2099">
       <c r="A2099" t="str">
-        <v>Kmtsfe5v8wnhh</v>
+        <v>Kmtsferhmimju</v>
       </c>
       <c r="B2099" t="str">
         <v>Pranata Keuangan APBN Penyelia/Pengawas Keuangan Negara Penyelia</v>
@@ -80339,7 +80339,7 @@
     </row>
     <row r="2100">
       <c r="A2100" t="str">
-        <v>Kmtsfe5v8ng5f</v>
+        <v>Kmtsferhmkoap</v>
       </c>
       <c r="B2100" t="str">
         <v>Pranata Keuangan APBN Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -80377,7 +80377,7 @@
     </row>
     <row r="2101">
       <c r="A2101" t="str">
-        <v>Kmtsfe5v8m7su</v>
+        <v>Kmtsferhmhxel</v>
       </c>
       <c r="B2101" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -80415,7 +80415,7 @@
     </row>
     <row r="2102">
       <c r="A2102" t="str">
-        <v>Kmtsfe5v8ow8t</v>
+        <v>Kmtsferhmih3m</v>
       </c>
       <c r="B2102" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -80453,7 +80453,7 @@
     </row>
     <row r="2103">
       <c r="A2103" t="str">
-        <v>Kmtsfe5v88y1b</v>
+        <v>Kmtsferhm0q6f</v>
       </c>
       <c r="B2103" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -80491,7 +80491,7 @@
     </row>
     <row r="2104">
       <c r="A2104" t="str">
-        <v>Kmtsfe5v8pd2v</v>
+        <v>Kmtsferhmhnxh</v>
       </c>
       <c r="B2104" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -80529,7 +80529,7 @@
     </row>
     <row r="2105">
       <c r="A2105" t="str">
-        <v>Kmtsfe5v8dtby</v>
+        <v>Kmtsferhm9j92</v>
       </c>
       <c r="B2105" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -80567,7 +80567,7 @@
     </row>
     <row r="2106">
       <c r="A2106" t="str">
-        <v>Kmtsfe5v8sipx</v>
+        <v>Kmtsferhm6r11</v>
       </c>
       <c r="B2106" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -80681,7 +80681,7 @@
     </row>
     <row r="2109">
       <c r="A2109" t="str">
-        <v>Kmtsfe5v81zox</v>
+        <v>Kmtsferhme1wl</v>
       </c>
       <c r="B2109" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80719,7 +80719,7 @@
     </row>
     <row r="2110">
       <c r="A2110" t="str">
-        <v>Kmtsfe5v8uixu</v>
+        <v>Kmtsferhmmd78</v>
       </c>
       <c r="B2110" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80757,7 +80757,7 @@
     </row>
     <row r="2111">
       <c r="A2111" t="str">
-        <v>Kmtsfe5v8fmog</v>
+        <v>Kmtsferhm279s</v>
       </c>
       <c r="B2111" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80833,7 +80833,7 @@
     </row>
     <row r="2113">
       <c r="A2113" t="str">
-        <v>Kmtsfe5v8ecvd</v>
+        <v>Kmtsferhmdd1d</v>
       </c>
       <c r="B2113" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80871,7 +80871,7 @@
     </row>
     <row r="2114">
       <c r="A2114" t="str">
-        <v>Kmtsfe5v8dv9u</v>
+        <v>Kmtsferhmgv1g</v>
       </c>
       <c r="B2114" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80909,7 +80909,7 @@
     </row>
     <row r="2115">
       <c r="A2115" t="str">
-        <v>Kmtsfe5v8i25b</v>
+        <v>Kmtsferhm3lhw</v>
       </c>
       <c r="B2115" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80985,7 +80985,7 @@
     </row>
     <row r="2117">
       <c r="A2117" t="str">
-        <v>Kmtsfe5v8fxri</v>
+        <v>Kmtsferhmuuot</v>
       </c>
       <c r="B2117" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -81023,7 +81023,7 @@
     </row>
     <row r="2118">
       <c r="A2118" t="str">
-        <v>Kmtsfe5v8o8jm</v>
+        <v>Kmtsferhmtyl2</v>
       </c>
       <c r="B2118" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81061,7 +81061,7 @@
     </row>
     <row r="2119">
       <c r="A2119" t="str">
-        <v>Kmtsfe5v81b3f</v>
+        <v>Kmtsferhmxs33</v>
       </c>
       <c r="B2119" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81099,7 +81099,7 @@
     </row>
     <row r="2120">
       <c r="A2120" t="str">
-        <v>Kmtsfe5v8tw2v</v>
+        <v>Kmtsferhma1i7</v>
       </c>
       <c r="B2120" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -81137,7 +81137,7 @@
     </row>
     <row r="2121">
       <c r="A2121" t="str">
-        <v>Kmtsfe5v8oker</v>
+        <v>Kmtsferhmr9ah</v>
       </c>
       <c r="B2121" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -81175,7 +81175,7 @@
     </row>
     <row r="2122">
       <c r="A2122" t="str">
-        <v>Kmtsfe5v8p9y8</v>
+        <v>Kmtsferhm9ckf</v>
       </c>
       <c r="B2122" t="str">
         <v>Pengawas Keuangan Negara Mahir</v>
@@ -81213,7 +81213,7 @@
     </row>
     <row r="2123">
       <c r="A2123" t="str">
-        <v>Kmtsfe5v8hrbt</v>
+        <v>Kmtsferhm3juh</v>
       </c>
       <c r="B2123" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -81327,7 +81327,7 @@
     </row>
     <row r="2126">
       <c r="A2126" t="str">
-        <v>Kmtsfe5v82orl</v>
+        <v>Kmtsferhm6uk6</v>
       </c>
       <c r="B2126" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81365,7 +81365,7 @@
     </row>
     <row r="2127">
       <c r="A2127" t="str">
-        <v>Kmtsfe5v8ab4a</v>
+        <v>Kmtsferhmolg9</v>
       </c>
       <c r="B2127" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81403,7 +81403,7 @@
     </row>
     <row r="2128">
       <c r="A2128" t="str">
-        <v>Kmtsfe5v8gbpv</v>
+        <v>Kmtsferhmngbo</v>
       </c>
       <c r="B2128" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81441,7 +81441,7 @@
     </row>
     <row r="2129">
       <c r="A2129" t="str">
-        <v>Kmtsfe5v89qo8</v>
+        <v>Kmtsferhmepfb</v>
       </c>
       <c r="B2129" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81517,7 +81517,7 @@
     </row>
     <row r="2131">
       <c r="A2131" t="str">
-        <v>Kmtsfe5v8i89l</v>
+        <v>Kmtsferhmenp7</v>
       </c>
       <c r="B2131" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81555,7 +81555,7 @@
     </row>
     <row r="2132">
       <c r="A2132" t="str">
-        <v>Kmtsfe5v8q9zq</v>
+        <v>Kmtsferhmol5e</v>
       </c>
       <c r="B2132" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81593,7 +81593,7 @@
     </row>
     <row r="2133">
       <c r="A2133" t="str">
-        <v>Kmtsfe5v86rz7</v>
+        <v>Kmtsferhmjvzo</v>
       </c>
       <c r="B2133" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81631,7 +81631,7 @@
     </row>
     <row r="2134">
       <c r="A2134" t="str">
-        <v>Kmtsfe5v8jkep</v>
+        <v>Kmtsferhmb6jv</v>
       </c>
       <c r="B2134" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81707,7 +81707,7 @@
     </row>
     <row r="2136">
       <c r="A2136" t="str">
-        <v>Kmtsfe5v89l4a</v>
+        <v>Kmtsferhmayhk</v>
       </c>
       <c r="B2136" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81745,7 +81745,7 @@
     </row>
     <row r="2137">
       <c r="A2137" t="str">
-        <v>Kmtsfe5v8nu4a</v>
+        <v>Kmtsferhmkxhd</v>
       </c>
       <c r="B2137" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81783,7 +81783,7 @@
     </row>
     <row r="2138">
       <c r="A2138" t="str">
-        <v>Kmtsfe5v8qgna</v>
+        <v>Kmtsferhmhfaq</v>
       </c>
       <c r="B2138" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81821,7 +81821,7 @@
     </row>
     <row r="2139">
       <c r="A2139" t="str">
-        <v>Kmtsfe5v8wrs6</v>
+        <v>Kmtsferhmplap</v>
       </c>
       <c r="B2139" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -81859,7 +81859,7 @@
     </row>
     <row r="2140">
       <c r="A2140" t="str">
-        <v>Kmtsfe5v84gh7</v>
+        <v>Kmtsferhmcnpk</v>
       </c>
       <c r="B2140" t="str">
         <v>Pengawas Keuangan Negara Pertama</v>
@@ -81897,7 +81897,7 @@
     </row>
     <row r="2141">
       <c r="A2141" t="str">
-        <v>Kmtsfe5v8u317</v>
+        <v>Kmtsferhmfpfl</v>
       </c>
       <c r="B2141" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -81935,7 +81935,7 @@
     </row>
     <row r="2142">
       <c r="A2142" t="str">
-        <v>Kmtsfe5v8fxig</v>
+        <v>Kmtsferhm9e02</v>
       </c>
       <c r="B2142" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -81973,7 +81973,7 @@
     </row>
     <row r="2143">
       <c r="A2143" t="str">
-        <v>Kmtsfe5v8ugr8</v>
+        <v>Kmtsferhm9yf7</v>
       </c>
       <c r="B2143" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -82011,7 +82011,7 @@
     </row>
     <row r="2144">
       <c r="A2144" t="str">
-        <v>Kmtsfe5v80onf</v>
+        <v>Kmtsferhmhhh8</v>
       </c>
       <c r="B2144" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -82049,7 +82049,7 @@
     </row>
     <row r="2145">
       <c r="A2145" t="str">
-        <v>Kmtsfe5v8kiu0</v>
+        <v>Kmtsferhmoauy</v>
       </c>
       <c r="B2145" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -82087,7 +82087,7 @@
     </row>
     <row r="2146">
       <c r="A2146" t="str">
-        <v>Kmtsfe5v8jfto</v>
+        <v>Kmtsferhmnf0c</v>
       </c>
       <c r="B2146" t="str">
         <v>Arsiparis Penyelia</v>
@@ -82125,7 +82125,7 @@
     </row>
     <row r="2147">
       <c r="A2147" t="str">
-        <v>Kmtsfe5v8k1gn</v>
+        <v>Kmtsferhm9g3m</v>
       </c>
       <c r="B2147" t="str">
         <v>Arsiparis Mahir</v>
@@ -82163,7 +82163,7 @@
     </row>
     <row r="2148">
       <c r="A2148" t="str">
-        <v>Kmtsfe5v8emoj</v>
+        <v>Kmtsferhm9z7c</v>
       </c>
       <c r="B2148" t="str">
         <v>Arsiparis Terampil</v>
@@ -82277,7 +82277,7 @@
     </row>
     <row r="2151">
       <c r="A2151" t="str">
-        <v>Kmtsfe5v80wr1</v>
+        <v>Kmtsferhn7s1m</v>
       </c>
       <c r="B2151" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -82315,7 +82315,7 @@
     </row>
     <row r="2152">
       <c r="A2152" t="str">
-        <v>Kmtsfe5v8tt8d</v>
+        <v>Kmtsferhnfb2y</v>
       </c>
       <c r="B2152" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82353,7 +82353,7 @@
     </row>
     <row r="2153">
       <c r="A2153" t="str">
-        <v>Kmtsfe5v8rrwd</v>
+        <v>Kmtsferhnwkqj</v>
       </c>
       <c r="B2153" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82391,7 +82391,7 @@
     </row>
     <row r="2154">
       <c r="A2154" t="str">
-        <v>Kmtsfe5v8hyi5</v>
+        <v>Kmtsferhngue4</v>
       </c>
       <c r="B2154" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82429,7 +82429,7 @@
     </row>
     <row r="2155">
       <c r="A2155" t="str">
-        <v>Kmtsfe5v88dj9</v>
+        <v>Kmtsferhnvqy0</v>
       </c>
       <c r="B2155" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82467,7 +82467,7 @@
     </row>
     <row r="2156">
       <c r="A2156" t="str">
-        <v>Kmtsfe5v8wy3f</v>
+        <v>Kmtsferhnvwnx</v>
       </c>
       <c r="B2156" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82505,7 +82505,7 @@
     </row>
     <row r="2157">
       <c r="A2157" t="str">
-        <v>Kmtsfe5v88e9o</v>
+        <v>Kmtsferhnv0sr</v>
       </c>
       <c r="B2157" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82581,7 +82581,7 @@
     </row>
     <row r="2159">
       <c r="A2159" t="str">
-        <v>Kmtsfe5v8041b</v>
+        <v>Kmtsferhn89i4</v>
       </c>
       <c r="B2159" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82619,7 +82619,7 @@
     </row>
     <row r="2160">
       <c r="A2160" t="str">
-        <v>Kmtsfe5v8mphb</v>
+        <v>Kmtsferhngl5b</v>
       </c>
       <c r="B2160" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82657,7 +82657,7 @@
     </row>
     <row r="2161">
       <c r="A2161" t="str">
-        <v>Kmtsfe5v8r77b</v>
+        <v>Kmtsferhn95ll</v>
       </c>
       <c r="B2161" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82695,7 +82695,7 @@
     </row>
     <row r="2162">
       <c r="A2162" t="str">
-        <v>Kmtsfe5v8aapa</v>
+        <v>Kmtsferhnxf76</v>
       </c>
       <c r="B2162" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82733,7 +82733,7 @@
     </row>
     <row r="2163">
       <c r="A2163" t="str">
-        <v>Kmtsfe5v8nr54</v>
+        <v>Kmtsferhnaqc7</v>
       </c>
       <c r="B2163" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82771,7 +82771,7 @@
     </row>
     <row r="2164">
       <c r="A2164" t="str">
-        <v>Kmtsfe5v8nyqy</v>
+        <v>Kmtsferhnp1l8</v>
       </c>
       <c r="B2164" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82809,7 +82809,7 @@
     </row>
     <row r="2165">
       <c r="A2165" t="str">
-        <v>Kmtsfe5v8xkl5</v>
+        <v>Kmtsferhngmf3</v>
       </c>
       <c r="B2165" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82885,7 +82885,7 @@
     </row>
     <row r="2167">
       <c r="A2167" t="str">
-        <v>Kmtsfe5v853h0</v>
+        <v>Kmtsferhn7cpy</v>
       </c>
       <c r="B2167" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82923,7 +82923,7 @@
     </row>
     <row r="2168">
       <c r="A2168" t="str">
-        <v>Kmtsfe5v80tor</v>
+        <v>Kmtsferhn3365</v>
       </c>
       <c r="B2168" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82961,7 +82961,7 @@
     </row>
     <row r="2169">
       <c r="A2169" t="str">
-        <v>Kmtsfe5v8nzzr</v>
+        <v>Kmtsferhnmun3</v>
       </c>
       <c r="B2169" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82999,7 +82999,7 @@
     </row>
     <row r="2170">
       <c r="A2170" t="str">
-        <v>Kmtsfe5v8hlv4</v>
+        <v>Kmtsferhn5yd9</v>
       </c>
       <c r="B2170" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83037,7 +83037,7 @@
     </row>
     <row r="2171">
       <c r="A2171" t="str">
-        <v>Kmtsfe5v8rthy</v>
+        <v>Kmtsferhn59hg</v>
       </c>
       <c r="B2171" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83075,7 +83075,7 @@
     </row>
     <row r="2172">
       <c r="A2172" t="str">
-        <v>Kmtsfe5v883wy</v>
+        <v>Kmtsferhndb37</v>
       </c>
       <c r="B2172" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83113,7 +83113,7 @@
     </row>
     <row r="2173">
       <c r="A2173" t="str">
-        <v>Kmtsfe5v8pt35</v>
+        <v>Kmtsferhn836x</v>
       </c>
       <c r="B2173" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83151,7 +83151,7 @@
     </row>
     <row r="2174">
       <c r="A2174" t="str">
-        <v>Kmtsfe5v8z2d6</v>
+        <v>Kmtsferhng8pn</v>
       </c>
       <c r="B2174" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -83189,7 +83189,7 @@
     </row>
     <row r="2175">
       <c r="A2175" t="str">
-        <v>Kmtsfe5v8qp4l</v>
+        <v>Kmtsferhnj06e</v>
       </c>
       <c r="B2175" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83227,7 +83227,7 @@
     </row>
     <row r="2176">
       <c r="A2176" t="str">
-        <v>Kmtsfe5v88ewg</v>
+        <v>Kmtsferhn3nt6</v>
       </c>
       <c r="B2176" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83265,7 +83265,7 @@
     </row>
     <row r="2177">
       <c r="A2177" t="str">
-        <v>Kmtsfe5v9amqw</v>
+        <v>Kmtsferhn8r8l</v>
       </c>
       <c r="B2177" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83303,7 +83303,7 @@
     </row>
     <row r="2178">
       <c r="A2178" t="str">
-        <v>Kmtsfe5v9r1pa</v>
+        <v>Kmtsferhnvwny</v>
       </c>
       <c r="B2178" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83341,7 +83341,7 @@
     </row>
     <row r="2179">
       <c r="A2179" t="str">
-        <v>Kmtsfe5v9adqk</v>
+        <v>Kmtsferhn6ojn</v>
       </c>
       <c r="B2179" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -83379,7 +83379,7 @@
     </row>
     <row r="2180">
       <c r="A2180" t="str">
-        <v>Kmtsfe5v9kyj6</v>
+        <v>Kmtsferhn2a3q</v>
       </c>
       <c r="B2180" t="str">
         <v>Asisten Perpustakaan Penyelia</v>
@@ -83417,7 +83417,7 @@
     </row>
     <row r="2181">
       <c r="A2181" t="str">
-        <v>Kmtsfe5v9uw97</v>
+        <v>Kmtsferhn716b</v>
       </c>
       <c r="B2181" t="str">
         <v>Asisten Perpustakaan Mahir</v>
@@ -83455,7 +83455,7 @@
     </row>
     <row r="2182">
       <c r="A2182" t="str">
-        <v>Kmtsfe5v9slp0</v>
+        <v>Kmtsferhnmft7</v>
       </c>
       <c r="B2182" t="str">
         <v>Asisten Perpustakaan Terampil</v>
@@ -83493,7 +83493,7 @@
     </row>
     <row r="2183">
       <c r="A2183" t="str">
-        <v>Kmtsfe5v91but</v>
+        <v>Kmtsferhntmno</v>
       </c>
       <c r="B2183" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -83531,7 +83531,7 @@
     </row>
     <row r="2184">
       <c r="A2184" t="str">
-        <v>Kmtsfe5v9uh59</v>
+        <v>Kmtsferhnlfpn</v>
       </c>
       <c r="B2184" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -83569,7 +83569,7 @@
     </row>
     <row r="2185">
       <c r="A2185" t="str">
-        <v>Kmtsfe5v9tvxu</v>
+        <v>Kmtsferhnx0mq</v>
       </c>
       <c r="B2185" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -83683,7 +83683,7 @@
     </row>
     <row r="2188">
       <c r="A2188" t="str">
-        <v>Kmtsfe5v9s0cd</v>
+        <v>Kmtsferhndddt</v>
       </c>
       <c r="B2188" t="str">
         <v>Penata Layanan Operasional</v>
@@ -83721,7 +83721,7 @@
     </row>
     <row r="2189">
       <c r="A2189" t="str">
-        <v>Kmtsfe5v9hx4e</v>
+        <v>Kmtsferhn50yq</v>
       </c>
       <c r="B2189" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83759,7 +83759,7 @@
     </row>
     <row r="2190">
       <c r="A2190" t="str">
-        <v>Kmtsfe5v9pfd9</v>
+        <v>Kmtsferhne0l1</v>
       </c>
       <c r="B2190" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -83797,7 +83797,7 @@
     </row>
     <row r="2191">
       <c r="A2191" t="str">
-        <v>Kmtsfe5v9hocs</v>
+        <v>Kmtsferhnusp4</v>
       </c>
       <c r="B2191" t="str">
         <v>Penata Keprotokolan*</v>
@@ -83911,7 +83911,7 @@
     </row>
     <row r="2194">
       <c r="A2194" t="str">
-        <v>Kmtsfe5v96pf7</v>
+        <v>Kmtsferhnfhy9</v>
       </c>
       <c r="B2194" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -83949,7 +83949,7 @@
     </row>
     <row r="2195">
       <c r="A2195" t="str">
-        <v>Kmtsfe5v9rlzj</v>
+        <v>Kmtsferhnjnco</v>
       </c>
       <c r="B2195" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83987,7 +83987,7 @@
     </row>
     <row r="2196">
       <c r="A2196" t="str">
-        <v>Kmtsfe5v92g1u</v>
+        <v>Kmtsferhn9atc</v>
       </c>
       <c r="B2196" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84063,7 +84063,7 @@
     </row>
     <row r="2198">
       <c r="A2198" t="str">
-        <v>Kmtsfe5v9wp83</v>
+        <v>Kmtsferhnu484</v>
       </c>
       <c r="B2198" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84101,7 +84101,7 @@
     </row>
     <row r="2199">
       <c r="A2199" t="str">
-        <v>Kmtsfe5v92buh</v>
+        <v>Kmtsferhnucz2</v>
       </c>
       <c r="B2199" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84139,7 +84139,7 @@
     </row>
     <row r="2200">
       <c r="A2200" t="str">
-        <v>Kmtsfe5v9joc8</v>
+        <v>Kmtsferhn9jb2</v>
       </c>
       <c r="B2200" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84177,7 +84177,7 @@
     </row>
     <row r="2201">
       <c r="A2201" t="str">
-        <v>Kmtsfe5v9cz21</v>
+        <v>Kmtsferhnru8s</v>
       </c>
       <c r="B2201" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84215,7 +84215,7 @@
     </row>
     <row r="2202">
       <c r="A2202" t="str">
-        <v>Kmtsfe5v99dy9</v>
+        <v>Kmtsferhn5cub</v>
       </c>
       <c r="B2202" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84253,7 +84253,7 @@
     </row>
     <row r="2203">
       <c r="A2203" t="str">
-        <v>Kmtsfe5v9hwh9</v>
+        <v>Kmtsferhnl89k</v>
       </c>
       <c r="B2203" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -84291,7 +84291,7 @@
     </row>
     <row r="2204">
       <c r="A2204" t="str">
-        <v>Kmtsfe5v913ar</v>
+        <v>Kmtsferhnij2a</v>
       </c>
       <c r="B2204" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -84405,7 +84405,7 @@
     </row>
     <row r="2207">
       <c r="A2207" t="str">
-        <v>Kmtsfe5v9mfhv</v>
+        <v>Kmtsferhn4k1e</v>
       </c>
       <c r="B2207" t="str">
         <v>Penata Layanan Operasional</v>
@@ -84443,7 +84443,7 @@
     </row>
     <row r="2208">
       <c r="A2208" t="str">
-        <v>Kmtsfe5v9mhm3</v>
+        <v>Kmtsferhnhiqr</v>
       </c>
       <c r="B2208" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84481,7 +84481,7 @@
     </row>
     <row r="2209">
       <c r="A2209" t="str">
-        <v>Kmtsfe5v98z2i</v>
+        <v>Kmtsferhngjd5</v>
       </c>
       <c r="B2209" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84519,7 +84519,7 @@
     </row>
     <row r="2210">
       <c r="A2210" t="str">
-        <v>Kmtsfe5v9f4bq</v>
+        <v>Kmtsferhn8fsr</v>
       </c>
       <c r="B2210" t="str">
         <v>Penata Keprotokolan*</v>
@@ -84633,7 +84633,7 @@
     </row>
     <row r="2213">
       <c r="A2213" t="str">
-        <v>Kmtsfe5v93xnx</v>
+        <v>Kmtsferhnecaf</v>
       </c>
       <c r="B2213" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84671,7 +84671,7 @@
     </row>
     <row r="2214">
       <c r="A2214" t="str">
-        <v>Kmtsfe5v9jvvb</v>
+        <v>Kmtsferhnn8pg</v>
       </c>
       <c r="B2214" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84709,7 +84709,7 @@
     </row>
     <row r="2215">
       <c r="A2215" t="str">
-        <v>Kmtsfe5v9zj48</v>
+        <v>Kmtsferhntieq</v>
       </c>
       <c r="B2215" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84785,7 +84785,7 @@
     </row>
     <row r="2217">
       <c r="A2217" t="str">
-        <v>Kmtsfe5v9mfid</v>
+        <v>Kmtsferhnjvbt</v>
       </c>
       <c r="B2217" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84823,7 +84823,7 @@
     </row>
     <row r="2218">
       <c r="A2218" t="str">
-        <v>Kmtsfe5v9lb0l</v>
+        <v>Kmtsferhn2n1c</v>
       </c>
       <c r="B2218" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84861,7 +84861,7 @@
     </row>
     <row r="2219">
       <c r="A2219" t="str">
-        <v>Kmtsfe5v92355</v>
+        <v>Kmtsferhnraqj</v>
       </c>
       <c r="B2219" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84899,7 +84899,7 @@
     </row>
     <row r="2220">
       <c r="A2220" t="str">
-        <v>Kmtsfe5v9s3fp</v>
+        <v>Kmtsferhnv5b4</v>
       </c>
       <c r="B2220" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84937,7 +84937,7 @@
     </row>
     <row r="2221">
       <c r="A2221" t="str">
-        <v>Kmtsfe5v94ywz</v>
+        <v>Kmtsferhnnacq</v>
       </c>
       <c r="B2221" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84975,7 +84975,7 @@
     </row>
     <row r="2222">
       <c r="A2222" t="str">
-        <v>Kmtsfe5v9q16m</v>
+        <v>Kmtsferhn1jpf</v>
       </c>
       <c r="B2222" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85013,7 +85013,7 @@
     </row>
     <row r="2223">
       <c r="A2223" t="str">
-        <v>Kmtsfe5v9w3ms</v>
+        <v>Kmtsferhnx2oh</v>
       </c>
       <c r="B2223" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85127,7 +85127,7 @@
     </row>
     <row r="2226">
       <c r="A2226" t="str">
-        <v>Kmtsfe5v92xar</v>
+        <v>Kmtsferhnb6nj</v>
       </c>
       <c r="B2226" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85165,7 +85165,7 @@
     </row>
     <row r="2227">
       <c r="A2227" t="str">
-        <v>Kmtsfe5v99a1y</v>
+        <v>Kmtsferhnx7ux</v>
       </c>
       <c r="B2227" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85203,7 +85203,7 @@
     </row>
     <row r="2228">
       <c r="A2228" t="str">
-        <v>Kmtsfe5v93nbt</v>
+        <v>Kmtsferhnnkf3</v>
       </c>
       <c r="B2228" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85241,7 +85241,7 @@
     </row>
     <row r="2229">
       <c r="A2229" t="str">
-        <v>Kmtsfe5v95kzu</v>
+        <v>Kmtsferhnz94j</v>
       </c>
       <c r="B2229" t="str">
         <v>Penata Keprotokolan*</v>
@@ -85355,7 +85355,7 @@
     </row>
     <row r="2232">
       <c r="A2232" t="str">
-        <v>Kmtsfe5v91k6y</v>
+        <v>Kmtsferhnpe9j</v>
       </c>
       <c r="B2232" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85393,7 +85393,7 @@
     </row>
     <row r="2233">
       <c r="A2233" t="str">
-        <v>Kmtsfe5v9da34</v>
+        <v>Kmtsferhn0su0</v>
       </c>
       <c r="B2233" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85431,7 +85431,7 @@
     </row>
     <row r="2234">
       <c r="A2234" t="str">
-        <v>Kmtsfe5v9brgz</v>
+        <v>Kmtsferhnavqz</v>
       </c>
       <c r="B2234" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85507,7 +85507,7 @@
     </row>
     <row r="2236">
       <c r="A2236" t="str">
-        <v>Kmtsfe5v9nsqh</v>
+        <v>Kmtsferhnyq0x</v>
       </c>
       <c r="B2236" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85545,7 +85545,7 @@
     </row>
     <row r="2237">
       <c r="A2237" t="str">
-        <v>Kmtsfe5v9ybmw</v>
+        <v>Kmtsferhnfich</v>
       </c>
       <c r="B2237" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85583,7 +85583,7 @@
     </row>
     <row r="2238">
       <c r="A2238" t="str">
-        <v>Kmtsfe5v94mkh</v>
+        <v>Kmtsferhnkiam</v>
       </c>
       <c r="B2238" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85621,7 +85621,7 @@
     </row>
     <row r="2239">
       <c r="A2239" t="str">
-        <v>Kmtsfe5v9jycm</v>
+        <v>Kmtsferhnacg0</v>
       </c>
       <c r="B2239" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -85659,7 +85659,7 @@
     </row>
     <row r="2240">
       <c r="A2240" t="str">
-        <v>Kmtsfe5v9zz26</v>
+        <v>Kmtsferhn10aj</v>
       </c>
       <c r="B2240" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -85697,7 +85697,7 @@
     </row>
     <row r="2241">
       <c r="A2241" t="str">
-        <v>Kmtsfe5v9ae5a</v>
+        <v>Kmtsferhnmzak</v>
       </c>
       <c r="B2241" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85735,7 +85735,7 @@
     </row>
     <row r="2242">
       <c r="A2242" t="str">
-        <v>Kmtsfe5v966sv</v>
+        <v>Kmtsferhngoyg</v>
       </c>
       <c r="B2242" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85849,7 +85849,7 @@
     </row>
     <row r="2245">
       <c r="A2245" t="str">
-        <v>Kmtsfe5v9wzir</v>
+        <v>Kmtsferhnx78k</v>
       </c>
       <c r="B2245" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85887,7 +85887,7 @@
     </row>
     <row r="2246">
       <c r="A2246" t="str">
-        <v>Kmtsfe5v95bth</v>
+        <v>Kmtsferhn3cli</v>
       </c>
       <c r="B2246" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85925,7 +85925,7 @@
     </row>
     <row r="2247">
       <c r="A2247" t="str">
-        <v>Kmtsfe5v9c02g</v>
+        <v>Kmtsferhnfp33</v>
       </c>
       <c r="B2247" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85963,7 +85963,7 @@
     </row>
     <row r="2248">
       <c r="A2248" t="str">
-        <v>Kmtsfe5v9fkjb</v>
+        <v>Kmtsferhnyu93</v>
       </c>
       <c r="B2248" t="str">
         <v>Penata Keprotokolan*</v>
@@ -86039,7 +86039,7 @@
     </row>
     <row r="2250">
       <c r="A2250" t="str">
-        <v>Kmtsfe5v90v2g</v>
+        <v>Kmtsferhnoqah</v>
       </c>
       <c r="B2250" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86077,7 +86077,7 @@
     </row>
     <row r="2251">
       <c r="A2251" t="str">
-        <v>Kmtsfe5v9uke2</v>
+        <v>Kmtsferhngtct</v>
       </c>
       <c r="B2251" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86115,7 +86115,7 @@
     </row>
     <row r="2252">
       <c r="A2252" t="str">
-        <v>Kmtsfe5v9cdok</v>
+        <v>Kmtsferhnirsb</v>
       </c>
       <c r="B2252" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86153,7 +86153,7 @@
     </row>
     <row r="2253">
       <c r="A2253" t="str">
-        <v>Kmtsfe5v9mok3</v>
+        <v>Kmtsferhno8u9</v>
       </c>
       <c r="B2253" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86191,7 +86191,7 @@
     </row>
     <row r="2254">
       <c r="A2254" t="str">
-        <v>Kmtsfe5v9rwxq</v>
+        <v>Kmtsferhndzss</v>
       </c>
       <c r="B2254" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86305,7 +86305,7 @@
     </row>
     <row r="2257">
       <c r="A2257" t="str">
-        <v>Kmtsfe5v9xy11</v>
+        <v>Kmtsferhn9ydq</v>
       </c>
       <c r="B2257" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86343,7 +86343,7 @@
     </row>
     <row r="2258">
       <c r="A2258" t="str">
-        <v>Kmtsfe5v9ln21</v>
+        <v>Kmtsferhn98xg</v>
       </c>
       <c r="B2258" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86381,7 +86381,7 @@
     </row>
     <row r="2259">
       <c r="A2259" t="str">
-        <v>Kmtsfe5v9311b</v>
+        <v>Kmtsferhn7joz</v>
       </c>
       <c r="B2259" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86457,7 +86457,7 @@
     </row>
     <row r="2261">
       <c r="A2261" t="str">
-        <v>Kmtsfe5v9eyhm</v>
+        <v>Kmtsferhnlilo</v>
       </c>
       <c r="B2261" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86495,7 +86495,7 @@
     </row>
     <row r="2262">
       <c r="A2262" t="str">
-        <v>Kmtsfe5v9lum0</v>
+        <v>Kmtsferhnp7u8</v>
       </c>
       <c r="B2262" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86533,7 +86533,7 @@
     </row>
     <row r="2263">
       <c r="A2263" t="str">
-        <v>Kmtsfe5v9v3e8</v>
+        <v>Kmtsferhnlcau</v>
       </c>
       <c r="B2263" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86571,7 +86571,7 @@
     </row>
     <row r="2264">
       <c r="A2264" t="str">
-        <v>Kmtsfe5v9wuda</v>
+        <v>Kmtsferhnsffy</v>
       </c>
       <c r="B2264" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -86609,7 +86609,7 @@
     </row>
     <row r="2265">
       <c r="A2265" t="str">
-        <v>Kmtsfe5v9k5ry</v>
+        <v>Kmtsferhn4rgr</v>
       </c>
       <c r="B2265" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -86647,7 +86647,7 @@
     </row>
     <row r="2266">
       <c r="A2266" t="str">
-        <v>Kmtsfe5v985dd</v>
+        <v>Kmtsferhnq9ez</v>
       </c>
       <c r="B2266" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86685,7 +86685,7 @@
     </row>
     <row r="2267">
       <c r="A2267" t="str">
-        <v>Kmtsfe5v9c1fc</v>
+        <v>Kmtsferhnqmiu</v>
       </c>
       <c r="B2267" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86799,7 +86799,7 @@
     </row>
     <row r="2270">
       <c r="A2270" t="str">
-        <v>Kmtsfe5v97jmt</v>
+        <v>Kmtsferhnq8no</v>
       </c>
       <c r="B2270" t="str">
         <v>Penata Layanan Operasional</v>
@@ -86837,7 +86837,7 @@
     </row>
     <row r="2271">
       <c r="A2271" t="str">
-        <v>Kmtsfe5v9k41b</v>
+        <v>Kmtsferhnakgg</v>
       </c>
       <c r="B2271" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86875,7 +86875,7 @@
     </row>
     <row r="2272">
       <c r="A2272" t="str">
-        <v>Kmtsfe5v9xugh</v>
+        <v>Kmtsferhntbaz</v>
       </c>
       <c r="B2272" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86913,7 +86913,7 @@
     </row>
     <row r="2273">
       <c r="A2273" t="str">
-        <v>Kmtsfe5v9993n</v>
+        <v>Kmtsferhnyklg</v>
       </c>
       <c r="B2273" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87027,7 +87027,7 @@
     </row>
     <row r="2276">
       <c r="A2276" t="str">
-        <v>Kmtsfe5v9ssf1</v>
+        <v>Kmtsferhnt1o2</v>
       </c>
       <c r="B2276" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87065,7 +87065,7 @@
     </row>
     <row r="2277">
       <c r="A2277" t="str">
-        <v>Kmtsfe5v9crr8</v>
+        <v>Kmtsferhnc9cy</v>
       </c>
       <c r="B2277" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87103,7 +87103,7 @@
     </row>
     <row r="2278">
       <c r="A2278" t="str">
-        <v>Kmtsfe5v9z6z7</v>
+        <v>Kmtsferhnyujv</v>
       </c>
       <c r="B2278" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87179,7 +87179,7 @@
     </row>
     <row r="2280">
       <c r="A2280" t="str">
-        <v>Kmtsfe5v9042i</v>
+        <v>Kmtsferhnkedj</v>
       </c>
       <c r="B2280" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87217,7 +87217,7 @@
     </row>
     <row r="2281">
       <c r="A2281" t="str">
-        <v>Kmtsfe5v9h5p8</v>
+        <v>Kmtsferhncmhm</v>
       </c>
       <c r="B2281" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87255,7 +87255,7 @@
     </row>
     <row r="2282">
       <c r="A2282" t="str">
-        <v>Kmtsfe5v9zky1</v>
+        <v>Kmtsferhnrxf3</v>
       </c>
       <c r="B2282" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87293,7 +87293,7 @@
     </row>
     <row r="2283">
       <c r="A2283" t="str">
-        <v>Kmtsfe5v91gxr</v>
+        <v>Kmtsferhn6m6i</v>
       </c>
       <c r="B2283" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -87331,7 +87331,7 @@
     </row>
     <row r="2284">
       <c r="A2284" t="str">
-        <v>Kmtsfe5v99xkf</v>
+        <v>Kmtsferhnfe59</v>
       </c>
       <c r="B2284" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -87369,7 +87369,7 @@
     </row>
     <row r="2285">
       <c r="A2285" t="str">
-        <v>Kmtsfe5v9v6b9</v>
+        <v>Kmtsferhn8zlw</v>
       </c>
       <c r="B2285" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -87407,7 +87407,7 @@
     </row>
     <row r="2286">
       <c r="A2286" t="str">
-        <v>Kmtsfe5v9lqii</v>
+        <v>Kmtsferhncbxj</v>
       </c>
       <c r="B2286" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -87521,7 +87521,7 @@
     </row>
     <row r="2289">
       <c r="A2289" t="str">
-        <v>Kmtsfe5v9y4i7</v>
+        <v>Kmtsferhnxb8f</v>
       </c>
       <c r="B2289" t="str">
         <v>Penata Layanan Operasional</v>
@@ -87559,7 +87559,7 @@
     </row>
     <row r="2290">
       <c r="A2290" t="str">
-        <v>Kmtsfe5v94leq</v>
+        <v>Kmtsferhn167u</v>
       </c>
       <c r="B2290" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87597,7 +87597,7 @@
     </row>
     <row r="2291">
       <c r="A2291" t="str">
-        <v>Kmtsfe5v9ulrq</v>
+        <v>Kmtsferhncods</v>
       </c>
       <c r="B2291" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87635,7 +87635,7 @@
     </row>
     <row r="2292">
       <c r="A2292" t="str">
-        <v>Kmtsfe5v91z68</v>
+        <v>Kmtsferhntj7t</v>
       </c>
       <c r="B2292" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87749,7 +87749,7 @@
     </row>
     <row r="2295">
       <c r="A2295" t="str">
-        <v>Kmtsfe5v9d9x9</v>
+        <v>Kmtsferhnbjyr</v>
       </c>
       <c r="B2295" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87787,7 +87787,7 @@
     </row>
     <row r="2296">
       <c r="A2296" t="str">
-        <v>Kmtsfe5v9hr8k</v>
+        <v>Kmtsferhn5q69</v>
       </c>
       <c r="B2296" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87825,7 +87825,7 @@
     </row>
     <row r="2297">
       <c r="A2297" t="str">
-        <v>Kmtsfe5v9jfms</v>
+        <v>Kmtsferhnwi9y</v>
       </c>
       <c r="B2297" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87901,7 +87901,7 @@
     </row>
     <row r="2299">
       <c r="A2299" t="str">
-        <v>Kmtsfe5v9ns8v</v>
+        <v>Kmtsferhnd0fx</v>
       </c>
       <c r="B2299" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87939,7 +87939,7 @@
     </row>
     <row r="2300">
       <c r="A2300" t="str">
-        <v>Kmtsfe5v95pn5</v>
+        <v>Kmtsferhnxc8p</v>
       </c>
       <c r="B2300" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87977,7 +87977,7 @@
     </row>
     <row r="2301">
       <c r="A2301" t="str">
-        <v>Kmtsfe5v9v573</v>
+        <v>Kmtsferhnx8d9</v>
       </c>
       <c r="B2301" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88015,7 +88015,7 @@
     </row>
     <row r="2302">
       <c r="A2302" t="str">
-        <v>Kmtsfe5v91fwe</v>
+        <v>Kmtsferhnshd6</v>
       </c>
       <c r="B2302" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -88053,7 +88053,7 @@
     </row>
     <row r="2303">
       <c r="A2303" t="str">
-        <v>Kmtsfe5v9wyxy</v>
+        <v>Kmtsferhn41as</v>
       </c>
       <c r="B2303" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -88091,7 +88091,7 @@
     </row>
     <row r="2304">
       <c r="A2304" t="str">
-        <v>Kmtsfe5v9b0wr</v>
+        <v>Kmtsferhnsphl</v>
       </c>
       <c r="B2304" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -88129,7 +88129,7 @@
     </row>
     <row r="2305">
       <c r="A2305" t="str">
-        <v>Kmtsfe5v9wh3l</v>
+        <v>Kmtsferhn6ahz</v>
       </c>
       <c r="B2305" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -88243,7 +88243,7 @@
     </row>
     <row r="2308">
       <c r="A2308" t="str">
-        <v>Kmtsfe5v9x908</v>
+        <v>Kmtsferhn0bgx</v>
       </c>
       <c r="B2308" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88281,7 +88281,7 @@
     </row>
     <row r="2309">
       <c r="A2309" t="str">
-        <v>Kmtsfe5v9drxf</v>
+        <v>Kmtsferhnxmoi</v>
       </c>
       <c r="B2309" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88319,7 +88319,7 @@
     </row>
     <row r="2310">
       <c r="A2310" t="str">
-        <v>Kmtsfe5v9fad5</v>
+        <v>Kmtsferhnuvn9</v>
       </c>
       <c r="B2310" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88357,7 +88357,7 @@
     </row>
     <row r="2311">
       <c r="A2311" t="str">
-        <v>Kmtsfe5v9i5e2</v>
+        <v>Kmtsferhngz5x</v>
       </c>
       <c r="B2311" t="str">
         <v>Penata Keprotokolan*</v>
@@ -88471,7 +88471,7 @@
     </row>
     <row r="2314">
       <c r="A2314" t="str">
-        <v>Kmtsfe5v99cwm</v>
+        <v>Kmtsferhn3f91</v>
       </c>
       <c r="B2314" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88509,7 +88509,7 @@
     </row>
     <row r="2315">
       <c r="A2315" t="str">
-        <v>Kmtsfe5v9s9yx</v>
+        <v>Kmtsferhnpf6w</v>
       </c>
       <c r="B2315" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88547,7 +88547,7 @@
     </row>
     <row r="2316">
       <c r="A2316" t="str">
-        <v>Kmtsfe5v999xz</v>
+        <v>Kmtsferhn3xuk</v>
       </c>
       <c r="B2316" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88623,7 +88623,7 @@
     </row>
     <row r="2318">
       <c r="A2318" t="str">
-        <v>Kmtsfe5v9bhns</v>
+        <v>Kmtsferhnt631</v>
       </c>
       <c r="B2318" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88661,7 +88661,7 @@
     </row>
     <row r="2319">
       <c r="A2319" t="str">
-        <v>Kmtsfe5v93t5d</v>
+        <v>Kmtsferhnyy5g</v>
       </c>
       <c r="B2319" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88699,7 +88699,7 @@
     </row>
     <row r="2320">
       <c r="A2320" t="str">
-        <v>Kmtsfe5v9g4ij</v>
+        <v>Kmtsferhnxm46</v>
       </c>
       <c r="B2320" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88775,7 +88775,7 @@
     </row>
     <row r="2322">
       <c r="A2322" t="str">
-        <v>Kmtsfe5v9jp41</v>
+        <v>Kmtsferhn8n59</v>
       </c>
       <c r="B2322" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88813,7 +88813,7 @@
     </row>
     <row r="2323">
       <c r="A2323" t="str">
-        <v>Kmtsfe5v945z6</v>
+        <v>Kmtsferhnffrc</v>
       </c>
       <c r="B2323" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88851,7 +88851,7 @@
     </row>
     <row r="2324">
       <c r="A2324" t="str">
-        <v>Kmtsfe5v9zjcg</v>
+        <v>Kmtsferhn1zfn</v>
       </c>
       <c r="B2324" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88927,7 +88927,7 @@
     </row>
     <row r="2326">
       <c r="A2326" t="str">
-        <v>Kmtsfe5v9j750</v>
+        <v>Kmtsferhn20yy</v>
       </c>
       <c r="B2326" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88965,7 +88965,7 @@
     </row>
     <row r="2327">
       <c r="A2327" t="str">
-        <v>Kmtsfe5v9a5e8</v>
+        <v>Kmtsferhn53z6</v>
       </c>
       <c r="B2327" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89003,7 +89003,7 @@
     </row>
     <row r="2328">
       <c r="A2328" t="str">
-        <v>Kmtsfe5v9k5ll</v>
+        <v>Kmtsferhn2vqa</v>
       </c>
       <c r="B2328" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89117,7 +89117,7 @@
     </row>
     <row r="2331">
       <c r="A2331" t="str">
-        <v>Kmtsfe5v9nilm</v>
+        <v>Kmtsferhntt83</v>
       </c>
       <c r="B2331" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89155,7 +89155,7 @@
     </row>
     <row r="2332">
       <c r="A2332" t="str">
-        <v>Kmtsfe5v9iisu</v>
+        <v>Kmtsferhn99x7</v>
       </c>
       <c r="B2332" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89193,7 +89193,7 @@
     </row>
     <row r="2333">
       <c r="A2333" t="str">
-        <v>Kmtsfe5v94acl</v>
+        <v>Kmtsferhnx33b</v>
       </c>
       <c r="B2333" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89269,7 +89269,7 @@
     </row>
     <row r="2335">
       <c r="A2335" t="str">
-        <v>Kmtsfe5v9kney</v>
+        <v>Kmtsferhn7amp</v>
       </c>
       <c r="B2335" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89307,7 +89307,7 @@
     </row>
     <row r="2336">
       <c r="A2336" t="str">
-        <v>Kmtsfe5v9n3l1</v>
+        <v>Kmtsferhns2ml</v>
       </c>
       <c r="B2336" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89345,7 +89345,7 @@
     </row>
     <row r="2337">
       <c r="A2337" t="str">
-        <v>Kmtsfe5v9kns1</v>
+        <v>Kmtsferhn06y2</v>
       </c>
       <c r="B2337" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89383,7 +89383,7 @@
     </row>
     <row r="2338">
       <c r="A2338" t="str">
-        <v>Kmtsfe5v9vsai</v>
+        <v>Kmtsferhn54ro</v>
       </c>
       <c r="B2338" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -89421,7 +89421,7 @@
     </row>
     <row r="2339">
       <c r="A2339" t="str">
-        <v>Kmtsfe5v9c4wi</v>
+        <v>Kmtsferhn2qpi</v>
       </c>
       <c r="B2339" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -89459,7 +89459,7 @@
     </row>
     <row r="2340">
       <c r="A2340" t="str">
-        <v>Kmtsfe5v92zzk</v>
+        <v>Kmtsferhn3tnp</v>
       </c>
       <c r="B2340" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -89497,7 +89497,7 @@
     </row>
     <row r="2341">
       <c r="A2341" t="str">
-        <v>Kmtsfe5v9ne1h</v>
+        <v>Kmtsferhn24dz</v>
       </c>
       <c r="B2341" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -89611,7 +89611,7 @@
     </row>
     <row r="2344">
       <c r="A2344" t="str">
-        <v>Kmtsfe5v9f5yo</v>
+        <v>Kmtsferhncan8</v>
       </c>
       <c r="B2344" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89649,7 +89649,7 @@
     </row>
     <row r="2345">
       <c r="A2345" t="str">
-        <v>Kmtsfe5v951nz</v>
+        <v>Kmtsferhngo7q</v>
       </c>
       <c r="B2345" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89687,7 +89687,7 @@
     </row>
     <row r="2346">
       <c r="A2346" t="str">
-        <v>Kmtsfe5v9yuzx</v>
+        <v>Kmtsferhnlu0f</v>
       </c>
       <c r="B2346" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89801,7 +89801,7 @@
     </row>
     <row r="2349">
       <c r="A2349" t="str">
-        <v>Kmtsfe5v9y8sc</v>
+        <v>Kmtsferhn3wow</v>
       </c>
       <c r="B2349" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89839,7 +89839,7 @@
     </row>
     <row r="2350">
       <c r="A2350" t="str">
-        <v>Kmtsfe5v9how0</v>
+        <v>Kmtsferhnn7gf</v>
       </c>
       <c r="B2350" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89877,7 +89877,7 @@
     </row>
     <row r="2351">
       <c r="A2351" t="str">
-        <v>Kmtsfe5v95ug8</v>
+        <v>Kmtsferhnvx43</v>
       </c>
       <c r="B2351" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89953,7 +89953,7 @@
     </row>
     <row r="2353">
       <c r="A2353" t="str">
-        <v>Kmtsfe5v9xbna</v>
+        <v>Kmtsferhnu98d</v>
       </c>
       <c r="B2353" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89991,7 +89991,7 @@
     </row>
     <row r="2354">
       <c r="A2354" t="str">
-        <v>Kmtsfe5v9xvsa</v>
+        <v>Kmtsferhnfo5u</v>
       </c>
       <c r="B2354" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90029,7 +90029,7 @@
     </row>
     <row r="2355">
       <c r="A2355" t="str">
-        <v>Kmtsfe5v9l3j5</v>
+        <v>Kmtsferhn11xg</v>
       </c>
       <c r="B2355" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90067,7 +90067,7 @@
     </row>
     <row r="2356">
       <c r="A2356" t="str">
-        <v>Kmtsfe5v925ho</v>
+        <v>Kmtsferhndzsm</v>
       </c>
       <c r="B2356" t="str">
         <v>Penata Keprotokolan*</v>
@@ -90143,7 +90143,7 @@
     </row>
     <row r="2358">
       <c r="A2358" t="str">
-        <v>Kmtsfe5v9w9n4</v>
+        <v>Kmtsferhnzcxu</v>
       </c>
       <c r="B2358" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90181,7 +90181,7 @@
     </row>
     <row r="2359">
       <c r="A2359" t="str">
-        <v>Kmtsfe5v9mm8q</v>
+        <v>Kmtsferhnpved</v>
       </c>
       <c r="B2359" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90219,7 +90219,7 @@
     </row>
     <row r="2360">
       <c r="A2360" t="str">
-        <v>Kmtsfe5v96yvy</v>
+        <v>Kmtsferhnxegl</v>
       </c>
       <c r="B2360" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90333,7 +90333,7 @@
     </row>
     <row r="2363">
       <c r="A2363" t="str">
-        <v>Kmtsfe5v9cjcg</v>
+        <v>Kmtsferhnew9u</v>
       </c>
       <c r="B2363" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90371,7 +90371,7 @@
     </row>
     <row r="2364">
       <c r="A2364" t="str">
-        <v>Kmtsfe5v92znu</v>
+        <v>Kmtsferhnjjyi</v>
       </c>
       <c r="B2364" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90409,7 +90409,7 @@
     </row>
     <row r="2365">
       <c r="A2365" t="str">
-        <v>Kmtsfe5vaqt2n</v>
+        <v>Kmtsferhnj321</v>
       </c>
       <c r="B2365" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90485,7 +90485,7 @@
     </row>
     <row r="2367">
       <c r="A2367" t="str">
-        <v>Kmtsfe5va2mhp</v>
+        <v>Kmtsferhn629x</v>
       </c>
       <c r="B2367" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90523,7 +90523,7 @@
     </row>
     <row r="2368">
       <c r="A2368" t="str">
-        <v>Kmtsfe5va6kym</v>
+        <v>Kmtsferhnf94g</v>
       </c>
       <c r="B2368" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90561,7 +90561,7 @@
     </row>
     <row r="2369">
       <c r="A2369" t="str">
-        <v>Kmtsfe5vaw4tl</v>
+        <v>Kmtsferhnyntp</v>
       </c>
       <c r="B2369" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90637,7 +90637,7 @@
     </row>
     <row r="2371">
       <c r="A2371" t="str">
-        <v>Kmtsfe5vaqs5d</v>
+        <v>Kmtsferhn1eah</v>
       </c>
       <c r="B2371" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90675,7 +90675,7 @@
     </row>
     <row r="2372">
       <c r="A2372" t="str">
-        <v>Kmtsfe5vas8vj</v>
+        <v>Kmtsferhny17e</v>
       </c>
       <c r="B2372" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90713,7 +90713,7 @@
     </row>
     <row r="2373">
       <c r="A2373" t="str">
-        <v>Kmtsfe5va7kl9</v>
+        <v>Kmtsferhn40t3</v>
       </c>
       <c r="B2373" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90789,7 +90789,7 @@
     </row>
     <row r="2375">
       <c r="A2375" t="str">
-        <v>Kmtsfe5va0862</v>
+        <v>Kmtsferhn0apd</v>
       </c>
       <c r="B2375" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90827,7 +90827,7 @@
     </row>
     <row r="2376">
       <c r="A2376" t="str">
-        <v>Kmtsfe5va40rc</v>
+        <v>Kmtsferhnsi3s</v>
       </c>
       <c r="B2376" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90865,7 +90865,7 @@
     </row>
     <row r="2377">
       <c r="A2377" t="str">
-        <v>Kmtsfe5vaiv18</v>
+        <v>Kmtsferhnd4bh</v>
       </c>
       <c r="B2377" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90903,7 +90903,7 @@
     </row>
     <row r="2378">
       <c r="A2378" t="str">
-        <v>Kmtsfe5vadrxi</v>
+        <v>Kmtsferhn5agx</v>
       </c>
       <c r="B2378" t="str">
         <v xml:space="preserve">Analis Pembiayaan Risiko dan Keuangan/ Analis Keuangan Negara Ahli Utama									</v>

--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -78173,7 +78173,7 @@
     </row>
     <row r="2043">
       <c r="A2043" t="str">
-        <v>Kmtsferhmr99w</v>
+        <v>Kmtsffp8ldl0s</v>
       </c>
       <c r="B2043" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78211,7 +78211,7 @@
     </row>
     <row r="2044">
       <c r="A2044" t="str">
-        <v>Kmtsferhmqbib</v>
+        <v>Kmtsffp8lgm0d</v>
       </c>
       <c r="B2044" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78249,7 +78249,7 @@
     </row>
     <row r="2045">
       <c r="A2045" t="str">
-        <v>Kmtsferhmxfzj</v>
+        <v>Kmtsffp8lyxu4</v>
       </c>
       <c r="B2045" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78325,7 +78325,7 @@
     </row>
     <row r="2047">
       <c r="A2047" t="str">
-        <v>Kmtsferhm25g3</v>
+        <v>Kmtsffp8ljwvy</v>
       </c>
       <c r="B2047" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78363,7 +78363,7 @@
     </row>
     <row r="2048">
       <c r="A2048" t="str">
-        <v>Kmtsferhm9ouv</v>
+        <v>Kmtsffp8lutlk</v>
       </c>
       <c r="B2048" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78401,7 +78401,7 @@
     </row>
     <row r="2049">
       <c r="A2049" t="str">
-        <v>Kmtsferhmlcv8</v>
+        <v>Kmtsffp8ltrrr</v>
       </c>
       <c r="B2049" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78477,7 +78477,7 @@
     </row>
     <row r="2051">
       <c r="A2051" t="str">
-        <v>Kmtsferhmkg6a</v>
+        <v>Kmtsffp8l2mum</v>
       </c>
       <c r="B2051" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78515,7 +78515,7 @@
     </row>
     <row r="2052">
       <c r="A2052" t="str">
-        <v>Kmtsferhmzdy4</v>
+        <v>Kmtsffp8l3rnn</v>
       </c>
       <c r="B2052" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78553,7 +78553,7 @@
     </row>
     <row r="2053">
       <c r="A2053" t="str">
-        <v>Kmtsferhml8en</v>
+        <v>Kmtsffp8lihi4</v>
       </c>
       <c r="B2053" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78591,7 +78591,7 @@
     </row>
     <row r="2054">
       <c r="A2054" t="str">
-        <v>Kmtsferhmrrvm</v>
+        <v>Kmtsffp8lna2e</v>
       </c>
       <c r="B2054" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -78629,7 +78629,7 @@
     </row>
     <row r="2055">
       <c r="A2055" t="str">
-        <v>Kmtsferhm7epw</v>
+        <v>Kmtsffp8l0cyf</v>
       </c>
       <c r="B2055" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -78667,7 +78667,7 @@
     </row>
     <row r="2056">
       <c r="A2056" t="str">
-        <v>Kmtsferhm91bq</v>
+        <v>Kmtsffp8leriu</v>
       </c>
       <c r="B2056" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -78705,7 +78705,7 @@
     </row>
     <row r="2057">
       <c r="A2057" t="str">
-        <v>Kmtsferhmxn6k</v>
+        <v>Kmtsffp8lq5xk</v>
       </c>
       <c r="B2057" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -78743,7 +78743,7 @@
     </row>
     <row r="2058">
       <c r="A2058" t="str">
-        <v>Kmtsferhmuccz</v>
+        <v>Kmtsffp8lhdkf</v>
       </c>
       <c r="B2058" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -78857,7 +78857,7 @@
     </row>
     <row r="2061">
       <c r="A2061" t="str">
-        <v>Kmtsferhm1kkq</v>
+        <v>Kmtsffp8l4j3c</v>
       </c>
       <c r="B2061" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78895,7 +78895,7 @@
     </row>
     <row r="2062">
       <c r="A2062" t="str">
-        <v>Kmtsferhmoj64</v>
+        <v>Kmtsffp8l809b</v>
       </c>
       <c r="B2062" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78933,7 +78933,7 @@
     </row>
     <row r="2063">
       <c r="A2063" t="str">
-        <v>Kmtsferhm8l4y</v>
+        <v>Kmtsffp8lvobd</v>
       </c>
       <c r="B2063" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79009,7 +79009,7 @@
     </row>
     <row r="2065">
       <c r="A2065" t="str">
-        <v>Kmtsferhms2ct</v>
+        <v>Kmtsffp8l0dz9</v>
       </c>
       <c r="B2065" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79047,7 +79047,7 @@
     </row>
     <row r="2066">
       <c r="A2066" t="str">
-        <v>Kmtsferhmoifl</v>
+        <v>Kmtsffp8lv33n</v>
       </c>
       <c r="B2066" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79085,7 +79085,7 @@
     </row>
     <row r="2067">
       <c r="A2067" t="str">
-        <v>Kmtsferhm8bs4</v>
+        <v>Kmtsffp8lxt1l</v>
       </c>
       <c r="B2067" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79161,7 +79161,7 @@
     </row>
     <row r="2069">
       <c r="A2069" t="str">
-        <v>Kmtsferhmg27y</v>
+        <v>Kmtsffp8ljqow</v>
       </c>
       <c r="B2069" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79199,7 +79199,7 @@
     </row>
     <row r="2070">
       <c r="A2070" t="str">
-        <v>Kmtsferhm8goy</v>
+        <v>Kmtsffp8l1p4p</v>
       </c>
       <c r="B2070" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79237,7 +79237,7 @@
     </row>
     <row r="2071">
       <c r="A2071" t="str">
-        <v>Kmtsferhmmo90</v>
+        <v>Kmtsffp8lrvf1</v>
       </c>
       <c r="B2071" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79313,7 +79313,7 @@
     </row>
     <row r="2073">
       <c r="A2073" t="str">
-        <v>Kmtsferhmstrm</v>
+        <v>Kmtsffp8ljsmb</v>
       </c>
       <c r="B2073" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79351,7 +79351,7 @@
     </row>
     <row r="2074">
       <c r="A2074" t="str">
-        <v>Kmtsferhm45jj</v>
+        <v>Kmtsffp8lpnzb</v>
       </c>
       <c r="B2074" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79389,7 +79389,7 @@
     </row>
     <row r="2075">
       <c r="A2075" t="str">
-        <v>Kmtsferhmi9fs</v>
+        <v>Kmtsffp8lv2p1</v>
       </c>
       <c r="B2075" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79427,7 +79427,7 @@
     </row>
     <row r="2076">
       <c r="A2076" t="str">
-        <v>Kmtsferhmfvxk</v>
+        <v>Kmtsffp8lup77</v>
       </c>
       <c r="B2076" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -79465,7 +79465,7 @@
     </row>
     <row r="2077">
       <c r="A2077" t="str">
-        <v>Kmtsferhmhica</v>
+        <v>Kmtsffp8lxo3h</v>
       </c>
       <c r="B2077" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -79503,7 +79503,7 @@
     </row>
     <row r="2078">
       <c r="A2078" t="str">
-        <v>Kmtsferhmcsgx</v>
+        <v>Kmtsffp8llcqi</v>
       </c>
       <c r="B2078" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -79541,7 +79541,7 @@
     </row>
     <row r="2079">
       <c r="A2079" t="str">
-        <v>Kmtsferhmd9ze</v>
+        <v>Kmtsffp8lg81n</v>
       </c>
       <c r="B2079" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -79579,7 +79579,7 @@
     </row>
     <row r="2080">
       <c r="A2080" t="str">
-        <v>Kmtsferhm2l86</v>
+        <v>Kmtsffp8l0fuw</v>
       </c>
       <c r="B2080" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -79617,7 +79617,7 @@
     </row>
     <row r="2081">
       <c r="A2081" t="str">
-        <v>Kmtsferhmk7cv</v>
+        <v>Kmtsffp8lpx4v</v>
       </c>
       <c r="B2081" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -79655,7 +79655,7 @@
     </row>
     <row r="2082">
       <c r="A2082" t="str">
-        <v>Kmtsferhmvx99</v>
+        <v>Kmtsffp8l6ia3</v>
       </c>
       <c r="B2082" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -79769,7 +79769,7 @@
     </row>
     <row r="2085">
       <c r="A2085" t="str">
-        <v>Kmtsferhmj8hz</v>
+        <v>Kmtsffp8l0ah0</v>
       </c>
       <c r="B2085" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79807,7 +79807,7 @@
     </row>
     <row r="2086">
       <c r="A2086" t="str">
-        <v>Kmtsferhm7eo7</v>
+        <v>Kmtsffp8lizj7</v>
       </c>
       <c r="B2086" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79845,7 +79845,7 @@
     </row>
     <row r="2087">
       <c r="A2087" t="str">
-        <v>Kmtsferhmcds3</v>
+        <v>Kmtsffp8lz6em</v>
       </c>
       <c r="B2087" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79921,7 +79921,7 @@
     </row>
     <row r="2089">
       <c r="A2089" t="str">
-        <v>Kmtsferhmn81g</v>
+        <v>Kmtsffp8l8f4l</v>
       </c>
       <c r="B2089" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79959,7 +79959,7 @@
     </row>
     <row r="2090">
       <c r="A2090" t="str">
-        <v>Kmtsferhmf254</v>
+        <v>Kmtsffp8ljwxj</v>
       </c>
       <c r="B2090" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79997,7 +79997,7 @@
     </row>
     <row r="2091">
       <c r="A2091" t="str">
-        <v>Kmtsferhmigo8</v>
+        <v>Kmtsffp8lrhfo</v>
       </c>
       <c r="B2091" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80073,7 +80073,7 @@
     </row>
     <row r="2093">
       <c r="A2093" t="str">
-        <v>Kmtsferhmtuqw</v>
+        <v>Kmtsffp8lsl3q</v>
       </c>
       <c r="B2093" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80111,7 +80111,7 @@
     </row>
     <row r="2094">
       <c r="A2094" t="str">
-        <v>Kmtsferhm741k</v>
+        <v>Kmtsffp8l694k</v>
       </c>
       <c r="B2094" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80149,7 +80149,7 @@
     </row>
     <row r="2095">
       <c r="A2095" t="str">
-        <v>Kmtsferhmahsr</v>
+        <v>Kmtsffp8lrk00</v>
       </c>
       <c r="B2095" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80187,7 +80187,7 @@
     </row>
     <row r="2096">
       <c r="A2096" t="str">
-        <v>Kmtsferhmecnl</v>
+        <v>Kmtsffp8lajis</v>
       </c>
       <c r="B2096" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -80225,7 +80225,7 @@
     </row>
     <row r="2097">
       <c r="A2097" t="str">
-        <v>Kmtsferhmxi92</v>
+        <v>Kmtsffp8lo9vx</v>
       </c>
       <c r="B2097" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Muda</v>
@@ -80263,7 +80263,7 @@
     </row>
     <row r="2098">
       <c r="A2098" t="str">
-        <v>Kmtsferhm0onl</v>
+        <v>Kmtsffp8lb2os</v>
       </c>
       <c r="B2098" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -80301,7 +80301,7 @@
     </row>
     <row r="2099">
       <c r="A2099" t="str">
-        <v>Kmtsferhmimju</v>
+        <v>Kmtsffp8lyy74</v>
       </c>
       <c r="B2099" t="str">
         <v>Pranata Keuangan APBN Penyelia/Pengawas Keuangan Negara Penyelia</v>
@@ -80339,7 +80339,7 @@
     </row>
     <row r="2100">
       <c r="A2100" t="str">
-        <v>Kmtsferhmkoap</v>
+        <v>Kmtsffp8l7slf</v>
       </c>
       <c r="B2100" t="str">
         <v>Pranata Keuangan APBN Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -80377,7 +80377,7 @@
     </row>
     <row r="2101">
       <c r="A2101" t="str">
-        <v>Kmtsferhmhxel</v>
+        <v>Kmtsffp8lgnfp</v>
       </c>
       <c r="B2101" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -80415,7 +80415,7 @@
     </row>
     <row r="2102">
       <c r="A2102" t="str">
-        <v>Kmtsferhmih3m</v>
+        <v>Kmtsffp8l3he8</v>
       </c>
       <c r="B2102" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -80453,7 +80453,7 @@
     </row>
     <row r="2103">
       <c r="A2103" t="str">
-        <v>Kmtsferhm0q6f</v>
+        <v>Kmtsffp8l13h8</v>
       </c>
       <c r="B2103" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -80491,7 +80491,7 @@
     </row>
     <row r="2104">
       <c r="A2104" t="str">
-        <v>Kmtsferhmhnxh</v>
+        <v>Kmtsffp8lb67f</v>
       </c>
       <c r="B2104" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -80529,7 +80529,7 @@
     </row>
     <row r="2105">
       <c r="A2105" t="str">
-        <v>Kmtsferhm9j92</v>
+        <v>Kmtsffp8lxcsk</v>
       </c>
       <c r="B2105" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -80567,7 +80567,7 @@
     </row>
     <row r="2106">
       <c r="A2106" t="str">
-        <v>Kmtsferhm6r11</v>
+        <v>Kmtsffp8l53e4</v>
       </c>
       <c r="B2106" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -80681,7 +80681,7 @@
     </row>
     <row r="2109">
       <c r="A2109" t="str">
-        <v>Kmtsferhme1wl</v>
+        <v>Kmtsffp8lzq8d</v>
       </c>
       <c r="B2109" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80719,7 +80719,7 @@
     </row>
     <row r="2110">
       <c r="A2110" t="str">
-        <v>Kmtsferhmmd78</v>
+        <v>Kmtsffp8ljmdw</v>
       </c>
       <c r="B2110" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80757,7 +80757,7 @@
     </row>
     <row r="2111">
       <c r="A2111" t="str">
-        <v>Kmtsferhm279s</v>
+        <v>Kmtsffp8l1jtt</v>
       </c>
       <c r="B2111" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80833,7 +80833,7 @@
     </row>
     <row r="2113">
       <c r="A2113" t="str">
-        <v>Kmtsferhmdd1d</v>
+        <v>Kmtsffp8lnw5l</v>
       </c>
       <c r="B2113" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80871,7 +80871,7 @@
     </row>
     <row r="2114">
       <c r="A2114" t="str">
-        <v>Kmtsferhmgv1g</v>
+        <v>Kmtsffp8lo2ob</v>
       </c>
       <c r="B2114" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80909,7 +80909,7 @@
     </row>
     <row r="2115">
       <c r="A2115" t="str">
-        <v>Kmtsferhm3lhw</v>
+        <v>Kmtsffp8lwjsm</v>
       </c>
       <c r="B2115" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80985,7 +80985,7 @@
     </row>
     <row r="2117">
       <c r="A2117" t="str">
-        <v>Kmtsferhmuuot</v>
+        <v>Kmtsffp8lerd8</v>
       </c>
       <c r="B2117" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -81023,7 +81023,7 @@
     </row>
     <row r="2118">
       <c r="A2118" t="str">
-        <v>Kmtsferhmtyl2</v>
+        <v>Kmtsffp8lzrrv</v>
       </c>
       <c r="B2118" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81061,7 +81061,7 @@
     </row>
     <row r="2119">
       <c r="A2119" t="str">
-        <v>Kmtsferhmxs33</v>
+        <v>Kmtsffp8le668</v>
       </c>
       <c r="B2119" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81099,7 +81099,7 @@
     </row>
     <row r="2120">
       <c r="A2120" t="str">
-        <v>Kmtsferhma1i7</v>
+        <v>Kmtsffp8ltikn</v>
       </c>
       <c r="B2120" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -81137,7 +81137,7 @@
     </row>
     <row r="2121">
       <c r="A2121" t="str">
-        <v>Kmtsferhmr9ah</v>
+        <v>Kmtsffp8leeeo</v>
       </c>
       <c r="B2121" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -81175,7 +81175,7 @@
     </row>
     <row r="2122">
       <c r="A2122" t="str">
-        <v>Kmtsferhm9ckf</v>
+        <v>Kmtsffp8lfwcd</v>
       </c>
       <c r="B2122" t="str">
         <v>Pengawas Keuangan Negara Mahir</v>
@@ -81213,7 +81213,7 @@
     </row>
     <row r="2123">
       <c r="A2123" t="str">
-        <v>Kmtsferhm3juh</v>
+        <v>Kmtsffp8logwy</v>
       </c>
       <c r="B2123" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -81327,7 +81327,7 @@
     </row>
     <row r="2126">
       <c r="A2126" t="str">
-        <v>Kmtsferhm6uk6</v>
+        <v>Kmtsffp8lq1vv</v>
       </c>
       <c r="B2126" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81365,7 +81365,7 @@
     </row>
     <row r="2127">
       <c r="A2127" t="str">
-        <v>Kmtsferhmolg9</v>
+        <v>Kmtsffp8lkwiz</v>
       </c>
       <c r="B2127" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81403,7 +81403,7 @@
     </row>
     <row r="2128">
       <c r="A2128" t="str">
-        <v>Kmtsferhmngbo</v>
+        <v>Kmtsffp8lvy9c</v>
       </c>
       <c r="B2128" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81441,7 +81441,7 @@
     </row>
     <row r="2129">
       <c r="A2129" t="str">
-        <v>Kmtsferhmepfb</v>
+        <v>Kmtsffp8ldnzm</v>
       </c>
       <c r="B2129" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81517,7 +81517,7 @@
     </row>
     <row r="2131">
       <c r="A2131" t="str">
-        <v>Kmtsferhmenp7</v>
+        <v>Kmtsffp8lhj46</v>
       </c>
       <c r="B2131" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81555,7 +81555,7 @@
     </row>
     <row r="2132">
       <c r="A2132" t="str">
-        <v>Kmtsferhmol5e</v>
+        <v>Kmtsffp8la5fb</v>
       </c>
       <c r="B2132" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81593,7 +81593,7 @@
     </row>
     <row r="2133">
       <c r="A2133" t="str">
-        <v>Kmtsferhmjvzo</v>
+        <v>Kmtsffp8llm6f</v>
       </c>
       <c r="B2133" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81631,7 +81631,7 @@
     </row>
     <row r="2134">
       <c r="A2134" t="str">
-        <v>Kmtsferhmb6jv</v>
+        <v>Kmtsffp8ludr0</v>
       </c>
       <c r="B2134" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81707,7 +81707,7 @@
     </row>
     <row r="2136">
       <c r="A2136" t="str">
-        <v>Kmtsferhmayhk</v>
+        <v>Kmtsffp8lp4ii</v>
       </c>
       <c r="B2136" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81745,7 +81745,7 @@
     </row>
     <row r="2137">
       <c r="A2137" t="str">
-        <v>Kmtsferhmkxhd</v>
+        <v>Kmtsffp8lqu8a</v>
       </c>
       <c r="B2137" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81783,7 +81783,7 @@
     </row>
     <row r="2138">
       <c r="A2138" t="str">
-        <v>Kmtsferhmhfaq</v>
+        <v>Kmtsffp8lee2o</v>
       </c>
       <c r="B2138" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81821,7 +81821,7 @@
     </row>
     <row r="2139">
       <c r="A2139" t="str">
-        <v>Kmtsferhmplap</v>
+        <v>Kmtsffp8lzl26</v>
       </c>
       <c r="B2139" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -81859,7 +81859,7 @@
     </row>
     <row r="2140">
       <c r="A2140" t="str">
-        <v>Kmtsferhmcnpk</v>
+        <v>Kmtsffp8l83v0</v>
       </c>
       <c r="B2140" t="str">
         <v>Pengawas Keuangan Negara Pertama</v>
@@ -81897,7 +81897,7 @@
     </row>
     <row r="2141">
       <c r="A2141" t="str">
-        <v>Kmtsferhmfpfl</v>
+        <v>Kmtsffp8lw617</v>
       </c>
       <c r="B2141" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -81935,7 +81935,7 @@
     </row>
     <row r="2142">
       <c r="A2142" t="str">
-        <v>Kmtsferhm9e02</v>
+        <v>Kmtsffp8l07xs</v>
       </c>
       <c r="B2142" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -81973,7 +81973,7 @@
     </row>
     <row r="2143">
       <c r="A2143" t="str">
-        <v>Kmtsferhm9yf7</v>
+        <v>Kmtsffp8luj9x</v>
       </c>
       <c r="B2143" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -82011,7 +82011,7 @@
     </row>
     <row r="2144">
       <c r="A2144" t="str">
-        <v>Kmtsferhmhhh8</v>
+        <v>Kmtsffp8l1ydt</v>
       </c>
       <c r="B2144" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -82049,7 +82049,7 @@
     </row>
     <row r="2145">
       <c r="A2145" t="str">
-        <v>Kmtsferhmoauy</v>
+        <v>Kmtsffp8lq7za</v>
       </c>
       <c r="B2145" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -82087,7 +82087,7 @@
     </row>
     <row r="2146">
       <c r="A2146" t="str">
-        <v>Kmtsferhmnf0c</v>
+        <v>Kmtsffp8lldha</v>
       </c>
       <c r="B2146" t="str">
         <v>Arsiparis Penyelia</v>
@@ -82125,7 +82125,7 @@
     </row>
     <row r="2147">
       <c r="A2147" t="str">
-        <v>Kmtsferhm9g3m</v>
+        <v>Kmtsffp8lc60l</v>
       </c>
       <c r="B2147" t="str">
         <v>Arsiparis Mahir</v>
@@ -82163,7 +82163,7 @@
     </row>
     <row r="2148">
       <c r="A2148" t="str">
-        <v>Kmtsferhm9z7c</v>
+        <v>Kmtsffp8lkegx</v>
       </c>
       <c r="B2148" t="str">
         <v>Arsiparis Terampil</v>
@@ -82277,7 +82277,7 @@
     </row>
     <row r="2151">
       <c r="A2151" t="str">
-        <v>Kmtsferhn7s1m</v>
+        <v>Kmtsffp8lk002</v>
       </c>
       <c r="B2151" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -82315,7 +82315,7 @@
     </row>
     <row r="2152">
       <c r="A2152" t="str">
-        <v>Kmtsferhnfb2y</v>
+        <v>Kmtsffp8l5we7</v>
       </c>
       <c r="B2152" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82353,7 +82353,7 @@
     </row>
     <row r="2153">
       <c r="A2153" t="str">
-        <v>Kmtsferhnwkqj</v>
+        <v>Kmtsffp8llib5</v>
       </c>
       <c r="B2153" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82391,7 +82391,7 @@
     </row>
     <row r="2154">
       <c r="A2154" t="str">
-        <v>Kmtsferhngue4</v>
+        <v>Kmtsffp8ltnab</v>
       </c>
       <c r="B2154" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82429,7 +82429,7 @@
     </row>
     <row r="2155">
       <c r="A2155" t="str">
-        <v>Kmtsferhnvqy0</v>
+        <v>Kmtsffp8lce29</v>
       </c>
       <c r="B2155" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82467,7 +82467,7 @@
     </row>
     <row r="2156">
       <c r="A2156" t="str">
-        <v>Kmtsferhnvwnx</v>
+        <v>Kmtsffp8ly8ig</v>
       </c>
       <c r="B2156" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82505,7 +82505,7 @@
     </row>
     <row r="2157">
       <c r="A2157" t="str">
-        <v>Kmtsferhnv0sr</v>
+        <v>Kmtsffp8lgcz8</v>
       </c>
       <c r="B2157" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82581,7 +82581,7 @@
     </row>
     <row r="2159">
       <c r="A2159" t="str">
-        <v>Kmtsferhn89i4</v>
+        <v>Kmtsffp8lqars</v>
       </c>
       <c r="B2159" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82619,7 +82619,7 @@
     </row>
     <row r="2160">
       <c r="A2160" t="str">
-        <v>Kmtsferhngl5b</v>
+        <v>Kmtsffp8lkcv6</v>
       </c>
       <c r="B2160" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82657,7 +82657,7 @@
     </row>
     <row r="2161">
       <c r="A2161" t="str">
-        <v>Kmtsferhn95ll</v>
+        <v>Kmtsffp8lbqad</v>
       </c>
       <c r="B2161" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82695,7 +82695,7 @@
     </row>
     <row r="2162">
       <c r="A2162" t="str">
-        <v>Kmtsferhnxf76</v>
+        <v>Kmtsffp8lnijk</v>
       </c>
       <c r="B2162" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82733,7 +82733,7 @@
     </row>
     <row r="2163">
       <c r="A2163" t="str">
-        <v>Kmtsferhnaqc7</v>
+        <v>Kmtsffp8loofu</v>
       </c>
       <c r="B2163" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82771,7 +82771,7 @@
     </row>
     <row r="2164">
       <c r="A2164" t="str">
-        <v>Kmtsferhnp1l8</v>
+        <v>Kmtsffp8lyejt</v>
       </c>
       <c r="B2164" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82809,7 +82809,7 @@
     </row>
     <row r="2165">
       <c r="A2165" t="str">
-        <v>Kmtsferhngmf3</v>
+        <v>Kmtsffp8ldan5</v>
       </c>
       <c r="B2165" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82885,7 +82885,7 @@
     </row>
     <row r="2167">
       <c r="A2167" t="str">
-        <v>Kmtsferhn7cpy</v>
+        <v>Kmtsffp8layl0</v>
       </c>
       <c r="B2167" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82923,7 +82923,7 @@
     </row>
     <row r="2168">
       <c r="A2168" t="str">
-        <v>Kmtsferhn3365</v>
+        <v>Kmtsffp8lwrhu</v>
       </c>
       <c r="B2168" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82961,7 +82961,7 @@
     </row>
     <row r="2169">
       <c r="A2169" t="str">
-        <v>Kmtsferhnmun3</v>
+        <v>Kmtsffp8l9y09</v>
       </c>
       <c r="B2169" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82999,7 +82999,7 @@
     </row>
     <row r="2170">
       <c r="A2170" t="str">
-        <v>Kmtsferhn5yd9</v>
+        <v>Kmtsffp8l6uoy</v>
       </c>
       <c r="B2170" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83037,7 +83037,7 @@
     </row>
     <row r="2171">
       <c r="A2171" t="str">
-        <v>Kmtsferhn59hg</v>
+        <v>Kmtsffp8lv96e</v>
       </c>
       <c r="B2171" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83075,7 +83075,7 @@
     </row>
     <row r="2172">
       <c r="A2172" t="str">
-        <v>Kmtsferhndb37</v>
+        <v>Kmtsffp8lrdf4</v>
       </c>
       <c r="B2172" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83113,7 +83113,7 @@
     </row>
     <row r="2173">
       <c r="A2173" t="str">
-        <v>Kmtsferhn836x</v>
+        <v>Kmtsffp8l6boo</v>
       </c>
       <c r="B2173" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83151,7 +83151,7 @@
     </row>
     <row r="2174">
       <c r="A2174" t="str">
-        <v>Kmtsferhng8pn</v>
+        <v>Kmtsffp8lmoh3</v>
       </c>
       <c r="B2174" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -83189,7 +83189,7 @@
     </row>
     <row r="2175">
       <c r="A2175" t="str">
-        <v>Kmtsferhnj06e</v>
+        <v>Kmtsffp8l57ok</v>
       </c>
       <c r="B2175" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83227,7 +83227,7 @@
     </row>
     <row r="2176">
       <c r="A2176" t="str">
-        <v>Kmtsferhn3nt6</v>
+        <v>Kmtsffp8l75lx</v>
       </c>
       <c r="B2176" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83265,7 +83265,7 @@
     </row>
     <row r="2177">
       <c r="A2177" t="str">
-        <v>Kmtsferhn8r8l</v>
+        <v>Kmtsffp8lxlwp</v>
       </c>
       <c r="B2177" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83303,7 +83303,7 @@
     </row>
     <row r="2178">
       <c r="A2178" t="str">
-        <v>Kmtsferhnvwny</v>
+        <v>Kmtsffp8lumzk</v>
       </c>
       <c r="B2178" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83341,7 +83341,7 @@
     </row>
     <row r="2179">
       <c r="A2179" t="str">
-        <v>Kmtsferhn6ojn</v>
+        <v>Kmtsffp8lxxhz</v>
       </c>
       <c r="B2179" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -83379,7 +83379,7 @@
     </row>
     <row r="2180">
       <c r="A2180" t="str">
-        <v>Kmtsferhn2a3q</v>
+        <v>Kmtsffp8lmh0z</v>
       </c>
       <c r="B2180" t="str">
         <v>Asisten Perpustakaan Penyelia</v>
@@ -83417,7 +83417,7 @@
     </row>
     <row r="2181">
       <c r="A2181" t="str">
-        <v>Kmtsferhn716b</v>
+        <v>Kmtsffp8l8x9s</v>
       </c>
       <c r="B2181" t="str">
         <v>Asisten Perpustakaan Mahir</v>
@@ -83455,7 +83455,7 @@
     </row>
     <row r="2182">
       <c r="A2182" t="str">
-        <v>Kmtsferhnmft7</v>
+        <v>Kmtsffp8l67xr</v>
       </c>
       <c r="B2182" t="str">
         <v>Asisten Perpustakaan Terampil</v>
@@ -83493,7 +83493,7 @@
     </row>
     <row r="2183">
       <c r="A2183" t="str">
-        <v>Kmtsferhntmno</v>
+        <v>Kmtsffp8lt9a6</v>
       </c>
       <c r="B2183" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -83531,7 +83531,7 @@
     </row>
     <row r="2184">
       <c r="A2184" t="str">
-        <v>Kmtsferhnlfpn</v>
+        <v>Kmtsffp8l0pgy</v>
       </c>
       <c r="B2184" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -83569,7 +83569,7 @@
     </row>
     <row r="2185">
       <c r="A2185" t="str">
-        <v>Kmtsferhnx0mq</v>
+        <v>Kmtsffp8lk850</v>
       </c>
       <c r="B2185" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -83683,7 +83683,7 @@
     </row>
     <row r="2188">
       <c r="A2188" t="str">
-        <v>Kmtsferhndddt</v>
+        <v>Kmtsffp8l5avg</v>
       </c>
       <c r="B2188" t="str">
         <v>Penata Layanan Operasional</v>
@@ -83721,7 +83721,7 @@
     </row>
     <row r="2189">
       <c r="A2189" t="str">
-        <v>Kmtsferhn50yq</v>
+        <v>Kmtsffp8lzaz2</v>
       </c>
       <c r="B2189" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83759,7 +83759,7 @@
     </row>
     <row r="2190">
       <c r="A2190" t="str">
-        <v>Kmtsferhne0l1</v>
+        <v>Kmtsffp8ljexd</v>
       </c>
       <c r="B2190" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -83797,7 +83797,7 @@
     </row>
     <row r="2191">
       <c r="A2191" t="str">
-        <v>Kmtsferhnusp4</v>
+        <v>Kmtsffp8lukfq</v>
       </c>
       <c r="B2191" t="str">
         <v>Penata Keprotokolan*</v>
@@ -83911,7 +83911,7 @@
     </row>
     <row r="2194">
       <c r="A2194" t="str">
-        <v>Kmtsferhnfhy9</v>
+        <v>Kmtsffp8lcsst</v>
       </c>
       <c r="B2194" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -83949,7 +83949,7 @@
     </row>
     <row r="2195">
       <c r="A2195" t="str">
-        <v>Kmtsferhnjnco</v>
+        <v>Kmtsffp8luo8r</v>
       </c>
       <c r="B2195" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83987,7 +83987,7 @@
     </row>
     <row r="2196">
       <c r="A2196" t="str">
-        <v>Kmtsferhn9atc</v>
+        <v>Kmtsffp8lf1i1</v>
       </c>
       <c r="B2196" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84063,7 +84063,7 @@
     </row>
     <row r="2198">
       <c r="A2198" t="str">
-        <v>Kmtsferhnu484</v>
+        <v>Kmtsffp8lvw40</v>
       </c>
       <c r="B2198" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84101,7 +84101,7 @@
     </row>
     <row r="2199">
       <c r="A2199" t="str">
-        <v>Kmtsferhnucz2</v>
+        <v>Kmtsffp8lv95b</v>
       </c>
       <c r="B2199" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84139,7 +84139,7 @@
     </row>
     <row r="2200">
       <c r="A2200" t="str">
-        <v>Kmtsferhn9jb2</v>
+        <v>Kmtsffp8lvdqv</v>
       </c>
       <c r="B2200" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84177,7 +84177,7 @@
     </row>
     <row r="2201">
       <c r="A2201" t="str">
-        <v>Kmtsferhnru8s</v>
+        <v>Kmtsffp8l6anw</v>
       </c>
       <c r="B2201" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84215,7 +84215,7 @@
     </row>
     <row r="2202">
       <c r="A2202" t="str">
-        <v>Kmtsferhn5cub</v>
+        <v>Kmtsffp8l3qk8</v>
       </c>
       <c r="B2202" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84253,7 +84253,7 @@
     </row>
     <row r="2203">
       <c r="A2203" t="str">
-        <v>Kmtsferhnl89k</v>
+        <v>Kmtsffp8l3ya1</v>
       </c>
       <c r="B2203" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -84291,7 +84291,7 @@
     </row>
     <row r="2204">
       <c r="A2204" t="str">
-        <v>Kmtsferhnij2a</v>
+        <v>Kmtsffp8lgupf</v>
       </c>
       <c r="B2204" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -84405,7 +84405,7 @@
     </row>
     <row r="2207">
       <c r="A2207" t="str">
-        <v>Kmtsferhn4k1e</v>
+        <v>Kmtsffp8ltz2h</v>
       </c>
       <c r="B2207" t="str">
         <v>Penata Layanan Operasional</v>
@@ -84443,7 +84443,7 @@
     </row>
     <row r="2208">
       <c r="A2208" t="str">
-        <v>Kmtsferhnhiqr</v>
+        <v>Kmtsffp8lyhlr</v>
       </c>
       <c r="B2208" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84481,7 +84481,7 @@
     </row>
     <row r="2209">
       <c r="A2209" t="str">
-        <v>Kmtsferhngjd5</v>
+        <v>Kmtsffp8li2sd</v>
       </c>
       <c r="B2209" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84519,7 +84519,7 @@
     </row>
     <row r="2210">
       <c r="A2210" t="str">
-        <v>Kmtsferhn8fsr</v>
+        <v>Kmtsffp8lv2ig</v>
       </c>
       <c r="B2210" t="str">
         <v>Penata Keprotokolan*</v>
@@ -84633,7 +84633,7 @@
     </row>
     <row r="2213">
       <c r="A2213" t="str">
-        <v>Kmtsferhnecaf</v>
+        <v>Kmtsffp8l3wg5</v>
       </c>
       <c r="B2213" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84671,7 +84671,7 @@
     </row>
     <row r="2214">
       <c r="A2214" t="str">
-        <v>Kmtsferhnn8pg</v>
+        <v>Kmtsffp8lvqax</v>
       </c>
       <c r="B2214" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84709,7 +84709,7 @@
     </row>
     <row r="2215">
       <c r="A2215" t="str">
-        <v>Kmtsferhntieq</v>
+        <v>Kmtsffp8ltewp</v>
       </c>
       <c r="B2215" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84785,7 +84785,7 @@
     </row>
     <row r="2217">
       <c r="A2217" t="str">
-        <v>Kmtsferhnjvbt</v>
+        <v>Kmtsffp8l9ekn</v>
       </c>
       <c r="B2217" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84823,7 +84823,7 @@
     </row>
     <row r="2218">
       <c r="A2218" t="str">
-        <v>Kmtsferhn2n1c</v>
+        <v>Kmtsffp8lzkf9</v>
       </c>
       <c r="B2218" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84861,7 +84861,7 @@
     </row>
     <row r="2219">
       <c r="A2219" t="str">
-        <v>Kmtsferhnraqj</v>
+        <v>Kmtsffp8lx3f5</v>
       </c>
       <c r="B2219" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84899,7 +84899,7 @@
     </row>
     <row r="2220">
       <c r="A2220" t="str">
-        <v>Kmtsferhnv5b4</v>
+        <v>Kmtsffp8lnl4k</v>
       </c>
       <c r="B2220" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84937,7 +84937,7 @@
     </row>
     <row r="2221">
       <c r="A2221" t="str">
-        <v>Kmtsferhnnacq</v>
+        <v>Kmtsffp8lkpxq</v>
       </c>
       <c r="B2221" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84975,7 +84975,7 @@
     </row>
     <row r="2222">
       <c r="A2222" t="str">
-        <v>Kmtsferhn1jpf</v>
+        <v>Kmtsffp8lfnn1</v>
       </c>
       <c r="B2222" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85013,7 +85013,7 @@
     </row>
     <row r="2223">
       <c r="A2223" t="str">
-        <v>Kmtsferhnx2oh</v>
+        <v>Kmtsffp8liue9</v>
       </c>
       <c r="B2223" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85127,7 +85127,7 @@
     </row>
     <row r="2226">
       <c r="A2226" t="str">
-        <v>Kmtsferhnb6nj</v>
+        <v>Kmtsffp8lys98</v>
       </c>
       <c r="B2226" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85165,7 +85165,7 @@
     </row>
     <row r="2227">
       <c r="A2227" t="str">
-        <v>Kmtsferhnx7ux</v>
+        <v>Kmtsffp8ldplm</v>
       </c>
       <c r="B2227" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85203,7 +85203,7 @@
     </row>
     <row r="2228">
       <c r="A2228" t="str">
-        <v>Kmtsferhnnkf3</v>
+        <v>Kmtsffp8lae5z</v>
       </c>
       <c r="B2228" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85241,7 +85241,7 @@
     </row>
     <row r="2229">
       <c r="A2229" t="str">
-        <v>Kmtsferhnz94j</v>
+        <v>Kmtsffp8l9am3</v>
       </c>
       <c r="B2229" t="str">
         <v>Penata Keprotokolan*</v>
@@ -85355,7 +85355,7 @@
     </row>
     <row r="2232">
       <c r="A2232" t="str">
-        <v>Kmtsferhnpe9j</v>
+        <v>Kmtsffp8lkt6p</v>
       </c>
       <c r="B2232" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85393,7 +85393,7 @@
     </row>
     <row r="2233">
       <c r="A2233" t="str">
-        <v>Kmtsferhn0su0</v>
+        <v>Kmtsffp8lsdg2</v>
       </c>
       <c r="B2233" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85431,7 +85431,7 @@
     </row>
     <row r="2234">
       <c r="A2234" t="str">
-        <v>Kmtsferhnavqz</v>
+        <v>Kmtsffp8ld7ed</v>
       </c>
       <c r="B2234" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85507,7 +85507,7 @@
     </row>
     <row r="2236">
       <c r="A2236" t="str">
-        <v>Kmtsferhnyq0x</v>
+        <v>Kmtsffp8lqvek</v>
       </c>
       <c r="B2236" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85545,7 +85545,7 @@
     </row>
     <row r="2237">
       <c r="A2237" t="str">
-        <v>Kmtsferhnfich</v>
+        <v>Kmtsffp8llt6v</v>
       </c>
       <c r="B2237" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85583,7 +85583,7 @@
     </row>
     <row r="2238">
       <c r="A2238" t="str">
-        <v>Kmtsferhnkiam</v>
+        <v>Kmtsffp8ltsfb</v>
       </c>
       <c r="B2238" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85621,7 +85621,7 @@
     </row>
     <row r="2239">
       <c r="A2239" t="str">
-        <v>Kmtsferhnacg0</v>
+        <v>Kmtsffp8lkdjb</v>
       </c>
       <c r="B2239" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -85659,7 +85659,7 @@
     </row>
     <row r="2240">
       <c r="A2240" t="str">
-        <v>Kmtsferhn10aj</v>
+        <v>Kmtsffp8l7xoz</v>
       </c>
       <c r="B2240" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -85697,7 +85697,7 @@
     </row>
     <row r="2241">
       <c r="A2241" t="str">
-        <v>Kmtsferhnmzak</v>
+        <v>Kmtsffp8lm9kx</v>
       </c>
       <c r="B2241" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85735,7 +85735,7 @@
     </row>
     <row r="2242">
       <c r="A2242" t="str">
-        <v>Kmtsferhngoyg</v>
+        <v>Kmtsffp8leu2d</v>
       </c>
       <c r="B2242" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85849,7 +85849,7 @@
     </row>
     <row r="2245">
       <c r="A2245" t="str">
-        <v>Kmtsferhnx78k</v>
+        <v>Kmtsffp8lqclh</v>
       </c>
       <c r="B2245" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85887,7 +85887,7 @@
     </row>
     <row r="2246">
       <c r="A2246" t="str">
-        <v>Kmtsferhn3cli</v>
+        <v>Kmtsffp8lkodq</v>
       </c>
       <c r="B2246" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85925,7 +85925,7 @@
     </row>
     <row r="2247">
       <c r="A2247" t="str">
-        <v>Kmtsferhnfp33</v>
+        <v>Kmtsffp8l3pzk</v>
       </c>
       <c r="B2247" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85963,7 +85963,7 @@
     </row>
     <row r="2248">
       <c r="A2248" t="str">
-        <v>Kmtsferhnyu93</v>
+        <v>Kmtsffp8lu79v</v>
       </c>
       <c r="B2248" t="str">
         <v>Penata Keprotokolan*</v>
@@ -86039,7 +86039,7 @@
     </row>
     <row r="2250">
       <c r="A2250" t="str">
-        <v>Kmtsferhnoqah</v>
+        <v>Kmtsffp8lebs3</v>
       </c>
       <c r="B2250" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86077,7 +86077,7 @@
     </row>
     <row r="2251">
       <c r="A2251" t="str">
-        <v>Kmtsferhngtct</v>
+        <v>Kmtsffp8lk3l5</v>
       </c>
       <c r="B2251" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86115,7 +86115,7 @@
     </row>
     <row r="2252">
       <c r="A2252" t="str">
-        <v>Kmtsferhnirsb</v>
+        <v>Kmtsffp8lgwrp</v>
       </c>
       <c r="B2252" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86153,7 +86153,7 @@
     </row>
     <row r="2253">
       <c r="A2253" t="str">
-        <v>Kmtsferhno8u9</v>
+        <v>Kmtsffp8l238y</v>
       </c>
       <c r="B2253" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86191,7 +86191,7 @@
     </row>
     <row r="2254">
       <c r="A2254" t="str">
-        <v>Kmtsferhndzss</v>
+        <v>Kmtsffp8ltoe1</v>
       </c>
       <c r="B2254" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86305,7 +86305,7 @@
     </row>
     <row r="2257">
       <c r="A2257" t="str">
-        <v>Kmtsferhn9ydq</v>
+        <v>Kmtsffp8lo7tp</v>
       </c>
       <c r="B2257" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86343,7 +86343,7 @@
     </row>
     <row r="2258">
       <c r="A2258" t="str">
-        <v>Kmtsferhn98xg</v>
+        <v>Kmtsffp8lgrl4</v>
       </c>
       <c r="B2258" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86381,7 +86381,7 @@
     </row>
     <row r="2259">
       <c r="A2259" t="str">
-        <v>Kmtsferhn7joz</v>
+        <v>Kmtsffp8lqjyt</v>
       </c>
       <c r="B2259" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86457,7 +86457,7 @@
     </row>
     <row r="2261">
       <c r="A2261" t="str">
-        <v>Kmtsferhnlilo</v>
+        <v>Kmtsffp8laul8</v>
       </c>
       <c r="B2261" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86495,7 +86495,7 @@
     </row>
     <row r="2262">
       <c r="A2262" t="str">
-        <v>Kmtsferhnp7u8</v>
+        <v>Kmtsffp8locc6</v>
       </c>
       <c r="B2262" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86533,7 +86533,7 @@
     </row>
     <row r="2263">
       <c r="A2263" t="str">
-        <v>Kmtsferhnlcau</v>
+        <v>Kmtsffp8ll0yl</v>
       </c>
       <c r="B2263" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86571,7 +86571,7 @@
     </row>
     <row r="2264">
       <c r="A2264" t="str">
-        <v>Kmtsferhnsffy</v>
+        <v>Kmtsffp8lsy65</v>
       </c>
       <c r="B2264" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -86609,7 +86609,7 @@
     </row>
     <row r="2265">
       <c r="A2265" t="str">
-        <v>Kmtsferhn4rgr</v>
+        <v>Kmtsffp8l9xfy</v>
       </c>
       <c r="B2265" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -86647,7 +86647,7 @@
     </row>
     <row r="2266">
       <c r="A2266" t="str">
-        <v>Kmtsferhnq9ez</v>
+        <v>Kmtsffp8l7xh7</v>
       </c>
       <c r="B2266" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86685,7 +86685,7 @@
     </row>
     <row r="2267">
       <c r="A2267" t="str">
-        <v>Kmtsferhnqmiu</v>
+        <v>Kmtsffp8lvbbo</v>
       </c>
       <c r="B2267" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86799,7 +86799,7 @@
     </row>
     <row r="2270">
       <c r="A2270" t="str">
-        <v>Kmtsferhnq8no</v>
+        <v>Kmtsffp8loir7</v>
       </c>
       <c r="B2270" t="str">
         <v>Penata Layanan Operasional</v>
@@ -86837,7 +86837,7 @@
     </row>
     <row r="2271">
       <c r="A2271" t="str">
-        <v>Kmtsferhnakgg</v>
+        <v>Kmtsffp8ltqwq</v>
       </c>
       <c r="B2271" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86875,7 +86875,7 @@
     </row>
     <row r="2272">
       <c r="A2272" t="str">
-        <v>Kmtsferhntbaz</v>
+        <v>Kmtsffp8lk5tw</v>
       </c>
       <c r="B2272" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86913,7 +86913,7 @@
     </row>
     <row r="2273">
       <c r="A2273" t="str">
-        <v>Kmtsferhnyklg</v>
+        <v>Kmtsffp8lte8h</v>
       </c>
       <c r="B2273" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87027,7 +87027,7 @@
     </row>
     <row r="2276">
       <c r="A2276" t="str">
-        <v>Kmtsferhnt1o2</v>
+        <v>Kmtsffp8l0030</v>
       </c>
       <c r="B2276" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87065,7 +87065,7 @@
     </row>
     <row r="2277">
       <c r="A2277" t="str">
-        <v>Kmtsferhnc9cy</v>
+        <v>Kmtsffp8ldrry</v>
       </c>
       <c r="B2277" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87103,7 +87103,7 @@
     </row>
     <row r="2278">
       <c r="A2278" t="str">
-        <v>Kmtsferhnyujv</v>
+        <v>Kmtsffp8myzaf</v>
       </c>
       <c r="B2278" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87179,7 +87179,7 @@
     </row>
     <row r="2280">
       <c r="A2280" t="str">
-        <v>Kmtsferhnkedj</v>
+        <v>Kmtsffp8m0up8</v>
       </c>
       <c r="B2280" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87217,7 +87217,7 @@
     </row>
     <row r="2281">
       <c r="A2281" t="str">
-        <v>Kmtsferhncmhm</v>
+        <v>Kmtsffp8mr1go</v>
       </c>
       <c r="B2281" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87255,7 +87255,7 @@
     </row>
     <row r="2282">
       <c r="A2282" t="str">
-        <v>Kmtsferhnrxf3</v>
+        <v>Kmtsffp8mtsw2</v>
       </c>
       <c r="B2282" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87293,7 +87293,7 @@
     </row>
     <row r="2283">
       <c r="A2283" t="str">
-        <v>Kmtsferhn6m6i</v>
+        <v>Kmtsffp8mmic7</v>
       </c>
       <c r="B2283" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -87331,7 +87331,7 @@
     </row>
     <row r="2284">
       <c r="A2284" t="str">
-        <v>Kmtsferhnfe59</v>
+        <v>Kmtsffp8maqpa</v>
       </c>
       <c r="B2284" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -87369,7 +87369,7 @@
     </row>
     <row r="2285">
       <c r="A2285" t="str">
-        <v>Kmtsferhn8zlw</v>
+        <v>Kmtsffp8mz6c8</v>
       </c>
       <c r="B2285" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -87407,7 +87407,7 @@
     </row>
     <row r="2286">
       <c r="A2286" t="str">
-        <v>Kmtsferhncbxj</v>
+        <v>Kmtsffp8mc9zw</v>
       </c>
       <c r="B2286" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -87521,7 +87521,7 @@
     </row>
     <row r="2289">
       <c r="A2289" t="str">
-        <v>Kmtsferhnxb8f</v>
+        <v>Kmtsffp8m574q</v>
       </c>
       <c r="B2289" t="str">
         <v>Penata Layanan Operasional</v>
@@ -87559,7 +87559,7 @@
     </row>
     <row r="2290">
       <c r="A2290" t="str">
-        <v>Kmtsferhn167u</v>
+        <v>Kmtsffp8mm6o3</v>
       </c>
       <c r="B2290" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87597,7 +87597,7 @@
     </row>
     <row r="2291">
       <c r="A2291" t="str">
-        <v>Kmtsferhncods</v>
+        <v>Kmtsffp8mt9cj</v>
       </c>
       <c r="B2291" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87635,7 +87635,7 @@
     </row>
     <row r="2292">
       <c r="A2292" t="str">
-        <v>Kmtsferhntj7t</v>
+        <v>Kmtsffp8mjo8d</v>
       </c>
       <c r="B2292" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87749,7 +87749,7 @@
     </row>
     <row r="2295">
       <c r="A2295" t="str">
-        <v>Kmtsferhnbjyr</v>
+        <v>Kmtsffp8mdxxi</v>
       </c>
       <c r="B2295" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87787,7 +87787,7 @@
     </row>
     <row r="2296">
       <c r="A2296" t="str">
-        <v>Kmtsferhn5q69</v>
+        <v>Kmtsffp8m1hze</v>
       </c>
       <c r="B2296" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87825,7 +87825,7 @@
     </row>
     <row r="2297">
       <c r="A2297" t="str">
-        <v>Kmtsferhnwi9y</v>
+        <v>Kmtsffp8mmlbj</v>
       </c>
       <c r="B2297" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87901,7 +87901,7 @@
     </row>
     <row r="2299">
       <c r="A2299" t="str">
-        <v>Kmtsferhnd0fx</v>
+        <v>Kmtsffp8mt69v</v>
       </c>
       <c r="B2299" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87939,7 +87939,7 @@
     </row>
     <row r="2300">
       <c r="A2300" t="str">
-        <v>Kmtsferhnxc8p</v>
+        <v>Kmtsffp8mg4im</v>
       </c>
       <c r="B2300" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87977,7 +87977,7 @@
     </row>
     <row r="2301">
       <c r="A2301" t="str">
-        <v>Kmtsferhnx8d9</v>
+        <v>Kmtsffp8mhus1</v>
       </c>
       <c r="B2301" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88015,7 +88015,7 @@
     </row>
     <row r="2302">
       <c r="A2302" t="str">
-        <v>Kmtsferhnshd6</v>
+        <v>Kmtsffp8m4fd3</v>
       </c>
       <c r="B2302" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -88053,7 +88053,7 @@
     </row>
     <row r="2303">
       <c r="A2303" t="str">
-        <v>Kmtsferhn41as</v>
+        <v>Kmtsffp8mflpn</v>
       </c>
       <c r="B2303" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -88091,7 +88091,7 @@
     </row>
     <row r="2304">
       <c r="A2304" t="str">
-        <v>Kmtsferhnsphl</v>
+        <v>Kmtsffp8mkge4</v>
       </c>
       <c r="B2304" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -88129,7 +88129,7 @@
     </row>
     <row r="2305">
       <c r="A2305" t="str">
-        <v>Kmtsferhn6ahz</v>
+        <v>Kmtsffp8m9i28</v>
       </c>
       <c r="B2305" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -88243,7 +88243,7 @@
     </row>
     <row r="2308">
       <c r="A2308" t="str">
-        <v>Kmtsferhn0bgx</v>
+        <v>Kmtsffp8mllo8</v>
       </c>
       <c r="B2308" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88281,7 +88281,7 @@
     </row>
     <row r="2309">
       <c r="A2309" t="str">
-        <v>Kmtsferhnxmoi</v>
+        <v>Kmtsffp8malvk</v>
       </c>
       <c r="B2309" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88319,7 +88319,7 @@
     </row>
     <row r="2310">
       <c r="A2310" t="str">
-        <v>Kmtsferhnuvn9</v>
+        <v>Kmtsffp8mdd6e</v>
       </c>
       <c r="B2310" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88357,7 +88357,7 @@
     </row>
     <row r="2311">
       <c r="A2311" t="str">
-        <v>Kmtsferhngz5x</v>
+        <v>Kmtsffp8m9ljr</v>
       </c>
       <c r="B2311" t="str">
         <v>Penata Keprotokolan*</v>
@@ -88471,7 +88471,7 @@
     </row>
     <row r="2314">
       <c r="A2314" t="str">
-        <v>Kmtsferhn3f91</v>
+        <v>Kmtsffp8m46x3</v>
       </c>
       <c r="B2314" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88509,7 +88509,7 @@
     </row>
     <row r="2315">
       <c r="A2315" t="str">
-        <v>Kmtsferhnpf6w</v>
+        <v>Kmtsffp8m57vo</v>
       </c>
       <c r="B2315" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88547,7 +88547,7 @@
     </row>
     <row r="2316">
       <c r="A2316" t="str">
-        <v>Kmtsferhn3xuk</v>
+        <v>Kmtsffp8mos49</v>
       </c>
       <c r="B2316" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88623,7 +88623,7 @@
     </row>
     <row r="2318">
       <c r="A2318" t="str">
-        <v>Kmtsferhnt631</v>
+        <v>Kmtsffp8m0vns</v>
       </c>
       <c r="B2318" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88661,7 +88661,7 @@
     </row>
     <row r="2319">
       <c r="A2319" t="str">
-        <v>Kmtsferhnyy5g</v>
+        <v>Kmtsffp8muxvy</v>
       </c>
       <c r="B2319" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88699,7 +88699,7 @@
     </row>
     <row r="2320">
       <c r="A2320" t="str">
-        <v>Kmtsferhnxm46</v>
+        <v>Kmtsffp8msrzs</v>
       </c>
       <c r="B2320" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88775,7 +88775,7 @@
     </row>
     <row r="2322">
       <c r="A2322" t="str">
-        <v>Kmtsferhn8n59</v>
+        <v>Kmtsffp8mcig4</v>
       </c>
       <c r="B2322" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88813,7 +88813,7 @@
     </row>
     <row r="2323">
       <c r="A2323" t="str">
-        <v>Kmtsferhnffrc</v>
+        <v>Kmtsffp8m7tvu</v>
       </c>
       <c r="B2323" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88851,7 +88851,7 @@
     </row>
     <row r="2324">
       <c r="A2324" t="str">
-        <v>Kmtsferhn1zfn</v>
+        <v>Kmtsffp8msahc</v>
       </c>
       <c r="B2324" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88927,7 +88927,7 @@
     </row>
     <row r="2326">
       <c r="A2326" t="str">
-        <v>Kmtsferhn20yy</v>
+        <v>Kmtsffp8mdi3k</v>
       </c>
       <c r="B2326" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88965,7 +88965,7 @@
     </row>
     <row r="2327">
       <c r="A2327" t="str">
-        <v>Kmtsferhn53z6</v>
+        <v>Kmtsffp8max69</v>
       </c>
       <c r="B2327" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89003,7 +89003,7 @@
     </row>
     <row r="2328">
       <c r="A2328" t="str">
-        <v>Kmtsferhn2vqa</v>
+        <v>Kmtsffp8mhqk2</v>
       </c>
       <c r="B2328" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89117,7 +89117,7 @@
     </row>
     <row r="2331">
       <c r="A2331" t="str">
-        <v>Kmtsferhntt83</v>
+        <v>Kmtsffp8m776i</v>
       </c>
       <c r="B2331" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89155,7 +89155,7 @@
     </row>
     <row r="2332">
       <c r="A2332" t="str">
-        <v>Kmtsferhn99x7</v>
+        <v>Kmtsffp8mzbhs</v>
       </c>
       <c r="B2332" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89193,7 +89193,7 @@
     </row>
     <row r="2333">
       <c r="A2333" t="str">
-        <v>Kmtsferhnx33b</v>
+        <v>Kmtsffp8medu1</v>
       </c>
       <c r="B2333" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89269,7 +89269,7 @@
     </row>
     <row r="2335">
       <c r="A2335" t="str">
-        <v>Kmtsferhn7amp</v>
+        <v>Kmtsffp8mv44m</v>
       </c>
       <c r="B2335" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89307,7 +89307,7 @@
     </row>
     <row r="2336">
       <c r="A2336" t="str">
-        <v>Kmtsferhns2ml</v>
+        <v>Kmtsffp8mzuuj</v>
       </c>
       <c r="B2336" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89345,7 +89345,7 @@
     </row>
     <row r="2337">
       <c r="A2337" t="str">
-        <v>Kmtsferhn06y2</v>
+        <v>Kmtsffp8m3mg7</v>
       </c>
       <c r="B2337" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89383,7 +89383,7 @@
     </row>
     <row r="2338">
       <c r="A2338" t="str">
-        <v>Kmtsferhn54ro</v>
+        <v>Kmtsffp8m3l8r</v>
       </c>
       <c r="B2338" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -89421,7 +89421,7 @@
     </row>
     <row r="2339">
       <c r="A2339" t="str">
-        <v>Kmtsferhn2qpi</v>
+        <v>Kmtsffp8mz29n</v>
       </c>
       <c r="B2339" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -89459,7 +89459,7 @@
     </row>
     <row r="2340">
       <c r="A2340" t="str">
-        <v>Kmtsferhn3tnp</v>
+        <v>Kmtsffp8msos3</v>
       </c>
       <c r="B2340" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -89497,7 +89497,7 @@
     </row>
     <row r="2341">
       <c r="A2341" t="str">
-        <v>Kmtsferhn24dz</v>
+        <v>Kmtsffp8meicf</v>
       </c>
       <c r="B2341" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -89611,7 +89611,7 @@
     </row>
     <row r="2344">
       <c r="A2344" t="str">
-        <v>Kmtsferhncan8</v>
+        <v>Kmtsffp8m8clh</v>
       </c>
       <c r="B2344" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89649,7 +89649,7 @@
     </row>
     <row r="2345">
       <c r="A2345" t="str">
-        <v>Kmtsferhngo7q</v>
+        <v>Kmtsffp8mhe5b</v>
       </c>
       <c r="B2345" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89687,7 +89687,7 @@
     </row>
     <row r="2346">
       <c r="A2346" t="str">
-        <v>Kmtsferhnlu0f</v>
+        <v>Kmtsffp8mvjdw</v>
       </c>
       <c r="B2346" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89801,7 +89801,7 @@
     </row>
     <row r="2349">
       <c r="A2349" t="str">
-        <v>Kmtsferhn3wow</v>
+        <v>Kmtsffp8m2pi0</v>
       </c>
       <c r="B2349" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89839,7 +89839,7 @@
     </row>
     <row r="2350">
       <c r="A2350" t="str">
-        <v>Kmtsferhnn7gf</v>
+        <v>Kmtsffp8m7ueq</v>
       </c>
       <c r="B2350" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89877,7 +89877,7 @@
     </row>
     <row r="2351">
       <c r="A2351" t="str">
-        <v>Kmtsferhnvx43</v>
+        <v>Kmtsffp8mjlvz</v>
       </c>
       <c r="B2351" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89953,7 +89953,7 @@
     </row>
     <row r="2353">
       <c r="A2353" t="str">
-        <v>Kmtsferhnu98d</v>
+        <v>Kmtsffp8mjp07</v>
       </c>
       <c r="B2353" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89991,7 +89991,7 @@
     </row>
     <row r="2354">
       <c r="A2354" t="str">
-        <v>Kmtsferhnfo5u</v>
+        <v>Kmtsffp8mh2ad</v>
       </c>
       <c r="B2354" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90029,7 +90029,7 @@
     </row>
     <row r="2355">
       <c r="A2355" t="str">
-        <v>Kmtsferhn11xg</v>
+        <v>Kmtsffp8mdw00</v>
       </c>
       <c r="B2355" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90067,7 +90067,7 @@
     </row>
     <row r="2356">
       <c r="A2356" t="str">
-        <v>Kmtsferhndzsm</v>
+        <v>Kmtsffp8m43jf</v>
       </c>
       <c r="B2356" t="str">
         <v>Penata Keprotokolan*</v>
@@ -90143,7 +90143,7 @@
     </row>
     <row r="2358">
       <c r="A2358" t="str">
-        <v>Kmtsferhnzcxu</v>
+        <v>Kmtsffp8mr1li</v>
       </c>
       <c r="B2358" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90181,7 +90181,7 @@
     </row>
     <row r="2359">
       <c r="A2359" t="str">
-        <v>Kmtsferhnpved</v>
+        <v>Kmtsffp8mvz6d</v>
       </c>
       <c r="B2359" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90219,7 +90219,7 @@
     </row>
     <row r="2360">
       <c r="A2360" t="str">
-        <v>Kmtsferhnxegl</v>
+        <v>Kmtsffp8msjao</v>
       </c>
       <c r="B2360" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90333,7 +90333,7 @@
     </row>
     <row r="2363">
       <c r="A2363" t="str">
-        <v>Kmtsferhnew9u</v>
+        <v>Kmtsffp8mx1n2</v>
       </c>
       <c r="B2363" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90371,7 +90371,7 @@
     </row>
     <row r="2364">
       <c r="A2364" t="str">
-        <v>Kmtsferhnjjyi</v>
+        <v>Kmtsffp8m2gfp</v>
       </c>
       <c r="B2364" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90409,7 +90409,7 @@
     </row>
     <row r="2365">
       <c r="A2365" t="str">
-        <v>Kmtsferhnj321</v>
+        <v>Kmtsffp8msc22</v>
       </c>
       <c r="B2365" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90485,7 +90485,7 @@
     </row>
     <row r="2367">
       <c r="A2367" t="str">
-        <v>Kmtsferhn629x</v>
+        <v>Kmtsffp8mzjqx</v>
       </c>
       <c r="B2367" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90523,7 +90523,7 @@
     </row>
     <row r="2368">
       <c r="A2368" t="str">
-        <v>Kmtsferhnf94g</v>
+        <v>Kmtsffp8moek1</v>
       </c>
       <c r="B2368" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90561,7 +90561,7 @@
     </row>
     <row r="2369">
       <c r="A2369" t="str">
-        <v>Kmtsferhnyntp</v>
+        <v>Kmtsffp8m60hu</v>
       </c>
       <c r="B2369" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90637,7 +90637,7 @@
     </row>
     <row r="2371">
       <c r="A2371" t="str">
-        <v>Kmtsferhn1eah</v>
+        <v>Kmtsffp8md7ei</v>
       </c>
       <c r="B2371" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90675,7 +90675,7 @@
     </row>
     <row r="2372">
       <c r="A2372" t="str">
-        <v>Kmtsferhny17e</v>
+        <v>Kmtsffp8m20lq</v>
       </c>
       <c r="B2372" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90713,7 +90713,7 @@
     </row>
     <row r="2373">
       <c r="A2373" t="str">
-        <v>Kmtsferhn40t3</v>
+        <v>Kmtsffp8md9wp</v>
       </c>
       <c r="B2373" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90789,7 +90789,7 @@
     </row>
     <row r="2375">
       <c r="A2375" t="str">
-        <v>Kmtsferhn0apd</v>
+        <v>Kmtsffp8m1zl2</v>
       </c>
       <c r="B2375" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90827,7 +90827,7 @@
     </row>
     <row r="2376">
       <c r="A2376" t="str">
-        <v>Kmtsferhnsi3s</v>
+        <v>Kmtsffp8m3983</v>
       </c>
       <c r="B2376" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90865,7 +90865,7 @@
     </row>
     <row r="2377">
       <c r="A2377" t="str">
-        <v>Kmtsferhnd4bh</v>
+        <v>Kmtsffp8mx3y4</v>
       </c>
       <c r="B2377" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90903,7 +90903,7 @@
     </row>
     <row r="2378">
       <c r="A2378" t="str">
-        <v>Kmtsferhn5agx</v>
+        <v>Kmtsffp8mkc7i</v>
       </c>
       <c r="B2378" t="str">
         <v xml:space="preserve">Analis Pembiayaan Risiko dan Keuangan/ Analis Keuangan Negara Ahli Utama									</v>

--- a/data/struktur-organisasi.xlsx
+++ b/data/struktur-organisasi.xlsx
@@ -78173,7 +78173,7 @@
     </row>
     <row r="2043">
       <c r="A2043" t="str">
-        <v>Kmtsffp8ldl0s</v>
+        <v>Kmtuxmti18qss</v>
       </c>
       <c r="B2043" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78211,7 +78211,7 @@
     </row>
     <row r="2044">
       <c r="A2044" t="str">
-        <v>Kmtsffp8lgm0d</v>
+        <v>Kmtuxmti1bm4y</v>
       </c>
       <c r="B2044" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78249,7 +78249,7 @@
     </row>
     <row r="2045">
       <c r="A2045" t="str">
-        <v>Kmtsffp8lyxu4</v>
+        <v>Kmtuxmti1g5pj</v>
       </c>
       <c r="B2045" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78325,7 +78325,7 @@
     </row>
     <row r="2047">
       <c r="A2047" t="str">
-        <v>Kmtsffp8ljwvy</v>
+        <v>Kmtuxmti1dpb7</v>
       </c>
       <c r="B2047" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78363,7 +78363,7 @@
     </row>
     <row r="2048">
       <c r="A2048" t="str">
-        <v>Kmtsffp8lutlk</v>
+        <v>Kmtuxmti1hvtz</v>
       </c>
       <c r="B2048" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78401,7 +78401,7 @@
     </row>
     <row r="2049">
       <c r="A2049" t="str">
-        <v>Kmtsffp8ltrrr</v>
+        <v>Kmtuxmti1m8ct</v>
       </c>
       <c r="B2049" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78477,7 +78477,7 @@
     </row>
     <row r="2051">
       <c r="A2051" t="str">
-        <v>Kmtsffp8l2mum</v>
+        <v>Kmtuxmti1fhz4</v>
       </c>
       <c r="B2051" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78515,7 +78515,7 @@
     </row>
     <row r="2052">
       <c r="A2052" t="str">
-        <v>Kmtsffp8l3rnn</v>
+        <v>Kmtuxmti1tsnj</v>
       </c>
       <c r="B2052" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78553,7 +78553,7 @@
     </row>
     <row r="2053">
       <c r="A2053" t="str">
-        <v>Kmtsffp8lihi4</v>
+        <v>Kmtuxmti1u3hq</v>
       </c>
       <c r="B2053" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -78591,7 +78591,7 @@
     </row>
     <row r="2054">
       <c r="A2054" t="str">
-        <v>Kmtsffp8lna2e</v>
+        <v>Kmtuxmti1q6qj</v>
       </c>
       <c r="B2054" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -78629,7 +78629,7 @@
     </row>
     <row r="2055">
       <c r="A2055" t="str">
-        <v>Kmtsffp8l0cyf</v>
+        <v>Kmtuxmti1lz1q</v>
       </c>
       <c r="B2055" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -78667,7 +78667,7 @@
     </row>
     <row r="2056">
       <c r="A2056" t="str">
-        <v>Kmtsffp8leriu</v>
+        <v>Kmtuxmti1xyzi</v>
       </c>
       <c r="B2056" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -78705,7 +78705,7 @@
     </row>
     <row r="2057">
       <c r="A2057" t="str">
-        <v>Kmtsffp8lq5xk</v>
+        <v>Kmtuxmti1uz5t</v>
       </c>
       <c r="B2057" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -78743,7 +78743,7 @@
     </row>
     <row r="2058">
       <c r="A2058" t="str">
-        <v>Kmtsffp8lhdkf</v>
+        <v>Kmtuxmti1nf5k</v>
       </c>
       <c r="B2058" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -78857,7 +78857,7 @@
     </row>
     <row r="2061">
       <c r="A2061" t="str">
-        <v>Kmtsffp8l4j3c</v>
+        <v>Kmtuxmti1kkd6</v>
       </c>
       <c r="B2061" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -78895,7 +78895,7 @@
     </row>
     <row r="2062">
       <c r="A2062" t="str">
-        <v>Kmtsffp8l809b</v>
+        <v>Kmtuxmti1cmjk</v>
       </c>
       <c r="B2062" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -78933,7 +78933,7 @@
     </row>
     <row r="2063">
       <c r="A2063" t="str">
-        <v>Kmtsffp8lvobd</v>
+        <v>Kmtuxmti1jpbw</v>
       </c>
       <c r="B2063" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79009,7 +79009,7 @@
     </row>
     <row r="2065">
       <c r="A2065" t="str">
-        <v>Kmtsffp8l0dz9</v>
+        <v>Kmtuxmti1iyjo</v>
       </c>
       <c r="B2065" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79047,7 +79047,7 @@
     </row>
     <row r="2066">
       <c r="A2066" t="str">
-        <v>Kmtsffp8lv33n</v>
+        <v>Kmtuxmti1l7q3</v>
       </c>
       <c r="B2066" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79085,7 +79085,7 @@
     </row>
     <row r="2067">
       <c r="A2067" t="str">
-        <v>Kmtsffp8lxt1l</v>
+        <v>Kmtuxmti1ef9f</v>
       </c>
       <c r="B2067" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79161,7 +79161,7 @@
     </row>
     <row r="2069">
       <c r="A2069" t="str">
-        <v>Kmtsffp8ljqow</v>
+        <v>Kmtuxmti1azb6</v>
       </c>
       <c r="B2069" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79199,7 +79199,7 @@
     </row>
     <row r="2070">
       <c r="A2070" t="str">
-        <v>Kmtsffp8l1p4p</v>
+        <v>Kmtuxmti1f9ut</v>
       </c>
       <c r="B2070" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79237,7 +79237,7 @@
     </row>
     <row r="2071">
       <c r="A2071" t="str">
-        <v>Kmtsffp8lrvf1</v>
+        <v>Kmtuxmti1ktrm</v>
       </c>
       <c r="B2071" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79313,7 +79313,7 @@
     </row>
     <row r="2073">
       <c r="A2073" t="str">
-        <v>Kmtsffp8ljsmb</v>
+        <v>Kmtuxmti1bh35</v>
       </c>
       <c r="B2073" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79351,7 +79351,7 @@
     </row>
     <row r="2074">
       <c r="A2074" t="str">
-        <v>Kmtsffp8lpnzb</v>
+        <v>Kmtuxmti1b8s5</v>
       </c>
       <c r="B2074" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79389,7 +79389,7 @@
     </row>
     <row r="2075">
       <c r="A2075" t="str">
-        <v>Kmtsffp8lv2p1</v>
+        <v>Kmtuxmti1zq85</v>
       </c>
       <c r="B2075" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79427,7 +79427,7 @@
     </row>
     <row r="2076">
       <c r="A2076" t="str">
-        <v>Kmtsffp8lup77</v>
+        <v>Kmtuxmti1q28t</v>
       </c>
       <c r="B2076" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -79465,7 +79465,7 @@
     </row>
     <row r="2077">
       <c r="A2077" t="str">
-        <v>Kmtsffp8lxo3h</v>
+        <v>Kmtuxmti112tg</v>
       </c>
       <c r="B2077" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -79503,7 +79503,7 @@
     </row>
     <row r="2078">
       <c r="A2078" t="str">
-        <v>Kmtsffp8llcqi</v>
+        <v>Kmtuxmti1caxi</v>
       </c>
       <c r="B2078" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -79541,7 +79541,7 @@
     </row>
     <row r="2079">
       <c r="A2079" t="str">
-        <v>Kmtsffp8lg81n</v>
+        <v>Kmtuxmti1r637</v>
       </c>
       <c r="B2079" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -79579,7 +79579,7 @@
     </row>
     <row r="2080">
       <c r="A2080" t="str">
-        <v>Kmtsffp8l0fuw</v>
+        <v>Kmtuxmti1px49</v>
       </c>
       <c r="B2080" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -79617,7 +79617,7 @@
     </row>
     <row r="2081">
       <c r="A2081" t="str">
-        <v>Kmtsffp8lpx4v</v>
+        <v>Kmtuxmti1kjgm</v>
       </c>
       <c r="B2081" t="str">
         <v>Asesor SDM Aparatur Ahli Muda</v>
@@ -79655,7 +79655,7 @@
     </row>
     <row r="2082">
       <c r="A2082" t="str">
-        <v>Kmtsffp8l6ia3</v>
+        <v>Kmtuxmti1ln3d</v>
       </c>
       <c r="B2082" t="str">
         <v>Asesor SDM Aparatur Ahli Pertama</v>
@@ -79769,7 +79769,7 @@
     </row>
     <row r="2085">
       <c r="A2085" t="str">
-        <v>Kmtsffp8l0ah0</v>
+        <v>Kmtuxmti1qt4b</v>
       </c>
       <c r="B2085" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -79807,7 +79807,7 @@
     </row>
     <row r="2086">
       <c r="A2086" t="str">
-        <v>Kmtsffp8lizj7</v>
+        <v>Kmtuxmti1g7z4</v>
       </c>
       <c r="B2086" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79845,7 +79845,7 @@
     </row>
     <row r="2087">
       <c r="A2087" t="str">
-        <v>Kmtsffp8lz6em</v>
+        <v>Kmtuxmti1lysu</v>
       </c>
       <c r="B2087" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -79921,7 +79921,7 @@
     </row>
     <row r="2089">
       <c r="A2089" t="str">
-        <v>Kmtsffp8l8f4l</v>
+        <v>Kmtuxmti11ay7</v>
       </c>
       <c r="B2089" t="str">
         <v>Penata Layanan Operasional</v>
@@ -79959,7 +79959,7 @@
     </row>
     <row r="2090">
       <c r="A2090" t="str">
-        <v>Kmtsffp8ljwxj</v>
+        <v>Kmtuxmti1vkev</v>
       </c>
       <c r="B2090" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -79997,7 +79997,7 @@
     </row>
     <row r="2091">
       <c r="A2091" t="str">
-        <v>Kmtsffp8lrhfo</v>
+        <v>Kmtuxmti1b0xf</v>
       </c>
       <c r="B2091" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80073,7 +80073,7 @@
     </row>
     <row r="2093">
       <c r="A2093" t="str">
-        <v>Kmtsffp8lsl3q</v>
+        <v>Kmtuxmti1236s</v>
       </c>
       <c r="B2093" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80111,7 +80111,7 @@
     </row>
     <row r="2094">
       <c r="A2094" t="str">
-        <v>Kmtsffp8l694k</v>
+        <v>Kmtuxmti1ihhg</v>
       </c>
       <c r="B2094" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80149,7 +80149,7 @@
     </row>
     <row r="2095">
       <c r="A2095" t="str">
-        <v>Kmtsffp8lrk00</v>
+        <v>Kmtuxmti1ydoz</v>
       </c>
       <c r="B2095" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80187,7 +80187,7 @@
     </row>
     <row r="2096">
       <c r="A2096" t="str">
-        <v>Kmtsffp8lajis</v>
+        <v>Kmtuxmti1ttk3</v>
       </c>
       <c r="B2096" t="str">
         <v>Analis Anggaran Ahli Pertama/ Analis Keuangan Negara Ahli Pertama</v>
@@ -80225,7 +80225,7 @@
     </row>
     <row r="2097">
       <c r="A2097" t="str">
-        <v>Kmtsffp8lo9vx</v>
+        <v>Kmtuxmti1vwmx</v>
       </c>
       <c r="B2097" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Muda/Pengawas Keuangan Negara Ahli Muda</v>
@@ -80263,7 +80263,7 @@
     </row>
     <row r="2098">
       <c r="A2098" t="str">
-        <v>Kmtsffp8lb2os</v>
+        <v>Kmtuxmti1rgeu</v>
       </c>
       <c r="B2098" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Pertama/Pengawas Keuangan Negara Ahli Pertama</v>
@@ -80301,7 +80301,7 @@
     </row>
     <row r="2099">
       <c r="A2099" t="str">
-        <v>Kmtsffp8lyy74</v>
+        <v>Kmtuxmti1hw0s</v>
       </c>
       <c r="B2099" t="str">
         <v>Pranata Keuangan APBN Penyelia/Pengawas Keuangan Negara Penyelia</v>
@@ -80339,7 +80339,7 @@
     </row>
     <row r="2100">
       <c r="A2100" t="str">
-        <v>Kmtsffp8l7slf</v>
+        <v>Kmtuxmti15aop</v>
       </c>
       <c r="B2100" t="str">
         <v>Pranata Keuangan APBN Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -80377,7 +80377,7 @@
     </row>
     <row r="2101">
       <c r="A2101" t="str">
-        <v>Kmtsffp8lgnfp</v>
+        <v>Kmtuxmti1i0ir</v>
       </c>
       <c r="B2101" t="str">
         <v>Pranata Keuangan APBN Terampil/Pengawas Keuangan Negara Terampil</v>
@@ -80415,7 +80415,7 @@
     </row>
     <row r="2102">
       <c r="A2102" t="str">
-        <v>Kmtsffp8l3he8</v>
+        <v>Kmtuxmti10n7o</v>
       </c>
       <c r="B2102" t="str">
         <v>Analis SDM Aparatur Ahli Muda</v>
@@ -80453,7 +80453,7 @@
     </row>
     <row r="2103">
       <c r="A2103" t="str">
-        <v>Kmtsffp8l13h8</v>
+        <v>Kmtuxmti1ktv0</v>
       </c>
       <c r="B2103" t="str">
         <v>Analis SDM Aparatur Ahli Pertama</v>
@@ -80491,7 +80491,7 @@
     </row>
     <row r="2104">
       <c r="A2104" t="str">
-        <v>Kmtsffp8lb67f</v>
+        <v>Kmtuxmti1ioqn</v>
       </c>
       <c r="B2104" t="str">
         <v>Pranata SDM Aparatur Penyelia</v>
@@ -80529,7 +80529,7 @@
     </row>
     <row r="2105">
       <c r="A2105" t="str">
-        <v>Kmtsffp8lxcsk</v>
+        <v>Kmtuxmti176wi</v>
       </c>
       <c r="B2105" t="str">
         <v>Pranata SDM Aparatur Mahir</v>
@@ -80567,7 +80567,7 @@
     </row>
     <row r="2106">
       <c r="A2106" t="str">
-        <v>Kmtsffp8l53e4</v>
+        <v>Kmtuxmti18hy8</v>
       </c>
       <c r="B2106" t="str">
         <v>Pranata SDM Aparatur Terampil</v>
@@ -80681,7 +80681,7 @@
     </row>
     <row r="2109">
       <c r="A2109" t="str">
-        <v>Kmtsffp8lzq8d</v>
+        <v>Kmtuxmti1xa6t</v>
       </c>
       <c r="B2109" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80719,7 +80719,7 @@
     </row>
     <row r="2110">
       <c r="A2110" t="str">
-        <v>Kmtsffp8ljmdw</v>
+        <v>Kmtuxmti11ea1</v>
       </c>
       <c r="B2110" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80757,7 +80757,7 @@
     </row>
     <row r="2111">
       <c r="A2111" t="str">
-        <v>Kmtsffp8l1jtt</v>
+        <v>Kmtuxmti1h7nl</v>
       </c>
       <c r="B2111" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80833,7 +80833,7 @@
     </row>
     <row r="2113">
       <c r="A2113" t="str">
-        <v>Kmtsffp8lnw5l</v>
+        <v>Kmtuxmti1tigh</v>
       </c>
       <c r="B2113" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -80871,7 +80871,7 @@
     </row>
     <row r="2114">
       <c r="A2114" t="str">
-        <v>Kmtsffp8lo2ob</v>
+        <v>Kmtuxmti18vaj</v>
       </c>
       <c r="B2114" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -80909,7 +80909,7 @@
     </row>
     <row r="2115">
       <c r="A2115" t="str">
-        <v>Kmtsffp8lwjsm</v>
+        <v>Kmtuxmti1csjv</v>
       </c>
       <c r="B2115" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -80985,7 +80985,7 @@
     </row>
     <row r="2117">
       <c r="A2117" t="str">
-        <v>Kmtsffp8lerd8</v>
+        <v>Kmtuxmti1r3m0</v>
       </c>
       <c r="B2117" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -81023,7 +81023,7 @@
     </row>
     <row r="2118">
       <c r="A2118" t="str">
-        <v>Kmtsffp8lzrrv</v>
+        <v>Kmtuxmti1j68t</v>
       </c>
       <c r="B2118" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81061,7 +81061,7 @@
     </row>
     <row r="2119">
       <c r="A2119" t="str">
-        <v>Kmtsffp8le668</v>
+        <v>Kmtuxmti1juk3</v>
       </c>
       <c r="B2119" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81099,7 +81099,7 @@
     </row>
     <row r="2120">
       <c r="A2120" t="str">
-        <v>Kmtsffp8ltikn</v>
+        <v>Kmtuxmti14hz8</v>
       </c>
       <c r="B2120" t="str">
         <v>Pengawas Keuangan Negara Ahli Pertama</v>
@@ -81137,7 +81137,7 @@
     </row>
     <row r="2121">
       <c r="A2121" t="str">
-        <v>Kmtsffp8leeeo</v>
+        <v>Kmtuxmti1yzne</v>
       </c>
       <c r="B2121" t="str">
         <v>Pengawas Keuangan Negara Penyelia</v>
@@ -81175,7 +81175,7 @@
     </row>
     <row r="2122">
       <c r="A2122" t="str">
-        <v>Kmtsffp8lfwcd</v>
+        <v>Kmtuxmti15stz</v>
       </c>
       <c r="B2122" t="str">
         <v>Pengawas Keuangan Negara Mahir</v>
@@ -81213,7 +81213,7 @@
     </row>
     <row r="2123">
       <c r="A2123" t="str">
-        <v>Kmtsffp8logwy</v>
+        <v>Kmtuxmti1xhzv</v>
       </c>
       <c r="B2123" t="str">
         <v>Pengawas Keuangan Negara Terampil</v>
@@ -81327,7 +81327,7 @@
     </row>
     <row r="2126">
       <c r="A2126" t="str">
-        <v>Kmtsffp8lq1vv</v>
+        <v>Kmtuxmti16y58</v>
       </c>
       <c r="B2126" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81365,7 +81365,7 @@
     </row>
     <row r="2127">
       <c r="A2127" t="str">
-        <v>Kmtsffp8lkwiz</v>
+        <v>Kmtuxmti17g24</v>
       </c>
       <c r="B2127" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81403,7 +81403,7 @@
     </row>
     <row r="2128">
       <c r="A2128" t="str">
-        <v>Kmtsffp8lvy9c</v>
+        <v>Kmtuxmti1b22a</v>
       </c>
       <c r="B2128" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81441,7 +81441,7 @@
     </row>
     <row r="2129">
       <c r="A2129" t="str">
-        <v>Kmtsffp8ldnzm</v>
+        <v>Kmtuxmti142oj</v>
       </c>
       <c r="B2129" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81517,7 +81517,7 @@
     </row>
     <row r="2131">
       <c r="A2131" t="str">
-        <v>Kmtsffp8lhj46</v>
+        <v>Kmtuxmti1hr8l</v>
       </c>
       <c r="B2131" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81555,7 +81555,7 @@
     </row>
     <row r="2132">
       <c r="A2132" t="str">
-        <v>Kmtsffp8la5fb</v>
+        <v>Kmtuxmti1phh9</v>
       </c>
       <c r="B2132" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81593,7 +81593,7 @@
     </row>
     <row r="2133">
       <c r="A2133" t="str">
-        <v>Kmtsffp8llm6f</v>
+        <v>Kmtuxmti1juof</v>
       </c>
       <c r="B2133" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81631,7 +81631,7 @@
     </row>
     <row r="2134">
       <c r="A2134" t="str">
-        <v>Kmtsffp8ludr0</v>
+        <v>Kmtuxmti1u849</v>
       </c>
       <c r="B2134" t="str">
         <v>Penata Keprotokolan*</v>
@@ -81707,7 +81707,7 @@
     </row>
     <row r="2136">
       <c r="A2136" t="str">
-        <v>Kmtsffp8lp4ii</v>
+        <v>Kmtuxmti13y8v</v>
       </c>
       <c r="B2136" t="str">
         <v>Penata Layanan Operasional</v>
@@ -81745,7 +81745,7 @@
     </row>
     <row r="2137">
       <c r="A2137" t="str">
-        <v>Kmtsffp8lqu8a</v>
+        <v>Kmtuxmti13njp</v>
       </c>
       <c r="B2137" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -81783,7 +81783,7 @@
     </row>
     <row r="2138">
       <c r="A2138" t="str">
-        <v>Kmtsffp8lee2o</v>
+        <v>Kmtuxmti1bsb7</v>
       </c>
       <c r="B2138" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -81821,7 +81821,7 @@
     </row>
     <row r="2139">
       <c r="A2139" t="str">
-        <v>Kmtsffp8lzl26</v>
+        <v>Kmtuxmti1cev6</v>
       </c>
       <c r="B2139" t="str">
         <v>Pengawas Keuangan Negara Ahli Muda</v>
@@ -81859,7 +81859,7 @@
     </row>
     <row r="2140">
       <c r="A2140" t="str">
-        <v>Kmtsffp8l83v0</v>
+        <v>Kmtuxmti1oi5g</v>
       </c>
       <c r="B2140" t="str">
         <v>Pengawas Keuangan Negara Pertama</v>
@@ -81897,7 +81897,7 @@
     </row>
     <row r="2141">
       <c r="A2141" t="str">
-        <v>Kmtsffp8lw617</v>
+        <v>Kmtuxmti1k5hr</v>
       </c>
       <c r="B2141" t="str">
         <v>Penata Laksana Barang Penyelia/ Pengawas Keuangan Negara Penyelia</v>
@@ -81935,7 +81935,7 @@
     </row>
     <row r="2142">
       <c r="A2142" t="str">
-        <v>Kmtsffp8l07xs</v>
+        <v>Kmtuxmti1h6vp</v>
       </c>
       <c r="B2142" t="str">
         <v>Penata Laksana Barang Mahir/ Pengawas Keuangan Negara Mahir</v>
@@ -81973,7 +81973,7 @@
     </row>
     <row r="2143">
       <c r="A2143" t="str">
-        <v>Kmtsffp8luj9x</v>
+        <v>Kmtuxmti108dl</v>
       </c>
       <c r="B2143" t="str">
         <v>Penata Laksana Barang Terampil/ Pengawas Keuangan Negara Terampil</v>
@@ -82011,7 +82011,7 @@
     </row>
     <row r="2144">
       <c r="A2144" t="str">
-        <v>Kmtsffp8l1ydt</v>
+        <v>Kmtuxmti1pfn1</v>
       </c>
       <c r="B2144" t="str">
         <v>Arsiparis Ahli Muda</v>
@@ -82049,7 +82049,7 @@
     </row>
     <row r="2145">
       <c r="A2145" t="str">
-        <v>Kmtsffp8lq7za</v>
+        <v>Kmtuxmti1av6h</v>
       </c>
       <c r="B2145" t="str">
         <v>Arsiparis Ahli Pertama</v>
@@ -82087,7 +82087,7 @@
     </row>
     <row r="2146">
       <c r="A2146" t="str">
-        <v>Kmtsffp8lldha</v>
+        <v>Kmtuxmti13wbl</v>
       </c>
       <c r="B2146" t="str">
         <v>Arsiparis Penyelia</v>
@@ -82125,7 +82125,7 @@
     </row>
     <row r="2147">
       <c r="A2147" t="str">
-        <v>Kmtsffp8lc60l</v>
+        <v>Kmtuxmti1wocv</v>
       </c>
       <c r="B2147" t="str">
         <v>Arsiparis Mahir</v>
@@ -82163,7 +82163,7 @@
     </row>
     <row r="2148">
       <c r="A2148" t="str">
-        <v>Kmtsffp8lkegx</v>
+        <v>Kmtuxmti1r7it</v>
       </c>
       <c r="B2148" t="str">
         <v>Arsiparis Terampil</v>
@@ -82277,7 +82277,7 @@
     </row>
     <row r="2151">
       <c r="A2151" t="str">
-        <v>Kmtsffp8lk002</v>
+        <v>Kmtuxmti1qnyt</v>
       </c>
       <c r="B2151" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -82315,7 +82315,7 @@
     </row>
     <row r="2152">
       <c r="A2152" t="str">
-        <v>Kmtsffp8l5we7</v>
+        <v>Kmtuxmti1eu0c</v>
       </c>
       <c r="B2152" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82353,7 +82353,7 @@
     </row>
     <row r="2153">
       <c r="A2153" t="str">
-        <v>Kmtsffp8llib5</v>
+        <v>Kmtuxmti1zyi6</v>
       </c>
       <c r="B2153" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82391,7 +82391,7 @@
     </row>
     <row r="2154">
       <c r="A2154" t="str">
-        <v>Kmtsffp8ltnab</v>
+        <v>Kmtuxmti18lwd</v>
       </c>
       <c r="B2154" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82429,7 +82429,7 @@
     </row>
     <row r="2155">
       <c r="A2155" t="str">
-        <v>Kmtsffp8lce29</v>
+        <v>Kmtuxmti1vj3p</v>
       </c>
       <c r="B2155" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82467,7 +82467,7 @@
     </row>
     <row r="2156">
       <c r="A2156" t="str">
-        <v>Kmtsffp8ly8ig</v>
+        <v>Kmtuxmti1z22v</v>
       </c>
       <c r="B2156" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82505,7 +82505,7 @@
     </row>
     <row r="2157">
       <c r="A2157" t="str">
-        <v>Kmtsffp8lgcz8</v>
+        <v>Kmtuxmti1yfq2</v>
       </c>
       <c r="B2157" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82581,7 +82581,7 @@
     </row>
     <row r="2159">
       <c r="A2159" t="str">
-        <v>Kmtsffp8lqars</v>
+        <v>Kmtuxmti1y8ag</v>
       </c>
       <c r="B2159" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82619,7 +82619,7 @@
     </row>
     <row r="2160">
       <c r="A2160" t="str">
-        <v>Kmtsffp8lkcv6</v>
+        <v>Kmtuxmti1exvd</v>
       </c>
       <c r="B2160" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82657,7 +82657,7 @@
     </row>
     <row r="2161">
       <c r="A2161" t="str">
-        <v>Kmtsffp8lbqad</v>
+        <v>Kmtuxmti1r3ur</v>
       </c>
       <c r="B2161" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82695,7 +82695,7 @@
     </row>
     <row r="2162">
       <c r="A2162" t="str">
-        <v>Kmtsffp8lnijk</v>
+        <v>Kmtuxmti1h01y</v>
       </c>
       <c r="B2162" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -82733,7 +82733,7 @@
     </row>
     <row r="2163">
       <c r="A2163" t="str">
-        <v>Kmtsffp8loofu</v>
+        <v>Kmtuxmti1rj1j</v>
       </c>
       <c r="B2163" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -82771,7 +82771,7 @@
     </row>
     <row r="2164">
       <c r="A2164" t="str">
-        <v>Kmtsffp8lyejt</v>
+        <v>Kmtuxmti1x3oy</v>
       </c>
       <c r="B2164" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -82809,7 +82809,7 @@
     </row>
     <row r="2165">
       <c r="A2165" t="str">
-        <v>Kmtsffp8ldan5</v>
+        <v>Kmtuxmti1fei8</v>
       </c>
       <c r="B2165" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -82885,7 +82885,7 @@
     </row>
     <row r="2167">
       <c r="A2167" t="str">
-        <v>Kmtsffp8layl0</v>
+        <v>Kmtuxmti1yhpu</v>
       </c>
       <c r="B2167" t="str">
         <v>Penata Layanan Operasional</v>
@@ -82923,7 +82923,7 @@
     </row>
     <row r="2168">
       <c r="A2168" t="str">
-        <v>Kmtsffp8lwrhu</v>
+        <v>Kmtuxmti1f1yv</v>
       </c>
       <c r="B2168" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -82961,7 +82961,7 @@
     </row>
     <row r="2169">
       <c r="A2169" t="str">
-        <v>Kmtsffp8l9y09</v>
+        <v>Kmtuxmti1uauk</v>
       </c>
       <c r="B2169" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -82999,7 +82999,7 @@
     </row>
     <row r="2170">
       <c r="A2170" t="str">
-        <v>Kmtsffp8l6uoy</v>
+        <v>Kmtuxmti1ljg5</v>
       </c>
       <c r="B2170" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83037,7 +83037,7 @@
     </row>
     <row r="2171">
       <c r="A2171" t="str">
-        <v>Kmtsffp8lv96e</v>
+        <v>Kmtuxmti1lhsb</v>
       </c>
       <c r="B2171" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83075,7 +83075,7 @@
     </row>
     <row r="2172">
       <c r="A2172" t="str">
-        <v>Kmtsffp8lrdf4</v>
+        <v>Kmtuxmti12dfx</v>
       </c>
       <c r="B2172" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83113,7 +83113,7 @@
     </row>
     <row r="2173">
       <c r="A2173" t="str">
-        <v>Kmtsffp8l6boo</v>
+        <v>Kmtuxmti16mza</v>
       </c>
       <c r="B2173" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83151,7 +83151,7 @@
     </row>
     <row r="2174">
       <c r="A2174" t="str">
-        <v>Kmtsffp8lmoh3</v>
+        <v>Kmtuxmti1norg</v>
       </c>
       <c r="B2174" t="str">
         <v>Pranata Humas Ahli Muda</v>
@@ -83189,7 +83189,7 @@
     </row>
     <row r="2175">
       <c r="A2175" t="str">
-        <v>Kmtsffp8l57ok</v>
+        <v>Kmtuxmti1hck7</v>
       </c>
       <c r="B2175" t="str">
         <v>Pranata Humas Ahli Pertama**</v>
@@ -83227,7 +83227,7 @@
     </row>
     <row r="2176">
       <c r="A2176" t="str">
-        <v>Kmtsffp8l75lx</v>
+        <v>Kmtuxmti1gv5w</v>
       </c>
       <c r="B2176" t="str">
         <v>Pranata Humas Penyelia**</v>
@@ -83265,7 +83265,7 @@
     </row>
     <row r="2177">
       <c r="A2177" t="str">
-        <v>Kmtsffp8lxlwp</v>
+        <v>Kmtuxmti1vx68</v>
       </c>
       <c r="B2177" t="str">
         <v>Pranata Humas Mahir**</v>
@@ -83303,7 +83303,7 @@
     </row>
     <row r="2178">
       <c r="A2178" t="str">
-        <v>Kmtsffp8lumzk</v>
+        <v>Kmtuxmti1i515</v>
       </c>
       <c r="B2178" t="str">
         <v>Pranata Humas Terampil**</v>
@@ -83341,7 +83341,7 @@
     </row>
     <row r="2179">
       <c r="A2179" t="str">
-        <v>Kmtsffp8lxxhz</v>
+        <v>Kmtuxmti195hi</v>
       </c>
       <c r="B2179" t="str">
         <v>Pustakawan Ahli Pertama</v>
@@ -83379,7 +83379,7 @@
     </row>
     <row r="2180">
       <c r="A2180" t="str">
-        <v>Kmtsffp8lmh0z</v>
+        <v>Kmtuxmti11mvu</v>
       </c>
       <c r="B2180" t="str">
         <v>Asisten Perpustakaan Penyelia</v>
@@ -83417,7 +83417,7 @@
     </row>
     <row r="2181">
       <c r="A2181" t="str">
-        <v>Kmtsffp8l8x9s</v>
+        <v>Kmtuxmti1w8kp</v>
       </c>
       <c r="B2181" t="str">
         <v>Asisten Perpustakaan Mahir</v>
@@ -83455,7 +83455,7 @@
     </row>
     <row r="2182">
       <c r="A2182" t="str">
-        <v>Kmtsffp8l67xr</v>
+        <v>Kmtuxmti1oboq</v>
       </c>
       <c r="B2182" t="str">
         <v>Asisten Perpustakaan Terampil</v>
@@ -83493,7 +83493,7 @@
     </row>
     <row r="2183">
       <c r="A2183" t="str">
-        <v>Kmtsffp8lt9a6</v>
+        <v>Kmtuxmti1jn93</v>
       </c>
       <c r="B2183" t="str">
         <v>Analis Pengelolaan Keuangan APBN Ahli Madya/Pengawas Keuangan Negara Ahli Madya</v>
@@ -83531,7 +83531,7 @@
     </row>
     <row r="2184">
       <c r="A2184" t="str">
-        <v>Kmtsffp8l0pgy</v>
+        <v>Kmtuxmti1qvog</v>
       </c>
       <c r="B2184" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Muda</v>
@@ -83569,7 +83569,7 @@
     </row>
     <row r="2185">
       <c r="A2185" t="str">
-        <v>Kmtsffp8lk850</v>
+        <v>Kmtuxmti1iiad</v>
       </c>
       <c r="B2185" t="str">
         <v>Perancang Peraturan Perundang-Undangan Ahli Pertama</v>
@@ -83683,7 +83683,7 @@
     </row>
     <row r="2188">
       <c r="A2188" t="str">
-        <v>Kmtsffp8l5avg</v>
+        <v>Kmtuxmti1x1k9</v>
       </c>
       <c r="B2188" t="str">
         <v>Penata Layanan Operasional</v>
@@ -83721,7 +83721,7 @@
     </row>
     <row r="2189">
       <c r="A2189" t="str">
-        <v>Kmtsffp8lzaz2</v>
+        <v>Kmtuxmti1bswh</v>
       </c>
       <c r="B2189" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83759,7 +83759,7 @@
     </row>
     <row r="2190">
       <c r="A2190" t="str">
-        <v>Kmtsffp8ljexd</v>
+        <v>Kmtuxmti1k747</v>
       </c>
       <c r="B2190" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -83797,7 +83797,7 @@
     </row>
     <row r="2191">
       <c r="A2191" t="str">
-        <v>Kmtsffp8lukfq</v>
+        <v>Kmtuxmti1pspr</v>
       </c>
       <c r="B2191" t="str">
         <v>Penata Keprotokolan*</v>
@@ -83911,7 +83911,7 @@
     </row>
     <row r="2194">
       <c r="A2194" t="str">
-        <v>Kmtsffp8lcsst</v>
+        <v>Kmtuxmti1jc84</v>
       </c>
       <c r="B2194" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -83949,7 +83949,7 @@
     </row>
     <row r="2195">
       <c r="A2195" t="str">
-        <v>Kmtsffp8luo8r</v>
+        <v>Kmtuxmti1u9c5</v>
       </c>
       <c r="B2195" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -83987,7 +83987,7 @@
     </row>
     <row r="2196">
       <c r="A2196" t="str">
-        <v>Kmtsffp8lf1i1</v>
+        <v>Kmtuxmti1xuki</v>
       </c>
       <c r="B2196" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84063,7 +84063,7 @@
     </row>
     <row r="2198">
       <c r="A2198" t="str">
-        <v>Kmtsffp8lvw40</v>
+        <v>Kmtuxmti195pu</v>
       </c>
       <c r="B2198" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84101,7 +84101,7 @@
     </row>
     <row r="2199">
       <c r="A2199" t="str">
-        <v>Kmtsffp8lv95b</v>
+        <v>Kmtuxmti2smcz</v>
       </c>
       <c r="B2199" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84139,7 +84139,7 @@
     </row>
     <row r="2200">
       <c r="A2200" t="str">
-        <v>Kmtsffp8lvdqv</v>
+        <v>Kmtuxmti20n2b</v>
       </c>
       <c r="B2200" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84177,7 +84177,7 @@
     </row>
     <row r="2201">
       <c r="A2201" t="str">
-        <v>Kmtsffp8l6anw</v>
+        <v>Kmtuxmti2l0om</v>
       </c>
       <c r="B2201" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84215,7 +84215,7 @@
     </row>
     <row r="2202">
       <c r="A2202" t="str">
-        <v>Kmtsffp8l3qk8</v>
+        <v>Kmtuxmti27vfh</v>
       </c>
       <c r="B2202" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84253,7 +84253,7 @@
     </row>
     <row r="2203">
       <c r="A2203" t="str">
-        <v>Kmtsffp8l3ya1</v>
+        <v>Kmtuxmti2lkor</v>
       </c>
       <c r="B2203" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -84291,7 +84291,7 @@
     </row>
     <row r="2204">
       <c r="A2204" t="str">
-        <v>Kmtsffp8lgupf</v>
+        <v>Kmtuxmti2op8t</v>
       </c>
       <c r="B2204" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -84405,7 +84405,7 @@
     </row>
     <row r="2207">
       <c r="A2207" t="str">
-        <v>Kmtsffp8ltz2h</v>
+        <v>Kmtuxmti2wxv9</v>
       </c>
       <c r="B2207" t="str">
         <v>Penata Layanan Operasional</v>
@@ -84443,7 +84443,7 @@
     </row>
     <row r="2208">
       <c r="A2208" t="str">
-        <v>Kmtsffp8lyhlr</v>
+        <v>Kmtuxmti27maj</v>
       </c>
       <c r="B2208" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84481,7 +84481,7 @@
     </row>
     <row r="2209">
       <c r="A2209" t="str">
-        <v>Kmtsffp8li2sd</v>
+        <v>Kmtuxmti2cmst</v>
       </c>
       <c r="B2209" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84519,7 +84519,7 @@
     </row>
     <row r="2210">
       <c r="A2210" t="str">
-        <v>Kmtsffp8lv2ig</v>
+        <v>Kmtuxmti2cvoz</v>
       </c>
       <c r="B2210" t="str">
         <v>Penata Keprotokolan*</v>
@@ -84633,7 +84633,7 @@
     </row>
     <row r="2213">
       <c r="A2213" t="str">
-        <v>Kmtsffp8l3wg5</v>
+        <v>Kmtuxmti2dsex</v>
       </c>
       <c r="B2213" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84671,7 +84671,7 @@
     </row>
     <row r="2214">
       <c r="A2214" t="str">
-        <v>Kmtsffp8lvqax</v>
+        <v>Kmtuxmti2qb6m</v>
       </c>
       <c r="B2214" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84709,7 +84709,7 @@
     </row>
     <row r="2215">
       <c r="A2215" t="str">
-        <v>Kmtsffp8ltewp</v>
+        <v>Kmtuxmti2m0mp</v>
       </c>
       <c r="B2215" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84785,7 +84785,7 @@
     </row>
     <row r="2217">
       <c r="A2217" t="str">
-        <v>Kmtsffp8l9ekn</v>
+        <v>Kmtuxmti2guz4</v>
       </c>
       <c r="B2217" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -84823,7 +84823,7 @@
     </row>
     <row r="2218">
       <c r="A2218" t="str">
-        <v>Kmtsffp8lzkf9</v>
+        <v>Kmtuxmti2qs7z</v>
       </c>
       <c r="B2218" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -84861,7 +84861,7 @@
     </row>
     <row r="2219">
       <c r="A2219" t="str">
-        <v>Kmtsffp8lx3f5</v>
+        <v>Kmtuxmti2aus7</v>
       </c>
       <c r="B2219" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -84899,7 +84899,7 @@
     </row>
     <row r="2220">
       <c r="A2220" t="str">
-        <v>Kmtsffp8lnl4k</v>
+        <v>Kmtuxmti2n87h</v>
       </c>
       <c r="B2220" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -84937,7 +84937,7 @@
     </row>
     <row r="2221">
       <c r="A2221" t="str">
-        <v>Kmtsffp8lkpxq</v>
+        <v>Kmtuxmti26a0o</v>
       </c>
       <c r="B2221" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -84975,7 +84975,7 @@
     </row>
     <row r="2222">
       <c r="A2222" t="str">
-        <v>Kmtsffp8lfnn1</v>
+        <v>Kmtuxmti2kder</v>
       </c>
       <c r="B2222" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85013,7 +85013,7 @@
     </row>
     <row r="2223">
       <c r="A2223" t="str">
-        <v>Kmtsffp8liue9</v>
+        <v>Kmtuxmti21hkv</v>
       </c>
       <c r="B2223" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85127,7 +85127,7 @@
     </row>
     <row r="2226">
       <c r="A2226" t="str">
-        <v>Kmtsffp8lys98</v>
+        <v>Kmtuxmti2bjt9</v>
       </c>
       <c r="B2226" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85165,7 +85165,7 @@
     </row>
     <row r="2227">
       <c r="A2227" t="str">
-        <v>Kmtsffp8ldplm</v>
+        <v>Kmtuxmti2ih4z</v>
       </c>
       <c r="B2227" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85203,7 +85203,7 @@
     </row>
     <row r="2228">
       <c r="A2228" t="str">
-        <v>Kmtsffp8lae5z</v>
+        <v>Kmtuxmti2slkm</v>
       </c>
       <c r="B2228" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85241,7 +85241,7 @@
     </row>
     <row r="2229">
       <c r="A2229" t="str">
-        <v>Kmtsffp8l9am3</v>
+        <v>Kmtuxmti2kklk</v>
       </c>
       <c r="B2229" t="str">
         <v>Penata Keprotokolan*</v>
@@ -85355,7 +85355,7 @@
     </row>
     <row r="2232">
       <c r="A2232" t="str">
-        <v>Kmtsffp8lkt6p</v>
+        <v>Kmtuxmti22dz2</v>
       </c>
       <c r="B2232" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85393,7 +85393,7 @@
     </row>
     <row r="2233">
       <c r="A2233" t="str">
-        <v>Kmtsffp8lsdg2</v>
+        <v>Kmtuxmti2ck4e</v>
       </c>
       <c r="B2233" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85431,7 +85431,7 @@
     </row>
     <row r="2234">
       <c r="A2234" t="str">
-        <v>Kmtsffp8ld7ed</v>
+        <v>Kmtuxmti2gsyi</v>
       </c>
       <c r="B2234" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85507,7 +85507,7 @@
     </row>
     <row r="2236">
       <c r="A2236" t="str">
-        <v>Kmtsffp8lqvek</v>
+        <v>Kmtuxmti2tayx</v>
       </c>
       <c r="B2236" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -85545,7 +85545,7 @@
     </row>
     <row r="2237">
       <c r="A2237" t="str">
-        <v>Kmtsffp8llt6v</v>
+        <v>Kmtuxmti2k8y0</v>
       </c>
       <c r="B2237" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85583,7 +85583,7 @@
     </row>
     <row r="2238">
       <c r="A2238" t="str">
-        <v>Kmtsffp8ltsfb</v>
+        <v>Kmtuxmti2k3bv</v>
       </c>
       <c r="B2238" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85621,7 +85621,7 @@
     </row>
     <row r="2239">
       <c r="A2239" t="str">
-        <v>Kmtsffp8lkdjb</v>
+        <v>Kmtuxmti2u7kw</v>
       </c>
       <c r="B2239" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -85659,7 +85659,7 @@
     </row>
     <row r="2240">
       <c r="A2240" t="str">
-        <v>Kmtsffp8l7xoz</v>
+        <v>Kmtuxmti2lwpd</v>
       </c>
       <c r="B2240" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -85697,7 +85697,7 @@
     </row>
     <row r="2241">
       <c r="A2241" t="str">
-        <v>Kmtsffp8lm9kx</v>
+        <v>Kmtuxmti2gi39</v>
       </c>
       <c r="B2241" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -85735,7 +85735,7 @@
     </row>
     <row r="2242">
       <c r="A2242" t="str">
-        <v>Kmtsffp8leu2d</v>
+        <v>Kmtuxmti2bocp</v>
       </c>
       <c r="B2242" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -85849,7 +85849,7 @@
     </row>
     <row r="2245">
       <c r="A2245" t="str">
-        <v>Kmtsffp8lqclh</v>
+        <v>Kmtuxmti2sqqs</v>
       </c>
       <c r="B2245" t="str">
         <v>Penata Layanan Operasional</v>
@@ -85887,7 +85887,7 @@
     </row>
     <row r="2246">
       <c r="A2246" t="str">
-        <v>Kmtsffp8lkodq</v>
+        <v>Kmtuxmti2vtxy</v>
       </c>
       <c r="B2246" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -85925,7 +85925,7 @@
     </row>
     <row r="2247">
       <c r="A2247" t="str">
-        <v>Kmtsffp8l3pzk</v>
+        <v>Kmtuxmti2spfi</v>
       </c>
       <c r="B2247" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -85963,7 +85963,7 @@
     </row>
     <row r="2248">
       <c r="A2248" t="str">
-        <v>Kmtsffp8lu79v</v>
+        <v>Kmtuxmti2auwq</v>
       </c>
       <c r="B2248" t="str">
         <v>Penata Keprotokolan*</v>
@@ -86039,7 +86039,7 @@
     </row>
     <row r="2250">
       <c r="A2250" t="str">
-        <v>Kmtsffp8lebs3</v>
+        <v>Kmtuxmti2i5wk</v>
       </c>
       <c r="B2250" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86077,7 +86077,7 @@
     </row>
     <row r="2251">
       <c r="A2251" t="str">
-        <v>Kmtsffp8lk3l5</v>
+        <v>Kmtuxmti2kixc</v>
       </c>
       <c r="B2251" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86115,7 +86115,7 @@
     </row>
     <row r="2252">
       <c r="A2252" t="str">
-        <v>Kmtsffp8lgwrp</v>
+        <v>Kmtuxmti29x7d</v>
       </c>
       <c r="B2252" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86153,7 +86153,7 @@
     </row>
     <row r="2253">
       <c r="A2253" t="str">
-        <v>Kmtsffp8l238y</v>
+        <v>Kmtuxmti2op9a</v>
       </c>
       <c r="B2253" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86191,7 +86191,7 @@
     </row>
     <row r="2254">
       <c r="A2254" t="str">
-        <v>Kmtsffp8ltoe1</v>
+        <v>Kmtuxmti2j8h6</v>
       </c>
       <c r="B2254" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86305,7 +86305,7 @@
     </row>
     <row r="2257">
       <c r="A2257" t="str">
-        <v>Kmtsffp8lo7tp</v>
+        <v>Kmtuxmti2pt24</v>
       </c>
       <c r="B2257" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86343,7 +86343,7 @@
     </row>
     <row r="2258">
       <c r="A2258" t="str">
-        <v>Kmtsffp8lgrl4</v>
+        <v>Kmtuxmti2vj21</v>
       </c>
       <c r="B2258" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86381,7 +86381,7 @@
     </row>
     <row r="2259">
       <c r="A2259" t="str">
-        <v>Kmtsffp8lqjyt</v>
+        <v>Kmtuxmti2ffy8</v>
       </c>
       <c r="B2259" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86457,7 +86457,7 @@
     </row>
     <row r="2261">
       <c r="A2261" t="str">
-        <v>Kmtsffp8laul8</v>
+        <v>Kmtuxmti2y3gy</v>
       </c>
       <c r="B2261" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -86495,7 +86495,7 @@
     </row>
     <row r="2262">
       <c r="A2262" t="str">
-        <v>Kmtsffp8locc6</v>
+        <v>Kmtuxmti2exg9</v>
       </c>
       <c r="B2262" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86533,7 +86533,7 @@
     </row>
     <row r="2263">
       <c r="A2263" t="str">
-        <v>Kmtsffp8ll0yl</v>
+        <v>Kmtuxmti2gwsq</v>
       </c>
       <c r="B2263" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86571,7 +86571,7 @@
     </row>
     <row r="2264">
       <c r="A2264" t="str">
-        <v>Kmtsffp8lsy65</v>
+        <v>Kmtuxmti2crpb</v>
       </c>
       <c r="B2264" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -86609,7 +86609,7 @@
     </row>
     <row r="2265">
       <c r="A2265" t="str">
-        <v>Kmtsffp8l9xfy</v>
+        <v>Kmtuxmti2qsev</v>
       </c>
       <c r="B2265" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -86647,7 +86647,7 @@
     </row>
     <row r="2266">
       <c r="A2266" t="str">
-        <v>Kmtsffp8l7xh7</v>
+        <v>Kmtuxmti2e524</v>
       </c>
       <c r="B2266" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -86685,7 +86685,7 @@
     </row>
     <row r="2267">
       <c r="A2267" t="str">
-        <v>Kmtsffp8lvbbo</v>
+        <v>Kmtuxmti2gis8</v>
       </c>
       <c r="B2267" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -86799,7 +86799,7 @@
     </row>
     <row r="2270">
       <c r="A2270" t="str">
-        <v>Kmtsffp8loir7</v>
+        <v>Kmtuxmti2mbkw</v>
       </c>
       <c r="B2270" t="str">
         <v>Penata Layanan Operasional</v>
@@ -86837,7 +86837,7 @@
     </row>
     <row r="2271">
       <c r="A2271" t="str">
-        <v>Kmtsffp8ltqwq</v>
+        <v>Kmtuxmti2kc0x</v>
       </c>
       <c r="B2271" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -86875,7 +86875,7 @@
     </row>
     <row r="2272">
       <c r="A2272" t="str">
-        <v>Kmtsffp8lk5tw</v>
+        <v>Kmtuxmti2c2xh</v>
       </c>
       <c r="B2272" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -86913,7 +86913,7 @@
     </row>
     <row r="2273">
       <c r="A2273" t="str">
-        <v>Kmtsffp8lte8h</v>
+        <v>Kmtuxmti2wwq3</v>
       </c>
       <c r="B2273" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87027,7 +87027,7 @@
     </row>
     <row r="2276">
       <c r="A2276" t="str">
-        <v>Kmtsffp8l0030</v>
+        <v>Kmtuxmti2w6e5</v>
       </c>
       <c r="B2276" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87065,7 +87065,7 @@
     </row>
     <row r="2277">
       <c r="A2277" t="str">
-        <v>Kmtsffp8ldrry</v>
+        <v>Kmtuxmti2gc4l</v>
       </c>
       <c r="B2277" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87103,7 +87103,7 @@
     </row>
     <row r="2278">
       <c r="A2278" t="str">
-        <v>Kmtsffp8myzaf</v>
+        <v>Kmtuxmti2q5it</v>
       </c>
       <c r="B2278" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87179,7 +87179,7 @@
     </row>
     <row r="2280">
       <c r="A2280" t="str">
-        <v>Kmtsffp8m0up8</v>
+        <v>Kmtuxmti2vhhl</v>
       </c>
       <c r="B2280" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87217,7 +87217,7 @@
     </row>
     <row r="2281">
       <c r="A2281" t="str">
-        <v>Kmtsffp8mr1go</v>
+        <v>Kmtuxmti26uri</v>
       </c>
       <c r="B2281" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87255,7 +87255,7 @@
     </row>
     <row r="2282">
       <c r="A2282" t="str">
-        <v>Kmtsffp8mtsw2</v>
+        <v>Kmtuxmti2vjjv</v>
       </c>
       <c r="B2282" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87293,7 +87293,7 @@
     </row>
     <row r="2283">
       <c r="A2283" t="str">
-        <v>Kmtsffp8mmic7</v>
+        <v>Kmtuxmti2uqzx</v>
       </c>
       <c r="B2283" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -87331,7 +87331,7 @@
     </row>
     <row r="2284">
       <c r="A2284" t="str">
-        <v>Kmtsffp8maqpa</v>
+        <v>Kmtuxmti2oevw</v>
       </c>
       <c r="B2284" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -87369,7 +87369,7 @@
     </row>
     <row r="2285">
       <c r="A2285" t="str">
-        <v>Kmtsffp8mz6c8</v>
+        <v>Kmtuxmti23cqa</v>
       </c>
       <c r="B2285" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -87407,7 +87407,7 @@
     </row>
     <row r="2286">
       <c r="A2286" t="str">
-        <v>Kmtsffp8mc9zw</v>
+        <v>Kmtuxmti20qf4</v>
       </c>
       <c r="B2286" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -87521,7 +87521,7 @@
     </row>
     <row r="2289">
       <c r="A2289" t="str">
-        <v>Kmtsffp8m574q</v>
+        <v>Kmtuxmti2x0ym</v>
       </c>
       <c r="B2289" t="str">
         <v>Penata Layanan Operasional</v>
@@ -87559,7 +87559,7 @@
     </row>
     <row r="2290">
       <c r="A2290" t="str">
-        <v>Kmtsffp8mm6o3</v>
+        <v>Kmtuxmti2g83v</v>
       </c>
       <c r="B2290" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87597,7 +87597,7 @@
     </row>
     <row r="2291">
       <c r="A2291" t="str">
-        <v>Kmtsffp8mt9cj</v>
+        <v>Kmtuxmti2r8ff</v>
       </c>
       <c r="B2291" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87635,7 +87635,7 @@
     </row>
     <row r="2292">
       <c r="A2292" t="str">
-        <v>Kmtsffp8mjo8d</v>
+        <v>Kmtuxmti2irvp</v>
       </c>
       <c r="B2292" t="str">
         <v>Penata Keprotokolan*</v>
@@ -87749,7 +87749,7 @@
     </row>
     <row r="2295">
       <c r="A2295" t="str">
-        <v>Kmtsffp8mdxxi</v>
+        <v>Kmtuxmti2xy0u</v>
       </c>
       <c r="B2295" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87787,7 +87787,7 @@
     </row>
     <row r="2296">
       <c r="A2296" t="str">
-        <v>Kmtsffp8m1hze</v>
+        <v>Kmtuxmti2dtrw</v>
       </c>
       <c r="B2296" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87825,7 +87825,7 @@
     </row>
     <row r="2297">
       <c r="A2297" t="str">
-        <v>Kmtsffp8mmlbj</v>
+        <v>Kmtuxmti2wule</v>
       </c>
       <c r="B2297" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -87901,7 +87901,7 @@
     </row>
     <row r="2299">
       <c r="A2299" t="str">
-        <v>Kmtsffp8mt69v</v>
+        <v>Kmtuxmti2pgkw</v>
       </c>
       <c r="B2299" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -87939,7 +87939,7 @@
     </row>
     <row r="2300">
       <c r="A2300" t="str">
-        <v>Kmtsffp8mg4im</v>
+        <v>Kmtuxmti2xwk5</v>
       </c>
       <c r="B2300" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -87977,7 +87977,7 @@
     </row>
     <row r="2301">
       <c r="A2301" t="str">
-        <v>Kmtsffp8mhus1</v>
+        <v>Kmtuxmti2tr3z</v>
       </c>
       <c r="B2301" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88015,7 +88015,7 @@
     </row>
     <row r="2302">
       <c r="A2302" t="str">
-        <v>Kmtsffp8m4fd3</v>
+        <v>Kmtuxmti2rl4w</v>
       </c>
       <c r="B2302" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -88053,7 +88053,7 @@
     </row>
     <row r="2303">
       <c r="A2303" t="str">
-        <v>Kmtsffp8mflpn</v>
+        <v>Kmtuxmti2hu7v</v>
       </c>
       <c r="B2303" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -88091,7 +88091,7 @@
     </row>
     <row r="2304">
       <c r="A2304" t="str">
-        <v>Kmtsffp8mkge4</v>
+        <v>Kmtuxmti2pl87</v>
       </c>
       <c r="B2304" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -88129,7 +88129,7 @@
     </row>
     <row r="2305">
       <c r="A2305" t="str">
-        <v>Kmtsffp8m9i28</v>
+        <v>Kmtuxmti2pzqe</v>
       </c>
       <c r="B2305" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -88243,7 +88243,7 @@
     </row>
     <row r="2308">
       <c r="A2308" t="str">
-        <v>Kmtsffp8mllo8</v>
+        <v>Kmtuxmti2i8cb</v>
       </c>
       <c r="B2308" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88281,7 +88281,7 @@
     </row>
     <row r="2309">
       <c r="A2309" t="str">
-        <v>Kmtsffp8malvk</v>
+        <v>Kmtuxmti2nukr</v>
       </c>
       <c r="B2309" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88319,7 +88319,7 @@
     </row>
     <row r="2310">
       <c r="A2310" t="str">
-        <v>Kmtsffp8mdd6e</v>
+        <v>Kmtuxmti24yya</v>
       </c>
       <c r="B2310" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88357,7 +88357,7 @@
     </row>
     <row r="2311">
       <c r="A2311" t="str">
-        <v>Kmtsffp8m9ljr</v>
+        <v>Kmtuxmti230dl</v>
       </c>
       <c r="B2311" t="str">
         <v>Penata Keprotokolan*</v>
@@ -88471,7 +88471,7 @@
     </row>
     <row r="2314">
       <c r="A2314" t="str">
-        <v>Kmtsffp8m46x3</v>
+        <v>Kmtuxmti2krdx</v>
       </c>
       <c r="B2314" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88509,7 +88509,7 @@
     </row>
     <row r="2315">
       <c r="A2315" t="str">
-        <v>Kmtsffp8m57vo</v>
+        <v>Kmtuxmti2m6rk</v>
       </c>
       <c r="B2315" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88547,7 +88547,7 @@
     </row>
     <row r="2316">
       <c r="A2316" t="str">
-        <v>Kmtsffp8mos49</v>
+        <v>Kmtuxmti2bmox</v>
       </c>
       <c r="B2316" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88623,7 +88623,7 @@
     </row>
     <row r="2318">
       <c r="A2318" t="str">
-        <v>Kmtsffp8m0vns</v>
+        <v>Kmtuxmti2ftnk</v>
       </c>
       <c r="B2318" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88661,7 +88661,7 @@
     </row>
     <row r="2319">
       <c r="A2319" t="str">
-        <v>Kmtsffp8muxvy</v>
+        <v>Kmtuxmti20v9p</v>
       </c>
       <c r="B2319" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88699,7 +88699,7 @@
     </row>
     <row r="2320">
       <c r="A2320" t="str">
-        <v>Kmtsffp8msrzs</v>
+        <v>Kmtuxmti2mcxn</v>
       </c>
       <c r="B2320" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88775,7 +88775,7 @@
     </row>
     <row r="2322">
       <c r="A2322" t="str">
-        <v>Kmtsffp8mcig4</v>
+        <v>Kmtuxmti27mos</v>
       </c>
       <c r="B2322" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88813,7 +88813,7 @@
     </row>
     <row r="2323">
       <c r="A2323" t="str">
-        <v>Kmtsffp8m7tvu</v>
+        <v>Kmtuxmti2or9p</v>
       </c>
       <c r="B2323" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -88851,7 +88851,7 @@
     </row>
     <row r="2324">
       <c r="A2324" t="str">
-        <v>Kmtsffp8msahc</v>
+        <v>Kmtuxmti2hgtb</v>
       </c>
       <c r="B2324" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -88927,7 +88927,7 @@
     </row>
     <row r="2326">
       <c r="A2326" t="str">
-        <v>Kmtsffp8mdi3k</v>
+        <v>Kmtuxmti2fiv1</v>
       </c>
       <c r="B2326" t="str">
         <v>Penata Layanan Operasional</v>
@@ -88965,7 +88965,7 @@
     </row>
     <row r="2327">
       <c r="A2327" t="str">
-        <v>Kmtsffp8max69</v>
+        <v>Kmtuxmti24egw</v>
       </c>
       <c r="B2327" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89003,7 +89003,7 @@
     </row>
     <row r="2328">
       <c r="A2328" t="str">
-        <v>Kmtsffp8mhqk2</v>
+        <v>Kmtuxmti29msb</v>
       </c>
       <c r="B2328" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89117,7 +89117,7 @@
     </row>
     <row r="2331">
       <c r="A2331" t="str">
-        <v>Kmtsffp8m776i</v>
+        <v>Kmtuxmti2pqi8</v>
       </c>
       <c r="B2331" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89155,7 +89155,7 @@
     </row>
     <row r="2332">
       <c r="A2332" t="str">
-        <v>Kmtsffp8mzbhs</v>
+        <v>Kmtuxmti206di</v>
       </c>
       <c r="B2332" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89193,7 +89193,7 @@
     </row>
     <row r="2333">
       <c r="A2333" t="str">
-        <v>Kmtsffp8medu1</v>
+        <v>Kmtuxmti2kg34</v>
       </c>
       <c r="B2333" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89269,7 +89269,7 @@
     </row>
     <row r="2335">
       <c r="A2335" t="str">
-        <v>Kmtsffp8mv44m</v>
+        <v>Kmtuxmti2o791</v>
       </c>
       <c r="B2335" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89307,7 +89307,7 @@
     </row>
     <row r="2336">
       <c r="A2336" t="str">
-        <v>Kmtsffp8mzuuj</v>
+        <v>Kmtuxmti2svah</v>
       </c>
       <c r="B2336" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89345,7 +89345,7 @@
     </row>
     <row r="2337">
       <c r="A2337" t="str">
-        <v>Kmtsffp8m3mg7</v>
+        <v>Kmtuxmti2kise</v>
       </c>
       <c r="B2337" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89383,7 +89383,7 @@
     </row>
     <row r="2338">
       <c r="A2338" t="str">
-        <v>Kmtsffp8m3l8r</v>
+        <v>Kmtuxmti2wxlv</v>
       </c>
       <c r="B2338" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Utama/Analis Keuangan Negara Ahli Utama</v>
@@ -89421,7 +89421,7 @@
     </row>
     <row r="2339">
       <c r="A2339" t="str">
-        <v>Kmtsffp8mz29n</v>
+        <v>Kmtuxmti2d8ti</v>
       </c>
       <c r="B2339" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Madya/Analis Keuangan Negara Ahli Madya</v>
@@ -89459,7 +89459,7 @@
     </row>
     <row r="2340">
       <c r="A2340" t="str">
-        <v>Kmtsffp8msos3</v>
+        <v>Kmtuxmti2uxvt</v>
       </c>
       <c r="B2340" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Muda/Analis Keuangan Negara Ahli Muda</v>
@@ -89497,7 +89497,7 @@
     </row>
     <row r="2341">
       <c r="A2341" t="str">
-        <v>Kmtsffp8meicf</v>
+        <v>Kmtuxmti2n2hk</v>
       </c>
       <c r="B2341" t="str">
         <v>Analis Pembiayaan Risiko dan Keuangan Ahli Pertama/Analis Keuangan Negara Ahli Pertama</v>
@@ -89611,7 +89611,7 @@
     </row>
     <row r="2344">
       <c r="A2344" t="str">
-        <v>Kmtsffp8m8clh</v>
+        <v>Kmtuxmti2jz1z</v>
       </c>
       <c r="B2344" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -89649,7 +89649,7 @@
     </row>
     <row r="2345">
       <c r="A2345" t="str">
-        <v>Kmtsffp8mhe5b</v>
+        <v>Kmtuxmti2hqra</v>
       </c>
       <c r="B2345" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89687,7 +89687,7 @@
     </row>
     <row r="2346">
       <c r="A2346" t="str">
-        <v>Kmtsffp8mvjdw</v>
+        <v>Kmtuxmti2a2vd</v>
       </c>
       <c r="B2346" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89801,7 +89801,7 @@
     </row>
     <row r="2349">
       <c r="A2349" t="str">
-        <v>Kmtsffp8m2pi0</v>
+        <v>Kmtuxmti2r4im</v>
       </c>
       <c r="B2349" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89839,7 +89839,7 @@
     </row>
     <row r="2350">
       <c r="A2350" t="str">
-        <v>Kmtsffp8m7ueq</v>
+        <v>Kmtuxmti258x3</v>
       </c>
       <c r="B2350" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -89877,7 +89877,7 @@
     </row>
     <row r="2351">
       <c r="A2351" t="str">
-        <v>Kmtsffp8mjlvz</v>
+        <v>Kmtuxmti290i9</v>
       </c>
       <c r="B2351" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -89953,7 +89953,7 @@
     </row>
     <row r="2353">
       <c r="A2353" t="str">
-        <v>Kmtsffp8mjp07</v>
+        <v>Kmtuxmti2emvl</v>
       </c>
       <c r="B2353" t="str">
         <v>Penata Layanan Operasional</v>
@@ -89991,7 +89991,7 @@
     </row>
     <row r="2354">
       <c r="A2354" t="str">
-        <v>Kmtsffp8mh2ad</v>
+        <v>Kmtuxmti28654</v>
       </c>
       <c r="B2354" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90029,7 +90029,7 @@
     </row>
     <row r="2355">
       <c r="A2355" t="str">
-        <v>Kmtsffp8mdw00</v>
+        <v>Kmtuxmti21uc3</v>
       </c>
       <c r="B2355" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90067,7 +90067,7 @@
     </row>
     <row r="2356">
       <c r="A2356" t="str">
-        <v>Kmtsffp8m43jf</v>
+        <v>Kmtuxmti2xryw</v>
       </c>
       <c r="B2356" t="str">
         <v>Penata Keprotokolan*</v>
@@ -90143,7 +90143,7 @@
     </row>
     <row r="2358">
       <c r="A2358" t="str">
-        <v>Kmtsffp8mr1li</v>
+        <v>Kmtuxmti2ap9q</v>
       </c>
       <c r="B2358" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90181,7 +90181,7 @@
     </row>
     <row r="2359">
       <c r="A2359" t="str">
-        <v>Kmtsffp8mvz6d</v>
+        <v>Kmtuxmti2l7x0</v>
       </c>
       <c r="B2359" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90219,7 +90219,7 @@
     </row>
     <row r="2360">
       <c r="A2360" t="str">
-        <v>Kmtsffp8msjao</v>
+        <v>Kmtuxmti2z3wa</v>
       </c>
       <c r="B2360" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90333,7 +90333,7 @@
     </row>
     <row r="2363">
       <c r="A2363" t="str">
-        <v>Kmtsffp8mx1n2</v>
+        <v>Kmtuxmti29wk4</v>
       </c>
       <c r="B2363" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90371,7 +90371,7 @@
     </row>
     <row r="2364">
       <c r="A2364" t="str">
-        <v>Kmtsffp8m2gfp</v>
+        <v>Kmtuxmti2k8k7</v>
       </c>
       <c r="B2364" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90409,7 +90409,7 @@
     </row>
     <row r="2365">
       <c r="A2365" t="str">
-        <v>Kmtsffp8msc22</v>
+        <v>Kmtuxmti22s21</v>
       </c>
       <c r="B2365" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90485,7 +90485,7 @@
     </row>
     <row r="2367">
       <c r="A2367" t="str">
-        <v>Kmtsffp8mzjqx</v>
+        <v>Kmtuxmti2rk5m</v>
       </c>
       <c r="B2367" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90523,7 +90523,7 @@
     </row>
     <row r="2368">
       <c r="A2368" t="str">
-        <v>Kmtsffp8moek1</v>
+        <v>Kmtuxmti2r1xx</v>
       </c>
       <c r="B2368" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90561,7 +90561,7 @@
     </row>
     <row r="2369">
       <c r="A2369" t="str">
-        <v>Kmtsffp8m60hu</v>
+        <v>Kmtuxmti2cs06</v>
       </c>
       <c r="B2369" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90637,7 +90637,7 @@
     </row>
     <row r="2371">
       <c r="A2371" t="str">
-        <v>Kmtsffp8md7ei</v>
+        <v>Kmtuxmti2o5p0</v>
       </c>
       <c r="B2371" t="str">
         <v>Penelaah Teknis Kebijakan</v>
@@ -90675,7 +90675,7 @@
     </row>
     <row r="2372">
       <c r="A2372" t="str">
-        <v>Kmtsffp8m20lq</v>
+        <v>Kmtuxmti2o6es</v>
       </c>
       <c r="B2372" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90713,7 +90713,7 @@
     </row>
     <row r="2373">
       <c r="A2373" t="str">
-        <v>Kmtsffp8md9wp</v>
+        <v>Kmtuxmti2edga</v>
       </c>
       <c r="B2373" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90789,7 +90789,7 @@
     </row>
     <row r="2375">
       <c r="A2375" t="str">
-        <v>Kmtsffp8m1zl2</v>
+        <v>Kmtuxmti2tg6g</v>
       </c>
       <c r="B2375" t="str">
         <v>Penata Layanan Operasional</v>
@@ -90827,7 +90827,7 @@
     </row>
     <row r="2376">
       <c r="A2376" t="str">
-        <v>Kmtsffp8m3983</v>
+        <v>Kmtuxmti26a50</v>
       </c>
       <c r="B2376" t="str">
         <v>Pengolah Data dan Informasi</v>
@@ -90865,7 +90865,7 @@
     </row>
     <row r="2377">
       <c r="A2377" t="str">
-        <v>Kmtsffp8mx3y4</v>
+        <v>Kmtuxmti2snuf</v>
       </c>
       <c r="B2377" t="str">
         <v>Pengadministrasi Perkantoran</v>
@@ -90903,7 +90903,7 @@
     </row>
     <row r="2378">
       <c r="A2378" t="str">
-        <v>Kmtsffp8mkc7i</v>
+        <v>Kmtuxmti2vpe8</v>
       </c>
       <c r="B2378" t="str">
         <v xml:space="preserve">Analis Pembiayaan Risiko dan Keuangan/ Analis Keuangan Negara Ahli Utama									</v>
